--- a/data/AppointmentReport_latest.xlsx
+++ b/data/AppointmentReport_latest.xlsx
@@ -16,7 +16,7 @@
     <x:sheet name="Blad1" sheetId="1" r:id="rId1"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="DataStart">Blad1!$A$631</x:definedName>
+    <x:definedName name="DataStart">Blad1!$A$633</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="191029"/>
   <x:extLst>
@@ -3397,7 +3397,7 @@
       </x:c>
       <x:c r="C26" s="4" t="inlineStr">
         <x:is>
-          <x:t>1704131</x:t>
+          <x:t>1721176</x:t>
         </x:is>
       </x:c>
       <x:c r="D26" s="4">
@@ -3405,7 +3405,7 @@
       </x:c>
       <x:c r="E26" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679364</x:t>
+          <x:t>4002697876</x:t>
         </x:is>
       </x:c>
       <x:c r="F26" s="1" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </x:c>
       <x:c r="G26" s="1" t="inlineStr">
         <x:is>
-          <x:t>-</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H26" s="1" t="inlineStr">
@@ -3425,17 +3425,17 @@
       </x:c>
       <x:c r="I26" s="1" t="inlineStr">
         <x:is>
-          <x:t>8997</x:t>
+          <x:t>9006</x:t>
         </x:is>
       </x:c>
       <x:c r="J26" s="1" t="inlineStr">
         <x:is>
-          <x:t>Verrières</x:t>
+          <x:t>Belleville</x:t>
         </x:is>
       </x:c>
       <x:c r="K26" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8997-1A</x:t>
+          <x:t>DCZONE-9006-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L26" s="1" t="inlineStr">
@@ -3456,29 +3456,29 @@
       </x:c>
       <x:c r="P26" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q26" s="2" t="n">
-        <x:v>46006.2951041667</x:v>
+        <x:v>46006.3576041667</x:v>
       </x:c>
       <x:c r="R26" s="2" t="n">
-        <x:v>46006.3036689815</x:v>
+        <x:v>46006.4275347222</x:v>
       </x:c>
       <x:c r="S26" s="2" t="n">
-        <x:v>46006.3270486111</x:v>
+        <x:v>46006.446875</x:v>
       </x:c>
       <x:c r="T26" s="3">
         <x:v/>
       </x:c>
       <x:c r="U26" s="3" t="inlineStr">
         <x:is>
-          <x:t>13</x:t>
+          <x:t>101</x:t>
         </x:is>
       </x:c>
       <x:c r="V26" s="3" t="inlineStr">
         <x:is>
-          <x:t>33</x:t>
+          <x:t>28</x:t>
         </x:is>
       </x:c>
       <x:c r="W26" s="1">
@@ -3512,7 +3512,7 @@
       </x:c>
       <x:c r="C27" s="4" t="inlineStr">
         <x:is>
-          <x:t>1721176</x:t>
+          <x:t>1704131</x:t>
         </x:is>
       </x:c>
       <x:c r="D27" s="4">
@@ -3520,7 +3520,7 @@
       </x:c>
       <x:c r="E27" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002697876</x:t>
+          <x:t>4002679364</x:t>
         </x:is>
       </x:c>
       <x:c r="F27" s="1" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </x:c>
       <x:c r="G27" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>-</x:t>
         </x:is>
       </x:c>
       <x:c r="H27" s="1" t="inlineStr">
@@ -3540,17 +3540,17 @@
       </x:c>
       <x:c r="I27" s="1" t="inlineStr">
         <x:is>
-          <x:t>9006</x:t>
+          <x:t>8997</x:t>
         </x:is>
       </x:c>
       <x:c r="J27" s="1" t="inlineStr">
         <x:is>
-          <x:t>Belleville</x:t>
+          <x:t>Verrières</x:t>
         </x:is>
       </x:c>
       <x:c r="K27" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9006-1A</x:t>
+          <x:t>DCZONE-8997-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L27" s="1" t="inlineStr">
@@ -3571,29 +3571,29 @@
       </x:c>
       <x:c r="P27" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q27" s="2" t="n">
-        <x:v>46006.3576041667</x:v>
+        <x:v>46006.2951041667</x:v>
       </x:c>
       <x:c r="R27" s="2" t="n">
-        <x:v>46006.4275347222</x:v>
+        <x:v>46006.3036689815</x:v>
       </x:c>
       <x:c r="S27" s="2" t="n">
-        <x:v>46006.446875</x:v>
+        <x:v>46006.3270486111</x:v>
       </x:c>
       <x:c r="T27" s="3">
         <x:v/>
       </x:c>
       <x:c r="U27" s="3" t="inlineStr">
         <x:is>
-          <x:t>101</x:t>
+          <x:t>13</x:t>
         </x:is>
       </x:c>
       <x:c r="V27" s="3" t="inlineStr">
         <x:is>
-          <x:t>28</x:t>
+          <x:t>33</x:t>
         </x:is>
       </x:c>
       <x:c r="W27" s="1">
@@ -8287,7 +8287,7 @@
       </x:c>
       <x:c r="C68" s="4" t="inlineStr">
         <x:is>
-          <x:t>1720717</x:t>
+          <x:t>1722930</x:t>
         </x:is>
       </x:c>
       <x:c r="D68" s="4">
@@ -8295,7 +8295,7 @@
       </x:c>
       <x:c r="E68" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002697866</x:t>
+          <x:t>4002699416</x:t>
         </x:is>
       </x:c>
       <x:c r="F68" s="1" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </x:c>
       <x:c r="I68" s="1" t="inlineStr">
         <x:is>
-          <x:t>9007</x:t>
+          <x:t>8998</x:t>
         </x:is>
       </x:c>
       <x:c r="J68" s="1" t="inlineStr">
         <x:is>
-          <x:t>Peine</x:t>
+          <x:t>Bratislava</x:t>
         </x:is>
       </x:c>
       <x:c r="K68" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9007-1A</x:t>
+          <x:t>DCZONE-8998-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L68" s="1" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </x:c>
       <x:c r="N68" s="1" t="inlineStr">
         <x:is>
-          <x:t>Yes</x:t>
+          <x:t>No</x:t>
         </x:is>
       </x:c>
       <x:c r="O68" s="2" t="n">
@@ -8346,31 +8346,31 @@
       </x:c>
       <x:c r="P68" s="1" t="inlineStr">
         <x:is>
-          <x:t>Late</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q68" s="2" t="n">
-        <x:v>46009.7093634259</x:v>
+        <x:v>46008.3080092593</x:v>
       </x:c>
       <x:c r="R68" s="2" t="n">
-        <x:v>46009.709849537</x:v>
+        <x:v>46008.3194675926</x:v>
       </x:c>
       <x:c r="S68" s="2" t="n">
-        <x:v>46009.7515393519</x:v>
+        <x:v>46008.4088657407</x:v>
       </x:c>
       <x:c r="T68" s="3" t="inlineStr">
         <x:is>
-          <x:t>2041</x:t>
+          <x:t>23</x:t>
         </x:is>
       </x:c>
       <x:c r="U68" s="3" t="inlineStr">
         <x:is>
-          <x:t>1</x:t>
+          <x:t>17</x:t>
         </x:is>
       </x:c>
       <x:c r="V68" s="3" t="inlineStr">
         <x:is>
-          <x:t>60</x:t>
+          <x:t>128</x:t>
         </x:is>
       </x:c>
       <x:c r="W68" s="1">
@@ -8387,10 +8387,8 @@
       <x:c r="Z68" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA68" s="1" t="inlineStr">
-        <x:is>
-          <x:t>kommt morgen um 16:30</x:t>
-        </x:is>
+      <x:c r="AA68" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -8406,7 +8404,7 @@
       </x:c>
       <x:c r="C69" s="4" t="inlineStr">
         <x:is>
-          <x:t>1722930</x:t>
+          <x:t>1720717</x:t>
         </x:is>
       </x:c>
       <x:c r="D69" s="4">
@@ -8414,7 +8412,7 @@
       </x:c>
       <x:c r="E69" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002699416</x:t>
+          <x:t>4002697866</x:t>
         </x:is>
       </x:c>
       <x:c r="F69" s="1" t="inlineStr">
@@ -8434,17 +8432,17 @@
       </x:c>
       <x:c r="I69" s="1" t="inlineStr">
         <x:is>
-          <x:t>8998</x:t>
+          <x:t>9007</x:t>
         </x:is>
       </x:c>
       <x:c r="J69" s="1" t="inlineStr">
         <x:is>
-          <x:t>Bratislava</x:t>
+          <x:t>Peine</x:t>
         </x:is>
       </x:c>
       <x:c r="K69" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8998-1A</x:t>
+          <x:t>DCZONE-9007-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L69" s="1" t="inlineStr">
@@ -8457,7 +8455,7 @@
       </x:c>
       <x:c r="N69" s="1" t="inlineStr">
         <x:is>
-          <x:t>No</x:t>
+          <x:t>Yes</x:t>
         </x:is>
       </x:c>
       <x:c r="O69" s="2" t="n">
@@ -8465,31 +8463,31 @@
       </x:c>
       <x:c r="P69" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Late</x:t>
         </x:is>
       </x:c>
       <x:c r="Q69" s="2" t="n">
-        <x:v>46008.3080092593</x:v>
+        <x:v>46009.7093634259</x:v>
       </x:c>
       <x:c r="R69" s="2" t="n">
-        <x:v>46008.3194675926</x:v>
+        <x:v>46009.709849537</x:v>
       </x:c>
       <x:c r="S69" s="2" t="n">
-        <x:v>46008.4088657407</x:v>
+        <x:v>46009.7515393519</x:v>
       </x:c>
       <x:c r="T69" s="3" t="inlineStr">
         <x:is>
-          <x:t>23</x:t>
+          <x:t>2041</x:t>
         </x:is>
       </x:c>
       <x:c r="U69" s="3" t="inlineStr">
         <x:is>
-          <x:t>17</x:t>
+          <x:t>1</x:t>
         </x:is>
       </x:c>
       <x:c r="V69" s="3" t="inlineStr">
         <x:is>
-          <x:t>128</x:t>
+          <x:t>60</x:t>
         </x:is>
       </x:c>
       <x:c r="W69" s="1">
@@ -8506,8 +8504,10 @@
       <x:c r="Z69" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA69" s="1">
-        <x:v/>
+      <x:c r="AA69" s="1" t="inlineStr">
+        <x:is>
+          <x:t>kommt morgen um 16:30</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -10950,7 +10950,7 @@
       </x:c>
       <x:c r="C91" s="4" t="inlineStr">
         <x:is>
-          <x:t>1721073</x:t>
+          <x:t>1705781</x:t>
         </x:is>
       </x:c>
       <x:c r="D91" s="4">
@@ -10958,7 +10958,7 @@
       </x:c>
       <x:c r="E91" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002697875</x:t>
+          <x:t>4002679399</x:t>
         </x:is>
       </x:c>
       <x:c r="F91" s="1" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </x:c>
       <x:c r="G91" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>-</x:t>
         </x:is>
       </x:c>
       <x:c r="H91" s="1" t="inlineStr">
@@ -10978,17 +10978,17 @@
       </x:c>
       <x:c r="I91" s="1" t="inlineStr">
         <x:is>
-          <x:t>9005</x:t>
+          <x:t>9002</x:t>
         </x:is>
       </x:c>
       <x:c r="J91" s="1" t="inlineStr">
         <x:is>
-          <x:t>Labastide</x:t>
+          <x:t>Echt</x:t>
         </x:is>
       </x:c>
       <x:c r="K91" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9005-1A</x:t>
+          <x:t>DCZONE-9002-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L91" s="1" t="inlineStr">
@@ -11009,29 +11009,29 @@
       </x:c>
       <x:c r="P91" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q91" s="2" t="n">
-        <x:v>46008.4712268518</x:v>
+        <x:v>46008.6179050926</x:v>
       </x:c>
       <x:c r="R91" s="2" t="n">
-        <x:v>46008.4806134259</x:v>
+        <x:v>46008.6283796296</x:v>
       </x:c>
       <x:c r="S91" s="2" t="n">
-        <x:v>46008.527962963</x:v>
+        <x:v>46008.7131134259</x:v>
       </x:c>
       <x:c r="T91" s="3">
         <x:v/>
       </x:c>
       <x:c r="U91" s="3" t="inlineStr">
         <x:is>
-          <x:t>14</x:t>
+          <x:t>15</x:t>
         </x:is>
       </x:c>
       <x:c r="V91" s="3" t="inlineStr">
         <x:is>
-          <x:t>68</x:t>
+          <x:t>122</x:t>
         </x:is>
       </x:c>
       <x:c r="W91" s="1">
@@ -11048,8 +11048,10 @@
       <x:c r="Z91" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA91" s="1">
-        <x:v/>
+      <x:c r="AA91" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001406360 -63</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -11065,7 +11067,7 @@
       </x:c>
       <x:c r="C92" s="4" t="inlineStr">
         <x:is>
-          <x:t>1705781</x:t>
+          <x:t>1721073</x:t>
         </x:is>
       </x:c>
       <x:c r="D92" s="4">
@@ -11073,7 +11075,7 @@
       </x:c>
       <x:c r="E92" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679399</x:t>
+          <x:t>4002697875</x:t>
         </x:is>
       </x:c>
       <x:c r="F92" s="1" t="inlineStr">
@@ -11083,7 +11085,7 @@
       </x:c>
       <x:c r="G92" s="1" t="inlineStr">
         <x:is>
-          <x:t>-</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H92" s="1" t="inlineStr">
@@ -11093,17 +11095,17 @@
       </x:c>
       <x:c r="I92" s="1" t="inlineStr">
         <x:is>
-          <x:t>9002</x:t>
+          <x:t>9005</x:t>
         </x:is>
       </x:c>
       <x:c r="J92" s="1" t="inlineStr">
         <x:is>
-          <x:t>Echt</x:t>
+          <x:t>Labastide</x:t>
         </x:is>
       </x:c>
       <x:c r="K92" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9002-1A</x:t>
+          <x:t>DCZONE-9005-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L92" s="1" t="inlineStr">
@@ -11124,29 +11126,29 @@
       </x:c>
       <x:c r="P92" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q92" s="2" t="n">
-        <x:v>46008.6179050926</x:v>
+        <x:v>46008.4712268518</x:v>
       </x:c>
       <x:c r="R92" s="2" t="n">
-        <x:v>46008.6283796296</x:v>
+        <x:v>46008.4806134259</x:v>
       </x:c>
       <x:c r="S92" s="2" t="n">
-        <x:v>46008.7131134259</x:v>
+        <x:v>46008.527962963</x:v>
       </x:c>
       <x:c r="T92" s="3">
         <x:v/>
       </x:c>
       <x:c r="U92" s="3" t="inlineStr">
         <x:is>
-          <x:t>15</x:t>
+          <x:t>14</x:t>
         </x:is>
       </x:c>
       <x:c r="V92" s="3" t="inlineStr">
         <x:is>
-          <x:t>122</x:t>
+          <x:t>68</x:t>
         </x:is>
       </x:c>
       <x:c r="W92" s="1">
@@ -11163,10 +11165,8 @@
       <x:c r="Z92" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA92" s="1" t="inlineStr">
-        <x:is>
-          <x:t>5001406360 -63</x:t>
-        </x:is>
+      <x:c r="AA92" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -12352,7 +12352,7 @@
       </x:c>
       <x:c r="C103" s="4" t="inlineStr">
         <x:is>
-          <x:t>1706800</x:t>
+          <x:t>1723894</x:t>
         </x:is>
       </x:c>
       <x:c r="D103" s="4">
@@ -12360,7 +12360,7 @@
       </x:c>
       <x:c r="E103" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679437</x:t>
+          <x:t>4002702418</x:t>
         </x:is>
       </x:c>
       <x:c r="F103" s="1" t="inlineStr">
@@ -12370,7 +12370,7 @@
       </x:c>
       <x:c r="G103" s="1" t="inlineStr">
         <x:is>
-          <x:t>-</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H103" s="1" t="inlineStr">
@@ -12380,17 +12380,17 @@
       </x:c>
       <x:c r="I103" s="1" t="inlineStr">
         <x:is>
-          <x:t>8990</x:t>
+          <x:t>8996</x:t>
         </x:is>
       </x:c>
       <x:c r="J103" s="1" t="inlineStr">
         <x:is>
-          <x:t>Wallersdorf</x:t>
+          <x:t>Bierun</x:t>
         </x:is>
       </x:c>
       <x:c r="K103" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8990-1A</x:t>
+          <x:t>DCZONE-8996-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L103" s="1" t="inlineStr">
@@ -12411,29 +12411,29 @@
       </x:c>
       <x:c r="P103" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q103" s="2" t="n">
-        <x:v>46009.3179166667</x:v>
+        <x:v>46009.3091898148</x:v>
       </x:c>
       <x:c r="R103" s="2" t="n">
-        <x:v>46009.3181481482</x:v>
+        <x:v>46009.3230439815</x:v>
       </x:c>
       <x:c r="S103" s="2" t="n">
-        <x:v>46009.3642592593</x:v>
+        <x:v>46009.3677777778</x:v>
       </x:c>
       <x:c r="T103" s="3">
         <x:v/>
       </x:c>
       <x:c r="U103" s="3" t="inlineStr">
         <x:is>
-          <x:t>1</x:t>
+          <x:t>20</x:t>
         </x:is>
       </x:c>
       <x:c r="V103" s="3" t="inlineStr">
         <x:is>
-          <x:t>66</x:t>
+          <x:t>64</x:t>
         </x:is>
       </x:c>
       <x:c r="W103" s="1">
@@ -12450,10 +12450,8 @@
       <x:c r="Z103" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA103" s="1" t="inlineStr">
-        <x:is>
-          <x:t>5001406969 opt. dock 15</x:t>
-        </x:is>
+      <x:c r="AA103" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -12469,7 +12467,7 @@
       </x:c>
       <x:c r="C104" s="4" t="inlineStr">
         <x:is>
-          <x:t>1723894</x:t>
+          <x:t>1706800</x:t>
         </x:is>
       </x:c>
       <x:c r="D104" s="4">
@@ -12477,7 +12475,7 @@
       </x:c>
       <x:c r="E104" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002702418</x:t>
+          <x:t>4002679437</x:t>
         </x:is>
       </x:c>
       <x:c r="F104" s="1" t="inlineStr">
@@ -12487,7 +12485,7 @@
       </x:c>
       <x:c r="G104" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>-</x:t>
         </x:is>
       </x:c>
       <x:c r="H104" s="1" t="inlineStr">
@@ -12497,17 +12495,17 @@
       </x:c>
       <x:c r="I104" s="1" t="inlineStr">
         <x:is>
-          <x:t>8996</x:t>
+          <x:t>8990</x:t>
         </x:is>
       </x:c>
       <x:c r="J104" s="1" t="inlineStr">
         <x:is>
-          <x:t>Bierun</x:t>
+          <x:t>Wallersdorf</x:t>
         </x:is>
       </x:c>
       <x:c r="K104" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8996-1A</x:t>
+          <x:t>DCZONE-8990-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L104" s="1" t="inlineStr">
@@ -12528,29 +12526,29 @@
       </x:c>
       <x:c r="P104" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q104" s="2" t="n">
-        <x:v>46009.3091898148</x:v>
+        <x:v>46009.3179166667</x:v>
       </x:c>
       <x:c r="R104" s="2" t="n">
-        <x:v>46009.3230439815</x:v>
+        <x:v>46009.3181481482</x:v>
       </x:c>
       <x:c r="S104" s="2" t="n">
-        <x:v>46009.3677777778</x:v>
+        <x:v>46009.3642592593</x:v>
       </x:c>
       <x:c r="T104" s="3">
         <x:v/>
       </x:c>
       <x:c r="U104" s="3" t="inlineStr">
         <x:is>
-          <x:t>20</x:t>
+          <x:t>1</x:t>
         </x:is>
       </x:c>
       <x:c r="V104" s="3" t="inlineStr">
         <x:is>
-          <x:t>64</x:t>
+          <x:t>66</x:t>
         </x:is>
       </x:c>
       <x:c r="W104" s="1">
@@ -12567,8 +12565,10 @@
       <x:c r="Z104" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA104" s="1">
-        <x:v/>
+      <x:c r="AA104" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001406969 opt. dock 15</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -14678,7 +14678,7 @@
       </x:c>
       <x:c r="C123" s="4" t="inlineStr">
         <x:is>
-          <x:t>1705513</x:t>
+          <x:t>1723847</x:t>
         </x:is>
       </x:c>
       <x:c r="D123" s="4">
@@ -14686,7 +14686,7 @@
       </x:c>
       <x:c r="E123" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002681516</x:t>
+          <x:t>4002702401</x:t>
         </x:is>
       </x:c>
       <x:c r="F123" s="1" t="inlineStr">
@@ -14696,12 +14696,12 @@
       </x:c>
       <x:c r="G123" s="1" t="inlineStr">
         <x:is>
-          <x:t>-</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H123" s="1" t="inlineStr">
         <x:is>
-          <x:t>Removed</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I123" s="1" t="inlineStr">
@@ -14729,7 +14729,7 @@
       </x:c>
       <x:c r="N123" s="1" t="inlineStr">
         <x:is>
-          <x:t>No</x:t>
+          <x:t>Yes</x:t>
         </x:is>
       </x:c>
       <x:c r="O123" s="2" t="n">
@@ -14737,29 +14737,29 @@
       </x:c>
       <x:c r="P123" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q123" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R123" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S123" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q123" s="2" t="n">
+        <x:v>46009.5693518519</x:v>
+      </x:c>
+      <x:c r="R123" s="2" t="n">
+        <x:v>46009.5723032407</x:v>
+      </x:c>
+      <x:c r="S123" s="2" t="n">
+        <x:v>46009.6520138889</x:v>
       </x:c>
       <x:c r="T123" s="3">
         <x:v/>
       </x:c>
       <x:c r="U123" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>5</x:t>
         </x:is>
       </x:c>
       <x:c r="V123" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>114</x:t>
         </x:is>
       </x:c>
       <x:c r="W123" s="1">
@@ -14770,13 +14770,11 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y123" s="1" t="inlineStr">
-        <x:is>
-          <x:t>Good(s)Factory</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Z123" s="2" t="n">
-        <x:v>46007.7317592593</x:v>
+      <x:c r="Y123" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z123" s="2">
+        <x:v/>
       </x:c>
       <x:c r="AA123" s="1">
         <x:v/>
@@ -14795,7 +14793,7 @@
       </x:c>
       <x:c r="C124" s="4" t="inlineStr">
         <x:is>
-          <x:t>1723847</x:t>
+          <x:t>1722885</x:t>
         </x:is>
       </x:c>
       <x:c r="D124" s="4">
@@ -14803,7 +14801,7 @@
       </x:c>
       <x:c r="E124" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002702401</x:t>
+          <x:t>4002699451</x:t>
         </x:is>
       </x:c>
       <x:c r="F124" s="1" t="inlineStr">
@@ -14818,7 +14816,7 @@
       </x:c>
       <x:c r="H124" s="1" t="inlineStr">
         <x:is>
-          <x:t>Finished</x:t>
+          <x:t>Removed</x:t>
         </x:is>
       </x:c>
       <x:c r="I124" s="1" t="inlineStr">
@@ -14846,7 +14844,7 @@
       </x:c>
       <x:c r="N124" s="1" t="inlineStr">
         <x:is>
-          <x:t>Yes</x:t>
+          <x:t>No</x:t>
         </x:is>
       </x:c>
       <x:c r="O124" s="2" t="n">
@@ -14854,29 +14852,29 @@
       </x:c>
       <x:c r="P124" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q124" s="2" t="n">
-        <x:v>46009.5693518519</x:v>
-      </x:c>
-      <x:c r="R124" s="2" t="n">
-        <x:v>46009.5723032407</x:v>
-      </x:c>
-      <x:c r="S124" s="2" t="n">
-        <x:v>46009.6520138889</x:v>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q124" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R124" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S124" s="2">
+        <x:v/>
       </x:c>
       <x:c r="T124" s="3">
         <x:v/>
       </x:c>
       <x:c r="U124" s="3" t="inlineStr">
         <x:is>
-          <x:t>5</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="V124" s="3" t="inlineStr">
         <x:is>
-          <x:t>114</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="W124" s="1">
@@ -14887,11 +14885,13 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y124" s="1">
-        <x:v/>
-      </x:c>
-      <x:c r="Z124" s="2">
-        <x:v/>
+      <x:c r="Y124" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z124" s="2" t="n">
+        <x:v>46007.7314583333</x:v>
       </x:c>
       <x:c r="AA124" s="1">
         <x:v/>
@@ -14910,7 +14910,7 @@
       </x:c>
       <x:c r="C125" s="4" t="inlineStr">
         <x:is>
-          <x:t>1722885</x:t>
+          <x:t>1706830</x:t>
         </x:is>
       </x:c>
       <x:c r="D125" s="4">
@@ -14918,7 +14918,7 @@
       </x:c>
       <x:c r="E125" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002699451</x:t>
+          <x:t>4002680824</x:t>
         </x:is>
       </x:c>
       <x:c r="F125" s="1" t="inlineStr">
@@ -14928,27 +14928,27 @@
       </x:c>
       <x:c r="G125" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>-</x:t>
         </x:is>
       </x:c>
       <x:c r="H125" s="1" t="inlineStr">
         <x:is>
-          <x:t>Removed</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I125" s="1" t="inlineStr">
         <x:is>
-          <x:t>9005</x:t>
+          <x:t>9000</x:t>
         </x:is>
       </x:c>
       <x:c r="J125" s="1" t="inlineStr">
         <x:is>
-          <x:t>Labastide</x:t>
+          <x:t>Zwaagdijk</x:t>
         </x:is>
       </x:c>
       <x:c r="K125" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9005-1A</x:t>
+          <x:t>DCZONE-9000-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L125" s="1" t="inlineStr">
@@ -14961,7 +14961,7 @@
       </x:c>
       <x:c r="N125" s="1" t="inlineStr">
         <x:is>
-          <x:t>No</x:t>
+          <x:t>Yes</x:t>
         </x:is>
       </x:c>
       <x:c r="O125" s="2" t="n">
@@ -14969,29 +14969,29 @@
       </x:c>
       <x:c r="P125" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q125" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R125" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S125" s="2">
-        <x:v/>
+          <x:t>On time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q125" s="2" t="n">
+        <x:v>46009.6242592593</x:v>
+      </x:c>
+      <x:c r="R125" s="2" t="n">
+        <x:v>46009.6721064815</x:v>
+      </x:c>
+      <x:c r="S125" s="2" t="n">
+        <x:v>46009.7105092593</x:v>
       </x:c>
       <x:c r="T125" s="3">
         <x:v/>
       </x:c>
       <x:c r="U125" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>69</x:t>
         </x:is>
       </x:c>
       <x:c r="V125" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>56</x:t>
         </x:is>
       </x:c>
       <x:c r="W125" s="1">
@@ -15002,16 +15002,16 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y125" s="1" t="inlineStr">
-        <x:is>
-          <x:t>Good(s)Factory</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Z125" s="2" t="n">
-        <x:v>46007.7314583333</x:v>
-      </x:c>
-      <x:c r="AA125" s="1">
-        <x:v/>
+      <x:c r="Y125" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z125" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA125" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DC1</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -15027,7 +15027,7 @@
       </x:c>
       <x:c r="C126" s="4" t="inlineStr">
         <x:is>
-          <x:t>1706830</x:t>
+          <x:t>1705513</x:t>
         </x:is>
       </x:c>
       <x:c r="D126" s="4">
@@ -15035,7 +15035,7 @@
       </x:c>
       <x:c r="E126" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002680824</x:t>
+          <x:t>4002681516</x:t>
         </x:is>
       </x:c>
       <x:c r="F126" s="1" t="inlineStr">
@@ -15050,22 +15050,22 @@
       </x:c>
       <x:c r="H126" s="1" t="inlineStr">
         <x:is>
-          <x:t>Finished</x:t>
+          <x:t>Removed</x:t>
         </x:is>
       </x:c>
       <x:c r="I126" s="1" t="inlineStr">
         <x:is>
-          <x:t>9000</x:t>
+          <x:t>9005</x:t>
         </x:is>
       </x:c>
       <x:c r="J126" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zwaagdijk</x:t>
+          <x:t>Labastide</x:t>
         </x:is>
       </x:c>
       <x:c r="K126" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9000-1A</x:t>
+          <x:t>DCZONE-9005-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L126" s="1" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </x:c>
       <x:c r="N126" s="1" t="inlineStr">
         <x:is>
-          <x:t>Yes</x:t>
+          <x:t>No</x:t>
         </x:is>
       </x:c>
       <x:c r="O126" s="2" t="n">
@@ -15086,29 +15086,29 @@
       </x:c>
       <x:c r="P126" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q126" s="2" t="n">
-        <x:v>46009.6242592593</x:v>
-      </x:c>
-      <x:c r="R126" s="2" t="n">
-        <x:v>46009.6721064815</x:v>
-      </x:c>
-      <x:c r="S126" s="2" t="n">
-        <x:v>46009.7105092593</x:v>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q126" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R126" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S126" s="2">
+        <x:v/>
       </x:c>
       <x:c r="T126" s="3">
         <x:v/>
       </x:c>
       <x:c r="U126" s="3" t="inlineStr">
         <x:is>
-          <x:t>69</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="V126" s="3" t="inlineStr">
         <x:is>
-          <x:t>56</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="W126" s="1">
@@ -15119,16 +15119,16 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y126" s="1">
-        <x:v/>
-      </x:c>
-      <x:c r="Z126" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="AA126" s="1" t="inlineStr">
-        <x:is>
-          <x:t>DC1</x:t>
-        </x:is>
+      <x:c r="Y126" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z126" s="2" t="n">
+        <x:v>46007.7317592593</x:v>
+      </x:c>
+      <x:c r="AA126" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -15733,7 +15733,7 @@
       </x:c>
       <x:c r="C132" s="4" t="inlineStr">
         <x:is>
-          <x:t>1705819</x:t>
+          <x:t>1706792</x:t>
         </x:is>
       </x:c>
       <x:c r="D132" s="4">
@@ -15741,7 +15741,7 @@
       </x:c>
       <x:c r="E132" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679342</x:t>
+          <x:t>4002679349</x:t>
         </x:is>
       </x:c>
       <x:c r="F132" s="1" t="inlineStr">
@@ -15761,17 +15761,17 @@
       </x:c>
       <x:c r="I132" s="1" t="inlineStr">
         <x:is>
-          <x:t>9004</x:t>
+          <x:t>9007</x:t>
         </x:is>
       </x:c>
       <x:c r="J132" s="1" t="inlineStr">
         <x:is>
-          <x:t>Biblis</x:t>
+          <x:t>Peine</x:t>
         </x:is>
       </x:c>
       <x:c r="K132" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9004-1A</x:t>
+          <x:t>DCZONE-9007-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L132" s="1" t="inlineStr">
@@ -15796,27 +15796,25 @@
         </x:is>
       </x:c>
       <x:c r="Q132" s="2" t="n">
-        <x:v>46010.2585648148</x:v>
+        <x:v>46010.2481828704</x:v>
       </x:c>
       <x:c r="R132" s="2" t="n">
-        <x:v>46010.2589583333</x:v>
+        <x:v>46010.2489467593</x:v>
       </x:c>
       <x:c r="S132" s="2" t="n">
-        <x:v>46010.290625</x:v>
-      </x:c>
-      <x:c r="T132" s="3" t="inlineStr">
-        <x:is>
-          <x:t>12</x:t>
-        </x:is>
+        <x:v>46010.2654166667</x:v>
+      </x:c>
+      <x:c r="T132" s="3">
+        <x:v/>
       </x:c>
       <x:c r="U132" s="3" t="inlineStr">
         <x:is>
-          <x:t>0</x:t>
+          <x:t>1</x:t>
         </x:is>
       </x:c>
       <x:c r="V132" s="3" t="inlineStr">
         <x:is>
-          <x:t>46</x:t>
+          <x:t>24</x:t>
         </x:is>
       </x:c>
       <x:c r="W132" s="1">
@@ -15850,7 +15848,7 @@
       </x:c>
       <x:c r="C133" s="4" t="inlineStr">
         <x:is>
-          <x:t>1706792</x:t>
+          <x:t>1705819</x:t>
         </x:is>
       </x:c>
       <x:c r="D133" s="4">
@@ -15858,7 +15856,7 @@
       </x:c>
       <x:c r="E133" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679349</x:t>
+          <x:t>4002679342</x:t>
         </x:is>
       </x:c>
       <x:c r="F133" s="1" t="inlineStr">
@@ -15878,17 +15876,17 @@
       </x:c>
       <x:c r="I133" s="1" t="inlineStr">
         <x:is>
-          <x:t>9007</x:t>
+          <x:t>9004</x:t>
         </x:is>
       </x:c>
       <x:c r="J133" s="1" t="inlineStr">
         <x:is>
-          <x:t>Peine</x:t>
+          <x:t>Biblis</x:t>
         </x:is>
       </x:c>
       <x:c r="K133" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9007-1A</x:t>
+          <x:t>DCZONE-9004-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L133" s="1" t="inlineStr">
@@ -15913,25 +15911,27 @@
         </x:is>
       </x:c>
       <x:c r="Q133" s="2" t="n">
-        <x:v>46010.2481828704</x:v>
+        <x:v>46010.2585648148</x:v>
       </x:c>
       <x:c r="R133" s="2" t="n">
-        <x:v>46010.2489467593</x:v>
+        <x:v>46010.2589583333</x:v>
       </x:c>
       <x:c r="S133" s="2" t="n">
-        <x:v>46010.2654166667</x:v>
-      </x:c>
-      <x:c r="T133" s="3">
-        <x:v/>
+        <x:v>46010.290625</x:v>
+      </x:c>
+      <x:c r="T133" s="3" t="inlineStr">
+        <x:is>
+          <x:t>12</x:t>
+        </x:is>
       </x:c>
       <x:c r="U133" s="3" t="inlineStr">
         <x:is>
-          <x:t>1</x:t>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="V133" s="3" t="inlineStr">
         <x:is>
-          <x:t>24</x:t>
+          <x:t>46</x:t>
         </x:is>
       </x:c>
       <x:c r="W133" s="1">
@@ -52043,27 +52043,25 @@
     <x:row r="444">
       <x:c r="A444" s="1" t="inlineStr">
         <x:is>
-          <x:t>50135</x:t>
+          <x:t>1001634</x:t>
         </x:is>
       </x:c>
       <x:c r="B444" s="1" t="inlineStr">
         <x:is>
-          <x:t>DSV Road sp. z o.o.</x:t>
+          <x:t>Good(s)Factory</x:t>
         </x:is>
       </x:c>
       <x:c r="C444" s="4" t="inlineStr">
         <x:is>
-          <x:t>1806306</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D444" s="4" t="inlineStr">
-        <x:is>
-          <x:t>000002858764</x:t>
-        </x:is>
+          <x:t>1803862</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D444" s="4">
+        <x:v/>
       </x:c>
       <x:c r="E444" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002783199, 4002784832</x:t>
+          <x:t>4002791655</x:t>
         </x:is>
       </x:c>
       <x:c r="F444" s="1" t="inlineStr">
@@ -52083,17 +52081,17 @@
       </x:c>
       <x:c r="I444" s="1" t="inlineStr">
         <x:is>
-          <x:t>8996</x:t>
+          <x:t>9000</x:t>
         </x:is>
       </x:c>
       <x:c r="J444" s="1" t="inlineStr">
         <x:is>
-          <x:t>Bierun</x:t>
+          <x:t>Zwaagdijk</x:t>
         </x:is>
       </x:c>
       <x:c r="K444" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8996-1A</x:t>
+          <x:t>DCZONE-9000-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L444" s="1" t="inlineStr">
@@ -52102,7 +52100,7 @@
         </x:is>
       </x:c>
       <x:c r="M444" s="3" t="n">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="N444" s="1" t="inlineStr">
         <x:is>
@@ -52114,29 +52112,29 @@
       </x:c>
       <x:c r="P444" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q444" s="2" t="n">
-        <x:v>46064.3255671296</x:v>
+        <x:v>46064.3632407407</x:v>
       </x:c>
       <x:c r="R444" s="2" t="n">
-        <x:v>46064.4187731482</x:v>
+        <x:v>46064.3841666667</x:v>
       </x:c>
       <x:c r="S444" s="2" t="n">
-        <x:v>46064.4423148148</x:v>
+        <x:v>46064.4143055556</x:v>
       </x:c>
       <x:c r="T444" s="3">
         <x:v/>
       </x:c>
       <x:c r="U444" s="3" t="inlineStr">
         <x:is>
-          <x:t>135</x:t>
+          <x:t>30</x:t>
         </x:is>
       </x:c>
       <x:c r="V444" s="3" t="inlineStr">
         <x:is>
-          <x:t>33</x:t>
+          <x:t>43</x:t>
         </x:is>
       </x:c>
       <x:c r="W444" s="1">
@@ -52155,32 +52153,34 @@
       </x:c>
       <x:c r="AA444" s="1" t="inlineStr">
         <x:is>
-          <x:t>783479987</x:t>
+          <x:t>DC1</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="445">
       <x:c r="A445" s="1" t="inlineStr">
         <x:is>
-          <x:t>1001634</x:t>
+          <x:t>50135</x:t>
         </x:is>
       </x:c>
       <x:c r="B445" s="1" t="inlineStr">
         <x:is>
-          <x:t>Good(s)Factory</x:t>
+          <x:t>DSV Road sp. z o.o.</x:t>
         </x:is>
       </x:c>
       <x:c r="C445" s="4" t="inlineStr">
         <x:is>
-          <x:t>1801301</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D445" s="4">
-        <x:v/>
+          <x:t>1806306</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D445" s="4" t="inlineStr">
+        <x:is>
+          <x:t>000002858764</x:t>
+        </x:is>
       </x:c>
       <x:c r="E445" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002786687</x:t>
+          <x:t>4002783199, 4002784832</x:t>
         </x:is>
       </x:c>
       <x:c r="F445" s="1" t="inlineStr">
@@ -52200,17 +52200,17 @@
       </x:c>
       <x:c r="I445" s="1" t="inlineStr">
         <x:is>
-          <x:t>9004</x:t>
+          <x:t>8996</x:t>
         </x:is>
       </x:c>
       <x:c r="J445" s="1" t="inlineStr">
         <x:is>
-          <x:t>Biblis</x:t>
+          <x:t>Bierun</x:t>
         </x:is>
       </x:c>
       <x:c r="K445" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9004-1A</x:t>
+          <x:t>DCZONE-8996-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L445" s="1" t="inlineStr">
@@ -52219,7 +52219,7 @@
         </x:is>
       </x:c>
       <x:c r="M445" s="3" t="n">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N445" s="1" t="inlineStr">
         <x:is>
@@ -52231,29 +52231,29 @@
       </x:c>
       <x:c r="P445" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q445" s="2" t="n">
-        <x:v>46064.3556481482</x:v>
+        <x:v>46064.3255671296</x:v>
       </x:c>
       <x:c r="R445" s="2" t="n">
-        <x:v>46064.3696412037</x:v>
+        <x:v>46064.4187731482</x:v>
       </x:c>
       <x:c r="S445" s="2" t="n">
-        <x:v>46064.4355787037</x:v>
+        <x:v>46064.4423148148</x:v>
       </x:c>
       <x:c r="T445" s="3">
         <x:v/>
       </x:c>
       <x:c r="U445" s="3" t="inlineStr">
         <x:is>
-          <x:t>20</x:t>
+          <x:t>135</x:t>
         </x:is>
       </x:c>
       <x:c r="V445" s="3" t="inlineStr">
         <x:is>
-          <x:t>95</x:t>
+          <x:t>33</x:t>
         </x:is>
       </x:c>
       <x:c r="W445" s="1">
@@ -52270,8 +52270,10 @@
       <x:c r="Z445" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA445" s="1">
-        <x:v/>
+      <x:c r="AA445" s="1" t="inlineStr">
+        <x:is>
+          <x:t>783479987</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="446">
@@ -52287,7 +52289,7 @@
       </x:c>
       <x:c r="C446" s="4" t="inlineStr">
         <x:is>
-          <x:t>1803862</x:t>
+          <x:t>1801301</x:t>
         </x:is>
       </x:c>
       <x:c r="D446" s="4">
@@ -52295,7 +52297,7 @@
       </x:c>
       <x:c r="E446" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002791655</x:t>
+          <x:t>4002786687</x:t>
         </x:is>
       </x:c>
       <x:c r="F446" s="1" t="inlineStr">
@@ -52315,17 +52317,17 @@
       </x:c>
       <x:c r="I446" s="1" t="inlineStr">
         <x:is>
-          <x:t>9000</x:t>
+          <x:t>9004</x:t>
         </x:is>
       </x:c>
       <x:c r="J446" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zwaagdijk</x:t>
+          <x:t>Biblis</x:t>
         </x:is>
       </x:c>
       <x:c r="K446" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9000-1A</x:t>
+          <x:t>DCZONE-9004-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L446" s="1" t="inlineStr">
@@ -52350,25 +52352,25 @@
         </x:is>
       </x:c>
       <x:c r="Q446" s="2" t="n">
-        <x:v>46064.3632407407</x:v>
+        <x:v>46064.3556481482</x:v>
       </x:c>
       <x:c r="R446" s="2" t="n">
-        <x:v>46064.3841666667</x:v>
+        <x:v>46064.3696412037</x:v>
       </x:c>
       <x:c r="S446" s="2" t="n">
-        <x:v>46064.4143055556</x:v>
+        <x:v>46064.4355787037</x:v>
       </x:c>
       <x:c r="T446" s="3">
         <x:v/>
       </x:c>
       <x:c r="U446" s="3" t="inlineStr">
         <x:is>
-          <x:t>30</x:t>
+          <x:t>20</x:t>
         </x:is>
       </x:c>
       <x:c r="V446" s="3" t="inlineStr">
         <x:is>
-          <x:t>43</x:t>
+          <x:t>95</x:t>
         </x:is>
       </x:c>
       <x:c r="W446" s="1">
@@ -52385,10 +52387,8 @@
       <x:c r="Z446" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA446" s="1" t="inlineStr">
-        <x:is>
-          <x:t>DC1</x:t>
-        </x:is>
+      <x:c r="AA446" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="447">
@@ -60921,7 +60921,7 @@
       </x:c>
       <x:c r="C520" s="4" t="inlineStr">
         <x:is>
-          <x:t>1812169</x:t>
+          <x:t>1811885</x:t>
         </x:is>
       </x:c>
       <x:c r="D520" s="4">
@@ -60929,7 +60929,7 @@
       </x:c>
       <x:c r="E520" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002799538</x:t>
+          <x:t>4002799495</x:t>
         </x:is>
       </x:c>
       <x:c r="F520" s="1" t="inlineStr">
@@ -60949,17 +60949,17 @@
       </x:c>
       <x:c r="I520" s="1" t="inlineStr">
         <x:is>
-          <x:t>8997</x:t>
+          <x:t>8992</x:t>
         </x:is>
       </x:c>
       <x:c r="J520" s="1" t="inlineStr">
         <x:is>
-          <x:t>Verrières</x:t>
+          <x:t>Illescas</x:t>
         </x:is>
       </x:c>
       <x:c r="K520" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8997-1A</x:t>
+          <x:t>DCZONE-8992-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L520" s="1" t="inlineStr">
@@ -60980,29 +60980,29 @@
       </x:c>
       <x:c r="P520" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q520" s="2" t="n">
-        <x:v>46076.5008333333</x:v>
+        <x:v>46076.5719097222</x:v>
       </x:c>
       <x:c r="R520" s="2" t="n">
-        <x:v>46076.5506018518</x:v>
+        <x:v>46076.573599537</x:v>
       </x:c>
       <x:c r="S520" s="2" t="n">
-        <x:v>46076.6222569444</x:v>
+        <x:v>46076.6047685185</x:v>
       </x:c>
       <x:c r="T520" s="3">
         <x:v/>
       </x:c>
       <x:c r="U520" s="3" t="inlineStr">
         <x:is>
-          <x:t>71</x:t>
+          <x:t>2</x:t>
         </x:is>
       </x:c>
       <x:c r="V520" s="3" t="inlineStr">
         <x:is>
-          <x:t>104</x:t>
+          <x:t>45</x:t>
         </x:is>
       </x:c>
       <x:c r="W520" s="1">
@@ -61019,8 +61019,10 @@
       <x:c r="Z520" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA520" s="1">
-        <x:v/>
+      <x:c r="AA520" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001463259</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="521">
@@ -61036,7 +61038,7 @@
       </x:c>
       <x:c r="C521" s="4" t="inlineStr">
         <x:is>
-          <x:t>1811885</x:t>
+          <x:t>1812169</x:t>
         </x:is>
       </x:c>
       <x:c r="D521" s="4">
@@ -61044,7 +61046,7 @@
       </x:c>
       <x:c r="E521" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002799495</x:t>
+          <x:t>4002799538</x:t>
         </x:is>
       </x:c>
       <x:c r="F521" s="1" t="inlineStr">
@@ -61064,17 +61066,17 @@
       </x:c>
       <x:c r="I521" s="1" t="inlineStr">
         <x:is>
-          <x:t>8992</x:t>
+          <x:t>8997</x:t>
         </x:is>
       </x:c>
       <x:c r="J521" s="1" t="inlineStr">
         <x:is>
-          <x:t>Illescas</x:t>
+          <x:t>Verrières</x:t>
         </x:is>
       </x:c>
       <x:c r="K521" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8992-1A</x:t>
+          <x:t>DCZONE-8997-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L521" s="1" t="inlineStr">
@@ -61095,29 +61097,29 @@
       </x:c>
       <x:c r="P521" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q521" s="2" t="n">
-        <x:v>46076.5719097222</x:v>
+        <x:v>46076.5008333333</x:v>
       </x:c>
       <x:c r="R521" s="2" t="n">
-        <x:v>46076.573599537</x:v>
+        <x:v>46076.5506018518</x:v>
       </x:c>
       <x:c r="S521" s="2" t="n">
-        <x:v>46076.6047685185</x:v>
+        <x:v>46076.6222569444</x:v>
       </x:c>
       <x:c r="T521" s="3">
         <x:v/>
       </x:c>
       <x:c r="U521" s="3" t="inlineStr">
         <x:is>
-          <x:t>2</x:t>
+          <x:t>71</x:t>
         </x:is>
       </x:c>
       <x:c r="V521" s="3" t="inlineStr">
         <x:is>
-          <x:t>45</x:t>
+          <x:t>104</x:t>
         </x:is>
       </x:c>
       <x:c r="W521" s="1">
@@ -61134,10 +61136,8 @@
       <x:c r="Z521" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA521" s="1" t="inlineStr">
-        <x:is>
-          <x:t>5001463259</x:t>
-        </x:is>
+      <x:c r="AA521" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="522">
@@ -73829,82 +73829,312 @@
         <x:v/>
       </x:c>
     </x:row>
-    <x:row r="631" spans="1:27" x14ac:dyDescent="0.25">
-      <x:c r="A631" s="1" t="s">
+    <x:row r="631">
+      <x:c r="A631" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B631" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C631" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1824127</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D631" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E631" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002817857</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F631" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G631" s="1" t="inlineStr">
+        <x:is>
+          <x:t>GOLD Regular</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H631" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I631" s="1" t="inlineStr">
+        <x:is>
+          <x:t>8997</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J631" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Verrières</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K631" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-8997-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L631" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M631" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N631" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O631" s="2" t="n">
+        <x:v>46087.2916666667</x:v>
+      </x:c>
+      <x:c r="P631" s="1" t="inlineStr">
+        <x:is>
+          <x:t>On time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q631" s="2" t="n">
+        <x:v>46087.2811921296</x:v>
+      </x:c>
+      <x:c r="R631" s="2" t="n">
+        <x:v>46087.2853356482</x:v>
+      </x:c>
+      <x:c r="S631" s="2" t="n">
+        <x:v>46087.3277777778</x:v>
+      </x:c>
+      <x:c r="T631" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U631" s="3" t="inlineStr">
+        <x:is>
+          <x:t>6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="V631" s="3" t="inlineStr">
+        <x:is>
+          <x:t>62</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W631" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X631" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y631" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z631" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA631" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="632">
+      <x:c r="A632" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B632" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C632" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1820757</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D632" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E632" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002812629</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F632" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G632" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Gold Allocation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H632" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I632" s="1" t="inlineStr">
+        <x:is>
+          <x:t>9005</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J632" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Labastide</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K632" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-9005-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L632" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M632" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N632" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O632" s="2" t="n">
+        <x:v>46087.4166666667</x:v>
+      </x:c>
+      <x:c r="P632" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q632" s="2" t="n">
+        <x:v>46087.3898148148</x:v>
+      </x:c>
+      <x:c r="R632" s="2" t="n">
+        <x:v>46087.4132986111</x:v>
+      </x:c>
+      <x:c r="S632" s="2" t="n">
+        <x:v>46087.5254861111</x:v>
+      </x:c>
+      <x:c r="T632" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U632" s="3" t="inlineStr">
+        <x:is>
+          <x:t>34</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="V632" s="3" t="inlineStr">
+        <x:is>
+          <x:t>161</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W632" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X632" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y632" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z632" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA632" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="633" spans="1:27" x14ac:dyDescent="0.25">
+      <x:c r="A633" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B631" s="1" t="s">
+      <x:c r="B633" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C631" s="4" t="s">
+      <x:c r="C633" s="4" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D631" s="4" t="s">
+      <x:c r="D633" s="4" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="E631" s="1" t="s">
+      <x:c r="E633" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F631" s="1"/>
-      <x:c r="G631" s="1"/>
-      <x:c r="H631" s="1" t="s">
+      <x:c r="F633" s="1"/>
+      <x:c r="G633" s="1"/>
+      <x:c r="H633" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I631" s="1" t="s">
+      <x:c r="I633" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="J631" s="1" t="s">
+      <x:c r="J633" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K631" s="1" t="s">
+      <x:c r="K633" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="L631" s="1" t="s">
+      <x:c r="L633" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="M631" s="3" t="s">
+      <x:c r="M633" s="3" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="N631" s="1" t="s">
+      <x:c r="N633" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="O631" s="2" t="s">
+      <x:c r="O633" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="P631" s="1" t="s">
+      <x:c r="P633" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="Q631" s="2" t="s">
+      <x:c r="Q633" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="R631" s="2" t="s">
+      <x:c r="R633" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="S631" s="2" t="s">
+      <x:c r="S633" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="T631" s="3" t="s">
+      <x:c r="T633" s="3" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="U631" s="3" t="s">
+      <x:c r="U633" s="3" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="V631" s="3" t="s">
+      <x:c r="V633" s="3" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="W631" s="1" t="s">
+      <x:c r="W633" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="X631" s="1" t="s">
+      <x:c r="X633" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="Y631" s="1" t="s">
+      <x:c r="Y633" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="Z631" s="2" t="s">
+      <x:c r="Z633" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="AA631" s="1"/>
+      <x:c r="AA633" s="1"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/AppointmentReport_latest.xlsx
+++ b/data/AppointmentReport_latest.xlsx
@@ -16,7 +16,7 @@
     <x:sheet name="Blad1" sheetId="1" r:id="rId1"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="DataStart">Blad1!$A$665</x:definedName>
+    <x:definedName name="DataStart">Blad1!$A$687</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="191029"/>
   <x:extLst>
@@ -3397,7 +3397,7 @@
       </x:c>
       <x:c r="C26" s="4" t="inlineStr">
         <x:is>
-          <x:t>1705744</x:t>
+          <x:t>1721176</x:t>
         </x:is>
       </x:c>
       <x:c r="D26" s="4">
@@ -3405,7 +3405,7 @@
       </x:c>
       <x:c r="E26" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679385</x:t>
+          <x:t>4002697876</x:t>
         </x:is>
       </x:c>
       <x:c r="F26" s="1" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </x:c>
       <x:c r="G26" s="1" t="inlineStr">
         <x:is>
-          <x:t>-</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H26" s="1" t="inlineStr">
@@ -3425,17 +3425,17 @@
       </x:c>
       <x:c r="I26" s="1" t="inlineStr">
         <x:is>
-          <x:t>8991</x:t>
+          <x:t>9006</x:t>
         </x:is>
       </x:c>
       <x:c r="J26" s="1" t="inlineStr">
         <x:is>
-          <x:t>Altedo</x:t>
+          <x:t>Belleville</x:t>
         </x:is>
       </x:c>
       <x:c r="K26" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8991-1A</x:t>
+          <x:t>DCZONE-9006-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L26" s="1" t="inlineStr">
@@ -3456,31 +3456,29 @@
       </x:c>
       <x:c r="P26" s="1" t="inlineStr">
         <x:is>
-          <x:t>Late</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q26" s="2" t="n">
-        <x:v>46006.5859722222</x:v>
+        <x:v>46006.3576041667</x:v>
       </x:c>
       <x:c r="R26" s="2" t="n">
-        <x:v>46006.6044560185</x:v>
+        <x:v>46006.4275347222</x:v>
       </x:c>
       <x:c r="S26" s="2" t="n">
-        <x:v>46006.632025463</x:v>
-      </x:c>
-      <x:c r="T26" s="3" t="inlineStr">
-        <x:is>
-          <x:t>303</x:t>
-        </x:is>
+        <x:v>46006.446875</x:v>
+      </x:c>
+      <x:c r="T26" s="3">
+        <x:v/>
       </x:c>
       <x:c r="U26" s="3" t="inlineStr">
         <x:is>
-          <x:t>27</x:t>
+          <x:t>101</x:t>
         </x:is>
       </x:c>
       <x:c r="V26" s="3" t="inlineStr">
         <x:is>
-          <x:t>40</x:t>
+          <x:t>28</x:t>
         </x:is>
       </x:c>
       <x:c r="W26" s="1">
@@ -3497,10 +3495,8 @@
       <x:c r="Z26" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA26" s="1" t="inlineStr">
-        <x:is>
-          <x:t>MAIL RITARDO (1), Baia 31</x:t>
-        </x:is>
+      <x:c r="AA26" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -3516,7 +3512,7 @@
       </x:c>
       <x:c r="C27" s="4" t="inlineStr">
         <x:is>
-          <x:t>1721176</x:t>
+          <x:t>1704131</x:t>
         </x:is>
       </x:c>
       <x:c r="D27" s="4">
@@ -3524,7 +3520,7 @@
       </x:c>
       <x:c r="E27" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002697876</x:t>
+          <x:t>4002679364</x:t>
         </x:is>
       </x:c>
       <x:c r="F27" s="1" t="inlineStr">
@@ -3534,7 +3530,7 @@
       </x:c>
       <x:c r="G27" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>-</x:t>
         </x:is>
       </x:c>
       <x:c r="H27" s="1" t="inlineStr">
@@ -3544,17 +3540,17 @@
       </x:c>
       <x:c r="I27" s="1" t="inlineStr">
         <x:is>
-          <x:t>9006</x:t>
+          <x:t>8997</x:t>
         </x:is>
       </x:c>
       <x:c r="J27" s="1" t="inlineStr">
         <x:is>
-          <x:t>Belleville</x:t>
+          <x:t>Verrières</x:t>
         </x:is>
       </x:c>
       <x:c r="K27" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9006-1A</x:t>
+          <x:t>DCZONE-8997-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L27" s="1" t="inlineStr">
@@ -3575,29 +3571,29 @@
       </x:c>
       <x:c r="P27" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q27" s="2" t="n">
-        <x:v>46006.3576041667</x:v>
+        <x:v>46006.2951041667</x:v>
       </x:c>
       <x:c r="R27" s="2" t="n">
-        <x:v>46006.4275347222</x:v>
+        <x:v>46006.3036689815</x:v>
       </x:c>
       <x:c r="S27" s="2" t="n">
-        <x:v>46006.446875</x:v>
+        <x:v>46006.3270486111</x:v>
       </x:c>
       <x:c r="T27" s="3">
         <x:v/>
       </x:c>
       <x:c r="U27" s="3" t="inlineStr">
         <x:is>
-          <x:t>101</x:t>
+          <x:t>13</x:t>
         </x:is>
       </x:c>
       <x:c r="V27" s="3" t="inlineStr">
         <x:is>
-          <x:t>28</x:t>
+          <x:t>33</x:t>
         </x:is>
       </x:c>
       <x:c r="W27" s="1">
@@ -3631,7 +3627,7 @@
       </x:c>
       <x:c r="C28" s="4" t="inlineStr">
         <x:is>
-          <x:t>1704131</x:t>
+          <x:t>1705744</x:t>
         </x:is>
       </x:c>
       <x:c r="D28" s="4">
@@ -3639,7 +3635,7 @@
       </x:c>
       <x:c r="E28" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679364</x:t>
+          <x:t>4002679385</x:t>
         </x:is>
       </x:c>
       <x:c r="F28" s="1" t="inlineStr">
@@ -3659,17 +3655,17 @@
       </x:c>
       <x:c r="I28" s="1" t="inlineStr">
         <x:is>
-          <x:t>8997</x:t>
+          <x:t>8991</x:t>
         </x:is>
       </x:c>
       <x:c r="J28" s="1" t="inlineStr">
         <x:is>
-          <x:t>Verrières</x:t>
+          <x:t>Altedo</x:t>
         </x:is>
       </x:c>
       <x:c r="K28" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8997-1A</x:t>
+          <x:t>DCZONE-8991-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L28" s="1" t="inlineStr">
@@ -3690,29 +3686,31 @@
       </x:c>
       <x:c r="P28" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>Late</x:t>
         </x:is>
       </x:c>
       <x:c r="Q28" s="2" t="n">
-        <x:v>46006.2951041667</x:v>
+        <x:v>46006.5859722222</x:v>
       </x:c>
       <x:c r="R28" s="2" t="n">
-        <x:v>46006.3036689815</x:v>
+        <x:v>46006.6044560185</x:v>
       </x:c>
       <x:c r="S28" s="2" t="n">
-        <x:v>46006.3270486111</x:v>
-      </x:c>
-      <x:c r="T28" s="3">
-        <x:v/>
+        <x:v>46006.632025463</x:v>
+      </x:c>
+      <x:c r="T28" s="3" t="inlineStr">
+        <x:is>
+          <x:t>303</x:t>
+        </x:is>
       </x:c>
       <x:c r="U28" s="3" t="inlineStr">
         <x:is>
-          <x:t>13</x:t>
+          <x:t>27</x:t>
         </x:is>
       </x:c>
       <x:c r="V28" s="3" t="inlineStr">
         <x:is>
-          <x:t>33</x:t>
+          <x:t>40</x:t>
         </x:is>
       </x:c>
       <x:c r="W28" s="1">
@@ -3729,8 +3727,10 @@
       <x:c r="Z28" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA28" s="1">
-        <x:v/>
+      <x:c r="AA28" s="1" t="inlineStr">
+        <x:is>
+          <x:t>MAIL RITARDO (1), Baia 31</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -5957,7 +5957,7 @@
       </x:c>
       <x:c r="C48" s="4" t="inlineStr">
         <x:is>
-          <x:t>1722246</x:t>
+          <x:t>1722917</x:t>
         </x:is>
       </x:c>
       <x:c r="D48" s="4">
@@ -5965,7 +5965,7 @@
       </x:c>
       <x:c r="E48" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002699458</x:t>
+          <x:t>4002698860</x:t>
         </x:is>
       </x:c>
       <x:c r="F48" s="1" t="inlineStr">
@@ -5985,17 +5985,17 @@
       </x:c>
       <x:c r="I48" s="1" t="inlineStr">
         <x:is>
-          <x:t>8995</x:t>
+          <x:t>8994</x:t>
         </x:is>
       </x:c>
       <x:c r="J48" s="1" t="inlineStr">
         <x:is>
-          <x:t>Ensues</x:t>
+          <x:t>Zakroczym</x:t>
         </x:is>
       </x:c>
       <x:c r="K48" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8995-1A</x:t>
+          <x:t>DCZONE-8994-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L48" s="1" t="inlineStr">
@@ -6016,31 +6016,29 @@
       </x:c>
       <x:c r="P48" s="1" t="inlineStr">
         <x:is>
-          <x:t>Late</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q48" s="2" t="n">
-        <x:v>46007.4316550926</x:v>
+        <x:v>46007.3506712963</x:v>
       </x:c>
       <x:c r="R48" s="2" t="n">
-        <x:v>46007.5971759259</x:v>
+        <x:v>46007.3513541667</x:v>
       </x:c>
       <x:c r="S48" s="2" t="n">
-        <x:v>46007.5972106481</x:v>
-      </x:c>
-      <x:c r="T48" s="3" t="inlineStr">
-        <x:is>
-          <x:t>81</x:t>
-        </x:is>
+        <x:v>46007.3764351852</x:v>
+      </x:c>
+      <x:c r="T48" s="3">
+        <x:v/>
       </x:c>
       <x:c r="U48" s="3" t="inlineStr">
         <x:is>
-          <x:t>238</x:t>
+          <x:t>1</x:t>
         </x:is>
       </x:c>
       <x:c r="V48" s="3" t="inlineStr">
         <x:is>
-          <x:t>0</x:t>
+          <x:t>37</x:t>
         </x:is>
       </x:c>
       <x:c r="W48" s="1">
@@ -6057,8 +6055,10 @@
       <x:c r="Z48" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA48" s="1">
-        <x:v/>
+      <x:c r="AA48" s="1" t="inlineStr">
+        <x:is>
+          <x:t>889102284</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -6074,7 +6074,7 @@
       </x:c>
       <x:c r="C49" s="4" t="inlineStr">
         <x:is>
-          <x:t>1705830</x:t>
+          <x:t>1722246</x:t>
         </x:is>
       </x:c>
       <x:c r="D49" s="4">
@@ -6082,7 +6082,7 @@
       </x:c>
       <x:c r="E49" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679382</x:t>
+          <x:t>4002699458</x:t>
         </x:is>
       </x:c>
       <x:c r="F49" s="1" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </x:c>
       <x:c r="G49" s="1" t="inlineStr">
         <x:is>
-          <x:t>-</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H49" s="1" t="inlineStr">
@@ -6102,17 +6102,17 @@
       </x:c>
       <x:c r="I49" s="1" t="inlineStr">
         <x:is>
-          <x:t>8998</x:t>
+          <x:t>8995</x:t>
         </x:is>
       </x:c>
       <x:c r="J49" s="1" t="inlineStr">
         <x:is>
-          <x:t>Bratislava</x:t>
+          <x:t>Ensues</x:t>
         </x:is>
       </x:c>
       <x:c r="K49" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8998-1A</x:t>
+          <x:t>DCZONE-8995-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L49" s="1" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </x:c>
       <x:c r="N49" s="1" t="inlineStr">
         <x:is>
-          <x:t>No</x:t>
+          <x:t>Yes</x:t>
         </x:is>
       </x:c>
       <x:c r="O49" s="2" t="n">
@@ -6133,31 +6133,31 @@
       </x:c>
       <x:c r="P49" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Late</x:t>
         </x:is>
       </x:c>
       <x:c r="Q49" s="2" t="n">
-        <x:v>46007.3786111111</x:v>
+        <x:v>46007.4316550926</x:v>
       </x:c>
       <x:c r="R49" s="2" t="n">
-        <x:v>46007.3958333333</x:v>
+        <x:v>46007.5971759259</x:v>
       </x:c>
       <x:c r="S49" s="2" t="n">
-        <x:v>46007.4166666667</x:v>
+        <x:v>46007.5972106481</x:v>
       </x:c>
       <x:c r="T49" s="3" t="inlineStr">
         <x:is>
-          <x:t>5</x:t>
+          <x:t>81</x:t>
         </x:is>
       </x:c>
       <x:c r="U49" s="3" t="inlineStr">
         <x:is>
-          <x:t>25</x:t>
+          <x:t>238</x:t>
         </x:is>
       </x:c>
       <x:c r="V49" s="3" t="inlineStr">
         <x:is>
-          <x:t>30</x:t>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="W49" s="1">
@@ -6191,7 +6191,7 @@
       </x:c>
       <x:c r="C50" s="4" t="inlineStr">
         <x:is>
-          <x:t>1722917</x:t>
+          <x:t>1705830</x:t>
         </x:is>
       </x:c>
       <x:c r="D50" s="4">
@@ -6199,7 +6199,7 @@
       </x:c>
       <x:c r="E50" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002698860</x:t>
+          <x:t>4002679382</x:t>
         </x:is>
       </x:c>
       <x:c r="F50" s="1" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </x:c>
       <x:c r="G50" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>-</x:t>
         </x:is>
       </x:c>
       <x:c r="H50" s="1" t="inlineStr">
@@ -6219,17 +6219,17 @@
       </x:c>
       <x:c r="I50" s="1" t="inlineStr">
         <x:is>
-          <x:t>8994</x:t>
+          <x:t>8998</x:t>
         </x:is>
       </x:c>
       <x:c r="J50" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zakroczym</x:t>
+          <x:t>Bratislava</x:t>
         </x:is>
       </x:c>
       <x:c r="K50" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8994-1A</x:t>
+          <x:t>DCZONE-8998-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L50" s="1" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </x:c>
       <x:c r="N50" s="1" t="inlineStr">
         <x:is>
-          <x:t>Yes</x:t>
+          <x:t>No</x:t>
         </x:is>
       </x:c>
       <x:c r="O50" s="2" t="n">
@@ -6250,29 +6250,31 @@
       </x:c>
       <x:c r="P50" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q50" s="2" t="n">
-        <x:v>46007.3506712963</x:v>
+        <x:v>46007.3786111111</x:v>
       </x:c>
       <x:c r="R50" s="2" t="n">
-        <x:v>46007.3513541667</x:v>
+        <x:v>46007.3958333333</x:v>
       </x:c>
       <x:c r="S50" s="2" t="n">
-        <x:v>46007.3764351852</x:v>
-      </x:c>
-      <x:c r="T50" s="3">
-        <x:v/>
+        <x:v>46007.4166666667</x:v>
+      </x:c>
+      <x:c r="T50" s="3" t="inlineStr">
+        <x:is>
+          <x:t>5</x:t>
+        </x:is>
       </x:c>
       <x:c r="U50" s="3" t="inlineStr">
         <x:is>
-          <x:t>1</x:t>
+          <x:t>25</x:t>
         </x:is>
       </x:c>
       <x:c r="V50" s="3" t="inlineStr">
         <x:is>
-          <x:t>37</x:t>
+          <x:t>30</x:t>
         </x:is>
       </x:c>
       <x:c r="W50" s="1">
@@ -6289,10 +6291,8 @@
       <x:c r="Z50" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA50" s="1" t="inlineStr">
-        <x:is>
-          <x:t>889102284</x:t>
-        </x:is>
+      <x:c r="AA50" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -6889,7 +6889,7 @@
       </x:c>
       <x:c r="C56" s="4" t="inlineStr">
         <x:is>
-          <x:t>1704109</x:t>
+          <x:t>1706450</x:t>
         </x:is>
       </x:c>
       <x:c r="D56" s="4">
@@ -6897,7 +6897,7 @@
       </x:c>
       <x:c r="E56" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002681520</x:t>
+          <x:t>4002679353</x:t>
         </x:is>
       </x:c>
       <x:c r="F56" s="1" t="inlineStr">
@@ -6917,17 +6917,17 @@
       </x:c>
       <x:c r="I56" s="1" t="inlineStr">
         <x:is>
-          <x:t>9006</x:t>
+          <x:t>8992</x:t>
         </x:is>
       </x:c>
       <x:c r="J56" s="1" t="inlineStr">
         <x:is>
-          <x:t>Belleville</x:t>
+          <x:t>Illescas</x:t>
         </x:is>
       </x:c>
       <x:c r="K56" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9006-1A</x:t>
+          <x:t>DCZONE-8992-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L56" s="1" t="inlineStr">
@@ -6948,29 +6948,31 @@
       </x:c>
       <x:c r="P56" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>Late</x:t>
         </x:is>
       </x:c>
       <x:c r="Q56" s="2" t="n">
-        <x:v>46007.4240046296</x:v>
+        <x:v>46007.4856365741</x:v>
       </x:c>
       <x:c r="R56" s="2" t="n">
-        <x:v>46007.4363310185</x:v>
+        <x:v>46007.4883680556</x:v>
       </x:c>
       <x:c r="S56" s="2" t="n">
-        <x:v>46007.5099305556</x:v>
-      </x:c>
-      <x:c r="T56" s="3">
-        <x:v/>
+        <x:v>46007.5242361111</x:v>
+      </x:c>
+      <x:c r="T56" s="3" t="inlineStr">
+        <x:is>
+          <x:t>39</x:t>
+        </x:is>
       </x:c>
       <x:c r="U56" s="3" t="inlineStr">
         <x:is>
-          <x:t>18</x:t>
+          <x:t>4</x:t>
         </x:is>
       </x:c>
       <x:c r="V56" s="3" t="inlineStr">
         <x:is>
-          <x:t>106</x:t>
+          <x:t>51</x:t>
         </x:is>
       </x:c>
       <x:c r="W56" s="1">
@@ -6987,8 +6989,10 @@
       <x:c r="Z56" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA56" s="1">
-        <x:v/>
+      <x:c r="AA56" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001404204</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -7004,7 +7008,7 @@
       </x:c>
       <x:c r="C57" s="4" t="inlineStr">
         <x:is>
-          <x:t>1705675</x:t>
+          <x:t>1724966</x:t>
         </x:is>
       </x:c>
       <x:c r="D57" s="4">
@@ -7012,7 +7016,7 @@
       </x:c>
       <x:c r="E57" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002681526</x:t>
+          <x:t>4002702413</x:t>
         </x:is>
       </x:c>
       <x:c r="F57" s="1" t="inlineStr">
@@ -7022,7 +7026,7 @@
       </x:c>
       <x:c r="G57" s="1" t="inlineStr">
         <x:is>
-          <x:t>-</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H57" s="1" t="inlineStr">
@@ -7032,17 +7036,17 @@
       </x:c>
       <x:c r="I57" s="1" t="inlineStr">
         <x:is>
-          <x:t>8995</x:t>
+          <x:t>8993</x:t>
         </x:is>
       </x:c>
       <x:c r="J57" s="1" t="inlineStr">
         <x:is>
-          <x:t>Ensues</x:t>
+          <x:t>Novara</x:t>
         </x:is>
       </x:c>
       <x:c r="K57" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8995-1A</x:t>
+          <x:t>DCZONE-8993-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L57" s="1" t="inlineStr">
@@ -7063,31 +7067,31 @@
       </x:c>
       <x:c r="P57" s="1" t="inlineStr">
         <x:is>
-          <x:t>Late</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q57" s="2" t="n">
-        <x:v>46007.4893518519</x:v>
+        <x:v>46007.4610416667</x:v>
       </x:c>
       <x:c r="R57" s="2" t="n">
-        <x:v>46007.5763888889</x:v>
+        <x:v>46007.4897800926</x:v>
       </x:c>
       <x:c r="S57" s="2" t="n">
-        <x:v>46007.6213657407</x:v>
+        <x:v>46007.516412037</x:v>
       </x:c>
       <x:c r="T57" s="3" t="inlineStr">
         <x:is>
-          <x:t>44</x:t>
+          <x:t>3</x:t>
         </x:is>
       </x:c>
       <x:c r="U57" s="3" t="inlineStr">
         <x:is>
-          <x:t>126</x:t>
+          <x:t>42</x:t>
         </x:is>
       </x:c>
       <x:c r="V57" s="3" t="inlineStr">
         <x:is>
-          <x:t>64</x:t>
+          <x:t>38</x:t>
         </x:is>
       </x:c>
       <x:c r="W57" s="1">
@@ -7121,7 +7125,7 @@
       </x:c>
       <x:c r="C58" s="4" t="inlineStr">
         <x:is>
-          <x:t>1724966</x:t>
+          <x:t>1704109</x:t>
         </x:is>
       </x:c>
       <x:c r="D58" s="4">
@@ -7129,7 +7133,7 @@
       </x:c>
       <x:c r="E58" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002702413</x:t>
+          <x:t>4002681520</x:t>
         </x:is>
       </x:c>
       <x:c r="F58" s="1" t="inlineStr">
@@ -7139,7 +7143,7 @@
       </x:c>
       <x:c r="G58" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>-</x:t>
         </x:is>
       </x:c>
       <x:c r="H58" s="1" t="inlineStr">
@@ -7149,17 +7153,17 @@
       </x:c>
       <x:c r="I58" s="1" t="inlineStr">
         <x:is>
-          <x:t>8993</x:t>
+          <x:t>9006</x:t>
         </x:is>
       </x:c>
       <x:c r="J58" s="1" t="inlineStr">
         <x:is>
-          <x:t>Novara</x:t>
+          <x:t>Belleville</x:t>
         </x:is>
       </x:c>
       <x:c r="K58" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8993-1A</x:t>
+          <x:t>DCZONE-9006-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L58" s="1" t="inlineStr">
@@ -7180,31 +7184,29 @@
       </x:c>
       <x:c r="P58" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q58" s="2" t="n">
-        <x:v>46007.4610416667</x:v>
+        <x:v>46007.4240046296</x:v>
       </x:c>
       <x:c r="R58" s="2" t="n">
-        <x:v>46007.4897800926</x:v>
+        <x:v>46007.4363310185</x:v>
       </x:c>
       <x:c r="S58" s="2" t="n">
-        <x:v>46007.516412037</x:v>
-      </x:c>
-      <x:c r="T58" s="3" t="inlineStr">
-        <x:is>
-          <x:t>3</x:t>
-        </x:is>
+        <x:v>46007.5099305556</x:v>
+      </x:c>
+      <x:c r="T58" s="3">
+        <x:v/>
       </x:c>
       <x:c r="U58" s="3" t="inlineStr">
         <x:is>
-          <x:t>42</x:t>
+          <x:t>18</x:t>
         </x:is>
       </x:c>
       <x:c r="V58" s="3" t="inlineStr">
         <x:is>
-          <x:t>38</x:t>
+          <x:t>106</x:t>
         </x:is>
       </x:c>
       <x:c r="W58" s="1">
@@ -7238,7 +7240,7 @@
       </x:c>
       <x:c r="C59" s="4" t="inlineStr">
         <x:is>
-          <x:t>1706450</x:t>
+          <x:t>1705675</x:t>
         </x:is>
       </x:c>
       <x:c r="D59" s="4">
@@ -7246,7 +7248,7 @@
       </x:c>
       <x:c r="E59" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679353</x:t>
+          <x:t>4002681526</x:t>
         </x:is>
       </x:c>
       <x:c r="F59" s="1" t="inlineStr">
@@ -7266,17 +7268,17 @@
       </x:c>
       <x:c r="I59" s="1" t="inlineStr">
         <x:is>
-          <x:t>8992</x:t>
+          <x:t>8995</x:t>
         </x:is>
       </x:c>
       <x:c r="J59" s="1" t="inlineStr">
         <x:is>
-          <x:t>Illescas</x:t>
+          <x:t>Ensues</x:t>
         </x:is>
       </x:c>
       <x:c r="K59" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8992-1A</x:t>
+          <x:t>DCZONE-8995-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L59" s="1" t="inlineStr">
@@ -7301,27 +7303,27 @@
         </x:is>
       </x:c>
       <x:c r="Q59" s="2" t="n">
-        <x:v>46007.4856365741</x:v>
+        <x:v>46007.4893518519</x:v>
       </x:c>
       <x:c r="R59" s="2" t="n">
-        <x:v>46007.4883680556</x:v>
+        <x:v>46007.5763888889</x:v>
       </x:c>
       <x:c r="S59" s="2" t="n">
-        <x:v>46007.5242361111</x:v>
+        <x:v>46007.6213657407</x:v>
       </x:c>
       <x:c r="T59" s="3" t="inlineStr">
         <x:is>
-          <x:t>39</x:t>
+          <x:t>44</x:t>
         </x:is>
       </x:c>
       <x:c r="U59" s="3" t="inlineStr">
         <x:is>
-          <x:t>4</x:t>
+          <x:t>126</x:t>
         </x:is>
       </x:c>
       <x:c r="V59" s="3" t="inlineStr">
         <x:is>
-          <x:t>51</x:t>
+          <x:t>64</x:t>
         </x:is>
       </x:c>
       <x:c r="W59" s="1">
@@ -7338,10 +7340,8 @@
       <x:c r="Z59" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA59" s="1" t="inlineStr">
-        <x:is>
-          <x:t>5001404204</x:t>
-        </x:is>
+      <x:c r="AA59" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -9334,7 +9334,7 @@
       </x:c>
       <x:c r="C77" s="4" t="inlineStr">
         <x:is>
-          <x:t>1722015</x:t>
+          <x:t>1721206</x:t>
         </x:is>
       </x:c>
       <x:c r="D77" s="4">
@@ -9342,7 +9342,7 @@
       </x:c>
       <x:c r="E77" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002697880</x:t>
+          <x:t>4002697869</x:t>
         </x:is>
       </x:c>
       <x:c r="F77" s="1" t="inlineStr">
@@ -9362,17 +9362,17 @@
       </x:c>
       <x:c r="I77" s="1" t="inlineStr">
         <x:is>
-          <x:t>8995</x:t>
+          <x:t>8990</x:t>
         </x:is>
       </x:c>
       <x:c r="J77" s="1" t="inlineStr">
         <x:is>
-          <x:t>Ensues</x:t>
+          <x:t>Wallersdorf</x:t>
         </x:is>
       </x:c>
       <x:c r="K77" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8995-1A</x:t>
+          <x:t>DCZONE-8990-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L77" s="1" t="inlineStr">
@@ -9381,7 +9381,7 @@
         </x:is>
       </x:c>
       <x:c r="M77" s="3" t="n">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="N77" s="1" t="inlineStr">
         <x:is>
@@ -9393,29 +9393,29 @@
       </x:c>
       <x:c r="P77" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q77" s="2" t="n">
-        <x:v>46008.3650115741</x:v>
+        <x:v>46008.3519560185</x:v>
       </x:c>
       <x:c r="R77" s="2" t="n">
-        <x:v>46008.3795486111</x:v>
+        <x:v>46008.3805439815</x:v>
       </x:c>
       <x:c r="S77" s="2" t="n">
-        <x:v>46008.4017013889</x:v>
+        <x:v>46008.4478356481</x:v>
       </x:c>
       <x:c r="T77" s="3">
         <x:v/>
       </x:c>
       <x:c r="U77" s="3" t="inlineStr">
         <x:is>
-          <x:t>21</x:t>
+          <x:t>41</x:t>
         </x:is>
       </x:c>
       <x:c r="V77" s="3" t="inlineStr">
         <x:is>
-          <x:t>32</x:t>
+          <x:t>97</x:t>
         </x:is>
       </x:c>
       <x:c r="W77" s="1">
@@ -9432,8 +9432,10 @@
       <x:c r="Z77" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA77" s="1">
-        <x:v/>
+      <x:c r="AA77" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001405691 opt. dock 15</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -9449,7 +9451,7 @@
       </x:c>
       <x:c r="C78" s="4" t="inlineStr">
         <x:is>
-          <x:t>1721206</x:t>
+          <x:t>1704135</x:t>
         </x:is>
       </x:c>
       <x:c r="D78" s="4">
@@ -9457,7 +9459,7 @@
       </x:c>
       <x:c r="E78" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002697869</x:t>
+          <x:t>4002679363</x:t>
         </x:is>
       </x:c>
       <x:c r="F78" s="1" t="inlineStr">
@@ -9467,7 +9469,7 @@
       </x:c>
       <x:c r="G78" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>-</x:t>
         </x:is>
       </x:c>
       <x:c r="H78" s="1" t="inlineStr">
@@ -9477,17 +9479,17 @@
       </x:c>
       <x:c r="I78" s="1" t="inlineStr">
         <x:is>
-          <x:t>8990</x:t>
+          <x:t>8997</x:t>
         </x:is>
       </x:c>
       <x:c r="J78" s="1" t="inlineStr">
         <x:is>
-          <x:t>Wallersdorf</x:t>
+          <x:t>Verrières</x:t>
         </x:is>
       </x:c>
       <x:c r="K78" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8990-1A</x:t>
+          <x:t>DCZONE-8997-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L78" s="1" t="inlineStr">
@@ -9508,29 +9510,29 @@
       </x:c>
       <x:c r="P78" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q78" s="2" t="n">
-        <x:v>46008.3519560185</x:v>
+        <x:v>46008.3673148148</x:v>
       </x:c>
       <x:c r="R78" s="2" t="n">
-        <x:v>46008.3805439815</x:v>
+        <x:v>46008.4060300926</x:v>
       </x:c>
       <x:c r="S78" s="2" t="n">
-        <x:v>46008.4478356481</x:v>
+        <x:v>46008.5131712963</x:v>
       </x:c>
       <x:c r="T78" s="3">
         <x:v/>
       </x:c>
       <x:c r="U78" s="3" t="inlineStr">
         <x:is>
-          <x:t>41</x:t>
+          <x:t>56</x:t>
         </x:is>
       </x:c>
       <x:c r="V78" s="3" t="inlineStr">
         <x:is>
-          <x:t>97</x:t>
+          <x:t>154</x:t>
         </x:is>
       </x:c>
       <x:c r="W78" s="1">
@@ -9547,10 +9549,8 @@
       <x:c r="Z78" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA78" s="1" t="inlineStr">
-        <x:is>
-          <x:t>5001405691 opt. dock 15</x:t>
-        </x:is>
+      <x:c r="AA78" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -9566,7 +9566,7 @@
       </x:c>
       <x:c r="C79" s="4" t="inlineStr">
         <x:is>
-          <x:t>1704135</x:t>
+          <x:t>1722015</x:t>
         </x:is>
       </x:c>
       <x:c r="D79" s="4">
@@ -9574,7 +9574,7 @@
       </x:c>
       <x:c r="E79" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679363</x:t>
+          <x:t>4002697880</x:t>
         </x:is>
       </x:c>
       <x:c r="F79" s="1" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </x:c>
       <x:c r="G79" s="1" t="inlineStr">
         <x:is>
-          <x:t>-</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H79" s="1" t="inlineStr">
@@ -9594,17 +9594,17 @@
       </x:c>
       <x:c r="I79" s="1" t="inlineStr">
         <x:is>
-          <x:t>8997</x:t>
+          <x:t>8995</x:t>
         </x:is>
       </x:c>
       <x:c r="J79" s="1" t="inlineStr">
         <x:is>
-          <x:t>Verrières</x:t>
+          <x:t>Ensues</x:t>
         </x:is>
       </x:c>
       <x:c r="K79" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8997-1A</x:t>
+          <x:t>DCZONE-8995-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L79" s="1" t="inlineStr">
@@ -9613,7 +9613,7 @@
         </x:is>
       </x:c>
       <x:c r="M79" s="3" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="N79" s="1" t="inlineStr">
         <x:is>
@@ -9629,25 +9629,25 @@
         </x:is>
       </x:c>
       <x:c r="Q79" s="2" t="n">
-        <x:v>46008.3673148148</x:v>
+        <x:v>46008.3650115741</x:v>
       </x:c>
       <x:c r="R79" s="2" t="n">
-        <x:v>46008.4060300926</x:v>
+        <x:v>46008.3795486111</x:v>
       </x:c>
       <x:c r="S79" s="2" t="n">
-        <x:v>46008.5131712963</x:v>
+        <x:v>46008.4017013889</x:v>
       </x:c>
       <x:c r="T79" s="3">
         <x:v/>
       </x:c>
       <x:c r="U79" s="3" t="inlineStr">
         <x:is>
-          <x:t>56</x:t>
+          <x:t>21</x:t>
         </x:is>
       </x:c>
       <x:c r="V79" s="3" t="inlineStr">
         <x:is>
-          <x:t>154</x:t>
+          <x:t>32</x:t>
         </x:is>
       </x:c>
       <x:c r="W79" s="1">
@@ -9796,7 +9796,7 @@
       </x:c>
       <x:c r="C81" s="4" t="inlineStr">
         <x:is>
-          <x:t>1722450</x:t>
+          <x:t>1722268</x:t>
         </x:is>
       </x:c>
       <x:c r="D81" s="4">
@@ -9804,7 +9804,7 @@
       </x:c>
       <x:c r="E81" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002702414</x:t>
+          <x:t>4002699456</x:t>
         </x:is>
       </x:c>
       <x:c r="F81" s="1" t="inlineStr">
@@ -9824,17 +9824,17 @@
       </x:c>
       <x:c r="I81" s="1" t="inlineStr">
         <x:is>
-          <x:t>8991</x:t>
+          <x:t>8997</x:t>
         </x:is>
       </x:c>
       <x:c r="J81" s="1" t="inlineStr">
         <x:is>
-          <x:t>Altedo</x:t>
+          <x:t>Verrières</x:t>
         </x:is>
       </x:c>
       <x:c r="K81" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8991-1A</x:t>
+          <x:t>DCZONE-8997-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L81" s="1" t="inlineStr">
@@ -9859,25 +9859,25 @@
         </x:is>
       </x:c>
       <x:c r="Q81" s="2" t="n">
-        <x:v>46008.3907986111</x:v>
+        <x:v>46008.3762615741</x:v>
       </x:c>
       <x:c r="R81" s="2" t="n">
-        <x:v>46008.392037037</x:v>
+        <x:v>46008.4302314815</x:v>
       </x:c>
       <x:c r="S81" s="2" t="n">
-        <x:v>46008.4203819444</x:v>
+        <x:v>46008.5609490741</x:v>
       </x:c>
       <x:c r="T81" s="3">
         <x:v/>
       </x:c>
       <x:c r="U81" s="3" t="inlineStr">
         <x:is>
-          <x:t>2</x:t>
+          <x:t>78</x:t>
         </x:is>
       </x:c>
       <x:c r="V81" s="3" t="inlineStr">
         <x:is>
-          <x:t>41</x:t>
+          <x:t>188</x:t>
         </x:is>
       </x:c>
       <x:c r="W81" s="1">
@@ -9911,7 +9911,7 @@
       </x:c>
       <x:c r="C82" s="4" t="inlineStr">
         <x:is>
-          <x:t>1722268</x:t>
+          <x:t>1722450</x:t>
         </x:is>
       </x:c>
       <x:c r="D82" s="4">
@@ -9919,7 +9919,7 @@
       </x:c>
       <x:c r="E82" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002699456</x:t>
+          <x:t>4002702414</x:t>
         </x:is>
       </x:c>
       <x:c r="F82" s="1" t="inlineStr">
@@ -9939,17 +9939,17 @@
       </x:c>
       <x:c r="I82" s="1" t="inlineStr">
         <x:is>
-          <x:t>8997</x:t>
+          <x:t>8991</x:t>
         </x:is>
       </x:c>
       <x:c r="J82" s="1" t="inlineStr">
         <x:is>
-          <x:t>Verrières</x:t>
+          <x:t>Altedo</x:t>
         </x:is>
       </x:c>
       <x:c r="K82" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8997-1A</x:t>
+          <x:t>DCZONE-8991-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L82" s="1" t="inlineStr">
@@ -9974,25 +9974,25 @@
         </x:is>
       </x:c>
       <x:c r="Q82" s="2" t="n">
-        <x:v>46008.3762615741</x:v>
+        <x:v>46008.3907986111</x:v>
       </x:c>
       <x:c r="R82" s="2" t="n">
-        <x:v>46008.4302314815</x:v>
+        <x:v>46008.392037037</x:v>
       </x:c>
       <x:c r="S82" s="2" t="n">
-        <x:v>46008.5609490741</x:v>
+        <x:v>46008.4203819444</x:v>
       </x:c>
       <x:c r="T82" s="3">
         <x:v/>
       </x:c>
       <x:c r="U82" s="3" t="inlineStr">
         <x:is>
-          <x:t>78</x:t>
+          <x:t>2</x:t>
         </x:is>
       </x:c>
       <x:c r="V82" s="3" t="inlineStr">
         <x:is>
-          <x:t>188</x:t>
+          <x:t>41</x:t>
         </x:is>
       </x:c>
       <x:c r="W82" s="1">
@@ -11880,7 +11880,7 @@
       </x:c>
       <x:c r="C99" s="4" t="inlineStr">
         <x:is>
-          <x:t>1722474</x:t>
+          <x:t>1705833</x:t>
         </x:is>
       </x:c>
       <x:c r="D99" s="4">
@@ -11888,7 +11888,7 @@
       </x:c>
       <x:c r="E99" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002698858</x:t>
+          <x:t>4002679438</x:t>
         </x:is>
       </x:c>
       <x:c r="F99" s="1" t="inlineStr">
@@ -11898,7 +11898,7 @@
       </x:c>
       <x:c r="G99" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>-</x:t>
         </x:is>
       </x:c>
       <x:c r="H99" s="1" t="inlineStr">
@@ -11908,17 +11908,17 @@
       </x:c>
       <x:c r="I99" s="1" t="inlineStr">
         <x:is>
-          <x:t>8996</x:t>
+          <x:t>8998</x:t>
         </x:is>
       </x:c>
       <x:c r="J99" s="1" t="inlineStr">
         <x:is>
-          <x:t>Bierun</x:t>
+          <x:t>Bratislava</x:t>
         </x:is>
       </x:c>
       <x:c r="K99" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8996-1A</x:t>
+          <x:t>DCZONE-8998-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L99" s="1" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </x:c>
       <x:c r="N99" s="1" t="inlineStr">
         <x:is>
-          <x:t>Yes</x:t>
+          <x:t>No</x:t>
         </x:is>
       </x:c>
       <x:c r="O99" s="2" t="n">
@@ -11939,29 +11939,31 @@
       </x:c>
       <x:c r="P99" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>Late - Reported</x:t>
         </x:is>
       </x:c>
       <x:c r="Q99" s="2" t="n">
-        <x:v>46009.2309375</x:v>
+        <x:v>46009.4178819444</x:v>
       </x:c>
       <x:c r="R99" s="2" t="n">
-        <x:v>46009.2325462963</x:v>
+        <x:v>46009.4756944444</x:v>
       </x:c>
       <x:c r="S99" s="2" t="n">
-        <x:v>46009.2915972222</x:v>
-      </x:c>
-      <x:c r="T99" s="3">
-        <x:v/>
+        <x:v>46009.492662037</x:v>
+      </x:c>
+      <x:c r="T99" s="3" t="inlineStr">
+        <x:is>
+          <x:t>181</x:t>
+        </x:is>
       </x:c>
       <x:c r="U99" s="3" t="inlineStr">
         <x:is>
-          <x:t>2</x:t>
+          <x:t>84</x:t>
         </x:is>
       </x:c>
       <x:c r="V99" s="3" t="inlineStr">
         <x:is>
-          <x:t>85</x:t>
+          <x:t>24</x:t>
         </x:is>
       </x:c>
       <x:c r="W99" s="1">
@@ -11980,7 +11982,7 @@
       </x:c>
       <x:c r="AA99" s="1" t="inlineStr">
         <x:is>
-          <x:t>451106337</x:t>
+          <x:t>ETA 11:30</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -12114,7 +12116,7 @@
       </x:c>
       <x:c r="C101" s="4" t="inlineStr">
         <x:is>
-          <x:t>1705833</x:t>
+          <x:t>1722474</x:t>
         </x:is>
       </x:c>
       <x:c r="D101" s="4">
@@ -12122,7 +12124,7 @@
       </x:c>
       <x:c r="E101" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679438</x:t>
+          <x:t>4002698858</x:t>
         </x:is>
       </x:c>
       <x:c r="F101" s="1" t="inlineStr">
@@ -12132,7 +12134,7 @@
       </x:c>
       <x:c r="G101" s="1" t="inlineStr">
         <x:is>
-          <x:t>-</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H101" s="1" t="inlineStr">
@@ -12142,17 +12144,17 @@
       </x:c>
       <x:c r="I101" s="1" t="inlineStr">
         <x:is>
-          <x:t>8998</x:t>
+          <x:t>8996</x:t>
         </x:is>
       </x:c>
       <x:c r="J101" s="1" t="inlineStr">
         <x:is>
-          <x:t>Bratislava</x:t>
+          <x:t>Bierun</x:t>
         </x:is>
       </x:c>
       <x:c r="K101" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8998-1A</x:t>
+          <x:t>DCZONE-8996-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L101" s="1" t="inlineStr">
@@ -12165,7 +12167,7 @@
       </x:c>
       <x:c r="N101" s="1" t="inlineStr">
         <x:is>
-          <x:t>No</x:t>
+          <x:t>Yes</x:t>
         </x:is>
       </x:c>
       <x:c r="O101" s="2" t="n">
@@ -12173,31 +12175,29 @@
       </x:c>
       <x:c r="P101" s="1" t="inlineStr">
         <x:is>
-          <x:t>Late - Reported</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q101" s="2" t="n">
-        <x:v>46009.4178819444</x:v>
+        <x:v>46009.2309375</x:v>
       </x:c>
       <x:c r="R101" s="2" t="n">
-        <x:v>46009.4756944444</x:v>
+        <x:v>46009.2325462963</x:v>
       </x:c>
       <x:c r="S101" s="2" t="n">
-        <x:v>46009.492662037</x:v>
-      </x:c>
-      <x:c r="T101" s="3" t="inlineStr">
-        <x:is>
-          <x:t>181</x:t>
-        </x:is>
+        <x:v>46009.2915972222</x:v>
+      </x:c>
+      <x:c r="T101" s="3">
+        <x:v/>
       </x:c>
       <x:c r="U101" s="3" t="inlineStr">
         <x:is>
-          <x:t>84</x:t>
+          <x:t>2</x:t>
         </x:is>
       </x:c>
       <x:c r="V101" s="3" t="inlineStr">
         <x:is>
-          <x:t>24</x:t>
+          <x:t>85</x:t>
         </x:is>
       </x:c>
       <x:c r="W101" s="1">
@@ -12216,7 +12216,7 @@
       </x:c>
       <x:c r="AA101" s="1" t="inlineStr">
         <x:is>
-          <x:t>ETA 11:30</x:t>
+          <x:t>451106337</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -15731,7 +15731,7 @@
       </x:c>
       <x:c r="C132" s="4" t="inlineStr">
         <x:is>
-          <x:t>1705819</x:t>
+          <x:t>1700365</x:t>
         </x:is>
       </x:c>
       <x:c r="D132" s="4">
@@ -15739,7 +15739,7 @@
       </x:c>
       <x:c r="E132" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679342</x:t>
+          <x:t>4002675811</x:t>
         </x:is>
       </x:c>
       <x:c r="F132" s="1" t="inlineStr">
@@ -15759,17 +15759,17 @@
       </x:c>
       <x:c r="I132" s="1" t="inlineStr">
         <x:is>
-          <x:t>9004</x:t>
+          <x:t>9000</x:t>
         </x:is>
       </x:c>
       <x:c r="J132" s="1" t="inlineStr">
         <x:is>
-          <x:t>Biblis</x:t>
+          <x:t>Zwaagdijk</x:t>
         </x:is>
       </x:c>
       <x:c r="K132" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9004-1A</x:t>
+          <x:t>DCZONE-9000-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L132" s="1" t="inlineStr">
@@ -15790,21 +15790,21 @@
       </x:c>
       <x:c r="P132" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Late</x:t>
         </x:is>
       </x:c>
       <x:c r="Q132" s="2" t="n">
-        <x:v>46010.2585648148</x:v>
+        <x:v>46010.2732986111</x:v>
       </x:c>
       <x:c r="R132" s="2" t="n">
-        <x:v>46010.2589583333</x:v>
+        <x:v>46010.2734143519</x:v>
       </x:c>
       <x:c r="S132" s="2" t="n">
-        <x:v>46010.290625</x:v>
+        <x:v>46010.2913425926</x:v>
       </x:c>
       <x:c r="T132" s="3" t="inlineStr">
         <x:is>
-          <x:t>12</x:t>
+          <x:t>33</x:t>
         </x:is>
       </x:c>
       <x:c r="U132" s="3" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </x:c>
       <x:c r="V132" s="3" t="inlineStr">
         <x:is>
-          <x:t>46</x:t>
+          <x:t>26</x:t>
         </x:is>
       </x:c>
       <x:c r="W132" s="1">
@@ -15848,7 +15848,7 @@
       </x:c>
       <x:c r="C133" s="4" t="inlineStr">
         <x:is>
-          <x:t>1700365</x:t>
+          <x:t>1705819</x:t>
         </x:is>
       </x:c>
       <x:c r="D133" s="4">
@@ -15856,7 +15856,7 @@
       </x:c>
       <x:c r="E133" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002675811</x:t>
+          <x:t>4002679342</x:t>
         </x:is>
       </x:c>
       <x:c r="F133" s="1" t="inlineStr">
@@ -15876,17 +15876,17 @@
       </x:c>
       <x:c r="I133" s="1" t="inlineStr">
         <x:is>
-          <x:t>9000</x:t>
+          <x:t>9004</x:t>
         </x:is>
       </x:c>
       <x:c r="J133" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zwaagdijk</x:t>
+          <x:t>Biblis</x:t>
         </x:is>
       </x:c>
       <x:c r="K133" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9000-1A</x:t>
+          <x:t>DCZONE-9004-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L133" s="1" t="inlineStr">
@@ -15907,21 +15907,21 @@
       </x:c>
       <x:c r="P133" s="1" t="inlineStr">
         <x:is>
-          <x:t>Late</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q133" s="2" t="n">
-        <x:v>46010.2732986111</x:v>
+        <x:v>46010.2585648148</x:v>
       </x:c>
       <x:c r="R133" s="2" t="n">
-        <x:v>46010.2734143519</x:v>
+        <x:v>46010.2589583333</x:v>
       </x:c>
       <x:c r="S133" s="2" t="n">
-        <x:v>46010.2913425926</x:v>
+        <x:v>46010.290625</x:v>
       </x:c>
       <x:c r="T133" s="3" t="inlineStr">
         <x:is>
-          <x:t>33</x:t>
+          <x:t>12</x:t>
         </x:is>
       </x:c>
       <x:c r="U133" s="3" t="inlineStr">
@@ -15931,7 +15931,7 @@
       </x:c>
       <x:c r="V133" s="3" t="inlineStr">
         <x:is>
-          <x:t>26</x:t>
+          <x:t>46</x:t>
         </x:is>
       </x:c>
       <x:c r="W133" s="1">
@@ -16197,7 +16197,7 @@
       </x:c>
       <x:c r="C136" s="4" t="inlineStr">
         <x:is>
-          <x:t>1705827</x:t>
+          <x:t>1705700</x:t>
         </x:is>
       </x:c>
       <x:c r="D136" s="4">
@@ -16205,7 +16205,7 @@
       </x:c>
       <x:c r="E136" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679436</x:t>
+          <x:t>4002679401</x:t>
         </x:is>
       </x:c>
       <x:c r="F136" s="1" t="inlineStr">
@@ -16225,17 +16225,17 @@
       </x:c>
       <x:c r="I136" s="1" t="inlineStr">
         <x:is>
-          <x:t>8996</x:t>
+          <x:t>9002</x:t>
         </x:is>
       </x:c>
       <x:c r="J136" s="1" t="inlineStr">
         <x:is>
-          <x:t>Bierun</x:t>
+          <x:t>Echt</x:t>
         </x:is>
       </x:c>
       <x:c r="K136" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8996-1A</x:t>
+          <x:t>DCZONE-9002-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L136" s="1" t="inlineStr">
@@ -16256,20 +16256,22 @@
       </x:c>
       <x:c r="P136" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q136" s="2" t="n">
-        <x:v>46010.2668055556</x:v>
+        <x:v>46010.2927314815</x:v>
       </x:c>
       <x:c r="R136" s="2" t="n">
-        <x:v>46010.2673611111</x:v>
+        <x:v>46010.293275463</x:v>
       </x:c>
       <x:c r="S136" s="2" t="n">
-        <x:v>46010.3013773148</x:v>
-      </x:c>
-      <x:c r="T136" s="3">
-        <x:v/>
+        <x:v>46010.3132638889</x:v>
+      </x:c>
+      <x:c r="T136" s="3" t="inlineStr">
+        <x:is>
+          <x:t>1</x:t>
+        </x:is>
       </x:c>
       <x:c r="U136" s="3" t="inlineStr">
         <x:is>
@@ -16278,7 +16280,7 @@
       </x:c>
       <x:c r="V136" s="3" t="inlineStr">
         <x:is>
-          <x:t>48</x:t>
+          <x:t>29</x:t>
         </x:is>
       </x:c>
       <x:c r="W136" s="1">
@@ -16286,7 +16288,7 @@
       </x:c>
       <x:c r="X136" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>Logistic quality: badly foiled</x:t>
         </x:is>
       </x:c>
       <x:c r="Y136" s="1">
@@ -16297,7 +16299,7 @@
       </x:c>
       <x:c r="AA136" s="1" t="inlineStr">
         <x:is>
-          <x:t>570081051</x:t>
+          <x:t>5001409471  64 / Chauffeur gaat zelf sealen</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -16314,7 +16316,7 @@
       </x:c>
       <x:c r="C137" s="4" t="inlineStr">
         <x:is>
-          <x:t>1705700</x:t>
+          <x:t>1705827</x:t>
         </x:is>
       </x:c>
       <x:c r="D137" s="4">
@@ -16322,7 +16324,7 @@
       </x:c>
       <x:c r="E137" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679401</x:t>
+          <x:t>4002679436</x:t>
         </x:is>
       </x:c>
       <x:c r="F137" s="1" t="inlineStr">
@@ -16342,17 +16344,17 @@
       </x:c>
       <x:c r="I137" s="1" t="inlineStr">
         <x:is>
-          <x:t>9002</x:t>
+          <x:t>8996</x:t>
         </x:is>
       </x:c>
       <x:c r="J137" s="1" t="inlineStr">
         <x:is>
-          <x:t>Echt</x:t>
+          <x:t>Bierun</x:t>
         </x:is>
       </x:c>
       <x:c r="K137" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9002-1A</x:t>
+          <x:t>DCZONE-8996-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L137" s="1" t="inlineStr">
@@ -16373,31 +16375,29 @@
       </x:c>
       <x:c r="P137" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q137" s="2" t="n">
-        <x:v>46010.2927314815</x:v>
+        <x:v>46010.2668055556</x:v>
       </x:c>
       <x:c r="R137" s="2" t="n">
-        <x:v>46010.293275463</x:v>
+        <x:v>46010.2673611111</x:v>
       </x:c>
       <x:c r="S137" s="2" t="n">
-        <x:v>46010.3132638889</x:v>
-      </x:c>
-      <x:c r="T137" s="3" t="inlineStr">
+        <x:v>46010.3013773148</x:v>
+      </x:c>
+      <x:c r="T137" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U137" s="3" t="inlineStr">
         <x:is>
           <x:t>1</x:t>
         </x:is>
       </x:c>
-      <x:c r="U137" s="3" t="inlineStr">
-        <x:is>
-          <x:t>1</x:t>
-        </x:is>
-      </x:c>
       <x:c r="V137" s="3" t="inlineStr">
         <x:is>
-          <x:t>29</x:t>
+          <x:t>48</x:t>
         </x:is>
       </x:c>
       <x:c r="W137" s="1">
@@ -16405,7 +16405,7 @@
       </x:c>
       <x:c r="X137" s="1" t="inlineStr">
         <x:is>
-          <x:t>Logistic quality: badly foiled</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="Y137" s="1">
@@ -16416,7 +16416,7 @@
       </x:c>
       <x:c r="AA137" s="1" t="inlineStr">
         <x:is>
-          <x:t>5001409471  64 / Chauffeur gaat zelf sealen</x:t>
+          <x:t>570081051</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -19689,7 +19689,7 @@
       </x:c>
       <x:c r="C166" s="4" t="inlineStr">
         <x:is>
-          <x:t>1744552</x:t>
+          <x:t>1744570</x:t>
         </x:is>
       </x:c>
       <x:c r="D166" s="4">
@@ -19697,7 +19697,7 @@
       </x:c>
       <x:c r="E166" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002728642</x:t>
+          <x:t>4002728644</x:t>
         </x:is>
       </x:c>
       <x:c r="F166" s="1" t="inlineStr">
@@ -19712,35 +19712,35 @@
       </x:c>
       <x:c r="H166" s="1" t="inlineStr">
         <x:is>
-          <x:t>Finished</x:t>
+          <x:t>Removed</x:t>
         </x:is>
       </x:c>
       <x:c r="I166" s="1" t="inlineStr">
         <x:is>
-          <x:t>9003</x:t>
+          <x:t>9000</x:t>
         </x:is>
       </x:c>
       <x:c r="J166" s="1" t="inlineStr">
         <x:is>
-          <x:t>Moissy</x:t>
+          <x:t>Zwaagdijk</x:t>
         </x:is>
       </x:c>
       <x:c r="K166" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9003-1A</x:t>
+          <x:t>DCZONE-9000-2A</x:t>
         </x:is>
       </x:c>
       <x:c r="L166" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zone 1 Truck</x:t>
+          <x:t>Zone 2 Truck</x:t>
         </x:is>
       </x:c>
       <x:c r="M166" s="3" t="n">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N166" s="1" t="inlineStr">
         <x:is>
-          <x:t>Yes</x:t>
+          <x:t>No</x:t>
         </x:is>
       </x:c>
       <x:c r="O166" s="2" t="n">
@@ -19748,29 +19748,29 @@
       </x:c>
       <x:c r="P166" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q166" s="2" t="n">
-        <x:v>46014.348125</x:v>
-      </x:c>
-      <x:c r="R166" s="2" t="n">
-        <x:v>46014.4496759259</x:v>
-      </x:c>
-      <x:c r="S166" s="2" t="n">
-        <x:v>46014.5156481481</x:v>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q166" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R166" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S166" s="2">
+        <x:v/>
       </x:c>
       <x:c r="T166" s="3">
         <x:v/>
       </x:c>
       <x:c r="U166" s="3" t="inlineStr">
         <x:is>
-          <x:t>146</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="V166" s="3" t="inlineStr">
         <x:is>
-          <x:t>95</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="W166" s="1">
@@ -19781,11 +19781,13 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y166" s="1">
-        <x:v/>
-      </x:c>
-      <x:c r="Z166" s="2">
-        <x:v/>
+      <x:c r="Y166" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z166" s="2" t="n">
+        <x:v>46003.4545486111</x:v>
       </x:c>
       <x:c r="AA166" s="1">
         <x:v/>
@@ -19804,7 +19806,7 @@
       </x:c>
       <x:c r="C167" s="4" t="inlineStr">
         <x:is>
-          <x:t>1744570</x:t>
+          <x:t>1744552</x:t>
         </x:is>
       </x:c>
       <x:c r="D167" s="4">
@@ -19812,7 +19814,7 @@
       </x:c>
       <x:c r="E167" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002728644</x:t>
+          <x:t>4002728642</x:t>
         </x:is>
       </x:c>
       <x:c r="F167" s="1" t="inlineStr">
@@ -19827,35 +19829,35 @@
       </x:c>
       <x:c r="H167" s="1" t="inlineStr">
         <x:is>
-          <x:t>Removed</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I167" s="1" t="inlineStr">
         <x:is>
-          <x:t>9000</x:t>
+          <x:t>9003</x:t>
         </x:is>
       </x:c>
       <x:c r="J167" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zwaagdijk</x:t>
+          <x:t>Moissy</x:t>
         </x:is>
       </x:c>
       <x:c r="K167" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9000-2A</x:t>
+          <x:t>DCZONE-9003-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L167" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zone 2 Truck</x:t>
+          <x:t>Zone 1 Truck</x:t>
         </x:is>
       </x:c>
       <x:c r="M167" s="3" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N167" s="1" t="inlineStr">
         <x:is>
-          <x:t>No</x:t>
+          <x:t>Yes</x:t>
         </x:is>
       </x:c>
       <x:c r="O167" s="2" t="n">
@@ -19863,29 +19865,29 @@
       </x:c>
       <x:c r="P167" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q167" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R167" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S167" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q167" s="2" t="n">
+        <x:v>46014.348125</x:v>
+      </x:c>
+      <x:c r="R167" s="2" t="n">
+        <x:v>46014.4496759259</x:v>
+      </x:c>
+      <x:c r="S167" s="2" t="n">
+        <x:v>46014.5156481481</x:v>
       </x:c>
       <x:c r="T167" s="3">
         <x:v/>
       </x:c>
       <x:c r="U167" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>146</x:t>
         </x:is>
       </x:c>
       <x:c r="V167" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>95</x:t>
         </x:is>
       </x:c>
       <x:c r="W167" s="1">
@@ -19896,13 +19898,11 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y167" s="1" t="inlineStr">
-        <x:is>
-          <x:t>Good(s)Factory</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Z167" s="2" t="n">
-        <x:v>46003.4545486111</x:v>
+      <x:c r="Y167" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z167" s="2">
+        <x:v/>
       </x:c>
       <x:c r="AA167" s="1">
         <x:v/>
@@ -20268,7 +20268,7 @@
       </x:c>
       <x:c r="C171" s="4" t="inlineStr">
         <x:is>
-          <x:t>1744819</x:t>
+          <x:t>1744871</x:t>
         </x:is>
       </x:c>
       <x:c r="D171" s="4">
@@ -20276,7 +20276,7 @@
       </x:c>
       <x:c r="E171" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002728651</x:t>
+          <x:t>4002728646</x:t>
         </x:is>
       </x:c>
       <x:c r="F171" s="1" t="inlineStr">
@@ -20291,22 +20291,22 @@
       </x:c>
       <x:c r="H171" s="1" t="inlineStr">
         <x:is>
-          <x:t>Removed</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I171" s="1" t="inlineStr">
         <x:is>
-          <x:t>9002</x:t>
+          <x:t>9000</x:t>
         </x:is>
       </x:c>
       <x:c r="J171" s="1" t="inlineStr">
         <x:is>
-          <x:t>Echt</x:t>
+          <x:t>Zwaagdijk</x:t>
         </x:is>
       </x:c>
       <x:c r="K171" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9002-1A</x:t>
+          <x:t>DCZONE-9000-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L171" s="1" t="inlineStr">
@@ -20315,11 +20315,11 @@
         </x:is>
       </x:c>
       <x:c r="M171" s="3" t="n">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="N171" s="1" t="inlineStr">
         <x:is>
-          <x:t>No</x:t>
+          <x:t>Yes</x:t>
         </x:is>
       </x:c>
       <x:c r="O171" s="2" t="n">
@@ -20327,29 +20327,29 @@
       </x:c>
       <x:c r="P171" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q171" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R171" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S171" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q171" s="2" t="n">
+        <x:v>46014.4124305556</x:v>
+      </x:c>
+      <x:c r="R171" s="2" t="n">
+        <x:v>46014.4129861111</x:v>
+      </x:c>
+      <x:c r="S171" s="2" t="n">
+        <x:v>46014.4373726852</x:v>
       </x:c>
       <x:c r="T171" s="3">
         <x:v/>
       </x:c>
       <x:c r="U171" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>1</x:t>
         </x:is>
       </x:c>
       <x:c r="V171" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>35</x:t>
         </x:is>
       </x:c>
       <x:c r="W171" s="1">
@@ -20360,16 +20360,16 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y171" s="1" t="inlineStr">
-        <x:is>
-          <x:t>Good(s)Factory</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Z171" s="2" t="n">
-        <x:v>46003.433587963</x:v>
-      </x:c>
-      <x:c r="AA171" s="1">
-        <x:v/>
+      <x:c r="Y171" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z171" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA171" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DC1</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -20385,7 +20385,7 @@
       </x:c>
       <x:c r="C172" s="4" t="inlineStr">
         <x:is>
-          <x:t>1744871</x:t>
+          <x:t>1745855</x:t>
         </x:is>
       </x:c>
       <x:c r="D172" s="4">
@@ -20393,7 +20393,7 @@
       </x:c>
       <x:c r="E172" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002728646</x:t>
+          <x:t>4002728651</x:t>
         </x:is>
       </x:c>
       <x:c r="F172" s="1" t="inlineStr">
@@ -20413,17 +20413,17 @@
       </x:c>
       <x:c r="I172" s="1" t="inlineStr">
         <x:is>
-          <x:t>9000</x:t>
+          <x:t>9002</x:t>
         </x:is>
       </x:c>
       <x:c r="J172" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zwaagdijk</x:t>
+          <x:t>Echt</x:t>
         </x:is>
       </x:c>
       <x:c r="K172" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9000-1A</x:t>
+          <x:t>DCZONE-9002-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L172" s="1" t="inlineStr">
@@ -20432,7 +20432,7 @@
         </x:is>
       </x:c>
       <x:c r="M172" s="3" t="n">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="N172" s="1" t="inlineStr">
         <x:is>
@@ -20444,29 +20444,29 @@
       </x:c>
       <x:c r="P172" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q172" s="2" t="n">
-        <x:v>46014.4124305556</x:v>
+        <x:v>46014.4405671296</x:v>
       </x:c>
       <x:c r="R172" s="2" t="n">
-        <x:v>46014.4129861111</x:v>
+        <x:v>46014.4606481481</x:v>
       </x:c>
       <x:c r="S172" s="2" t="n">
-        <x:v>46014.4373726852</x:v>
+        <x:v>46014.4952314815</x:v>
       </x:c>
       <x:c r="T172" s="3">
         <x:v/>
       </x:c>
       <x:c r="U172" s="3" t="inlineStr">
         <x:is>
-          <x:t>1</x:t>
+          <x:t>29</x:t>
         </x:is>
       </x:c>
       <x:c r="V172" s="3" t="inlineStr">
         <x:is>
-          <x:t>35</x:t>
+          <x:t>50</x:t>
         </x:is>
       </x:c>
       <x:c r="W172" s="1">
@@ -20485,7 +20485,7 @@
       </x:c>
       <x:c r="AA172" s="1" t="inlineStr">
         <x:is>
-          <x:t>DC1</x:t>
+          <x:t>5001412549  64</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -20502,7 +20502,7 @@
       </x:c>
       <x:c r="C173" s="4" t="inlineStr">
         <x:is>
-          <x:t>1745855</x:t>
+          <x:t>1744819</x:t>
         </x:is>
       </x:c>
       <x:c r="D173" s="4">
@@ -20525,7 +20525,7 @@
       </x:c>
       <x:c r="H173" s="1" t="inlineStr">
         <x:is>
-          <x:t>Finished</x:t>
+          <x:t>Removed</x:t>
         </x:is>
       </x:c>
       <x:c r="I173" s="1" t="inlineStr">
@@ -20549,11 +20549,11 @@
         </x:is>
       </x:c>
       <x:c r="M173" s="3" t="n">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N173" s="1" t="inlineStr">
         <x:is>
-          <x:t>Yes</x:t>
+          <x:t>No</x:t>
         </x:is>
       </x:c>
       <x:c r="O173" s="2" t="n">
@@ -20561,29 +20561,29 @@
       </x:c>
       <x:c r="P173" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q173" s="2" t="n">
-        <x:v>46014.4405671296</x:v>
-      </x:c>
-      <x:c r="R173" s="2" t="n">
-        <x:v>46014.4606481481</x:v>
-      </x:c>
-      <x:c r="S173" s="2" t="n">
-        <x:v>46014.4952314815</x:v>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q173" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R173" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S173" s="2">
+        <x:v/>
       </x:c>
       <x:c r="T173" s="3">
         <x:v/>
       </x:c>
       <x:c r="U173" s="3" t="inlineStr">
         <x:is>
-          <x:t>29</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="V173" s="3" t="inlineStr">
         <x:is>
-          <x:t>50</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="W173" s="1">
@@ -20594,16 +20594,16 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y173" s="1">
-        <x:v/>
-      </x:c>
-      <x:c r="Z173" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="AA173" s="1" t="inlineStr">
-        <x:is>
-          <x:t>5001412549  64</x:t>
-        </x:is>
+      <x:c r="Y173" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z173" s="2" t="n">
+        <x:v>46003.433587963</x:v>
+      </x:c>
+      <x:c r="AA173" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -25396,7 +25396,7 @@
       </x:c>
       <x:c r="C215" s="4" t="inlineStr">
         <x:is>
-          <x:t>1759453</x:t>
+          <x:t>1757340</x:t>
         </x:is>
       </x:c>
       <x:c r="D215" s="4">
@@ -25404,7 +25404,7 @@
       </x:c>
       <x:c r="E215" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002746321</x:t>
+          <x:t>4002743698</x:t>
         </x:is>
       </x:c>
       <x:c r="F215" s="1" t="inlineStr">
@@ -25414,7 +25414,7 @@
       </x:c>
       <x:c r="G215" s="1" t="inlineStr">
         <x:is>
-          <x:t>Gold Allocation</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H215" s="1" t="inlineStr">
@@ -25424,17 +25424,17 @@
       </x:c>
       <x:c r="I215" s="1" t="inlineStr">
         <x:is>
-          <x:t>9004</x:t>
+          <x:t>8992</x:t>
         </x:is>
       </x:c>
       <x:c r="J215" s="1" t="inlineStr">
         <x:is>
-          <x:t>Biblis</x:t>
+          <x:t>Illescas</x:t>
         </x:is>
       </x:c>
       <x:c r="K215" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9004-1A</x:t>
+          <x:t>DCZONE-8992-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L215" s="1" t="inlineStr">
@@ -25459,25 +25459,25 @@
         </x:is>
       </x:c>
       <x:c r="Q215" s="2" t="n">
-        <x:v>46031.4512847222</x:v>
+        <x:v>46031.3928240741</x:v>
       </x:c>
       <x:c r="R215" s="2" t="n">
-        <x:v>46031.4517824074</x:v>
+        <x:v>46031.4304513889</x:v>
       </x:c>
       <x:c r="S215" s="2" t="n">
-        <x:v>46031.4686805556</x:v>
+        <x:v>46031.4791319444</x:v>
       </x:c>
       <x:c r="T215" s="3">
         <x:v/>
       </x:c>
       <x:c r="U215" s="3" t="inlineStr">
         <x:is>
-          <x:t>1</x:t>
+          <x:t>54</x:t>
         </x:is>
       </x:c>
       <x:c r="V215" s="3" t="inlineStr">
         <x:is>
-          <x:t>24</x:t>
+          <x:t>70</x:t>
         </x:is>
       </x:c>
       <x:c r="W215" s="1">
@@ -25494,8 +25494,10 @@
       <x:c r="Z215" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA215" s="1">
-        <x:v/>
+      <x:c r="AA215" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001422529</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -25511,7 +25513,7 @@
       </x:c>
       <x:c r="C216" s="4" t="inlineStr">
         <x:is>
-          <x:t>1770528</x:t>
+          <x:t>1759453</x:t>
         </x:is>
       </x:c>
       <x:c r="D216" s="4">
@@ -25519,7 +25521,7 @@
       </x:c>
       <x:c r="E216" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002743697</x:t>
+          <x:t>4002746321</x:t>
         </x:is>
       </x:c>
       <x:c r="F216" s="1" t="inlineStr">
@@ -25529,7 +25531,7 @@
       </x:c>
       <x:c r="G216" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>Gold Allocation</x:t>
         </x:is>
       </x:c>
       <x:c r="H216" s="1" t="inlineStr">
@@ -25539,17 +25541,17 @@
       </x:c>
       <x:c r="I216" s="1" t="inlineStr">
         <x:is>
-          <x:t>8995</x:t>
+          <x:t>9004</x:t>
         </x:is>
       </x:c>
       <x:c r="J216" s="1" t="inlineStr">
         <x:is>
-          <x:t>Ensues</x:t>
+          <x:t>Biblis</x:t>
         </x:is>
       </x:c>
       <x:c r="K216" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8995-1A</x:t>
+          <x:t>DCZONE-9004-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L216" s="1" t="inlineStr">
@@ -25574,25 +25576,25 @@
         </x:is>
       </x:c>
       <x:c r="Q216" s="2" t="n">
-        <x:v>46031.3844328704</x:v>
+        <x:v>46031.4512847222</x:v>
       </x:c>
       <x:c r="R216" s="2" t="n">
-        <x:v>46031.4276967593</x:v>
+        <x:v>46031.4517824074</x:v>
       </x:c>
       <x:c r="S216" s="2" t="n">
-        <x:v>46031.457662037</x:v>
+        <x:v>46031.4686805556</x:v>
       </x:c>
       <x:c r="T216" s="3">
         <x:v/>
       </x:c>
       <x:c r="U216" s="3" t="inlineStr">
         <x:is>
-          <x:t>62</x:t>
+          <x:t>1</x:t>
         </x:is>
       </x:c>
       <x:c r="V216" s="3" t="inlineStr">
         <x:is>
-          <x:t>44</x:t>
+          <x:t>24</x:t>
         </x:is>
       </x:c>
       <x:c r="W216" s="1">
@@ -25626,7 +25628,7 @@
       </x:c>
       <x:c r="C217" s="4" t="inlineStr">
         <x:is>
-          <x:t>1757340</x:t>
+          <x:t>1770528</x:t>
         </x:is>
       </x:c>
       <x:c r="D217" s="4">
@@ -25634,7 +25636,7 @@
       </x:c>
       <x:c r="E217" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002743698</x:t>
+          <x:t>4002743697</x:t>
         </x:is>
       </x:c>
       <x:c r="F217" s="1" t="inlineStr">
@@ -25654,17 +25656,17 @@
       </x:c>
       <x:c r="I217" s="1" t="inlineStr">
         <x:is>
-          <x:t>8992</x:t>
+          <x:t>8995</x:t>
         </x:is>
       </x:c>
       <x:c r="J217" s="1" t="inlineStr">
         <x:is>
-          <x:t>Illescas</x:t>
+          <x:t>Ensues</x:t>
         </x:is>
       </x:c>
       <x:c r="K217" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8992-1A</x:t>
+          <x:t>DCZONE-8995-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L217" s="1" t="inlineStr">
@@ -25689,25 +25691,25 @@
         </x:is>
       </x:c>
       <x:c r="Q217" s="2" t="n">
-        <x:v>46031.3928240741</x:v>
+        <x:v>46031.3844328704</x:v>
       </x:c>
       <x:c r="R217" s="2" t="n">
-        <x:v>46031.4304513889</x:v>
+        <x:v>46031.4276967593</x:v>
       </x:c>
       <x:c r="S217" s="2" t="n">
-        <x:v>46031.4791319444</x:v>
+        <x:v>46031.457662037</x:v>
       </x:c>
       <x:c r="T217" s="3">
         <x:v/>
       </x:c>
       <x:c r="U217" s="3" t="inlineStr">
         <x:is>
-          <x:t>54</x:t>
+          <x:t>62</x:t>
         </x:is>
       </x:c>
       <x:c r="V217" s="3" t="inlineStr">
         <x:is>
-          <x:t>70</x:t>
+          <x:t>44</x:t>
         </x:is>
       </x:c>
       <x:c r="W217" s="1">
@@ -25724,10 +25726,8 @@
       <x:c r="Z217" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA217" s="1" t="inlineStr">
-        <x:is>
-          <x:t>5001422529</x:t>
-        </x:is>
+      <x:c r="AA217" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="218">
@@ -26314,25 +26314,27 @@
     <x:row r="223">
       <x:c r="A223" s="1" t="inlineStr">
         <x:is>
-          <x:t>1001634</x:t>
+          <x:t>50135</x:t>
         </x:is>
       </x:c>
       <x:c r="B223" s="1" t="inlineStr">
         <x:is>
-          <x:t>Good(s)Factory</x:t>
+          <x:t>DSV Road sp. z o.o.</x:t>
         </x:is>
       </x:c>
       <x:c r="C223" s="4" t="inlineStr">
         <x:is>
-          <x:t>1768060</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D223" s="4">
-        <x:v/>
+          <x:t>1770594</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D223" s="4" t="inlineStr">
+        <x:is>
+          <x:t>000002837762</x:t>
+        </x:is>
       </x:c>
       <x:c r="E223" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002754682</x:t>
+          <x:t>4002740707, 4002747730, 4002747731, 4002750979, 4002754619, 4002755869</x:t>
         </x:is>
       </x:c>
       <x:c r="F223" s="1" t="inlineStr">
@@ -26342,7 +26344,7 @@
       </x:c>
       <x:c r="G223" s="1" t="inlineStr">
         <x:is>
-          <x:t>-</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H223" s="1" t="inlineStr">
@@ -26352,17 +26354,17 @@
       </x:c>
       <x:c r="I223" s="1" t="inlineStr">
         <x:is>
-          <x:t>9002</x:t>
+          <x:t>8996</x:t>
         </x:is>
       </x:c>
       <x:c r="J223" s="1" t="inlineStr">
         <x:is>
-          <x:t>Echt</x:t>
+          <x:t>Bierun</x:t>
         </x:is>
       </x:c>
       <x:c r="K223" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9002-1A</x:t>
+          <x:t>DCZONE-8996-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L223" s="1" t="inlineStr">
@@ -26371,7 +26373,7 @@
         </x:is>
       </x:c>
       <x:c r="M223" s="3" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="N223" s="1" t="inlineStr">
         <x:is>
@@ -26418,16 +26420,14 @@
       </x:c>
       <x:c r="Y223" s="1" t="inlineStr">
         <x:is>
-          <x:t>Echt</x:t>
+          <x:t>Bierun</x:t>
         </x:is>
       </x:c>
       <x:c r="Z223" s="2" t="n">
-        <x:v>46034.4704398148</x:v>
-      </x:c>
-      <x:c r="AA223" s="1" t="inlineStr">
-        <x:is>
-          <x:t>5001424635 -63</x:t>
-        </x:is>
+        <x:v>46034.6632175926</x:v>
+      </x:c>
+      <x:c r="AA223" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="224">
@@ -26562,7 +26562,7 @@
       </x:c>
       <x:c r="C225" s="4" t="inlineStr">
         <x:is>
-          <x:t>1759965</x:t>
+          <x:t>1768060</x:t>
         </x:is>
       </x:c>
       <x:c r="D225" s="4">
@@ -26570,7 +26570,7 @@
       </x:c>
       <x:c r="E225" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002746326</x:t>
+          <x:t>4002754682</x:t>
         </x:is>
       </x:c>
       <x:c r="F225" s="1" t="inlineStr">
@@ -26580,27 +26580,27 @@
       </x:c>
       <x:c r="G225" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>-</x:t>
         </x:is>
       </x:c>
       <x:c r="H225" s="1" t="inlineStr">
         <x:is>
-          <x:t>Finished</x:t>
+          <x:t>NoShow</x:t>
         </x:is>
       </x:c>
       <x:c r="I225" s="1" t="inlineStr">
         <x:is>
-          <x:t>8999</x:t>
+          <x:t>9002</x:t>
         </x:is>
       </x:c>
       <x:c r="J225" s="1" t="inlineStr">
         <x:is>
-          <x:t>Osla</x:t>
+          <x:t>Echt</x:t>
         </x:is>
       </x:c>
       <x:c r="K225" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8999-1A</x:t>
+          <x:t>DCZONE-9002-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L225" s="1" t="inlineStr">
@@ -26613,7 +26613,7 @@
       </x:c>
       <x:c r="N225" s="1" t="inlineStr">
         <x:is>
-          <x:t>Yes</x:t>
+          <x:t>No</x:t>
         </x:is>
       </x:c>
       <x:c r="O225" s="2" t="n">
@@ -26621,29 +26621,29 @@
       </x:c>
       <x:c r="P225" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q225" s="2" t="n">
-        <x:v>46034.3639583333</x:v>
-      </x:c>
-      <x:c r="R225" s="2" t="n">
-        <x:v>46034.4603587963</x:v>
-      </x:c>
-      <x:c r="S225" s="2" t="n">
-        <x:v>46034.4997453704</x:v>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q225" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R225" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S225" s="2">
+        <x:v/>
       </x:c>
       <x:c r="T225" s="3">
         <x:v/>
       </x:c>
       <x:c r="U225" s="3" t="inlineStr">
         <x:is>
-          <x:t>138</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="V225" s="3" t="inlineStr">
         <x:is>
-          <x:t>57</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="W225" s="1">
@@ -26654,40 +26654,42 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y225" s="1">
-        <x:v/>
-      </x:c>
-      <x:c r="Z225" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="AA225" s="1">
-        <x:v/>
+      <x:c r="Y225" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Echt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z225" s="2" t="n">
+        <x:v>46034.4704398148</x:v>
+      </x:c>
+      <x:c r="AA225" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001424635 -63</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="1" t="inlineStr">
         <x:is>
-          <x:t>50135</x:t>
+          <x:t>1001634</x:t>
         </x:is>
       </x:c>
       <x:c r="B226" s="1" t="inlineStr">
         <x:is>
-          <x:t>DSV Road sp. z o.o.</x:t>
+          <x:t>Good(s)Factory</x:t>
         </x:is>
       </x:c>
       <x:c r="C226" s="4" t="inlineStr">
         <x:is>
-          <x:t>1770594</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D226" s="4" t="inlineStr">
-        <x:is>
-          <x:t>000002837762</x:t>
-        </x:is>
+          <x:t>1759965</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D226" s="4">
+        <x:v/>
       </x:c>
       <x:c r="E226" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002740707, 4002747730, 4002747731, 4002750979, 4002754619, 4002755869</x:t>
+          <x:t>4002746326</x:t>
         </x:is>
       </x:c>
       <x:c r="F226" s="1" t="inlineStr">
@@ -26702,22 +26704,22 @@
       </x:c>
       <x:c r="H226" s="1" t="inlineStr">
         <x:is>
-          <x:t>NoShow</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I226" s="1" t="inlineStr">
         <x:is>
-          <x:t>8996</x:t>
+          <x:t>8999</x:t>
         </x:is>
       </x:c>
       <x:c r="J226" s="1" t="inlineStr">
         <x:is>
-          <x:t>Bierun</x:t>
+          <x:t>Osla</x:t>
         </x:is>
       </x:c>
       <x:c r="K226" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8996-1A</x:t>
+          <x:t>DCZONE-8999-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L226" s="1" t="inlineStr">
@@ -26726,11 +26728,11 @@
         </x:is>
       </x:c>
       <x:c r="M226" s="3" t="n">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="N226" s="1" t="inlineStr">
         <x:is>
-          <x:t>No</x:t>
+          <x:t>Yes</x:t>
         </x:is>
       </x:c>
       <x:c r="O226" s="2" t="n">
@@ -26738,29 +26740,29 @@
       </x:c>
       <x:c r="P226" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q226" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R226" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S226" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q226" s="2" t="n">
+        <x:v>46034.3639583333</x:v>
+      </x:c>
+      <x:c r="R226" s="2" t="n">
+        <x:v>46034.4603587963</x:v>
+      </x:c>
+      <x:c r="S226" s="2" t="n">
+        <x:v>46034.4997453704</x:v>
       </x:c>
       <x:c r="T226" s="3">
         <x:v/>
       </x:c>
       <x:c r="U226" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>138</x:t>
         </x:is>
       </x:c>
       <x:c r="V226" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>57</x:t>
         </x:is>
       </x:c>
       <x:c r="W226" s="1">
@@ -26771,13 +26773,11 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y226" s="1" t="inlineStr">
-        <x:is>
-          <x:t>Bierun</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Z226" s="2" t="n">
-        <x:v>46034.6632175926</x:v>
+      <x:c r="Y226" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z226" s="2">
+        <x:v/>
       </x:c>
       <x:c r="AA226" s="1">
         <x:v/>
@@ -29725,7 +29725,7 @@
       </x:c>
       <x:c r="C252" s="4" t="inlineStr">
         <x:is>
-          <x:t>1767163</x:t>
+          <x:t>1767112</x:t>
         </x:is>
       </x:c>
       <x:c r="D252" s="4">
@@ -29733,7 +29733,7 @@
       </x:c>
       <x:c r="E252" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002754681</x:t>
+          <x:t>4002752989</x:t>
         </x:is>
       </x:c>
       <x:c r="F252" s="1" t="inlineStr">
@@ -29743,7 +29743,7 @@
       </x:c>
       <x:c r="G252" s="1" t="inlineStr">
         <x:is>
-          <x:t>-</x:t>
+          <x:t>Gold Allocation</x:t>
         </x:is>
       </x:c>
       <x:c r="H252" s="1" t="inlineStr">
@@ -29753,17 +29753,17 @@
       </x:c>
       <x:c r="I252" s="1" t="inlineStr">
         <x:is>
-          <x:t>9000</x:t>
+          <x:t>9004</x:t>
         </x:is>
       </x:c>
       <x:c r="J252" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zwaagdijk</x:t>
+          <x:t>Biblis</x:t>
         </x:is>
       </x:c>
       <x:c r="K252" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9000-1A</x:t>
+          <x:t>DCZONE-9004-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L252" s="1" t="inlineStr">
@@ -29788,25 +29788,25 @@
         </x:is>
       </x:c>
       <x:c r="Q252" s="2" t="n">
-        <x:v>46036.339837963</x:v>
+        <x:v>46036.3489351852</x:v>
       </x:c>
       <x:c r="R252" s="2" t="n">
-        <x:v>46036.340162037</x:v>
+        <x:v>46036.3722800926</x:v>
       </x:c>
       <x:c r="S252" s="2" t="n">
-        <x:v>46036.3726041667</x:v>
+        <x:v>46036.3983449074</x:v>
       </x:c>
       <x:c r="T252" s="3">
         <x:v/>
       </x:c>
       <x:c r="U252" s="3" t="inlineStr">
         <x:is>
-          <x:t>0</x:t>
+          <x:t>34</x:t>
         </x:is>
       </x:c>
       <x:c r="V252" s="3" t="inlineStr">
         <x:is>
-          <x:t>47</x:t>
+          <x:t>37</x:t>
         </x:is>
       </x:c>
       <x:c r="W252" s="1">
@@ -29823,10 +29823,8 @@
       <x:c r="Z252" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA252" s="1" t="inlineStr">
-        <x:is>
-          <x:t>DC1</x:t>
-        </x:is>
+      <x:c r="AA252" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="253">
@@ -29842,7 +29840,7 @@
       </x:c>
       <x:c r="C253" s="4" t="inlineStr">
         <x:is>
-          <x:t>1767112</x:t>
+          <x:t>1767163</x:t>
         </x:is>
       </x:c>
       <x:c r="D253" s="4">
@@ -29850,7 +29848,7 @@
       </x:c>
       <x:c r="E253" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002752989</x:t>
+          <x:t>4002754681</x:t>
         </x:is>
       </x:c>
       <x:c r="F253" s="1" t="inlineStr">
@@ -29860,7 +29858,7 @@
       </x:c>
       <x:c r="G253" s="1" t="inlineStr">
         <x:is>
-          <x:t>Gold Allocation</x:t>
+          <x:t>-</x:t>
         </x:is>
       </x:c>
       <x:c r="H253" s="1" t="inlineStr">
@@ -29870,17 +29868,17 @@
       </x:c>
       <x:c r="I253" s="1" t="inlineStr">
         <x:is>
-          <x:t>9004</x:t>
+          <x:t>9000</x:t>
         </x:is>
       </x:c>
       <x:c r="J253" s="1" t="inlineStr">
         <x:is>
-          <x:t>Biblis</x:t>
+          <x:t>Zwaagdijk</x:t>
         </x:is>
       </x:c>
       <x:c r="K253" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9004-1A</x:t>
+          <x:t>DCZONE-9000-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L253" s="1" t="inlineStr">
@@ -29905,25 +29903,25 @@
         </x:is>
       </x:c>
       <x:c r="Q253" s="2" t="n">
-        <x:v>46036.3489351852</x:v>
+        <x:v>46036.339837963</x:v>
       </x:c>
       <x:c r="R253" s="2" t="n">
-        <x:v>46036.3722800926</x:v>
+        <x:v>46036.340162037</x:v>
       </x:c>
       <x:c r="S253" s="2" t="n">
-        <x:v>46036.3983449074</x:v>
+        <x:v>46036.3726041667</x:v>
       </x:c>
       <x:c r="T253" s="3">
         <x:v/>
       </x:c>
       <x:c r="U253" s="3" t="inlineStr">
         <x:is>
-          <x:t>34</x:t>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="V253" s="3" t="inlineStr">
         <x:is>
-          <x:t>37</x:t>
+          <x:t>47</x:t>
         </x:is>
       </x:c>
       <x:c r="W253" s="1">
@@ -29940,8 +29938,10 @@
       <x:c r="Z253" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA253" s="1">
-        <x:v/>
+      <x:c r="AA253" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DC1</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="254">
@@ -34034,7 +34034,7 @@
       </x:c>
       <x:c r="C289" s="4" t="inlineStr">
         <x:is>
-          <x:t>1770612</x:t>
+          <x:t>1770605</x:t>
         </x:is>
       </x:c>
       <x:c r="D289" s="4">
@@ -34042,7 +34042,7 @@
       </x:c>
       <x:c r="E289" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002758049</x:t>
+          <x:t>4002758047</x:t>
         </x:is>
       </x:c>
       <x:c r="F289" s="1" t="inlineStr">
@@ -34052,27 +34052,27 @@
       </x:c>
       <x:c r="G289" s="1" t="inlineStr">
         <x:is>
-          <x:t>Gold Allocation</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H289" s="1" t="inlineStr">
         <x:is>
-          <x:t>Removed</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I289" s="1" t="inlineStr">
         <x:is>
-          <x:t>8994</x:t>
+          <x:t>9002</x:t>
         </x:is>
       </x:c>
       <x:c r="J289" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zakroczym</x:t>
+          <x:t>Echt</x:t>
         </x:is>
       </x:c>
       <x:c r="K289" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8994-1A</x:t>
+          <x:t>DCZONE-9002-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L289" s="1" t="inlineStr">
@@ -34085,7 +34085,7 @@
       </x:c>
       <x:c r="N289" s="1" t="inlineStr">
         <x:is>
-          <x:t>No</x:t>
+          <x:t>Yes</x:t>
         </x:is>
       </x:c>
       <x:c r="O289" s="2" t="n">
@@ -34093,29 +34093,29 @@
       </x:c>
       <x:c r="P289" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q289" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R289" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S289" s="2">
-        <x:v/>
+          <x:t>On time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q289" s="2" t="n">
+        <x:v>46038.5284259259</x:v>
+      </x:c>
+      <x:c r="R289" s="2" t="n">
+        <x:v>46038.5863657407</x:v>
+      </x:c>
+      <x:c r="S289" s="2" t="n">
+        <x:v>46038.6096064815</x:v>
       </x:c>
       <x:c r="T289" s="3">
         <x:v/>
       </x:c>
       <x:c r="U289" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>84</x:t>
         </x:is>
       </x:c>
       <x:c r="V289" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>33</x:t>
         </x:is>
       </x:c>
       <x:c r="W289" s="1">
@@ -34126,16 +34126,16 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y289" s="1" t="inlineStr">
-        <x:is>
-          <x:t>Good(s)Factory</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Z289" s="2" t="n">
-        <x:v>46035.6793865741</x:v>
-      </x:c>
-      <x:c r="AA289" s="1">
-        <x:v/>
+      <x:c r="Y289" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z289" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA289" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001430246 -63</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="290">
@@ -34151,7 +34151,7 @@
       </x:c>
       <x:c r="C290" s="4" t="inlineStr">
         <x:is>
-          <x:t>1770605</x:t>
+          <x:t>1770612</x:t>
         </x:is>
       </x:c>
       <x:c r="D290" s="4">
@@ -34159,7 +34159,7 @@
       </x:c>
       <x:c r="E290" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002758047</x:t>
+          <x:t>4002758049</x:t>
         </x:is>
       </x:c>
       <x:c r="F290" s="1" t="inlineStr">
@@ -34169,27 +34169,27 @@
       </x:c>
       <x:c r="G290" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>Gold Allocation</x:t>
         </x:is>
       </x:c>
       <x:c r="H290" s="1" t="inlineStr">
         <x:is>
-          <x:t>Finished</x:t>
+          <x:t>Removed</x:t>
         </x:is>
       </x:c>
       <x:c r="I290" s="1" t="inlineStr">
         <x:is>
-          <x:t>9002</x:t>
+          <x:t>8994</x:t>
         </x:is>
       </x:c>
       <x:c r="J290" s="1" t="inlineStr">
         <x:is>
-          <x:t>Echt</x:t>
+          <x:t>Zakroczym</x:t>
         </x:is>
       </x:c>
       <x:c r="K290" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9002-1A</x:t>
+          <x:t>DCZONE-8994-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L290" s="1" t="inlineStr">
@@ -34202,7 +34202,7 @@
       </x:c>
       <x:c r="N290" s="1" t="inlineStr">
         <x:is>
-          <x:t>Yes</x:t>
+          <x:t>No</x:t>
         </x:is>
       </x:c>
       <x:c r="O290" s="2" t="n">
@@ -34210,29 +34210,29 @@
       </x:c>
       <x:c r="P290" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q290" s="2" t="n">
-        <x:v>46038.5284259259</x:v>
-      </x:c>
-      <x:c r="R290" s="2" t="n">
-        <x:v>46038.5863657407</x:v>
-      </x:c>
-      <x:c r="S290" s="2" t="n">
-        <x:v>46038.6096064815</x:v>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q290" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R290" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S290" s="2">
+        <x:v/>
       </x:c>
       <x:c r="T290" s="3">
         <x:v/>
       </x:c>
       <x:c r="U290" s="3" t="inlineStr">
         <x:is>
-          <x:t>84</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="V290" s="3" t="inlineStr">
         <x:is>
-          <x:t>33</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="W290" s="1">
@@ -34243,16 +34243,16 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y290" s="1">
-        <x:v/>
-      </x:c>
-      <x:c r="Z290" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="AA290" s="1" t="inlineStr">
-        <x:is>
-          <x:t>5001430246 -63</x:t>
-        </x:is>
+      <x:c r="Y290" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z290" s="2" t="n">
+        <x:v>46035.6793865741</x:v>
+      </x:c>
+      <x:c r="AA290" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="291">
@@ -36366,7 +36366,7 @@
       </x:c>
       <x:c r="C309" s="4" t="inlineStr">
         <x:is>
-          <x:t>1777060</x:t>
+          <x:t>1780453</x:t>
         </x:is>
       </x:c>
       <x:c r="D309" s="4">
@@ -36374,7 +36374,7 @@
       </x:c>
       <x:c r="E309" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002758045</x:t>
+          <x:t>4002768106</x:t>
         </x:is>
       </x:c>
       <x:c r="F309" s="1" t="inlineStr">
@@ -36394,17 +36394,17 @@
       </x:c>
       <x:c r="I309" s="1" t="inlineStr">
         <x:is>
-          <x:t>9004</x:t>
+          <x:t>9000</x:t>
         </x:is>
       </x:c>
       <x:c r="J309" s="1" t="inlineStr">
         <x:is>
-          <x:t>Biblis</x:t>
+          <x:t>Zwaagdijk</x:t>
         </x:is>
       </x:c>
       <x:c r="K309" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9004-1A</x:t>
+          <x:t>DCZONE-9000-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L309" s="1" t="inlineStr">
@@ -36429,16 +36429,18 @@
         </x:is>
       </x:c>
       <x:c r="Q309" s="2" t="n">
-        <x:v>46043.3653703704</x:v>
+        <x:v>46043.3855208333</x:v>
       </x:c>
       <x:c r="R309" s="2" t="n">
-        <x:v>46043.365775463</x:v>
+        <x:v>46043.3855787037</x:v>
       </x:c>
       <x:c r="S309" s="2" t="n">
-        <x:v>46043.3791319444</x:v>
-      </x:c>
-      <x:c r="T309" s="3">
-        <x:v/>
+        <x:v>46043.4128819444</x:v>
+      </x:c>
+      <x:c r="T309" s="3" t="inlineStr">
+        <x:is>
+          <x:t>15</x:t>
+        </x:is>
       </x:c>
       <x:c r="U309" s="3" t="inlineStr">
         <x:is>
@@ -36447,7 +36449,7 @@
       </x:c>
       <x:c r="V309" s="3" t="inlineStr">
         <x:is>
-          <x:t>19</x:t>
+          <x:t>39</x:t>
         </x:is>
       </x:c>
       <x:c r="W309" s="1">
@@ -36481,7 +36483,7 @@
       </x:c>
       <x:c r="C310" s="4" t="inlineStr">
         <x:is>
-          <x:t>1780453</x:t>
+          <x:t>1777060</x:t>
         </x:is>
       </x:c>
       <x:c r="D310" s="4">
@@ -36489,7 +36491,7 @@
       </x:c>
       <x:c r="E310" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002768106</x:t>
+          <x:t>4002758045</x:t>
         </x:is>
       </x:c>
       <x:c r="F310" s="1" t="inlineStr">
@@ -36509,17 +36511,17 @@
       </x:c>
       <x:c r="I310" s="1" t="inlineStr">
         <x:is>
-          <x:t>9000</x:t>
+          <x:t>9004</x:t>
         </x:is>
       </x:c>
       <x:c r="J310" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zwaagdijk</x:t>
+          <x:t>Biblis</x:t>
         </x:is>
       </x:c>
       <x:c r="K310" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9000-1A</x:t>
+          <x:t>DCZONE-9004-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L310" s="1" t="inlineStr">
@@ -36544,18 +36546,16 @@
         </x:is>
       </x:c>
       <x:c r="Q310" s="2" t="n">
-        <x:v>46043.3855208333</x:v>
+        <x:v>46043.3653703704</x:v>
       </x:c>
       <x:c r="R310" s="2" t="n">
-        <x:v>46043.3855787037</x:v>
+        <x:v>46043.365775463</x:v>
       </x:c>
       <x:c r="S310" s="2" t="n">
-        <x:v>46043.4128819444</x:v>
-      </x:c>
-      <x:c r="T310" s="3" t="inlineStr">
-        <x:is>
-          <x:t>15</x:t>
-        </x:is>
+        <x:v>46043.3791319444</x:v>
+      </x:c>
+      <x:c r="T310" s="3">
+        <x:v/>
       </x:c>
       <x:c r="U310" s="3" t="inlineStr">
         <x:is>
@@ -36564,7 +36564,7 @@
       </x:c>
       <x:c r="V310" s="3" t="inlineStr">
         <x:is>
-          <x:t>39</x:t>
+          <x:t>19</x:t>
         </x:is>
       </x:c>
       <x:c r="W310" s="1">
@@ -40433,7 +40433,7 @@
       </x:c>
       <x:c r="C344" s="4" t="inlineStr">
         <x:is>
-          <x:t>1782211</x:t>
+          <x:t>1785692</x:t>
         </x:is>
       </x:c>
       <x:c r="D344" s="4">
@@ -40441,7 +40441,7 @@
       </x:c>
       <x:c r="E344" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002769959</x:t>
+          <x:t>4002774911</x:t>
         </x:is>
       </x:c>
       <x:c r="F344" s="1" t="inlineStr">
@@ -40461,17 +40461,17 @@
       </x:c>
       <x:c r="I344" s="1" t="inlineStr">
         <x:is>
-          <x:t>9004</x:t>
+          <x:t>9000</x:t>
         </x:is>
       </x:c>
       <x:c r="J344" s="1" t="inlineStr">
         <x:is>
-          <x:t>Biblis</x:t>
+          <x:t>Zwaagdijk</x:t>
         </x:is>
       </x:c>
       <x:c r="K344" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9004-1A</x:t>
+          <x:t>DCZONE-9000-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L344" s="1" t="inlineStr">
@@ -40492,17 +40492,17 @@
       </x:c>
       <x:c r="P344" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q344" s="2" t="n">
-        <x:v>46049.3649189815</x:v>
+        <x:v>46049.3185185185</x:v>
       </x:c>
       <x:c r="R344" s="2" t="n">
-        <x:v>46049.3657175926</x:v>
+        <x:v>46049.3192708333</x:v>
       </x:c>
       <x:c r="S344" s="2" t="n">
-        <x:v>46049.3761689815</x:v>
+        <x:v>46049.3484606482</x:v>
       </x:c>
       <x:c r="T344" s="3">
         <x:v/>
@@ -40514,7 +40514,7 @@
       </x:c>
       <x:c r="V344" s="3" t="inlineStr">
         <x:is>
-          <x:t>15</x:t>
+          <x:t>42</x:t>
         </x:is>
       </x:c>
       <x:c r="W344" s="1">
@@ -40531,8 +40531,10 @@
       <x:c r="Z344" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA344" s="1">
-        <x:v/>
+      <x:c r="AA344" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DC1 10-kant</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="345">
@@ -40548,7 +40550,7 @@
       </x:c>
       <x:c r="C345" s="4" t="inlineStr">
         <x:is>
-          <x:t>1785692</x:t>
+          <x:t>1782211</x:t>
         </x:is>
       </x:c>
       <x:c r="D345" s="4">
@@ -40556,7 +40558,7 @@
       </x:c>
       <x:c r="E345" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002774911</x:t>
+          <x:t>4002769959</x:t>
         </x:is>
       </x:c>
       <x:c r="F345" s="1" t="inlineStr">
@@ -40576,17 +40578,17 @@
       </x:c>
       <x:c r="I345" s="1" t="inlineStr">
         <x:is>
-          <x:t>9000</x:t>
+          <x:t>9004</x:t>
         </x:is>
       </x:c>
       <x:c r="J345" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zwaagdijk</x:t>
+          <x:t>Biblis</x:t>
         </x:is>
       </x:c>
       <x:c r="K345" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9000-1A</x:t>
+          <x:t>DCZONE-9004-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L345" s="1" t="inlineStr">
@@ -40607,17 +40609,17 @@
       </x:c>
       <x:c r="P345" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q345" s="2" t="n">
-        <x:v>46049.3185185185</x:v>
+        <x:v>46049.3649189815</x:v>
       </x:c>
       <x:c r="R345" s="2" t="n">
-        <x:v>46049.3192708333</x:v>
+        <x:v>46049.3657175926</x:v>
       </x:c>
       <x:c r="S345" s="2" t="n">
-        <x:v>46049.3484606482</x:v>
+        <x:v>46049.3761689815</x:v>
       </x:c>
       <x:c r="T345" s="3">
         <x:v/>
@@ -40629,7 +40631,7 @@
       </x:c>
       <x:c r="V345" s="3" t="inlineStr">
         <x:is>
-          <x:t>42</x:t>
+          <x:t>15</x:t>
         </x:is>
       </x:c>
       <x:c r="W345" s="1">
@@ -40646,10 +40648,8 @@
       <x:c r="Z345" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA345" s="1" t="inlineStr">
-        <x:is>
-          <x:t>DC1 10-kant</x:t>
-        </x:is>
+      <x:c r="AA345" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="346">
@@ -41714,7 +41714,7 @@
       </x:c>
       <x:c r="C355" s="4" t="inlineStr">
         <x:is>
-          <x:t>1781915</x:t>
+          <x:t>1782168</x:t>
         </x:is>
       </x:c>
       <x:c r="D355" s="4">
@@ -41722,7 +41722,7 @@
       </x:c>
       <x:c r="E355" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002769969</x:t>
+          <x:t>4002769961</x:t>
         </x:is>
       </x:c>
       <x:c r="F355" s="1" t="inlineStr">
@@ -41742,17 +41742,17 @@
       </x:c>
       <x:c r="I355" s="1" t="inlineStr">
         <x:is>
-          <x:t>8994</x:t>
+          <x:t>9006</x:t>
         </x:is>
       </x:c>
       <x:c r="J355" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zakroczym</x:t>
+          <x:t>Belleville</x:t>
         </x:is>
       </x:c>
       <x:c r="K355" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8994-1A</x:t>
+          <x:t>DCZONE-9006-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L355" s="1" t="inlineStr">
@@ -41773,31 +41773,29 @@
       </x:c>
       <x:c r="P355" s="1" t="inlineStr">
         <x:is>
-          <x:t>Late</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q355" s="2" t="n">
-        <x:v>46051.5412384259</x:v>
+        <x:v>46051.2825</x:v>
       </x:c>
       <x:c r="R355" s="2" t="n">
-        <x:v>46051.6163888889</x:v>
+        <x:v>46051.303287037</x:v>
       </x:c>
       <x:c r="S355" s="2" t="n">
-        <x:v>46051.6258449074</x:v>
-      </x:c>
-      <x:c r="T355" s="3" t="inlineStr">
-        <x:is>
-          <x:t>359</x:t>
-        </x:is>
+        <x:v>46051.3335532407</x:v>
+      </x:c>
+      <x:c r="T355" s="3">
+        <x:v/>
       </x:c>
       <x:c r="U355" s="3" t="inlineStr">
         <x:is>
-          <x:t>108</x:t>
+          <x:t>30</x:t>
         </x:is>
       </x:c>
       <x:c r="V355" s="3" t="inlineStr">
         <x:is>
-          <x:t>14</x:t>
+          <x:t>44</x:t>
         </x:is>
       </x:c>
       <x:c r="W355" s="1">
@@ -41814,10 +41812,8 @@
       <x:c r="Z355" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA355" s="1" t="inlineStr">
-        <x:is>
-          <x:t>666048051</x:t>
-        </x:is>
+      <x:c r="AA355" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="356">
@@ -41833,7 +41829,7 @@
       </x:c>
       <x:c r="C356" s="4" t="inlineStr">
         <x:is>
-          <x:t>1782168</x:t>
+          <x:t>1781915</x:t>
         </x:is>
       </x:c>
       <x:c r="D356" s="4">
@@ -41841,7 +41837,7 @@
       </x:c>
       <x:c r="E356" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002769961</x:t>
+          <x:t>4002769969</x:t>
         </x:is>
       </x:c>
       <x:c r="F356" s="1" t="inlineStr">
@@ -41861,17 +41857,17 @@
       </x:c>
       <x:c r="I356" s="1" t="inlineStr">
         <x:is>
-          <x:t>9006</x:t>
+          <x:t>8994</x:t>
         </x:is>
       </x:c>
       <x:c r="J356" s="1" t="inlineStr">
         <x:is>
-          <x:t>Belleville</x:t>
+          <x:t>Zakroczym</x:t>
         </x:is>
       </x:c>
       <x:c r="K356" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9006-1A</x:t>
+          <x:t>DCZONE-8994-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L356" s="1" t="inlineStr">
@@ -41892,29 +41888,31 @@
       </x:c>
       <x:c r="P356" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Late</x:t>
         </x:is>
       </x:c>
       <x:c r="Q356" s="2" t="n">
-        <x:v>46051.2825</x:v>
+        <x:v>46051.5412384259</x:v>
       </x:c>
       <x:c r="R356" s="2" t="n">
-        <x:v>46051.303287037</x:v>
+        <x:v>46051.6163888889</x:v>
       </x:c>
       <x:c r="S356" s="2" t="n">
-        <x:v>46051.3335532407</x:v>
-      </x:c>
-      <x:c r="T356" s="3">
-        <x:v/>
+        <x:v>46051.6258449074</x:v>
+      </x:c>
+      <x:c r="T356" s="3" t="inlineStr">
+        <x:is>
+          <x:t>359</x:t>
+        </x:is>
       </x:c>
       <x:c r="U356" s="3" t="inlineStr">
         <x:is>
-          <x:t>30</x:t>
+          <x:t>108</x:t>
         </x:is>
       </x:c>
       <x:c r="V356" s="3" t="inlineStr">
         <x:is>
-          <x:t>44</x:t>
+          <x:t>14</x:t>
         </x:is>
       </x:c>
       <x:c r="W356" s="1">
@@ -41931,8 +41929,10 @@
       <x:c r="Z356" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA356" s="1">
-        <x:v/>
+      <x:c r="AA356" s="1" t="inlineStr">
+        <x:is>
+          <x:t>666048051</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="357">
@@ -42527,7 +42527,7 @@
       </x:c>
       <x:c r="C362" s="4" t="inlineStr">
         <x:is>
-          <x:t>1786477</x:t>
+          <x:t>1781876</x:t>
         </x:is>
       </x:c>
       <x:c r="D362" s="4">
@@ -42535,7 +42535,7 @@
       </x:c>
       <x:c r="E362" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002774912</x:t>
+          <x:t>4002769971</x:t>
         </x:is>
       </x:c>
       <x:c r="F362" s="1" t="inlineStr">
@@ -42545,7 +42545,7 @@
       </x:c>
       <x:c r="G362" s="1" t="inlineStr">
         <x:is>
-          <x:t>Gold Allocation</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H362" s="1" t="inlineStr">
@@ -42555,17 +42555,17 @@
       </x:c>
       <x:c r="I362" s="1" t="inlineStr">
         <x:is>
-          <x:t>9002</x:t>
+          <x:t>8993</x:t>
         </x:is>
       </x:c>
       <x:c r="J362" s="1" t="inlineStr">
         <x:is>
-          <x:t>Echt</x:t>
+          <x:t>Novara</x:t>
         </x:is>
       </x:c>
       <x:c r="K362" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9002-1A</x:t>
+          <x:t>DCZONE-8993-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L362" s="1" t="inlineStr">
@@ -42586,29 +42586,29 @@
       </x:c>
       <x:c r="P362" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q362" s="2" t="n">
-        <x:v>46051.3790393519</x:v>
+        <x:v>46051.4107638889</x:v>
       </x:c>
       <x:c r="R362" s="2" t="n">
-        <x:v>46051.3791203704</x:v>
+        <x:v>46051.4277546296</x:v>
       </x:c>
       <x:c r="S362" s="2" t="n">
-        <x:v>46051.4180787037</x:v>
+        <x:v>46051.5237384259</x:v>
       </x:c>
       <x:c r="T362" s="3">
         <x:v/>
       </x:c>
       <x:c r="U362" s="3" t="inlineStr">
         <x:is>
-          <x:t>0</x:t>
+          <x:t>24</x:t>
         </x:is>
       </x:c>
       <x:c r="V362" s="3" t="inlineStr">
         <x:is>
-          <x:t>57</x:t>
+          <x:t>139</x:t>
         </x:is>
       </x:c>
       <x:c r="W362" s="1">
@@ -42625,10 +42625,8 @@
       <x:c r="Z362" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA362" s="1" t="inlineStr">
-        <x:is>
-          <x:t>5001442489 -63</x:t>
-        </x:is>
+      <x:c r="AA362" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="363">
@@ -42644,7 +42642,7 @@
       </x:c>
       <x:c r="C363" s="4" t="inlineStr">
         <x:is>
-          <x:t>1782163</x:t>
+          <x:t>1786477</x:t>
         </x:is>
       </x:c>
       <x:c r="D363" s="4">
@@ -42652,7 +42650,7 @@
       </x:c>
       <x:c r="E363" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002769956</x:t>
+          <x:t>4002774912</x:t>
         </x:is>
       </x:c>
       <x:c r="F363" s="1" t="inlineStr">
@@ -42662,7 +42660,7 @@
       </x:c>
       <x:c r="G363" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>Gold Allocation</x:t>
         </x:is>
       </x:c>
       <x:c r="H363" s="1" t="inlineStr">
@@ -42672,17 +42670,17 @@
       </x:c>
       <x:c r="I363" s="1" t="inlineStr">
         <x:is>
-          <x:t>9003</x:t>
+          <x:t>9002</x:t>
         </x:is>
       </x:c>
       <x:c r="J363" s="1" t="inlineStr">
         <x:is>
-          <x:t>Moissy</x:t>
+          <x:t>Echt</x:t>
         </x:is>
       </x:c>
       <x:c r="K363" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9003-1A</x:t>
+          <x:t>DCZONE-9002-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L363" s="1" t="inlineStr">
@@ -42707,25 +42705,25 @@
         </x:is>
       </x:c>
       <x:c r="Q363" s="2" t="n">
-        <x:v>46051.3745949074</x:v>
+        <x:v>46051.3790393519</x:v>
       </x:c>
       <x:c r="R363" s="2" t="n">
-        <x:v>46051.4626157407</x:v>
+        <x:v>46051.3791203704</x:v>
       </x:c>
       <x:c r="S363" s="2" t="n">
-        <x:v>46051.4629050926</x:v>
+        <x:v>46051.4180787037</x:v>
       </x:c>
       <x:c r="T363" s="3">
         <x:v/>
       </x:c>
       <x:c r="U363" s="3" t="inlineStr">
         <x:is>
-          <x:t>127</x:t>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="V363" s="3" t="inlineStr">
         <x:is>
-          <x:t>0</x:t>
+          <x:t>57</x:t>
         </x:is>
       </x:c>
       <x:c r="W363" s="1">
@@ -42733,7 +42731,7 @@
       </x:c>
       <x:c r="X363" s="1" t="inlineStr">
         <x:is>
-          <x:t>Logistic quality: pallets are too high</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="Y363" s="1">
@@ -42742,8 +42740,10 @@
       <x:c r="Z363" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA363" s="1">
-        <x:v/>
+      <x:c r="AA363" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001442489 -63</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="364">
@@ -42759,7 +42759,7 @@
       </x:c>
       <x:c r="C364" s="4" t="inlineStr">
         <x:is>
-          <x:t>1781876</x:t>
+          <x:t>1782163</x:t>
         </x:is>
       </x:c>
       <x:c r="D364" s="4">
@@ -42767,7 +42767,7 @@
       </x:c>
       <x:c r="E364" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002769971</x:t>
+          <x:t>4002769956</x:t>
         </x:is>
       </x:c>
       <x:c r="F364" s="1" t="inlineStr">
@@ -42787,17 +42787,17 @@
       </x:c>
       <x:c r="I364" s="1" t="inlineStr">
         <x:is>
-          <x:t>8993</x:t>
+          <x:t>9003</x:t>
         </x:is>
       </x:c>
       <x:c r="J364" s="1" t="inlineStr">
         <x:is>
-          <x:t>Novara</x:t>
+          <x:t>Moissy</x:t>
         </x:is>
       </x:c>
       <x:c r="K364" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8993-1A</x:t>
+          <x:t>DCZONE-9003-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L364" s="1" t="inlineStr">
@@ -42818,29 +42818,29 @@
       </x:c>
       <x:c r="P364" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q364" s="2" t="n">
-        <x:v>46051.4107638889</x:v>
+        <x:v>46051.3745949074</x:v>
       </x:c>
       <x:c r="R364" s="2" t="n">
-        <x:v>46051.4277546296</x:v>
+        <x:v>46051.4626157407</x:v>
       </x:c>
       <x:c r="S364" s="2" t="n">
-        <x:v>46051.5237384259</x:v>
+        <x:v>46051.4629050926</x:v>
       </x:c>
       <x:c r="T364" s="3">
         <x:v/>
       </x:c>
       <x:c r="U364" s="3" t="inlineStr">
         <x:is>
-          <x:t>24</x:t>
+          <x:t>127</x:t>
         </x:is>
       </x:c>
       <x:c r="V364" s="3" t="inlineStr">
         <x:is>
-          <x:t>139</x:t>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="W364" s="1">
@@ -42848,7 +42848,7 @@
       </x:c>
       <x:c r="X364" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>Logistic quality: pallets are too high</x:t>
         </x:is>
       </x:c>
       <x:c r="Y364" s="1">
@@ -45079,7 +45079,7 @@
       </x:c>
       <x:c r="C384" s="4" t="inlineStr">
         <x:is>
-          <x:t>1793305</x:t>
+          <x:t>1787647</x:t>
         </x:is>
       </x:c>
       <x:c r="D384" s="4">
@@ -45087,7 +45087,7 @@
       </x:c>
       <x:c r="E384" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002783225</x:t>
+          <x:t>4002774918</x:t>
         </x:is>
       </x:c>
       <x:c r="F384" s="1" t="inlineStr">
@@ -45097,7 +45097,7 @@
       </x:c>
       <x:c r="G384" s="1" t="inlineStr">
         <x:is>
-          <x:t>-</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H384" s="1" t="inlineStr">
@@ -45107,17 +45107,17 @@
       </x:c>
       <x:c r="I384" s="1" t="inlineStr">
         <x:is>
-          <x:t>9002</x:t>
+          <x:t>8997</x:t>
         </x:is>
       </x:c>
       <x:c r="J384" s="1" t="inlineStr">
         <x:is>
-          <x:t>Echt</x:t>
+          <x:t>Verrières</x:t>
         </x:is>
       </x:c>
       <x:c r="K384" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9002-1A</x:t>
+          <x:t>DCZONE-8997-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L384" s="1" t="inlineStr">
@@ -45142,25 +45142,25 @@
         </x:is>
       </x:c>
       <x:c r="Q384" s="2" t="n">
-        <x:v>46056.3953703704</x:v>
+        <x:v>46056.3630324074</x:v>
       </x:c>
       <x:c r="R384" s="2" t="n">
-        <x:v>46056.4151041667</x:v>
+        <x:v>46056.4511342593</x:v>
       </x:c>
       <x:c r="S384" s="2" t="n">
-        <x:v>46056.434212963</x:v>
+        <x:v>46056.4925694444</x:v>
       </x:c>
       <x:c r="T384" s="3">
         <x:v/>
       </x:c>
       <x:c r="U384" s="3" t="inlineStr">
         <x:is>
-          <x:t>28</x:t>
+          <x:t>127</x:t>
         </x:is>
       </x:c>
       <x:c r="V384" s="3" t="inlineStr">
         <x:is>
-          <x:t>28</x:t>
+          <x:t>60</x:t>
         </x:is>
       </x:c>
       <x:c r="W384" s="1">
@@ -45177,10 +45177,8 @@
       <x:c r="Z384" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA384" s="1" t="inlineStr">
-        <x:is>
-          <x:t>5001446404 -63</x:t>
-        </x:is>
+      <x:c r="AA384" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="385">
@@ -45196,7 +45194,7 @@
       </x:c>
       <x:c r="C385" s="4" t="inlineStr">
         <x:is>
-          <x:t>1787647</x:t>
+          <x:t>1793305</x:t>
         </x:is>
       </x:c>
       <x:c r="D385" s="4">
@@ -45204,7 +45202,7 @@
       </x:c>
       <x:c r="E385" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002774918</x:t>
+          <x:t>4002783225</x:t>
         </x:is>
       </x:c>
       <x:c r="F385" s="1" t="inlineStr">
@@ -45214,7 +45212,7 @@
       </x:c>
       <x:c r="G385" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>-</x:t>
         </x:is>
       </x:c>
       <x:c r="H385" s="1" t="inlineStr">
@@ -45224,17 +45222,17 @@
       </x:c>
       <x:c r="I385" s="1" t="inlineStr">
         <x:is>
-          <x:t>8997</x:t>
+          <x:t>9002</x:t>
         </x:is>
       </x:c>
       <x:c r="J385" s="1" t="inlineStr">
         <x:is>
-          <x:t>Verrières</x:t>
+          <x:t>Echt</x:t>
         </x:is>
       </x:c>
       <x:c r="K385" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8997-1A</x:t>
+          <x:t>DCZONE-9002-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L385" s="1" t="inlineStr">
@@ -45259,25 +45257,25 @@
         </x:is>
       </x:c>
       <x:c r="Q385" s="2" t="n">
-        <x:v>46056.3630324074</x:v>
+        <x:v>46056.3953703704</x:v>
       </x:c>
       <x:c r="R385" s="2" t="n">
-        <x:v>46056.4511342593</x:v>
+        <x:v>46056.4151041667</x:v>
       </x:c>
       <x:c r="S385" s="2" t="n">
-        <x:v>46056.4925694444</x:v>
+        <x:v>46056.434212963</x:v>
       </x:c>
       <x:c r="T385" s="3">
         <x:v/>
       </x:c>
       <x:c r="U385" s="3" t="inlineStr">
         <x:is>
-          <x:t>127</x:t>
+          <x:t>28</x:t>
         </x:is>
       </x:c>
       <x:c r="V385" s="3" t="inlineStr">
         <x:is>
-          <x:t>60</x:t>
+          <x:t>28</x:t>
         </x:is>
       </x:c>
       <x:c r="W385" s="1">
@@ -45294,8 +45292,10 @@
       <x:c r="Z385" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA385" s="1">
-        <x:v/>
+      <x:c r="AA385" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001446404 -63</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="386">
@@ -53681,7 +53681,7 @@
       </x:c>
       <x:c r="C458" s="4" t="inlineStr">
         <x:is>
-          <x:t>1801511</x:t>
+          <x:t>1803863</x:t>
         </x:is>
       </x:c>
       <x:c r="D458" s="4">
@@ -53689,7 +53689,7 @@
       </x:c>
       <x:c r="E458" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002786694</x:t>
+          <x:t>4002791657</x:t>
         </x:is>
       </x:c>
       <x:c r="F458" s="1" t="inlineStr">
@@ -53704,22 +53704,22 @@
       </x:c>
       <x:c r="H458" s="1" t="inlineStr">
         <x:is>
-          <x:t>Finished</x:t>
+          <x:t>Refused</x:t>
         </x:is>
       </x:c>
       <x:c r="I458" s="1" t="inlineStr">
         <x:is>
-          <x:t>8996</x:t>
+          <x:t>9003</x:t>
         </x:is>
       </x:c>
       <x:c r="J458" s="1" t="inlineStr">
         <x:is>
-          <x:t>Bierun</x:t>
+          <x:t>Moissy</x:t>
         </x:is>
       </x:c>
       <x:c r="K458" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8996-1A</x:t>
+          <x:t>DCZONE-9003-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L458" s="1" t="inlineStr">
@@ -53732,7 +53732,7 @@
       </x:c>
       <x:c r="N458" s="1" t="inlineStr">
         <x:is>
-          <x:t>Yes</x:t>
+          <x:t>No</x:t>
         </x:is>
       </x:c>
       <x:c r="O458" s="2" t="n">
@@ -53740,33 +53740,37 @@
       </x:c>
       <x:c r="P458" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q458" s="2" t="n">
-        <x:v>46065.3652777778</x:v>
-      </x:c>
-      <x:c r="R458" s="2" t="n">
-        <x:v>46065.3766550926</x:v>
-      </x:c>
-      <x:c r="S458" s="2" t="n">
-        <x:v>46065.4531828704</x:v>
-      </x:c>
-      <x:c r="T458" s="3">
-        <x:v/>
+        <x:v>46065.4250578704</x:v>
+      </x:c>
+      <x:c r="R458" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S458" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T458" s="3" t="inlineStr">
+        <x:is>
+          <x:t>12</x:t>
+        </x:is>
       </x:c>
       <x:c r="U458" s="3" t="inlineStr">
         <x:is>
-          <x:t>16</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="V458" s="3" t="inlineStr">
         <x:is>
-          <x:t>110</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="W458" s="1">
-        <x:v/>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W458" s="1" t="inlineStr">
+        <x:is>
+          <x:t>No inbound capacity</x:t>
+        </x:is>
       </x:c>
       <x:c r="X458" s="1" t="inlineStr">
         <x:is>
@@ -53781,7 +53785,7 @@
       </x:c>
       <x:c r="AA458" s="1" t="inlineStr">
         <x:is>
-          <x:t>+3725012961</x:t>
+          <x:t>UEP sees with its boss</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -53798,7 +53802,7 @@
       </x:c>
       <x:c r="C459" s="4" t="inlineStr">
         <x:is>
-          <x:t>1803855</x:t>
+          <x:t>1801511</x:t>
         </x:is>
       </x:c>
       <x:c r="D459" s="4">
@@ -53806,7 +53810,7 @@
       </x:c>
       <x:c r="E459" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002791656</x:t>
+          <x:t>4002786694</x:t>
         </x:is>
       </x:c>
       <x:c r="F459" s="1" t="inlineStr">
@@ -53826,17 +53830,17 @@
       </x:c>
       <x:c r="I459" s="1" t="inlineStr">
         <x:is>
-          <x:t>9002</x:t>
+          <x:t>8996</x:t>
         </x:is>
       </x:c>
       <x:c r="J459" s="1" t="inlineStr">
         <x:is>
-          <x:t>Echt</x:t>
+          <x:t>Bierun</x:t>
         </x:is>
       </x:c>
       <x:c r="K459" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9002-1A</x:t>
+          <x:t>DCZONE-8996-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L459" s="1" t="inlineStr">
@@ -53857,29 +53861,29 @@
       </x:c>
       <x:c r="P459" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q459" s="2" t="n">
-        <x:v>46065.3984259259</x:v>
+        <x:v>46065.3652777778</x:v>
       </x:c>
       <x:c r="R459" s="2" t="n">
-        <x:v>46065.4253356481</x:v>
+        <x:v>46065.3766550926</x:v>
       </x:c>
       <x:c r="S459" s="2" t="n">
-        <x:v>46065.5190162037</x:v>
+        <x:v>46065.4531828704</x:v>
       </x:c>
       <x:c r="T459" s="3">
         <x:v/>
       </x:c>
       <x:c r="U459" s="3" t="inlineStr">
         <x:is>
-          <x:t>39</x:t>
+          <x:t>16</x:t>
         </x:is>
       </x:c>
       <x:c r="V459" s="3" t="inlineStr">
         <x:is>
-          <x:t>135</x:t>
+          <x:t>110</x:t>
         </x:is>
       </x:c>
       <x:c r="W459" s="1">
@@ -53898,7 +53902,7 @@
       </x:c>
       <x:c r="AA459" s="1" t="inlineStr">
         <x:is>
-          <x:t>5001455149 -63</x:t>
+          <x:t>+3725012961</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -53915,7 +53919,7 @@
       </x:c>
       <x:c r="C460" s="4" t="inlineStr">
         <x:is>
-          <x:t>1803863</x:t>
+          <x:t>1803855</x:t>
         </x:is>
       </x:c>
       <x:c r="D460" s="4">
@@ -53923,7 +53927,7 @@
       </x:c>
       <x:c r="E460" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002791657</x:t>
+          <x:t>4002791656</x:t>
         </x:is>
       </x:c>
       <x:c r="F460" s="1" t="inlineStr">
@@ -53938,22 +53942,22 @@
       </x:c>
       <x:c r="H460" s="1" t="inlineStr">
         <x:is>
-          <x:t>Refused</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I460" s="1" t="inlineStr">
         <x:is>
-          <x:t>9003</x:t>
+          <x:t>9002</x:t>
         </x:is>
       </x:c>
       <x:c r="J460" s="1" t="inlineStr">
         <x:is>
-          <x:t>Moissy</x:t>
+          <x:t>Echt</x:t>
         </x:is>
       </x:c>
       <x:c r="K460" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9003-1A</x:t>
+          <x:t>DCZONE-9002-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L460" s="1" t="inlineStr">
@@ -53966,7 +53970,7 @@
       </x:c>
       <x:c r="N460" s="1" t="inlineStr">
         <x:is>
-          <x:t>No</x:t>
+          <x:t>Yes</x:t>
         </x:is>
       </x:c>
       <x:c r="O460" s="2" t="n">
@@ -53978,33 +53982,29 @@
         </x:is>
       </x:c>
       <x:c r="Q460" s="2" t="n">
-        <x:v>46065.4250578704</x:v>
-      </x:c>
-      <x:c r="R460" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S460" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="T460" s="3" t="inlineStr">
-        <x:is>
-          <x:t>12</x:t>
-        </x:is>
+        <x:v>46065.3984259259</x:v>
+      </x:c>
+      <x:c r="R460" s="2" t="n">
+        <x:v>46065.4253356481</x:v>
+      </x:c>
+      <x:c r="S460" s="2" t="n">
+        <x:v>46065.5190162037</x:v>
+      </x:c>
+      <x:c r="T460" s="3">
+        <x:v/>
       </x:c>
       <x:c r="U460" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>39</x:t>
         </x:is>
       </x:c>
       <x:c r="V460" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="W460" s="1" t="inlineStr">
-        <x:is>
-          <x:t>No inbound capacity</x:t>
-        </x:is>
+          <x:t>135</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W460" s="1">
+        <x:v/>
       </x:c>
       <x:c r="X460" s="1" t="inlineStr">
         <x:is>
@@ -54019,7 +54019,7 @@
       </x:c>
       <x:c r="AA460" s="1" t="inlineStr">
         <x:is>
-          <x:t>UEP sees with its boss</x:t>
+          <x:t>5001455149 -63</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -57189,27 +57189,25 @@
     <x:row r="488">
       <x:c r="A488" s="1" t="inlineStr">
         <x:is>
-          <x:t>50135</x:t>
+          <x:t>1001634</x:t>
         </x:is>
       </x:c>
       <x:c r="B488" s="1" t="inlineStr">
         <x:is>
-          <x:t>DSV Road sp. z o.o.</x:t>
+          <x:t>Good(s)Factory</x:t>
         </x:is>
       </x:c>
       <x:c r="C488" s="4" t="inlineStr">
         <x:is>
-          <x:t>1807716</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D488" s="4" t="inlineStr">
-        <x:is>
-          <x:t>ACDE30-0401</x:t>
-        </x:is>
+          <x:t>1812289</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D488" s="4">
+        <x:v/>
       </x:c>
       <x:c r="E488" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002769309, 4002791062, 4002791659, 4002792700, 4002797820, 4002798005</x:t>
+          <x:t>4002799694</x:t>
         </x:is>
       </x:c>
       <x:c r="F488" s="1" t="inlineStr">
@@ -57224,27 +57222,27 @@
       </x:c>
       <x:c r="H488" s="1" t="inlineStr">
         <x:is>
-          <x:t>Cancelled</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I488" s="1" t="inlineStr">
         <x:is>
-          <x:t>8990</x:t>
+          <x:t>9000</x:t>
         </x:is>
       </x:c>
       <x:c r="J488" s="1" t="inlineStr">
         <x:is>
-          <x:t>Wallersdorf</x:t>
+          <x:t>Zwaagdijk</x:t>
         </x:is>
       </x:c>
       <x:c r="K488" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8990-1C</x:t>
+          <x:t>DCZONE-9000-2C</x:t>
         </x:is>
       </x:c>
       <x:c r="L488" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zone 1 Handling</x:t>
+          <x:t>Zone 2 Handling</x:t>
         </x:is>
       </x:c>
       <x:c r="M488" s="3" t="n">
@@ -57252,7 +57250,7 @@
       </x:c>
       <x:c r="N488" s="1" t="inlineStr">
         <x:is>
-          <x:t>No</x:t>
+          <x:t>Yes</x:t>
         </x:is>
       </x:c>
       <x:c r="O488" s="2" t="n">
@@ -57260,29 +57258,29 @@
       </x:c>
       <x:c r="P488" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q488" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R488" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S488" s="2">
-        <x:v/>
+          <x:t>On time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q488" s="2" t="n">
+        <x:v>46071.453900463</x:v>
+      </x:c>
+      <x:c r="R488" s="2" t="n">
+        <x:v>46071.4539583333</x:v>
+      </x:c>
+      <x:c r="S488" s="2" t="n">
+        <x:v>46071.4778125</x:v>
       </x:c>
       <x:c r="T488" s="3">
         <x:v/>
       </x:c>
       <x:c r="U488" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="V488" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>35</x:t>
         </x:is>
       </x:c>
       <x:c r="W488" s="1">
@@ -57293,40 +57291,42 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y488" s="1" t="inlineStr">
-        <x:is>
-          <x:t>DSV Road sp. z o.o.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Z488" s="2" t="n">
-        <x:v>46071.3616319444</x:v>
-      </x:c>
-      <x:c r="AA488" s="1">
-        <x:v/>
+      <x:c r="Y488" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z488" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA488" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DC1 naar DC2</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="489">
       <x:c r="A489" s="1" t="inlineStr">
         <x:is>
-          <x:t>1001634</x:t>
+          <x:t>50135</x:t>
         </x:is>
       </x:c>
       <x:c r="B489" s="1" t="inlineStr">
         <x:is>
-          <x:t>Good(s)Factory</x:t>
+          <x:t>DSV Road sp. z o.o.</x:t>
         </x:is>
       </x:c>
       <x:c r="C489" s="4" t="inlineStr">
         <x:is>
-          <x:t>1812289</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D489" s="4">
-        <x:v/>
+          <x:t>1807716</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D489" s="4" t="inlineStr">
+        <x:is>
+          <x:t>ACDE30-0401</x:t>
+        </x:is>
       </x:c>
       <x:c r="E489" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002799694</x:t>
+          <x:t>4002769309, 4002791062, 4002791659, 4002792700, 4002797820, 4002798005</x:t>
         </x:is>
       </x:c>
       <x:c r="F489" s="1" t="inlineStr">
@@ -57341,27 +57341,27 @@
       </x:c>
       <x:c r="H489" s="1" t="inlineStr">
         <x:is>
-          <x:t>Finished</x:t>
+          <x:t>Cancelled</x:t>
         </x:is>
       </x:c>
       <x:c r="I489" s="1" t="inlineStr">
         <x:is>
-          <x:t>9000</x:t>
+          <x:t>8990</x:t>
         </x:is>
       </x:c>
       <x:c r="J489" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zwaagdijk</x:t>
+          <x:t>Wallersdorf</x:t>
         </x:is>
       </x:c>
       <x:c r="K489" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9000-2C</x:t>
+          <x:t>DCZONE-8990-1C</x:t>
         </x:is>
       </x:c>
       <x:c r="L489" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zone 2 Handling</x:t>
+          <x:t>Zone 1 Handling</x:t>
         </x:is>
       </x:c>
       <x:c r="M489" s="3" t="n">
@@ -57369,7 +57369,7 @@
       </x:c>
       <x:c r="N489" s="1" t="inlineStr">
         <x:is>
-          <x:t>Yes</x:t>
+          <x:t>No</x:t>
         </x:is>
       </x:c>
       <x:c r="O489" s="2" t="n">
@@ -57377,29 +57377,29 @@
       </x:c>
       <x:c r="P489" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q489" s="2" t="n">
-        <x:v>46071.453900463</x:v>
-      </x:c>
-      <x:c r="R489" s="2" t="n">
-        <x:v>46071.4539583333</x:v>
-      </x:c>
-      <x:c r="S489" s="2" t="n">
-        <x:v>46071.4778125</x:v>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q489" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R489" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S489" s="2">
+        <x:v/>
       </x:c>
       <x:c r="T489" s="3">
         <x:v/>
       </x:c>
       <x:c r="U489" s="3" t="inlineStr">
         <x:is>
-          <x:t>0</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="V489" s="3" t="inlineStr">
         <x:is>
-          <x:t>35</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="W489" s="1">
@@ -57410,16 +57410,16 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y489" s="1">
-        <x:v/>
-      </x:c>
-      <x:c r="Z489" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="AA489" s="1" t="inlineStr">
-        <x:is>
-          <x:t>DC1 naar DC2</x:t>
-        </x:is>
+      <x:c r="Y489" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DSV Road sp. z o.o.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z489" s="2" t="n">
+        <x:v>46071.3616319444</x:v>
+      </x:c>
+      <x:c r="AA489" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="490">
@@ -58369,7 +58369,7 @@
       </x:c>
       <x:c r="C498" s="4" t="inlineStr">
         <x:is>
-          <x:t>1810820</x:t>
+          <x:t>1810811</x:t>
         </x:is>
       </x:c>
       <x:c r="D498" s="4">
@@ -58377,7 +58377,7 @@
       </x:c>
       <x:c r="E498" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002799516</x:t>
+          <x:t>4002799526</x:t>
         </x:is>
       </x:c>
       <x:c r="F498" s="1" t="inlineStr">
@@ -58397,17 +58397,17 @@
       </x:c>
       <x:c r="I498" s="1" t="inlineStr">
         <x:is>
-          <x:t>8995</x:t>
+          <x:t>9005</x:t>
         </x:is>
       </x:c>
       <x:c r="J498" s="1" t="inlineStr">
         <x:is>
-          <x:t>Ensues</x:t>
+          <x:t>Labastide</x:t>
         </x:is>
       </x:c>
       <x:c r="K498" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8995-1A</x:t>
+          <x:t>DCZONE-9005-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L498" s="1" t="inlineStr">
@@ -58432,25 +58432,25 @@
         </x:is>
       </x:c>
       <x:c r="Q498" s="2" t="n">
-        <x:v>46072.298587963</x:v>
+        <x:v>46072.3066087963</x:v>
       </x:c>
       <x:c r="R498" s="2" t="n">
-        <x:v>46072.3372916667</x:v>
+        <x:v>46072.3678125</x:v>
       </x:c>
       <x:c r="S498" s="2" t="n">
-        <x:v>46072.3517824074</x:v>
+        <x:v>46072.4260300926</x:v>
       </x:c>
       <x:c r="T498" s="3">
         <x:v/>
       </x:c>
       <x:c r="U498" s="3" t="inlineStr">
         <x:is>
-          <x:t>56</x:t>
+          <x:t>88</x:t>
         </x:is>
       </x:c>
       <x:c r="V498" s="3" t="inlineStr">
         <x:is>
-          <x:t>21</x:t>
+          <x:t>84</x:t>
         </x:is>
       </x:c>
       <x:c r="W498" s="1">
@@ -58484,7 +58484,7 @@
       </x:c>
       <x:c r="C499" s="4" t="inlineStr">
         <x:is>
-          <x:t>1810811</x:t>
+          <x:t>1810820</x:t>
         </x:is>
       </x:c>
       <x:c r="D499" s="4">
@@ -58492,7 +58492,7 @@
       </x:c>
       <x:c r="E499" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002799526</x:t>
+          <x:t>4002799516</x:t>
         </x:is>
       </x:c>
       <x:c r="F499" s="1" t="inlineStr">
@@ -58512,17 +58512,17 @@
       </x:c>
       <x:c r="I499" s="1" t="inlineStr">
         <x:is>
-          <x:t>9005</x:t>
+          <x:t>8995</x:t>
         </x:is>
       </x:c>
       <x:c r="J499" s="1" t="inlineStr">
         <x:is>
-          <x:t>Labastide</x:t>
+          <x:t>Ensues</x:t>
         </x:is>
       </x:c>
       <x:c r="K499" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9005-1A</x:t>
+          <x:t>DCZONE-8995-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L499" s="1" t="inlineStr">
@@ -58547,25 +58547,25 @@
         </x:is>
       </x:c>
       <x:c r="Q499" s="2" t="n">
-        <x:v>46072.3066087963</x:v>
+        <x:v>46072.298587963</x:v>
       </x:c>
       <x:c r="R499" s="2" t="n">
-        <x:v>46072.3678125</x:v>
+        <x:v>46072.3372916667</x:v>
       </x:c>
       <x:c r="S499" s="2" t="n">
-        <x:v>46072.4260300926</x:v>
+        <x:v>46072.3517824074</x:v>
       </x:c>
       <x:c r="T499" s="3">
         <x:v/>
       </x:c>
       <x:c r="U499" s="3" t="inlineStr">
         <x:is>
-          <x:t>88</x:t>
+          <x:t>56</x:t>
         </x:is>
       </x:c>
       <x:c r="V499" s="3" t="inlineStr">
         <x:is>
-          <x:t>84</x:t>
+          <x:t>21</x:t>
         </x:is>
       </x:c>
       <x:c r="W499" s="1">
@@ -61964,7 +61964,7 @@
       </x:c>
       <x:c r="C529" s="4" t="inlineStr">
         <x:is>
-          <x:t>1812179</x:t>
+          <x:t>1812168</x:t>
         </x:is>
       </x:c>
       <x:c r="D529" s="4">
@@ -61972,7 +61972,7 @@
       </x:c>
       <x:c r="E529" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002799573</x:t>
+          <x:t>4002799539</x:t>
         </x:is>
       </x:c>
       <x:c r="F529" s="1" t="inlineStr">
@@ -61987,22 +61987,22 @@
       </x:c>
       <x:c r="H529" s="1" t="inlineStr">
         <x:is>
-          <x:t>Removed</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I529" s="1" t="inlineStr">
         <x:is>
-          <x:t>9003</x:t>
+          <x:t>8997</x:t>
         </x:is>
       </x:c>
       <x:c r="J529" s="1" t="inlineStr">
         <x:is>
-          <x:t>Moissy</x:t>
+          <x:t>Verrières</x:t>
         </x:is>
       </x:c>
       <x:c r="K529" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9003-1A</x:t>
+          <x:t>DCZONE-8997-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L529" s="1" t="inlineStr">
@@ -62015,7 +62015,7 @@
       </x:c>
       <x:c r="N529" s="1" t="inlineStr">
         <x:is>
-          <x:t>No</x:t>
+          <x:t>Yes</x:t>
         </x:is>
       </x:c>
       <x:c r="O529" s="2" t="n">
@@ -62023,29 +62023,29 @@
       </x:c>
       <x:c r="P529" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q529" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R529" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S529" s="2">
-        <x:v/>
+          <x:t>On time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q529" s="2" t="n">
+        <x:v>46077.3326736111</x:v>
+      </x:c>
+      <x:c r="R529" s="2" t="n">
+        <x:v>46077.3444328704</x:v>
+      </x:c>
+      <x:c r="S529" s="2" t="n">
+        <x:v>46077.3821064815</x:v>
       </x:c>
       <x:c r="T529" s="3">
         <x:v/>
       </x:c>
       <x:c r="U529" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>16</x:t>
         </x:is>
       </x:c>
       <x:c r="V529" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>55</x:t>
         </x:is>
       </x:c>
       <x:c r="W529" s="1">
@@ -62056,13 +62056,11 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y529" s="1" t="inlineStr">
-        <x:is>
-          <x:t>Good(s)Factory</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Z529" s="2" t="n">
-        <x:v>46073.6248611111</x:v>
+      <x:c r="Y529" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z529" s="2">
+        <x:v/>
       </x:c>
       <x:c r="AA529" s="1">
         <x:v/>
@@ -62081,7 +62079,7 @@
       </x:c>
       <x:c r="C530" s="4" t="inlineStr">
         <x:is>
-          <x:t>1812168</x:t>
+          <x:t>1815942</x:t>
         </x:is>
       </x:c>
       <x:c r="D530" s="4">
@@ -62089,7 +62087,7 @@
       </x:c>
       <x:c r="E530" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002799539</x:t>
+          <x:t>4002799685</x:t>
         </x:is>
       </x:c>
       <x:c r="F530" s="1" t="inlineStr">
@@ -62109,22 +62107,22 @@
       </x:c>
       <x:c r="I530" s="1" t="inlineStr">
         <x:is>
-          <x:t>8997</x:t>
+          <x:t>9004</x:t>
         </x:is>
       </x:c>
       <x:c r="J530" s="1" t="inlineStr">
         <x:is>
-          <x:t>Verrières</x:t>
+          <x:t>Biblis</x:t>
         </x:is>
       </x:c>
       <x:c r="K530" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8997-1A</x:t>
+          <x:t>DCZONE-9004-1C</x:t>
         </x:is>
       </x:c>
       <x:c r="L530" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zone 1 Truck</x:t>
+          <x:t>Zone 1 Handling</x:t>
         </x:is>
       </x:c>
       <x:c r="M530" s="3" t="n">
@@ -62144,25 +62142,27 @@
         </x:is>
       </x:c>
       <x:c r="Q530" s="2" t="n">
-        <x:v>46077.3326736111</x:v>
+        <x:v>46077.3450347222</x:v>
       </x:c>
       <x:c r="R530" s="2" t="n">
-        <x:v>46077.3444328704</x:v>
+        <x:v>46077.3454166667</x:v>
       </x:c>
       <x:c r="S530" s="2" t="n">
-        <x:v>46077.3821064815</x:v>
-      </x:c>
-      <x:c r="T530" s="3">
-        <x:v/>
+        <x:v>46077.3918171296</x:v>
+      </x:c>
+      <x:c r="T530" s="3" t="inlineStr">
+        <x:is>
+          <x:t>16</x:t>
+        </x:is>
       </x:c>
       <x:c r="U530" s="3" t="inlineStr">
         <x:is>
-          <x:t>16</x:t>
+          <x:t>1</x:t>
         </x:is>
       </x:c>
       <x:c r="V530" s="3" t="inlineStr">
         <x:is>
-          <x:t>55</x:t>
+          <x:t>67</x:t>
         </x:is>
       </x:c>
       <x:c r="W530" s="1">
@@ -62179,8 +62179,10 @@
       <x:c r="Z530" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA530" s="1">
-        <x:v/>
+      <x:c r="AA530" s="1" t="inlineStr">
+        <x:is>
+          <x:t>61</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="531">
@@ -62196,7 +62198,7 @@
       </x:c>
       <x:c r="C531" s="4" t="inlineStr">
         <x:is>
-          <x:t>1815942</x:t>
+          <x:t>1812179</x:t>
         </x:is>
       </x:c>
       <x:c r="D531" s="4">
@@ -62204,7 +62206,7 @@
       </x:c>
       <x:c r="E531" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002799685</x:t>
+          <x:t>4002799573</x:t>
         </x:is>
       </x:c>
       <x:c r="F531" s="1" t="inlineStr">
@@ -62219,27 +62221,27 @@
       </x:c>
       <x:c r="H531" s="1" t="inlineStr">
         <x:is>
-          <x:t>Finished</x:t>
+          <x:t>Removed</x:t>
         </x:is>
       </x:c>
       <x:c r="I531" s="1" t="inlineStr">
         <x:is>
-          <x:t>9004</x:t>
+          <x:t>9003</x:t>
         </x:is>
       </x:c>
       <x:c r="J531" s="1" t="inlineStr">
         <x:is>
-          <x:t>Biblis</x:t>
+          <x:t>Moissy</x:t>
         </x:is>
       </x:c>
       <x:c r="K531" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9004-1C</x:t>
+          <x:t>DCZONE-9003-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L531" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zone 1 Handling</x:t>
+          <x:t>Zone 1 Truck</x:t>
         </x:is>
       </x:c>
       <x:c r="M531" s="3" t="n">
@@ -62247,7 +62249,7 @@
       </x:c>
       <x:c r="N531" s="1" t="inlineStr">
         <x:is>
-          <x:t>Yes</x:t>
+          <x:t>No</x:t>
         </x:is>
       </x:c>
       <x:c r="O531" s="2" t="n">
@@ -62255,31 +62257,29 @@
       </x:c>
       <x:c r="P531" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q531" s="2" t="n">
-        <x:v>46077.3450347222</x:v>
-      </x:c>
-      <x:c r="R531" s="2" t="n">
-        <x:v>46077.3454166667</x:v>
-      </x:c>
-      <x:c r="S531" s="2" t="n">
-        <x:v>46077.3918171296</x:v>
-      </x:c>
-      <x:c r="T531" s="3" t="inlineStr">
-        <x:is>
-          <x:t>16</x:t>
-        </x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q531" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R531" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S531" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T531" s="3">
+        <x:v/>
       </x:c>
       <x:c r="U531" s="3" t="inlineStr">
         <x:is>
-          <x:t>1</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="V531" s="3" t="inlineStr">
         <x:is>
-          <x:t>67</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="W531" s="1">
@@ -62290,16 +62290,16 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y531" s="1">
-        <x:v/>
-      </x:c>
-      <x:c r="Z531" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="AA531" s="1" t="inlineStr">
-        <x:is>
-          <x:t>61</x:t>
-        </x:is>
+      <x:c r="Y531" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z531" s="2" t="n">
+        <x:v>46073.6248611111</x:v>
+      </x:c>
+      <x:c r="AA531" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="532">
@@ -63475,7 +63475,7 @@
       </x:c>
       <x:c r="C542" s="4" t="inlineStr">
         <x:is>
-          <x:t>1812161</x:t>
+          <x:t>1821198</x:t>
         </x:is>
       </x:c>
       <x:c r="D542" s="4">
@@ -63483,7 +63483,7 @@
       </x:c>
       <x:c r="E542" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002799530</x:t>
+          <x:t>4002791664</x:t>
         </x:is>
       </x:c>
       <x:c r="F542" s="1" t="inlineStr">
@@ -63503,17 +63503,17 @@
       </x:c>
       <x:c r="I542" s="1" t="inlineStr">
         <x:is>
-          <x:t>9005</x:t>
+          <x:t>8987</x:t>
         </x:is>
       </x:c>
       <x:c r="J542" s="1" t="inlineStr">
         <x:is>
-          <x:t>Labastide</x:t>
+          <x:t>Ferentino</x:t>
         </x:is>
       </x:c>
       <x:c r="K542" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9005-1A</x:t>
+          <x:t>DCZONE-8987-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L542" s="1" t="inlineStr">
@@ -63534,31 +63534,29 @@
       </x:c>
       <x:c r="P542" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q542" s="2" t="n">
-        <x:v>46077.5980787037</x:v>
+        <x:v>46077.5437847222</x:v>
       </x:c>
       <x:c r="R542" s="2" t="n">
-        <x:v>46077.6170486111</x:v>
+        <x:v>46077.5702314815</x:v>
       </x:c>
       <x:c r="S542" s="2" t="n">
-        <x:v>46077.6666550926</x:v>
-      </x:c>
-      <x:c r="T542" s="3" t="inlineStr">
-        <x:is>
-          <x:t>21</x:t>
-        </x:is>
+        <x:v>46077.5702662037</x:v>
+      </x:c>
+      <x:c r="T542" s="3">
+        <x:v/>
       </x:c>
       <x:c r="U542" s="3" t="inlineStr">
         <x:is>
-          <x:t>27</x:t>
+          <x:t>38</x:t>
         </x:is>
       </x:c>
       <x:c r="V542" s="3" t="inlineStr">
         <x:is>
-          <x:t>71</x:t>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="W542" s="1">
@@ -63575,8 +63573,10 @@
       <x:c r="Z542" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA542" s="1">
-        <x:v/>
+      <x:c r="AA542" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Past no show 1803934 turned into new slot by order. plann</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="543">
@@ -63592,7 +63592,7 @@
       </x:c>
       <x:c r="C543" s="4" t="inlineStr">
         <x:is>
-          <x:t>1821198</x:t>
+          <x:t>1812161</x:t>
         </x:is>
       </x:c>
       <x:c r="D543" s="4">
@@ -63600,7 +63600,7 @@
       </x:c>
       <x:c r="E543" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002791664</x:t>
+          <x:t>4002799530</x:t>
         </x:is>
       </x:c>
       <x:c r="F543" s="1" t="inlineStr">
@@ -63620,17 +63620,17 @@
       </x:c>
       <x:c r="I543" s="1" t="inlineStr">
         <x:is>
-          <x:t>8987</x:t>
+          <x:t>9005</x:t>
         </x:is>
       </x:c>
       <x:c r="J543" s="1" t="inlineStr">
         <x:is>
-          <x:t>Ferentino</x:t>
+          <x:t>Labastide</x:t>
         </x:is>
       </x:c>
       <x:c r="K543" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8987-1A</x:t>
+          <x:t>DCZONE-9005-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L543" s="1" t="inlineStr">
@@ -63651,29 +63651,31 @@
       </x:c>
       <x:c r="P543" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q543" s="2" t="n">
-        <x:v>46077.5437847222</x:v>
+        <x:v>46077.5980787037</x:v>
       </x:c>
       <x:c r="R543" s="2" t="n">
-        <x:v>46077.5702314815</x:v>
+        <x:v>46077.6170486111</x:v>
       </x:c>
       <x:c r="S543" s="2" t="n">
-        <x:v>46077.5702662037</x:v>
-      </x:c>
-      <x:c r="T543" s="3">
-        <x:v/>
+        <x:v>46077.6666550926</x:v>
+      </x:c>
+      <x:c r="T543" s="3" t="inlineStr">
+        <x:is>
+          <x:t>21</x:t>
+        </x:is>
       </x:c>
       <x:c r="U543" s="3" t="inlineStr">
         <x:is>
-          <x:t>38</x:t>
+          <x:t>27</x:t>
         </x:is>
       </x:c>
       <x:c r="V543" s="3" t="inlineStr">
         <x:is>
-          <x:t>0</x:t>
+          <x:t>71</x:t>
         </x:is>
       </x:c>
       <x:c r="W543" s="1">
@@ -63690,10 +63692,8 @@
       <x:c r="Z543" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA543" s="1" t="inlineStr">
-        <x:is>
-          <x:t>Past no show 1803934 turned into new slot by order. plann</x:t>
-        </x:is>
+      <x:c r="AA543" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="544">
@@ -65809,7 +65809,7 @@
       </x:c>
       <x:c r="C562" s="4" t="inlineStr">
         <x:is>
-          <x:t>1817684</x:t>
+          <x:t>1811987</x:t>
         </x:is>
       </x:c>
       <x:c r="D562" s="4">
@@ -65817,7 +65817,7 @@
       </x:c>
       <x:c r="E562" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002809009</x:t>
+          <x:t>4002799525</x:t>
         </x:is>
       </x:c>
       <x:c r="F562" s="1" t="inlineStr">
@@ -65827,7 +65827,7 @@
       </x:c>
       <x:c r="G562" s="1" t="inlineStr">
         <x:is>
-          <x:t>Gold Allocation</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H562" s="1" t="inlineStr">
@@ -65837,17 +65837,17 @@
       </x:c>
       <x:c r="I562" s="1" t="inlineStr">
         <x:is>
-          <x:t>9007</x:t>
+          <x:t>9006</x:t>
         </x:is>
       </x:c>
       <x:c r="J562" s="1" t="inlineStr">
         <x:is>
-          <x:t>Peine</x:t>
+          <x:t>Belleville</x:t>
         </x:is>
       </x:c>
       <x:c r="K562" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9007-1A</x:t>
+          <x:t>DCZONE-9006-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L562" s="1" t="inlineStr">
@@ -65868,29 +65868,31 @@
       </x:c>
       <x:c r="P562" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Late</x:t>
         </x:is>
       </x:c>
       <x:c r="Q562" s="2" t="n">
-        <x:v>46079.2875810185</x:v>
+        <x:v>46079.317037037</x:v>
       </x:c>
       <x:c r="R562" s="2" t="n">
-        <x:v>46079.2880092593</x:v>
+        <x:v>46079.3180902778</x:v>
       </x:c>
       <x:c r="S562" s="2" t="n">
-        <x:v>46079.3034722222</x:v>
-      </x:c>
-      <x:c r="T562" s="3">
-        <x:v/>
+        <x:v>46079.3469560185</x:v>
+      </x:c>
+      <x:c r="T562" s="3" t="inlineStr">
+        <x:is>
+          <x:t>36</x:t>
+        </x:is>
       </x:c>
       <x:c r="U562" s="3" t="inlineStr">
         <x:is>
-          <x:t>0</x:t>
+          <x:t>2</x:t>
         </x:is>
       </x:c>
       <x:c r="V562" s="3" t="inlineStr">
         <x:is>
-          <x:t>23</x:t>
+          <x:t>41</x:t>
         </x:is>
       </x:c>
       <x:c r="W562" s="1">
@@ -65924,7 +65926,7 @@
       </x:c>
       <x:c r="C563" s="4" t="inlineStr">
         <x:is>
-          <x:t>1811987</x:t>
+          <x:t>1817684</x:t>
         </x:is>
       </x:c>
       <x:c r="D563" s="4">
@@ -65932,7 +65934,7 @@
       </x:c>
       <x:c r="E563" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002799525</x:t>
+          <x:t>4002809009</x:t>
         </x:is>
       </x:c>
       <x:c r="F563" s="1" t="inlineStr">
@@ -65942,7 +65944,7 @@
       </x:c>
       <x:c r="G563" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>Gold Allocation</x:t>
         </x:is>
       </x:c>
       <x:c r="H563" s="1" t="inlineStr">
@@ -65952,17 +65954,17 @@
       </x:c>
       <x:c r="I563" s="1" t="inlineStr">
         <x:is>
-          <x:t>9006</x:t>
+          <x:t>9007</x:t>
         </x:is>
       </x:c>
       <x:c r="J563" s="1" t="inlineStr">
         <x:is>
-          <x:t>Belleville</x:t>
+          <x:t>Peine</x:t>
         </x:is>
       </x:c>
       <x:c r="K563" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9006-1A</x:t>
+          <x:t>DCZONE-9007-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L563" s="1" t="inlineStr">
@@ -65983,31 +65985,29 @@
       </x:c>
       <x:c r="P563" s="1" t="inlineStr">
         <x:is>
-          <x:t>Late</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q563" s="2" t="n">
-        <x:v>46079.317037037</x:v>
+        <x:v>46079.2875810185</x:v>
       </x:c>
       <x:c r="R563" s="2" t="n">
-        <x:v>46079.3180902778</x:v>
+        <x:v>46079.2880092593</x:v>
       </x:c>
       <x:c r="S563" s="2" t="n">
-        <x:v>46079.3469560185</x:v>
-      </x:c>
-      <x:c r="T563" s="3" t="inlineStr">
-        <x:is>
-          <x:t>36</x:t>
-        </x:is>
+        <x:v>46079.3034722222</x:v>
+      </x:c>
+      <x:c r="T563" s="3">
+        <x:v/>
       </x:c>
       <x:c r="U563" s="3" t="inlineStr">
         <x:is>
-          <x:t>2</x:t>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="V563" s="3" t="inlineStr">
         <x:is>
-          <x:t>41</x:t>
+          <x:t>23</x:t>
         </x:is>
       </x:c>
       <x:c r="W563" s="1">
@@ -73031,7 +73031,7 @@
       </x:c>
       <x:c r="C624" s="4" t="inlineStr">
         <x:is>
-          <x:t>1824122</x:t>
+          <x:t>1824134</x:t>
         </x:is>
       </x:c>
       <x:c r="D624" s="4">
@@ -73039,7 +73039,7 @@
       </x:c>
       <x:c r="E624" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002817855</x:t>
+          <x:t>4002817852</x:t>
         </x:is>
       </x:c>
       <x:c r="F624" s="1" t="inlineStr">
@@ -73059,17 +73059,17 @@
       </x:c>
       <x:c r="I624" s="1" t="inlineStr">
         <x:is>
-          <x:t>9004</x:t>
+          <x:t>9000</x:t>
         </x:is>
       </x:c>
       <x:c r="J624" s="1" t="inlineStr">
         <x:is>
-          <x:t>Biblis</x:t>
+          <x:t>Zwaagdijk</x:t>
         </x:is>
       </x:c>
       <x:c r="K624" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9004-1A</x:t>
+          <x:t>DCZONE-9000-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L624" s="1" t="inlineStr">
@@ -73090,29 +73090,29 @@
       </x:c>
       <x:c r="P624" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q624" s="2" t="n">
-        <x:v>46086.3359722222</x:v>
+        <x:v>46086.3633796296</x:v>
       </x:c>
       <x:c r="R624" s="2" t="n">
-        <x:v>46086.3752083333</x:v>
+        <x:v>46086.3635648148</x:v>
       </x:c>
       <x:c r="S624" s="2" t="n">
-        <x:v>46086.3909375</x:v>
+        <x:v>46086.3920138889</x:v>
       </x:c>
       <x:c r="T624" s="3">
         <x:v/>
       </x:c>
       <x:c r="U624" s="3" t="inlineStr">
         <x:is>
-          <x:t>57</x:t>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="V624" s="3" t="inlineStr">
         <x:is>
-          <x:t>22</x:t>
+          <x:t>41</x:t>
         </x:is>
       </x:c>
       <x:c r="W624" s="1">
@@ -73146,7 +73146,7 @@
       </x:c>
       <x:c r="C625" s="4" t="inlineStr">
         <x:is>
-          <x:t>1824134</x:t>
+          <x:t>1824122</x:t>
         </x:is>
       </x:c>
       <x:c r="D625" s="4">
@@ -73154,7 +73154,7 @@
       </x:c>
       <x:c r="E625" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002817852</x:t>
+          <x:t>4002817855</x:t>
         </x:is>
       </x:c>
       <x:c r="F625" s="1" t="inlineStr">
@@ -73174,17 +73174,17 @@
       </x:c>
       <x:c r="I625" s="1" t="inlineStr">
         <x:is>
-          <x:t>9000</x:t>
+          <x:t>9004</x:t>
         </x:is>
       </x:c>
       <x:c r="J625" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zwaagdijk</x:t>
+          <x:t>Biblis</x:t>
         </x:is>
       </x:c>
       <x:c r="K625" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9000-1A</x:t>
+          <x:t>DCZONE-9004-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L625" s="1" t="inlineStr">
@@ -73205,29 +73205,29 @@
       </x:c>
       <x:c r="P625" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q625" s="2" t="n">
-        <x:v>46086.3633796296</x:v>
+        <x:v>46086.3359722222</x:v>
       </x:c>
       <x:c r="R625" s="2" t="n">
-        <x:v>46086.3635648148</x:v>
+        <x:v>46086.3752083333</x:v>
       </x:c>
       <x:c r="S625" s="2" t="n">
-        <x:v>46086.3920138889</x:v>
+        <x:v>46086.3909375</x:v>
       </x:c>
       <x:c r="T625" s="3">
         <x:v/>
       </x:c>
       <x:c r="U625" s="3" t="inlineStr">
         <x:is>
-          <x:t>0</x:t>
+          <x:t>57</x:t>
         </x:is>
       </x:c>
       <x:c r="V625" s="3" t="inlineStr">
         <x:is>
-          <x:t>41</x:t>
+          <x:t>22</x:t>
         </x:is>
       </x:c>
       <x:c r="W625" s="1">
@@ -75581,7 +75581,7 @@
       </x:c>
       <x:c r="C646" s="4" t="inlineStr">
         <x:is>
-          <x:t>1832761</x:t>
+          <x:t>1827310</x:t>
         </x:is>
       </x:c>
       <x:c r="D646" s="4">
@@ -75589,7 +75589,7 @@
       </x:c>
       <x:c r="E646" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002826184</x:t>
+          <x:t>4002799574</x:t>
         </x:is>
       </x:c>
       <x:c r="F646" s="1" t="inlineStr">
@@ -75599,7 +75599,7 @@
       </x:c>
       <x:c r="G646" s="1" t="inlineStr">
         <x:is>
-          <x:t>Gold Allocation</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H646" s="1" t="inlineStr">
@@ -75609,17 +75609,17 @@
       </x:c>
       <x:c r="I646" s="1" t="inlineStr">
         <x:is>
-          <x:t>9002</x:t>
+          <x:t>9003</x:t>
         </x:is>
       </x:c>
       <x:c r="J646" s="1" t="inlineStr">
         <x:is>
-          <x:t>Echt</x:t>
+          <x:t>Moissy</x:t>
         </x:is>
       </x:c>
       <x:c r="K646" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9002-1A</x:t>
+          <x:t>DCZONE-9003-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L646" s="1" t="inlineStr">
@@ -75644,25 +75644,25 @@
         </x:is>
       </x:c>
       <x:c r="Q646" s="2" t="n">
-        <x:v>46092.2353009259</x:v>
+        <x:v>46092.2314930556</x:v>
       </x:c>
       <x:c r="R646" s="2" t="n">
-        <x:v>46092.2354050926</x:v>
+        <x:v>46092.2409606481</x:v>
       </x:c>
       <x:c r="S646" s="2" t="n">
-        <x:v>46092.2517939815</x:v>
+        <x:v>46092.2646759259</x:v>
       </x:c>
       <x:c r="T646" s="3">
         <x:v/>
       </x:c>
       <x:c r="U646" s="3" t="inlineStr">
         <x:is>
-          <x:t>0</x:t>
+          <x:t>13</x:t>
         </x:is>
       </x:c>
       <x:c r="V646" s="3" t="inlineStr">
         <x:is>
-          <x:t>24</x:t>
+          <x:t>35</x:t>
         </x:is>
       </x:c>
       <x:c r="W646" s="1">
@@ -75679,10 +75679,8 @@
       <x:c r="Z646" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA646" s="1" t="inlineStr">
-        <x:is>
-          <x:t>5001479073 -63</x:t>
-        </x:is>
+      <x:c r="AA646" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="647">
@@ -75698,7 +75696,7 @@
       </x:c>
       <x:c r="C647" s="4" t="inlineStr">
         <x:is>
-          <x:t>1827310</x:t>
+          <x:t>1832761</x:t>
         </x:is>
       </x:c>
       <x:c r="D647" s="4">
@@ -75706,7 +75704,7 @@
       </x:c>
       <x:c r="E647" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002799574</x:t>
+          <x:t>4002826184</x:t>
         </x:is>
       </x:c>
       <x:c r="F647" s="1" t="inlineStr">
@@ -75716,7 +75714,7 @@
       </x:c>
       <x:c r="G647" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>Gold Allocation</x:t>
         </x:is>
       </x:c>
       <x:c r="H647" s="1" t="inlineStr">
@@ -75726,17 +75724,17 @@
       </x:c>
       <x:c r="I647" s="1" t="inlineStr">
         <x:is>
-          <x:t>9003</x:t>
+          <x:t>9002</x:t>
         </x:is>
       </x:c>
       <x:c r="J647" s="1" t="inlineStr">
         <x:is>
-          <x:t>Moissy</x:t>
+          <x:t>Echt</x:t>
         </x:is>
       </x:c>
       <x:c r="K647" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9003-1A</x:t>
+          <x:t>DCZONE-9002-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L647" s="1" t="inlineStr">
@@ -75761,25 +75759,25 @@
         </x:is>
       </x:c>
       <x:c r="Q647" s="2" t="n">
-        <x:v>46092.2314930556</x:v>
+        <x:v>46092.2353009259</x:v>
       </x:c>
       <x:c r="R647" s="2" t="n">
-        <x:v>46092.2409606481</x:v>
+        <x:v>46092.2354050926</x:v>
       </x:c>
       <x:c r="S647" s="2" t="n">
-        <x:v>46092.2646759259</x:v>
+        <x:v>46092.2517939815</x:v>
       </x:c>
       <x:c r="T647" s="3">
         <x:v/>
       </x:c>
       <x:c r="U647" s="3" t="inlineStr">
         <x:is>
-          <x:t>13</x:t>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="V647" s="3" t="inlineStr">
         <x:is>
-          <x:t>35</x:t>
+          <x:t>24</x:t>
         </x:is>
       </x:c>
       <x:c r="W647" s="1">
@@ -75796,8 +75794,10 @@
       <x:c r="Z647" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA647" s="1">
-        <x:v/>
+      <x:c r="AA647" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001479073 -63</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="648">
@@ -75836,7 +75836,7 @@
       </x:c>
       <x:c r="H648" s="1" t="inlineStr">
         <x:is>
-          <x:t>Arrived</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I648" s="1" t="inlineStr">
@@ -75878,11 +75878,11 @@
       <x:c r="Q648" s="2" t="n">
         <x:v>46092.3164351852</x:v>
       </x:c>
-      <x:c r="R648" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S648" s="2">
-        <x:v/>
+      <x:c r="R648" s="2" t="n">
+        <x:v>46092.3581018519</x:v>
+      </x:c>
+      <x:c r="S648" s="2" t="n">
+        <x:v>46092.3618634259</x:v>
       </x:c>
       <x:c r="T648" s="3" t="inlineStr">
         <x:is>
@@ -75891,12 +75891,12 @@
       </x:c>
       <x:c r="U648" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>60</x:t>
         </x:is>
       </x:c>
       <x:c r="V648" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>6</x:t>
         </x:is>
       </x:c>
       <x:c r="W648" s="1">
@@ -76189,7 +76189,7 @@
       </x:c>
       <x:c r="H651" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I651" s="1" t="inlineStr">
@@ -76225,29 +76225,31 @@
       </x:c>
       <x:c r="P651" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q651" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R651" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S651" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="T651" s="3">
-        <x:v/>
+          <x:t>Late</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q651" s="2" t="n">
+        <x:v>46092.3857523148</x:v>
+      </x:c>
+      <x:c r="R651" s="2" t="n">
+        <x:v>46092.4500115741</x:v>
+      </x:c>
+      <x:c r="S651" s="2" t="n">
+        <x:v>46092.4948611111</x:v>
+      </x:c>
+      <x:c r="T651" s="3" t="inlineStr">
+        <x:is>
+          <x:t>45</x:t>
+        </x:is>
       </x:c>
       <x:c r="U651" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>93</x:t>
         </x:is>
       </x:c>
       <x:c r="V651" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>64</x:t>
         </x:is>
       </x:c>
       <x:c r="W651" s="1">
@@ -76266,7 +76268,7 @@
       </x:c>
       <x:c r="AA651" s="1" t="inlineStr">
         <x:is>
-          <x:t>INT:2552933-mistakes</x:t>
+          <x:t>INT:ramp37, 2552933-mistakes</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -76306,7 +76308,7 @@
       </x:c>
       <x:c r="H652" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I652" s="1" t="inlineStr">
@@ -76342,29 +76344,29 @@
       </x:c>
       <x:c r="P652" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q652" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R652" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S652" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q652" s="2" t="n">
+        <x:v>46092.3535185185</x:v>
+      </x:c>
+      <x:c r="R652" s="2" t="n">
+        <x:v>46092.353900463</x:v>
+      </x:c>
+      <x:c r="S652" s="2" t="n">
+        <x:v>46092.377650463</x:v>
       </x:c>
       <x:c r="T652" s="3">
         <x:v/>
       </x:c>
       <x:c r="U652" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="V652" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>34</x:t>
         </x:is>
       </x:c>
       <x:c r="W652" s="1">
@@ -76423,7 +76425,7 @@
       </x:c>
       <x:c r="H653" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I653" s="1" t="inlineStr">
@@ -76459,29 +76461,29 @@
       </x:c>
       <x:c r="P653" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q653" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R653" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S653" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q653" s="2" t="n">
+        <x:v>46092.3441087963</x:v>
+      </x:c>
+      <x:c r="R653" s="2" t="n">
+        <x:v>46092.3722685185</x:v>
+      </x:c>
+      <x:c r="S653" s="2" t="n">
+        <x:v>46092.4435185185</x:v>
       </x:c>
       <x:c r="T653" s="3">
         <x:v/>
       </x:c>
       <x:c r="U653" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>41</x:t>
         </x:is>
       </x:c>
       <x:c r="V653" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>102</x:t>
         </x:is>
       </x:c>
       <x:c r="W653" s="1">
@@ -76498,8 +76500,10 @@
       <x:c r="Z653" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA653" s="1">
-        <x:v/>
+      <x:c r="AA653" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zweite an 38</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="654">
@@ -76540,7 +76544,7 @@
       </x:c>
       <x:c r="H654" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I654" s="1" t="inlineStr">
@@ -76576,29 +76580,31 @@
       </x:c>
       <x:c r="P654" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q654" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R654" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S654" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="T654" s="3">
-        <x:v/>
+          <x:t>On time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q654" s="2" t="n">
+        <x:v>46092.3953472222</x:v>
+      </x:c>
+      <x:c r="R654" s="2" t="n">
+        <x:v>46092.3954050926</x:v>
+      </x:c>
+      <x:c r="S654" s="2" t="n">
+        <x:v>46092.4230092593</x:v>
+      </x:c>
+      <x:c r="T654" s="3" t="inlineStr">
+        <x:is>
+          <x:t>29</x:t>
+        </x:is>
       </x:c>
       <x:c r="U654" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="V654" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>40</x:t>
         </x:is>
       </x:c>
       <x:c r="W654" s="1">
@@ -76657,7 +76663,7 @@
       </x:c>
       <x:c r="H655" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I655" s="1" t="inlineStr">
@@ -76693,29 +76699,29 @@
       </x:c>
       <x:c r="P655" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q655" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R655" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S655" s="2">
-        <x:v/>
+          <x:t>On time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q655" s="2" t="n">
+        <x:v>46092.3650925926</x:v>
+      </x:c>
+      <x:c r="R655" s="2" t="n">
+        <x:v>46092.3667708333</x:v>
+      </x:c>
+      <x:c r="S655" s="2" t="n">
+        <x:v>46092.4820601852</x:v>
       </x:c>
       <x:c r="T655" s="3">
         <x:v/>
       </x:c>
       <x:c r="U655" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>3</x:t>
         </x:is>
       </x:c>
       <x:c r="V655" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>166</x:t>
         </x:is>
       </x:c>
       <x:c r="W655" s="1">
@@ -76732,8 +76738,10 @@
       <x:c r="Z655" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA655" s="1">
-        <x:v/>
+      <x:c r="AA655" s="1" t="inlineStr">
+        <x:is>
+          <x:t>739629473</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="656">
@@ -76772,7 +76780,7 @@
       </x:c>
       <x:c r="H656" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I656" s="1" t="inlineStr">
@@ -76808,29 +76816,31 @@
       </x:c>
       <x:c r="P656" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q656" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R656" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S656" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="T656" s="3">
-        <x:v/>
+          <x:t>Late - Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q656" s="2" t="n">
+        <x:v>46092.4524074074</x:v>
+      </x:c>
+      <x:c r="R656" s="2" t="n">
+        <x:v>46092.452650463</x:v>
+      </x:c>
+      <x:c r="S656" s="2" t="n">
+        <x:v>46092.4927546296</x:v>
+      </x:c>
+      <x:c r="T656" s="3" t="inlineStr">
+        <x:is>
+          <x:t>51</x:t>
+        </x:is>
       </x:c>
       <x:c r="U656" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="V656" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>58</x:t>
         </x:is>
       </x:c>
       <x:c r="W656" s="1">
@@ -76849,7 +76859,7 @@
       </x:c>
       <x:c r="AA656" s="1" t="inlineStr">
         <x:is>
-          <x:t>5001479076 -63</x:t>
+          <x:t>eta 11:30  5001479076 -63</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -76866,7 +76876,7 @@
       </x:c>
       <x:c r="C657" s="4" t="inlineStr">
         <x:is>
-          <x:t>1831612</x:t>
+          <x:t>1827479</x:t>
         </x:is>
       </x:c>
       <x:c r="D657" s="4">
@@ -76874,7 +76884,7 @@
       </x:c>
       <x:c r="E657" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002826003</x:t>
+          <x:t>4002821250</x:t>
         </x:is>
       </x:c>
       <x:c r="F657" s="1" t="inlineStr">
@@ -76884,27 +76894,27 @@
       </x:c>
       <x:c r="G657" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>Gold Allocation</x:t>
         </x:is>
       </x:c>
       <x:c r="H657" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I657" s="1" t="inlineStr">
         <x:is>
-          <x:t>8997</x:t>
+          <x:t>8994</x:t>
         </x:is>
       </x:c>
       <x:c r="J657" s="1" t="inlineStr">
         <x:is>
-          <x:t>Verrières</x:t>
+          <x:t>Zakroczym</x:t>
         </x:is>
       </x:c>
       <x:c r="K657" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8997-1A</x:t>
+          <x:t>DCZONE-8994-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L657" s="1" t="inlineStr">
@@ -76925,29 +76935,31 @@
       </x:c>
       <x:c r="P657" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q657" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R657" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S657" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="T657" s="3">
-        <x:v/>
+          <x:t>On time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q657" s="2" t="n">
+        <x:v>46092.4284953704</x:v>
+      </x:c>
+      <x:c r="R657" s="2" t="n">
+        <x:v>46092.4308564815</x:v>
+      </x:c>
+      <x:c r="S657" s="2" t="n">
+        <x:v>46092.4575462963</x:v>
+      </x:c>
+      <x:c r="T657" s="3" t="inlineStr">
+        <x:is>
+          <x:t>17</x:t>
+        </x:is>
       </x:c>
       <x:c r="U657" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>3</x:t>
         </x:is>
       </x:c>
       <x:c r="V657" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>38</x:t>
         </x:is>
       </x:c>
       <x:c r="W657" s="1">
@@ -76964,8 +76976,10 @@
       <x:c r="Z657" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA657" s="1">
-        <x:v/>
+      <x:c r="AA657" s="1" t="inlineStr">
+        <x:is>
+          <x:t>609050184</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="658">
@@ -76981,7 +76995,7 @@
       </x:c>
       <x:c r="C658" s="4" t="inlineStr">
         <x:is>
-          <x:t>1827479</x:t>
+          <x:t>1831612</x:t>
         </x:is>
       </x:c>
       <x:c r="D658" s="4">
@@ -76989,7 +77003,7 @@
       </x:c>
       <x:c r="E658" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002821250</x:t>
+          <x:t>4002826003</x:t>
         </x:is>
       </x:c>
       <x:c r="F658" s="1" t="inlineStr">
@@ -76999,27 +77013,27 @@
       </x:c>
       <x:c r="G658" s="1" t="inlineStr">
         <x:is>
-          <x:t>Gold Allocation</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H658" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I658" s="1" t="inlineStr">
         <x:is>
-          <x:t>8994</x:t>
+          <x:t>8997</x:t>
         </x:is>
       </x:c>
       <x:c r="J658" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zakroczym</x:t>
+          <x:t>Verrières</x:t>
         </x:is>
       </x:c>
       <x:c r="K658" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8994-1A</x:t>
+          <x:t>DCZONE-8997-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L658" s="1" t="inlineStr">
@@ -77040,29 +77054,29 @@
       </x:c>
       <x:c r="P658" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q658" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R658" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S658" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q658" s="2" t="n">
+        <x:v>46092.3725115741</x:v>
+      </x:c>
+      <x:c r="R658" s="2" t="n">
+        <x:v>46092.3963425926</x:v>
+      </x:c>
+      <x:c r="S658" s="2" t="n">
+        <x:v>46092.4725925926</x:v>
       </x:c>
       <x:c r="T658" s="3">
         <x:v/>
       </x:c>
       <x:c r="U658" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>34</x:t>
         </x:is>
       </x:c>
       <x:c r="V658" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>110</x:t>
         </x:is>
       </x:c>
       <x:c r="W658" s="1">
@@ -77119,7 +77133,7 @@
       </x:c>
       <x:c r="H659" s="1" t="inlineStr">
         <x:is>
-          <x:t>Arrived</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I659" s="1" t="inlineStr">
@@ -77161,23 +77175,23 @@
       <x:c r="Q659" s="2" t="n">
         <x:v>46092.2965740741</x:v>
       </x:c>
-      <x:c r="R659" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S659" s="2">
-        <x:v/>
+      <x:c r="R659" s="2" t="n">
+        <x:v>46092.336087963</x:v>
+      </x:c>
+      <x:c r="S659" s="2" t="n">
+        <x:v>46092.3361111111</x:v>
       </x:c>
       <x:c r="T659" s="3">
         <x:v/>
       </x:c>
       <x:c r="U659" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>56</x:t>
         </x:is>
       </x:c>
       <x:c r="V659" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>1</x:t>
         </x:is>
       </x:c>
       <x:c r="W659" s="1">
@@ -77211,7 +77225,7 @@
       </x:c>
       <x:c r="C660" s="4" t="inlineStr">
         <x:is>
-          <x:t>1827407</x:t>
+          <x:t>1827481</x:t>
         </x:is>
       </x:c>
       <x:c r="D660" s="4">
@@ -77219,7 +77233,7 @@
       </x:c>
       <x:c r="E660" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002821202</x:t>
+          <x:t>4002821254</x:t>
         </x:is>
       </x:c>
       <x:c r="F660" s="1" t="inlineStr">
@@ -77234,22 +77248,22 @@
       </x:c>
       <x:c r="H660" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I660" s="1" t="inlineStr">
         <x:is>
-          <x:t>8997</x:t>
+          <x:t>8992</x:t>
         </x:is>
       </x:c>
       <x:c r="J660" s="1" t="inlineStr">
         <x:is>
-          <x:t>Verrières</x:t>
+          <x:t>Illescas</x:t>
         </x:is>
       </x:c>
       <x:c r="K660" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8997-1A</x:t>
+          <x:t>DCZONE-8992-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L660" s="1" t="inlineStr">
@@ -77270,29 +77284,29 @@
       </x:c>
       <x:c r="P660" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q660" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R660" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S660" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q660" s="2" t="n">
+        <x:v>46092.421087963</x:v>
+      </x:c>
+      <x:c r="R660" s="2" t="n">
+        <x:v>46092.4504282407</x:v>
+      </x:c>
+      <x:c r="S660" s="2" t="n">
+        <x:v>46092.4827430556</x:v>
       </x:c>
       <x:c r="T660" s="3">
         <x:v/>
       </x:c>
       <x:c r="U660" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>42</x:t>
         </x:is>
       </x:c>
       <x:c r="V660" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>47</x:t>
         </x:is>
       </x:c>
       <x:c r="W660" s="1">
@@ -77309,8 +77323,10 @@
       <x:c r="Z660" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA660" s="1">
-        <x:v/>
+      <x:c r="AA660" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001478453</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="661">
@@ -77326,7 +77342,7 @@
       </x:c>
       <x:c r="C661" s="4" t="inlineStr">
         <x:is>
-          <x:t>1827481</x:t>
+          <x:t>1827407</x:t>
         </x:is>
       </x:c>
       <x:c r="D661" s="4">
@@ -77334,7 +77350,7 @@
       </x:c>
       <x:c r="E661" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002821254</x:t>
+          <x:t>4002821202</x:t>
         </x:is>
       </x:c>
       <x:c r="F661" s="1" t="inlineStr">
@@ -77349,22 +77365,22 @@
       </x:c>
       <x:c r="H661" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I661" s="1" t="inlineStr">
         <x:is>
-          <x:t>8992</x:t>
+          <x:t>8997</x:t>
         </x:is>
       </x:c>
       <x:c r="J661" s="1" t="inlineStr">
         <x:is>
-          <x:t>Illescas</x:t>
+          <x:t>Verrières</x:t>
         </x:is>
       </x:c>
       <x:c r="K661" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8992-1A</x:t>
+          <x:t>DCZONE-8997-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L661" s="1" t="inlineStr">
@@ -77385,29 +77401,29 @@
       </x:c>
       <x:c r="P661" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q661" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R661" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S661" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q661" s="2" t="n">
+        <x:v>46092.4253935185</x:v>
+      </x:c>
+      <x:c r="R661" s="2" t="n">
+        <x:v>46092.4717592593</x:v>
+      </x:c>
+      <x:c r="S661" s="2" t="n">
+        <x:v>46092.4844791667</x:v>
       </x:c>
       <x:c r="T661" s="3">
         <x:v/>
       </x:c>
       <x:c r="U661" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>67</x:t>
         </x:is>
       </x:c>
       <x:c r="V661" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>18</x:t>
         </x:is>
       </x:c>
       <x:c r="W661" s="1">
@@ -77424,10 +77440,8 @@
       <x:c r="Z661" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA661" s="1" t="inlineStr">
-        <x:is>
-          <x:t>5001478453</x:t>
-        </x:is>
+      <x:c r="AA661" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="662">
@@ -77468,7 +77482,7 @@
       </x:c>
       <x:c r="H662" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I662" s="1" t="inlineStr">
@@ -77504,29 +77518,29 @@
       </x:c>
       <x:c r="P662" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q662" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R662" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S662" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q662" s="2" t="n">
+        <x:v>46092.3765046296</x:v>
+      </x:c>
+      <x:c r="R662" s="2" t="n">
+        <x:v>46092.4351273148</x:v>
+      </x:c>
+      <x:c r="S662" s="2" t="n">
+        <x:v>46092.5081828704</x:v>
       </x:c>
       <x:c r="T662" s="3">
         <x:v/>
       </x:c>
       <x:c r="U662" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>84</x:t>
         </x:is>
       </x:c>
       <x:c r="V662" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>105</x:t>
         </x:is>
       </x:c>
       <x:c r="W662" s="1">
@@ -77543,8 +77557,10 @@
       <x:c r="Z662" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA662" s="1">
-        <x:v/>
+      <x:c r="AA662" s="1" t="inlineStr">
+        <x:is>
+          <x:t>535302809</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="663">
@@ -77585,7 +77601,7 @@
       </x:c>
       <x:c r="H663" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Cancelled</x:t>
         </x:is>
       </x:c>
       <x:c r="I663" s="1" t="inlineStr">
@@ -77613,7 +77629,7 @@
       </x:c>
       <x:c r="N663" s="1" t="inlineStr">
         <x:is>
-          <x:t>Yes</x:t>
+          <x:t>No</x:t>
         </x:is>
       </x:c>
       <x:c r="O663" s="2" t="n">
@@ -77654,11 +77670,13 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y663" s="1">
-        <x:v/>
-      </x:c>
-      <x:c r="Z663" s="2">
-        <x:v/>
+      <x:c r="Y663" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DSV Road sp. z o.o.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z663" s="2" t="n">
+        <x:v>46092.4494791667</x:v>
       </x:c>
       <x:c r="AA663" s="1">
         <x:v/>
@@ -77700,7 +77718,7 @@
       </x:c>
       <x:c r="H664" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I664" s="1" t="inlineStr">
@@ -77736,29 +77754,29 @@
       </x:c>
       <x:c r="P664" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q664" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R664" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S664" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q664" s="2" t="n">
+        <x:v>46092.6691550926</x:v>
+      </x:c>
+      <x:c r="R664" s="2" t="n">
+        <x:v>46092.6981944444</x:v>
+      </x:c>
+      <x:c r="S664" s="2" t="n">
+        <x:v>46092.7400231482</x:v>
       </x:c>
       <x:c r="T664" s="3">
         <x:v/>
       </x:c>
       <x:c r="U664" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>42</x:t>
         </x:is>
       </x:c>
       <x:c r="V664" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>60</x:t>
         </x:is>
       </x:c>
       <x:c r="W664" s="1">
@@ -77779,82 +77797,2630 @@
         <x:v/>
       </x:c>
     </x:row>
-    <x:row r="665" spans="1:27" x14ac:dyDescent="0.25">
-      <x:c r="A665" s="1" t="s">
+    <x:row r="665">
+      <x:c r="A665" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B665" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C665" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1827460</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D665" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E665" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002821205</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F665" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G665" s="1" t="inlineStr">
+        <x:is>
+          <x:t>GOLD Regular</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H665" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Unloading</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I665" s="1" t="inlineStr">
+        <x:is>
+          <x:t>8996</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J665" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Bierun</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K665" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-8996-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L665" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M665" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N665" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O665" s="2" t="n">
+        <x:v>46093.2916666667</x:v>
+      </x:c>
+      <x:c r="P665" s="1" t="inlineStr">
+        <x:is>
+          <x:t>On time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q665" s="2" t="n">
+        <x:v>46093.2760185185</x:v>
+      </x:c>
+      <x:c r="R665" s="2" t="n">
+        <x:v>46093.2776157407</x:v>
+      </x:c>
+      <x:c r="S665" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T665" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U665" s="3" t="inlineStr">
+        <x:is>
+          <x:t>2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="V665" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W665" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X665" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y665" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z665" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA665" s="1" t="inlineStr">
+        <x:is>
+          <x:t>+37255569851</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="666">
+      <x:c r="A666" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B666" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C666" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1831679</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D666" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E666" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002825996</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F666" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G666" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Gold Allocation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H666" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I666" s="1" t="inlineStr">
+        <x:is>
+          <x:t>9007</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J666" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Peine</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K666" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-9007-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L666" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M666" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N666" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O666" s="2" t="n">
+        <x:v>46093.2916666667</x:v>
+      </x:c>
+      <x:c r="P666" s="1" t="inlineStr">
+        <x:is>
+          <x:t>On time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q666" s="2" t="n">
+        <x:v>46093.27375</x:v>
+      </x:c>
+      <x:c r="R666" s="2" t="n">
+        <x:v>46093.2744328704</x:v>
+      </x:c>
+      <x:c r="S666" s="2" t="n">
+        <x:v>46093.2952430556</x:v>
+      </x:c>
+      <x:c r="T666" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U666" s="3" t="inlineStr">
+        <x:is>
+          <x:t>1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="V666" s="3" t="inlineStr">
+        <x:is>
+          <x:t>30</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W666" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X666" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y666" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z666" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA666" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="667">
+      <x:c r="A667" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B667" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C667" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1827414</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D667" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E667" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002821190</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F667" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G667" s="1" t="inlineStr">
+        <x:is>
+          <x:t>GOLD Regular</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H667" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I667" s="1" t="inlineStr">
+        <x:is>
+          <x:t>9006</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J667" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Belleville</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K667" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-9006-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L667" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M667" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N667" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O667" s="2" t="n">
+        <x:v>46093.2916666667</x:v>
+      </x:c>
+      <x:c r="P667" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q667" s="2" t="n">
+        <x:v>46093.2675462963</x:v>
+      </x:c>
+      <x:c r="R667" s="2" t="n">
+        <x:v>46093.2705671296</x:v>
+      </x:c>
+      <x:c r="S667" s="2" t="n">
+        <x:v>46093.3086111111</x:v>
+      </x:c>
+      <x:c r="T667" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U667" s="3" t="inlineStr">
+        <x:is>
+          <x:t>4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="V667" s="3" t="inlineStr">
+        <x:is>
+          <x:t>55</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W667" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X667" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y667" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z667" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA667" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="668">
+      <x:c r="A668" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B668" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C668" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1827415</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D668" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E668" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002821207</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F668" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G668" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Gold Allocation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H668" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Arrived</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I668" s="1" t="inlineStr">
+        <x:is>
+          <x:t>8995</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J668" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Ensues</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K668" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-8995-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L668" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M668" s="3" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N668" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O668" s="2" t="n">
+        <x:v>46093.3333333333</x:v>
+      </x:c>
+      <x:c r="P668" s="1" t="inlineStr">
+        <x:is>
+          <x:t>On time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q668" s="2" t="n">
+        <x:v>46093.3267708333</x:v>
+      </x:c>
+      <x:c r="R668" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S668" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T668" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U668" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V668" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W668" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X668" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y668" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z668" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA668" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="669">
+      <x:c r="A669" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B669" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C669" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1831658</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D669" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E669" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002825992</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F669" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G669" s="1" t="inlineStr">
+        <x:is>
+          <x:t>GOLD Regular</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H669" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Arrived</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I669" s="1" t="inlineStr">
+        <x:is>
+          <x:t>9004</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J669" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Biblis</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K669" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-9004-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L669" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M669" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N669" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O669" s="2" t="n">
+        <x:v>46093.375</x:v>
+      </x:c>
+      <x:c r="P669" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q669" s="2" t="n">
+        <x:v>46093.340775463</x:v>
+      </x:c>
+      <x:c r="R669" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S669" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T669" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U669" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V669" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W669" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X669" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y669" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z669" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA669" s="1" t="inlineStr">
+        <x:is>
+          <x:t>OD 30</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="670">
+      <x:c r="A670" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B670" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C670" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1832745</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D670" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E670" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002825834</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F670" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G670" s="1" t="inlineStr">
+        <x:is>
+          <x:t>GOLD Regular</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H670" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I670" s="1" t="inlineStr">
+        <x:is>
+          <x:t>9000</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J670" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zwaagdijk</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K670" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-9000-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L670" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M670" s="3" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N670" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O670" s="2" t="n">
+        <x:v>46093.375</x:v>
+      </x:c>
+      <x:c r="P670" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q670" s="2" t="n">
+        <x:v>46093.3179166667</x:v>
+      </x:c>
+      <x:c r="R670" s="2" t="n">
+        <x:v>46093.3183680556</x:v>
+      </x:c>
+      <x:c r="S670" s="2" t="n">
+        <x:v>46093.3428935185</x:v>
+      </x:c>
+      <x:c r="T670" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U670" s="3" t="inlineStr">
+        <x:is>
+          <x:t>1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="V670" s="3" t="inlineStr">
+        <x:is>
+          <x:t>35</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W670" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X670" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y670" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z670" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA670" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="671">
+      <x:c r="A671" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B671" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C671" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1827459</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D671" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E671" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002821196</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F671" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G671" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Gold Allocation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H671" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I671" s="1" t="inlineStr">
+        <x:is>
+          <x:t>8999</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J671" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Osla</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K671" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-8999-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L671" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M671" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N671" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O671" s="2" t="n">
+        <x:v>46093.3958333333</x:v>
+      </x:c>
+      <x:c r="P671" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q671" s="2" t="n">
+        <x:v>46092.4292939815</x:v>
+      </x:c>
+      <x:c r="R671" s="2" t="n">
+        <x:v>46092.5041435185</x:v>
+      </x:c>
+      <x:c r="S671" s="2" t="n">
+        <x:v>46092.532337963</x:v>
+      </x:c>
+      <x:c r="T671" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U671" s="3" t="inlineStr">
+        <x:is>
+          <x:t>107</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="V671" s="3" t="inlineStr">
+        <x:is>
+          <x:t>41</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W671" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X671" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y671" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z671" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA671" s="1" t="inlineStr">
+        <x:is>
+          <x:t>INT: extra truck 11.03</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="672">
+      <x:c r="A672" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B672" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C672" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1827480</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D672" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E672" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002821251</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F672" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G672" s="1" t="inlineStr">
+        <x:is>
+          <x:t>GOLD Regular</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H672" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Arrived</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I672" s="1" t="inlineStr">
+        <x:is>
+          <x:t>8994</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J672" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zakroczym</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K672" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-8994-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L672" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M672" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N672" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O672" s="2" t="n">
+        <x:v>46093.4166666667</x:v>
+      </x:c>
+      <x:c r="P672" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q672" s="2" t="n">
+        <x:v>46093.2863773148</x:v>
+      </x:c>
+      <x:c r="R672" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S672" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T672" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U672" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V672" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W672" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X672" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y672" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z672" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA672" s="1" t="inlineStr">
+        <x:is>
+          <x:t>607223775</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="673">
+      <x:c r="A673" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B673" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C673" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1831541</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D673" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E673" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002826010</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F673" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G673" s="1" t="inlineStr">
+        <x:is>
+          <x:t>GOLD Regular</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H673" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I673" s="1" t="inlineStr">
+        <x:is>
+          <x:t>9005</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J673" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Labastide</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K673" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-9005-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L673" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M673" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N673" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O673" s="2" t="n">
+        <x:v>46093.4166666667</x:v>
+      </x:c>
+      <x:c r="P673" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q673" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R673" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S673" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T673" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U673" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V673" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W673" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X673" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y673" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z673" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA673" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="674">
+      <x:c r="A674" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B674" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C674" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1827419</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D674" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E674" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002821186</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F674" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G674" s="1" t="inlineStr">
+        <x:is>
+          <x:t>GOLD Regular</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H674" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I674" s="1" t="inlineStr">
+        <x:is>
+          <x:t>9003</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J674" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Moissy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K674" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-9003-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L674" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M674" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N674" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O674" s="2" t="n">
+        <x:v>46093.4166666667</x:v>
+      </x:c>
+      <x:c r="P674" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q674" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R674" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S674" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T674" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U674" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V674" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W674" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X674" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y674" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z674" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA674" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="675">
+      <x:c r="A675" s="1" t="inlineStr">
+        <x:is>
+          <x:t>50135</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B675" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DSV Road sp. z o.o.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C675" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1835024</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D675" s="4" t="inlineStr">
+        <x:is>
+          <x:t>acsk30-0191</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E675" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002806793, 4002817864, 4002819380, 4002819607, 4002821884, 4002822748</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F675" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G675" s="1" t="inlineStr">
+        <x:is>
+          <x:t>GOLD Regular</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H675" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I675" s="1" t="inlineStr">
+        <x:is>
+          <x:t>8998</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J675" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Bratislava</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K675" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-8998-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L675" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M675" s="3" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="N675" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O675" s="2" t="n">
+        <x:v>46093.4166666667</x:v>
+      </x:c>
+      <x:c r="P675" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q675" s="2" t="n">
+        <x:v>46093.2902083333</x:v>
+      </x:c>
+      <x:c r="R675" s="2" t="n">
+        <x:v>46093.334537037</x:v>
+      </x:c>
+      <x:c r="S675" s="2" t="n">
+        <x:v>46093.3430324074</x:v>
+      </x:c>
+      <x:c r="T675" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U675" s="3" t="inlineStr">
+        <x:is>
+          <x:t>64</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="V675" s="3" t="inlineStr">
+        <x:is>
+          <x:t>12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W675" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X675" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y675" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z675" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA675" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="676">
+      <x:c r="A676" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B676" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C676" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1835550</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D676" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E676" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002830325</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F676" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G676" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Gold Allocation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H676" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I676" s="1" t="inlineStr">
+        <x:is>
+          <x:t>9002</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J676" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Echt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K676" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-9002-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L676" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M676" s="3" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N676" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O676" s="2" t="n">
+        <x:v>46093.4166666667</x:v>
+      </x:c>
+      <x:c r="P676" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q676" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R676" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S676" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T676" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U676" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V676" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W676" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X676" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y676" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z676" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA676" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001480405 -63</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="677">
+      <x:c r="A677" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B677" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C677" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1832747</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D677" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E677" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002825836</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F677" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G677" s="1" t="inlineStr">
+        <x:is>
+          <x:t>GOLD Regular</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H677" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I677" s="1" t="inlineStr">
+        <x:is>
+          <x:t>9002</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J677" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Echt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K677" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-9002-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L677" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M677" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N677" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O677" s="2" t="n">
+        <x:v>46093.4166666667</x:v>
+      </x:c>
+      <x:c r="P677" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q677" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R677" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S677" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T677" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U677" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V677" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W677" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X677" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y677" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z677" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA677" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001480397 -63</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="678">
+      <x:c r="A678" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B678" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C678" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1827485</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D678" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E678" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002821255</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F678" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G678" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Gold Allocation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H678" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I678" s="1" t="inlineStr">
+        <x:is>
+          <x:t>8991</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J678" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Altedo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K678" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-8991-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L678" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M678" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N678" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O678" s="2" t="n">
+        <x:v>46093.4583333333</x:v>
+      </x:c>
+      <x:c r="P678" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q678" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R678" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S678" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T678" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U678" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V678" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W678" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X678" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y678" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z678" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA678" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="679">
+      <x:c r="A679" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B679" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C679" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1827456</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D679" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E679" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002821195</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F679" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G679" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Gold Allocation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H679" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I679" s="1" t="inlineStr">
+        <x:is>
+          <x:t>8999</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J679" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Osla</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K679" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-8999-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L679" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M679" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N679" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O679" s="2" t="n">
+        <x:v>46093.4791666667</x:v>
+      </x:c>
+      <x:c r="P679" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q679" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R679" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S679" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T679" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U679" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V679" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W679" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X679" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y679" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z679" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA679" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="680">
+      <x:c r="A680" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B680" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C680" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1831547</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D680" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E680" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002826011</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F680" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G680" s="1" t="inlineStr">
+        <x:is>
+          <x:t>GOLD Regular</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H680" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I680" s="1" t="inlineStr">
+        <x:is>
+          <x:t>9005</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J680" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Labastide</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K680" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-9005-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L680" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M680" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N680" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O680" s="2" t="n">
+        <x:v>46093.5</x:v>
+      </x:c>
+      <x:c r="P680" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q680" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R680" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S680" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T680" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U680" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V680" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W680" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X680" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y680" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z680" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA680" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="681">
+      <x:c r="A681" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B681" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C681" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1827487</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D681" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E681" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002821256</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F681" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G681" s="1" t="inlineStr">
+        <x:is>
+          <x:t>GOLD Regular</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H681" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I681" s="1" t="inlineStr">
+        <x:is>
+          <x:t>8990</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J681" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Wallersdorf</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K681" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-8990-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L681" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M681" s="3" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N681" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O681" s="2" t="n">
+        <x:v>46093.5</x:v>
+      </x:c>
+      <x:c r="P681" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q681" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R681" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S681" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T681" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U681" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V681" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W681" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X681" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y681" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z681" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA681" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="682">
+      <x:c r="A682" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B682" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C682" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1827458</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D682" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E682" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002821197</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F682" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G682" s="1" t="inlineStr">
+        <x:is>
+          <x:t>GOLD Regular</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H682" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I682" s="1" t="inlineStr">
+        <x:is>
+          <x:t>8999</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J682" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Osla</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K682" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-8999-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L682" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M682" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N682" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O682" s="2" t="n">
+        <x:v>46093.5208333333</x:v>
+      </x:c>
+      <x:c r="P682" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q682" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R682" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S682" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T682" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U682" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V682" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W682" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X682" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y682" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z682" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA682" s="1" t="inlineStr">
+        <x:is>
+          <x:t>INT:3204620-mistakes</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="683">
+      <x:c r="A683" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B683" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C683" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1827484</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D683" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E683" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002821257</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F683" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G683" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Gold Allocation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H683" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I683" s="1" t="inlineStr">
+        <x:is>
+          <x:t>8989</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J683" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Dunikowo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K683" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-8989-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L683" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M683" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N683" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O683" s="2" t="n">
+        <x:v>46093.5416666667</x:v>
+      </x:c>
+      <x:c r="P683" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q683" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R683" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S683" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T683" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U683" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V683" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W683" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X683" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y683" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z683" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA683" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="684">
+      <x:c r="A684" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B684" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C684" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1833801</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D684" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E684" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002825837</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F684" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G684" s="1" t="inlineStr">
+        <x:is>
+          <x:t>GOLD Regular</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H684" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I684" s="1" t="inlineStr">
+        <x:is>
+          <x:t>9002</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J684" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Echt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K684" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-9002-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L684" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M684" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N684" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O684" s="2" t="n">
+        <x:v>46093.5416666667</x:v>
+      </x:c>
+      <x:c r="P684" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q684" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R684" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S684" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T684" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U684" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V684" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W684" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X684" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y684" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z684" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA684" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001480400 -63</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="685">
+      <x:c r="A685" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B685" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C685" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1831690</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D685" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E685" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002825997</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F685" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G685" s="1" t="inlineStr">
+        <x:is>
+          <x:t>GOLD Regular</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H685" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I685" s="1" t="inlineStr">
+        <x:is>
+          <x:t>9007</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J685" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Peine</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K685" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-9007-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L685" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M685" s="3" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N685" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O685" s="2" t="n">
+        <x:v>46093.5833333333</x:v>
+      </x:c>
+      <x:c r="P685" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q685" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R685" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S685" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T685" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U685" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V685" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W685" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X685" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y685" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z685" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA685" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="686">
+      <x:c r="A686" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B686" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C686" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1831634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D686" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E686" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002825995</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F686" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G686" s="1" t="inlineStr">
+        <x:is>
+          <x:t>GOLD Regular</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H686" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I686" s="1" t="inlineStr">
+        <x:is>
+          <x:t>9006</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J686" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Belleville</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K686" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-9006-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L686" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M686" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N686" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O686" s="2" t="n">
+        <x:v>46093.7083333333</x:v>
+      </x:c>
+      <x:c r="P686" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q686" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R686" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S686" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T686" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U686" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V686" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W686" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X686" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y686" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z686" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA686" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="687" spans="1:27" x14ac:dyDescent="0.25">
+      <x:c r="A687" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B665" s="1" t="s">
+      <x:c r="B687" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C665" s="4" t="s">
+      <x:c r="C687" s="4" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D665" s="4" t="s">
+      <x:c r="D687" s="4" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="E665" s="1" t="s">
+      <x:c r="E687" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F665" s="1"/>
-      <x:c r="G665" s="1"/>
-      <x:c r="H665" s="1" t="s">
+      <x:c r="F687" s="1"/>
+      <x:c r="G687" s="1"/>
+      <x:c r="H687" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I665" s="1" t="s">
+      <x:c r="I687" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="J665" s="1" t="s">
+      <x:c r="J687" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K665" s="1" t="s">
+      <x:c r="K687" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="L665" s="1" t="s">
+      <x:c r="L687" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="M665" s="3" t="s">
+      <x:c r="M687" s="3" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="N665" s="1" t="s">
+      <x:c r="N687" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="O665" s="2" t="s">
+      <x:c r="O687" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="P665" s="1" t="s">
+      <x:c r="P687" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="Q665" s="2" t="s">
+      <x:c r="Q687" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="R665" s="2" t="s">
+      <x:c r="R687" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="S665" s="2" t="s">
+      <x:c r="S687" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="T665" s="3" t="s">
+      <x:c r="T687" s="3" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="U665" s="3" t="s">
+      <x:c r="U687" s="3" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="V665" s="3" t="s">
+      <x:c r="V687" s="3" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="W665" s="1" t="s">
+      <x:c r="W687" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="X665" s="1" t="s">
+      <x:c r="X687" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="Y665" s="1" t="s">
+      <x:c r="Y687" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="Z665" s="2" t="s">
+      <x:c r="Z687" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="AA665" s="1"/>
+      <x:c r="AA687" s="1"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/AppointmentReport_latest.xlsx
+++ b/data/AppointmentReport_latest.xlsx
@@ -16,7 +16,7 @@
     <x:sheet name="Blad1" sheetId="1" r:id="rId1"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="DataStart">Blad1!$A$687</x:definedName>
+    <x:definedName name="DataStart">Blad1!$A$700</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="191029"/>
   <x:extLst>
@@ -1880,7 +1880,7 @@
       </x:c>
       <x:c r="C13" s="4" t="inlineStr">
         <x:is>
-          <x:t>1724947</x:t>
+          <x:t>1720623</x:t>
         </x:is>
       </x:c>
       <x:c r="D13" s="4">
@@ -1888,7 +1888,7 @@
       </x:c>
       <x:c r="E13" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002702410</x:t>
+          <x:t>4002698618</x:t>
         </x:is>
       </x:c>
       <x:c r="F13" s="1" t="inlineStr">
@@ -1908,17 +1908,17 @@
       </x:c>
       <x:c r="I13" s="1" t="inlineStr">
         <x:is>
-          <x:t>9006</x:t>
+          <x:t>9000</x:t>
         </x:is>
       </x:c>
       <x:c r="J13" s="1" t="inlineStr">
         <x:is>
-          <x:t>Belleville</x:t>
+          <x:t>Zwaagdijk</x:t>
         </x:is>
       </x:c>
       <x:c r="K13" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9006-1A</x:t>
+          <x:t>DCZONE-9000-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L13" s="1" t="inlineStr">
@@ -1939,29 +1939,29 @@
       </x:c>
       <x:c r="P13" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q13" s="2" t="n">
-        <x:v>46003.3706944444</x:v>
+        <x:v>46003.3529861111</x:v>
       </x:c>
       <x:c r="R13" s="2" t="n">
-        <x:v>46003.4039236111</x:v>
+        <x:v>46003.3531134259</x:v>
       </x:c>
       <x:c r="S13" s="2" t="n">
-        <x:v>46003.4474074074</x:v>
+        <x:v>46003.3723726852</x:v>
       </x:c>
       <x:c r="T13" s="3">
         <x:v/>
       </x:c>
       <x:c r="U13" s="3" t="inlineStr">
         <x:is>
-          <x:t>48</x:t>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="V13" s="3" t="inlineStr">
         <x:is>
-          <x:t>63</x:t>
+          <x:t>28</x:t>
         </x:is>
       </x:c>
       <x:c r="W13" s="1">
@@ -1995,7 +1995,7 @@
       </x:c>
       <x:c r="C14" s="4" t="inlineStr">
         <x:is>
-          <x:t>1720623</x:t>
+          <x:t>1724947</x:t>
         </x:is>
       </x:c>
       <x:c r="D14" s="4">
@@ -2003,7 +2003,7 @@
       </x:c>
       <x:c r="E14" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002698618</x:t>
+          <x:t>4002702410</x:t>
         </x:is>
       </x:c>
       <x:c r="F14" s="1" t="inlineStr">
@@ -2023,17 +2023,17 @@
       </x:c>
       <x:c r="I14" s="1" t="inlineStr">
         <x:is>
-          <x:t>9000</x:t>
+          <x:t>9006</x:t>
         </x:is>
       </x:c>
       <x:c r="J14" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zwaagdijk</x:t>
+          <x:t>Belleville</x:t>
         </x:is>
       </x:c>
       <x:c r="K14" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9000-1A</x:t>
+          <x:t>DCZONE-9006-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L14" s="1" t="inlineStr">
@@ -2054,29 +2054,29 @@
       </x:c>
       <x:c r="P14" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q14" s="2" t="n">
-        <x:v>46003.3529861111</x:v>
+        <x:v>46003.3706944444</x:v>
       </x:c>
       <x:c r="R14" s="2" t="n">
-        <x:v>46003.3531134259</x:v>
+        <x:v>46003.4039236111</x:v>
       </x:c>
       <x:c r="S14" s="2" t="n">
-        <x:v>46003.3723726852</x:v>
+        <x:v>46003.4474074074</x:v>
       </x:c>
       <x:c r="T14" s="3">
         <x:v/>
       </x:c>
       <x:c r="U14" s="3" t="inlineStr">
         <x:is>
-          <x:t>0</x:t>
+          <x:t>48</x:t>
         </x:is>
       </x:c>
       <x:c r="V14" s="3" t="inlineStr">
         <x:is>
-          <x:t>28</x:t>
+          <x:t>63</x:t>
         </x:is>
       </x:c>
       <x:c r="W14" s="1">
@@ -9566,7 +9566,7 @@
       </x:c>
       <x:c r="C79" s="4" t="inlineStr">
         <x:is>
-          <x:t>1722015</x:t>
+          <x:t>1706463</x:t>
         </x:is>
       </x:c>
       <x:c r="D79" s="4">
@@ -9574,7 +9574,7 @@
       </x:c>
       <x:c r="E79" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002697880</x:t>
+          <x:t>4002679375</x:t>
         </x:is>
       </x:c>
       <x:c r="F79" s="1" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </x:c>
       <x:c r="G79" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>-</x:t>
         </x:is>
       </x:c>
       <x:c r="H79" s="1" t="inlineStr">
@@ -9594,17 +9594,17 @@
       </x:c>
       <x:c r="I79" s="1" t="inlineStr">
         <x:is>
-          <x:t>8995</x:t>
+          <x:t>8993</x:t>
         </x:is>
       </x:c>
       <x:c r="J79" s="1" t="inlineStr">
         <x:is>
-          <x:t>Ensues</x:t>
+          <x:t>Novara</x:t>
         </x:is>
       </x:c>
       <x:c r="K79" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8995-1A</x:t>
+          <x:t>DCZONE-8993-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L79" s="1" t="inlineStr">
@@ -9613,7 +9613,7 @@
         </x:is>
       </x:c>
       <x:c r="M79" s="3" t="n">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="N79" s="1" t="inlineStr">
         <x:is>
@@ -9629,25 +9629,25 @@
         </x:is>
       </x:c>
       <x:c r="Q79" s="2" t="n">
-        <x:v>46008.3650115741</x:v>
+        <x:v>46008.3549768518</x:v>
       </x:c>
       <x:c r="R79" s="2" t="n">
-        <x:v>46008.3795486111</x:v>
+        <x:v>46008.3748842593</x:v>
       </x:c>
       <x:c r="S79" s="2" t="n">
-        <x:v>46008.4017013889</x:v>
+        <x:v>46008.4709606481</x:v>
       </x:c>
       <x:c r="T79" s="3">
         <x:v/>
       </x:c>
       <x:c r="U79" s="3" t="inlineStr">
         <x:is>
-          <x:t>21</x:t>
+          <x:t>28</x:t>
         </x:is>
       </x:c>
       <x:c r="V79" s="3" t="inlineStr">
         <x:is>
-          <x:t>32</x:t>
+          <x:t>139</x:t>
         </x:is>
       </x:c>
       <x:c r="W79" s="1">
@@ -9681,7 +9681,7 @@
       </x:c>
       <x:c r="C80" s="4" t="inlineStr">
         <x:is>
-          <x:t>1706463</x:t>
+          <x:t>1722015</x:t>
         </x:is>
       </x:c>
       <x:c r="D80" s="4">
@@ -9689,7 +9689,7 @@
       </x:c>
       <x:c r="E80" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679375</x:t>
+          <x:t>4002697880</x:t>
         </x:is>
       </x:c>
       <x:c r="F80" s="1" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </x:c>
       <x:c r="G80" s="1" t="inlineStr">
         <x:is>
-          <x:t>-</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H80" s="1" t="inlineStr">
@@ -9709,17 +9709,17 @@
       </x:c>
       <x:c r="I80" s="1" t="inlineStr">
         <x:is>
-          <x:t>8993</x:t>
+          <x:t>8995</x:t>
         </x:is>
       </x:c>
       <x:c r="J80" s="1" t="inlineStr">
         <x:is>
-          <x:t>Novara</x:t>
+          <x:t>Ensues</x:t>
         </x:is>
       </x:c>
       <x:c r="K80" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8993-1A</x:t>
+          <x:t>DCZONE-8995-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L80" s="1" t="inlineStr">
@@ -9728,7 +9728,7 @@
         </x:is>
       </x:c>
       <x:c r="M80" s="3" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="N80" s="1" t="inlineStr">
         <x:is>
@@ -9744,25 +9744,25 @@
         </x:is>
       </x:c>
       <x:c r="Q80" s="2" t="n">
-        <x:v>46008.3549768518</x:v>
+        <x:v>46008.3650115741</x:v>
       </x:c>
       <x:c r="R80" s="2" t="n">
-        <x:v>46008.3748842593</x:v>
+        <x:v>46008.3795486111</x:v>
       </x:c>
       <x:c r="S80" s="2" t="n">
-        <x:v>46008.4709606481</x:v>
+        <x:v>46008.4017013889</x:v>
       </x:c>
       <x:c r="T80" s="3">
         <x:v/>
       </x:c>
       <x:c r="U80" s="3" t="inlineStr">
         <x:is>
-          <x:t>28</x:t>
+          <x:t>21</x:t>
         </x:is>
       </x:c>
       <x:c r="V80" s="3" t="inlineStr">
         <x:is>
-          <x:t>139</x:t>
+          <x:t>32</x:t>
         </x:is>
       </x:c>
       <x:c r="W80" s="1">
@@ -10375,7 +10375,7 @@
       </x:c>
       <x:c r="C86" s="4" t="inlineStr">
         <x:is>
-          <x:t>1722272</x:t>
+          <x:t>1705816</x:t>
         </x:is>
       </x:c>
       <x:c r="D86" s="4">
@@ -10383,7 +10383,7 @@
       </x:c>
       <x:c r="E86" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002699457</x:t>
+          <x:t>4002679345</x:t>
         </x:is>
       </x:c>
       <x:c r="F86" s="1" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </x:c>
       <x:c r="G86" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>-</x:t>
         </x:is>
       </x:c>
       <x:c r="H86" s="1" t="inlineStr">
@@ -10403,17 +10403,17 @@
       </x:c>
       <x:c r="I86" s="1" t="inlineStr">
         <x:is>
-          <x:t>8997</x:t>
+          <x:t>9004</x:t>
         </x:is>
       </x:c>
       <x:c r="J86" s="1" t="inlineStr">
         <x:is>
-          <x:t>Verrières</x:t>
+          <x:t>Biblis</x:t>
         </x:is>
       </x:c>
       <x:c r="K86" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8997-1A</x:t>
+          <x:t>DCZONE-9004-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L86" s="1" t="inlineStr">
@@ -10434,29 +10434,29 @@
       </x:c>
       <x:c r="P86" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q86" s="2" t="n">
-        <x:v>46008.4328587963</x:v>
+        <x:v>46008.4541898148</x:v>
       </x:c>
       <x:c r="R86" s="2" t="n">
-        <x:v>46008.4823958333</x:v>
+        <x:v>46008.4549305556</x:v>
       </x:c>
       <x:c r="S86" s="2" t="n">
-        <x:v>46008.5956944444</x:v>
+        <x:v>46008.477349537</x:v>
       </x:c>
       <x:c r="T86" s="3">
         <x:v/>
       </x:c>
       <x:c r="U86" s="3" t="inlineStr">
         <x:is>
-          <x:t>71</x:t>
+          <x:t>1</x:t>
         </x:is>
       </x:c>
       <x:c r="V86" s="3" t="inlineStr">
         <x:is>
-          <x:t>163</x:t>
+          <x:t>32</x:t>
         </x:is>
       </x:c>
       <x:c r="W86" s="1">
@@ -10464,7 +10464,7 @@
       </x:c>
       <x:c r="X86" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>Logistic quality: badly foiled</x:t>
         </x:is>
       </x:c>
       <x:c r="Y86" s="1">
@@ -10490,7 +10490,7 @@
       </x:c>
       <x:c r="C87" s="4" t="inlineStr">
         <x:is>
-          <x:t>1705816</x:t>
+          <x:t>1724481</x:t>
         </x:is>
       </x:c>
       <x:c r="D87" s="4">
@@ -10498,7 +10498,7 @@
       </x:c>
       <x:c r="E87" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679345</x:t>
+          <x:t>4002702422</x:t>
         </x:is>
       </x:c>
       <x:c r="F87" s="1" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </x:c>
       <x:c r="G87" s="1" t="inlineStr">
         <x:is>
-          <x:t>-</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H87" s="1" t="inlineStr">
@@ -10518,17 +10518,17 @@
       </x:c>
       <x:c r="I87" s="1" t="inlineStr">
         <x:is>
-          <x:t>9004</x:t>
+          <x:t>8998</x:t>
         </x:is>
       </x:c>
       <x:c r="J87" s="1" t="inlineStr">
         <x:is>
-          <x:t>Biblis</x:t>
+          <x:t>Bratislava</x:t>
         </x:is>
       </x:c>
       <x:c r="K87" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9004-1A</x:t>
+          <x:t>DCZONE-8998-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L87" s="1" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </x:c>
       <x:c r="N87" s="1" t="inlineStr">
         <x:is>
-          <x:t>Yes</x:t>
+          <x:t>No</x:t>
         </x:is>
       </x:c>
       <x:c r="O87" s="2" t="n">
@@ -10549,29 +10549,29 @@
       </x:c>
       <x:c r="P87" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q87" s="2" t="n">
-        <x:v>46008.4541898148</x:v>
+        <x:v>46008.4229513889</x:v>
       </x:c>
       <x:c r="R87" s="2" t="n">
-        <x:v>46008.4549305556</x:v>
+        <x:v>46008.4459259259</x:v>
       </x:c>
       <x:c r="S87" s="2" t="n">
-        <x:v>46008.477349537</x:v>
+        <x:v>46008.4975115741</x:v>
       </x:c>
       <x:c r="T87" s="3">
         <x:v/>
       </x:c>
       <x:c r="U87" s="3" t="inlineStr">
         <x:is>
-          <x:t>1</x:t>
+          <x:t>33</x:t>
         </x:is>
       </x:c>
       <x:c r="V87" s="3" t="inlineStr">
         <x:is>
-          <x:t>32</x:t>
+          <x:t>74</x:t>
         </x:is>
       </x:c>
       <x:c r="W87" s="1">
@@ -10579,7 +10579,7 @@
       </x:c>
       <x:c r="X87" s="1" t="inlineStr">
         <x:is>
-          <x:t>Logistic quality: badly foiled</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="Y87" s="1">
@@ -10605,7 +10605,7 @@
       </x:c>
       <x:c r="C88" s="4" t="inlineStr">
         <x:is>
-          <x:t>1724481</x:t>
+          <x:t>1722272</x:t>
         </x:is>
       </x:c>
       <x:c r="D88" s="4">
@@ -10613,7 +10613,7 @@
       </x:c>
       <x:c r="E88" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002702422</x:t>
+          <x:t>4002699457</x:t>
         </x:is>
       </x:c>
       <x:c r="F88" s="1" t="inlineStr">
@@ -10633,17 +10633,17 @@
       </x:c>
       <x:c r="I88" s="1" t="inlineStr">
         <x:is>
-          <x:t>8998</x:t>
+          <x:t>8997</x:t>
         </x:is>
       </x:c>
       <x:c r="J88" s="1" t="inlineStr">
         <x:is>
-          <x:t>Bratislava</x:t>
+          <x:t>Verrières</x:t>
         </x:is>
       </x:c>
       <x:c r="K88" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8998-1A</x:t>
+          <x:t>DCZONE-8997-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L88" s="1" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </x:c>
       <x:c r="N88" s="1" t="inlineStr">
         <x:is>
-          <x:t>No</x:t>
+          <x:t>Yes</x:t>
         </x:is>
       </x:c>
       <x:c r="O88" s="2" t="n">
@@ -10668,25 +10668,25 @@
         </x:is>
       </x:c>
       <x:c r="Q88" s="2" t="n">
-        <x:v>46008.4229513889</x:v>
+        <x:v>46008.4328587963</x:v>
       </x:c>
       <x:c r="R88" s="2" t="n">
-        <x:v>46008.4459259259</x:v>
+        <x:v>46008.4823958333</x:v>
       </x:c>
       <x:c r="S88" s="2" t="n">
-        <x:v>46008.4975115741</x:v>
+        <x:v>46008.5956944444</x:v>
       </x:c>
       <x:c r="T88" s="3">
         <x:v/>
       </x:c>
       <x:c r="U88" s="3" t="inlineStr">
         <x:is>
-          <x:t>33</x:t>
+          <x:t>71</x:t>
         </x:is>
       </x:c>
       <x:c r="V88" s="3" t="inlineStr">
         <x:is>
-          <x:t>74</x:t>
+          <x:t>163</x:t>
         </x:is>
       </x:c>
       <x:c r="W88" s="1">
@@ -11067,7 +11067,7 @@
       </x:c>
       <x:c r="C92" s="4" t="inlineStr">
         <x:is>
-          <x:t>1721073</x:t>
+          <x:t>1706789</x:t>
         </x:is>
       </x:c>
       <x:c r="D92" s="4">
@@ -11075,7 +11075,7 @@
       </x:c>
       <x:c r="E92" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002697875</x:t>
+          <x:t>4002679348</x:t>
         </x:is>
       </x:c>
       <x:c r="F92" s="1" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </x:c>
       <x:c r="G92" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>-</x:t>
         </x:is>
       </x:c>
       <x:c r="H92" s="1" t="inlineStr">
@@ -11095,17 +11095,17 @@
       </x:c>
       <x:c r="I92" s="1" t="inlineStr">
         <x:is>
-          <x:t>9005</x:t>
+          <x:t>9007</x:t>
         </x:is>
       </x:c>
       <x:c r="J92" s="1" t="inlineStr">
         <x:is>
-          <x:t>Labastide</x:t>
+          <x:t>Peine</x:t>
         </x:is>
       </x:c>
       <x:c r="K92" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9005-1A</x:t>
+          <x:t>DCZONE-9007-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L92" s="1" t="inlineStr">
@@ -11130,25 +11130,25 @@
         </x:is>
       </x:c>
       <x:c r="Q92" s="2" t="n">
-        <x:v>46008.4712268518</x:v>
+        <x:v>46008.4446180556</x:v>
       </x:c>
       <x:c r="R92" s="2" t="n">
-        <x:v>46008.4806134259</x:v>
+        <x:v>46008.5929976852</x:v>
       </x:c>
       <x:c r="S92" s="2" t="n">
-        <x:v>46008.527962963</x:v>
+        <x:v>46008.6132986111</x:v>
       </x:c>
       <x:c r="T92" s="3">
         <x:v/>
       </x:c>
       <x:c r="U92" s="3" t="inlineStr">
         <x:is>
-          <x:t>14</x:t>
+          <x:t>213</x:t>
         </x:is>
       </x:c>
       <x:c r="V92" s="3" t="inlineStr">
         <x:is>
-          <x:t>68</x:t>
+          <x:t>30</x:t>
         </x:is>
       </x:c>
       <x:c r="W92" s="1">
@@ -11182,7 +11182,7 @@
       </x:c>
       <x:c r="C93" s="4" t="inlineStr">
         <x:is>
-          <x:t>1706789</x:t>
+          <x:t>1721073</x:t>
         </x:is>
       </x:c>
       <x:c r="D93" s="4">
@@ -11190,7 +11190,7 @@
       </x:c>
       <x:c r="E93" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679348</x:t>
+          <x:t>4002697875</x:t>
         </x:is>
       </x:c>
       <x:c r="F93" s="1" t="inlineStr">
@@ -11200,7 +11200,7 @@
       </x:c>
       <x:c r="G93" s="1" t="inlineStr">
         <x:is>
-          <x:t>-</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H93" s="1" t="inlineStr">
@@ -11210,17 +11210,17 @@
       </x:c>
       <x:c r="I93" s="1" t="inlineStr">
         <x:is>
-          <x:t>9007</x:t>
+          <x:t>9005</x:t>
         </x:is>
       </x:c>
       <x:c r="J93" s="1" t="inlineStr">
         <x:is>
-          <x:t>Peine</x:t>
+          <x:t>Labastide</x:t>
         </x:is>
       </x:c>
       <x:c r="K93" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9007-1A</x:t>
+          <x:t>DCZONE-9005-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L93" s="1" t="inlineStr">
@@ -11245,25 +11245,25 @@
         </x:is>
       </x:c>
       <x:c r="Q93" s="2" t="n">
-        <x:v>46008.4446180556</x:v>
+        <x:v>46008.4712268518</x:v>
       </x:c>
       <x:c r="R93" s="2" t="n">
-        <x:v>46008.5929976852</x:v>
+        <x:v>46008.4806134259</x:v>
       </x:c>
       <x:c r="S93" s="2" t="n">
-        <x:v>46008.6132986111</x:v>
+        <x:v>46008.527962963</x:v>
       </x:c>
       <x:c r="T93" s="3">
         <x:v/>
       </x:c>
       <x:c r="U93" s="3" t="inlineStr">
         <x:is>
-          <x:t>213</x:t>
+          <x:t>14</x:t>
         </x:is>
       </x:c>
       <x:c r="V93" s="3" t="inlineStr">
         <x:is>
-          <x:t>30</x:t>
+          <x:t>68</x:t>
         </x:is>
       </x:c>
       <x:c r="W93" s="1">
@@ -13048,7 +13048,7 @@
       </x:c>
       <x:c r="C109" s="4" t="inlineStr">
         <x:is>
-          <x:t>1723926</x:t>
+          <x:t>1721150</x:t>
         </x:is>
       </x:c>
       <x:c r="D109" s="4">
@@ -13056,7 +13056,7 @@
       </x:c>
       <x:c r="E109" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002702419</x:t>
+          <x:t>4002697878</x:t>
         </x:is>
       </x:c>
       <x:c r="F109" s="1" t="inlineStr">
@@ -13076,17 +13076,17 @@
       </x:c>
       <x:c r="I109" s="1" t="inlineStr">
         <x:is>
-          <x:t>8994</x:t>
+          <x:t>8997</x:t>
         </x:is>
       </x:c>
       <x:c r="J109" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zakroczym</x:t>
+          <x:t>Verrières</x:t>
         </x:is>
       </x:c>
       <x:c r="K109" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8994-1A</x:t>
+          <x:t>DCZONE-8997-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L109" s="1" t="inlineStr">
@@ -13111,25 +13111,25 @@
         </x:is>
       </x:c>
       <x:c r="Q109" s="2" t="n">
-        <x:v>46009.3320949074</x:v>
+        <x:v>46009.3525115741</x:v>
       </x:c>
       <x:c r="R109" s="2" t="n">
-        <x:v>46009.3427893519</x:v>
+        <x:v>46009.3622916667</x:v>
       </x:c>
       <x:c r="S109" s="2" t="n">
-        <x:v>46009.3648263889</x:v>
+        <x:v>46009.4129861111</x:v>
       </x:c>
       <x:c r="T109" s="3">
         <x:v/>
       </x:c>
       <x:c r="U109" s="3" t="inlineStr">
         <x:is>
-          <x:t>15</x:t>
+          <x:t>14</x:t>
         </x:is>
       </x:c>
       <x:c r="V109" s="3" t="inlineStr">
         <x:is>
-          <x:t>32</x:t>
+          <x:t>73</x:t>
         </x:is>
       </x:c>
       <x:c r="W109" s="1">
@@ -13146,10 +13146,8 @@
       <x:c r="Z109" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA109" s="1" t="inlineStr">
-        <x:is>
-          <x:t>697908182</x:t>
-        </x:is>
+      <x:c r="AA109" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -13165,7 +13163,7 @@
       </x:c>
       <x:c r="C110" s="4" t="inlineStr">
         <x:is>
-          <x:t>1721150</x:t>
+          <x:t>1723926</x:t>
         </x:is>
       </x:c>
       <x:c r="D110" s="4">
@@ -13173,7 +13171,7 @@
       </x:c>
       <x:c r="E110" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002697878</x:t>
+          <x:t>4002702419</x:t>
         </x:is>
       </x:c>
       <x:c r="F110" s="1" t="inlineStr">
@@ -13193,17 +13191,17 @@
       </x:c>
       <x:c r="I110" s="1" t="inlineStr">
         <x:is>
-          <x:t>8997</x:t>
+          <x:t>8994</x:t>
         </x:is>
       </x:c>
       <x:c r="J110" s="1" t="inlineStr">
         <x:is>
-          <x:t>Verrières</x:t>
+          <x:t>Zakroczym</x:t>
         </x:is>
       </x:c>
       <x:c r="K110" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8997-1A</x:t>
+          <x:t>DCZONE-8994-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L110" s="1" t="inlineStr">
@@ -13228,25 +13226,25 @@
         </x:is>
       </x:c>
       <x:c r="Q110" s="2" t="n">
-        <x:v>46009.3525115741</x:v>
+        <x:v>46009.3320949074</x:v>
       </x:c>
       <x:c r="R110" s="2" t="n">
-        <x:v>46009.3622916667</x:v>
+        <x:v>46009.3427893519</x:v>
       </x:c>
       <x:c r="S110" s="2" t="n">
-        <x:v>46009.4129861111</x:v>
+        <x:v>46009.3648263889</x:v>
       </x:c>
       <x:c r="T110" s="3">
         <x:v/>
       </x:c>
       <x:c r="U110" s="3" t="inlineStr">
         <x:is>
-          <x:t>14</x:t>
+          <x:t>15</x:t>
         </x:is>
       </x:c>
       <x:c r="V110" s="3" t="inlineStr">
         <x:is>
-          <x:t>73</x:t>
+          <x:t>32</x:t>
         </x:is>
       </x:c>
       <x:c r="W110" s="1">
@@ -13263,8 +13261,10 @@
       <x:c r="Z110" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA110" s="1">
-        <x:v/>
+      <x:c r="AA110" s="1" t="inlineStr">
+        <x:is>
+          <x:t>697908182</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -13861,7 +13861,7 @@
       </x:c>
       <x:c r="C116" s="4" t="inlineStr">
         <x:is>
-          <x:t>1705717</x:t>
+          <x:t>1705505</x:t>
         </x:is>
       </x:c>
       <x:c r="D116" s="4">
@@ -13869,7 +13869,7 @@
       </x:c>
       <x:c r="E116" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002680829</x:t>
+          <x:t>4002679359</x:t>
         </x:is>
       </x:c>
       <x:c r="F116" s="1" t="inlineStr">
@@ -13889,17 +13889,17 @@
       </x:c>
       <x:c r="I116" s="1" t="inlineStr">
         <x:is>
-          <x:t>9002</x:t>
+          <x:t>8997</x:t>
         </x:is>
       </x:c>
       <x:c r="J116" s="1" t="inlineStr">
         <x:is>
-          <x:t>Echt</x:t>
+          <x:t>Verrières</x:t>
         </x:is>
       </x:c>
       <x:c r="K116" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9002-1A</x:t>
+          <x:t>DCZONE-8997-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L116" s="1" t="inlineStr">
@@ -13920,29 +13920,29 @@
       </x:c>
       <x:c r="P116" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q116" s="2" t="n">
-        <x:v>46009.500150463</x:v>
+        <x:v>46009.4703703704</x:v>
       </x:c>
       <x:c r="R116" s="2" t="n">
-        <x:v>46009.5253472222</x:v>
+        <x:v>46009.5198726852</x:v>
       </x:c>
       <x:c r="S116" s="2" t="n">
-        <x:v>46009.5553935185</x:v>
+        <x:v>46009.5733796296</x:v>
       </x:c>
       <x:c r="T116" s="3">
         <x:v/>
       </x:c>
       <x:c r="U116" s="3" t="inlineStr">
         <x:is>
-          <x:t>36</x:t>
+          <x:t>71</x:t>
         </x:is>
       </x:c>
       <x:c r="V116" s="3" t="inlineStr">
         <x:is>
-          <x:t>43</x:t>
+          <x:t>77</x:t>
         </x:is>
       </x:c>
       <x:c r="W116" s="1">
@@ -13959,10 +13959,8 @@
       <x:c r="Z116" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA116" s="1" t="inlineStr">
-        <x:is>
-          <x:t>5001407915  64</x:t>
-        </x:is>
+      <x:c r="AA116" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -13978,7 +13976,7 @@
       </x:c>
       <x:c r="C117" s="4" t="inlineStr">
         <x:is>
-          <x:t>1705505</x:t>
+          <x:t>1705717</x:t>
         </x:is>
       </x:c>
       <x:c r="D117" s="4">
@@ -13986,7 +13984,7 @@
       </x:c>
       <x:c r="E117" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679359</x:t>
+          <x:t>4002680829</x:t>
         </x:is>
       </x:c>
       <x:c r="F117" s="1" t="inlineStr">
@@ -14006,17 +14004,17 @@
       </x:c>
       <x:c r="I117" s="1" t="inlineStr">
         <x:is>
-          <x:t>8997</x:t>
+          <x:t>9002</x:t>
         </x:is>
       </x:c>
       <x:c r="J117" s="1" t="inlineStr">
         <x:is>
-          <x:t>Verrières</x:t>
+          <x:t>Echt</x:t>
         </x:is>
       </x:c>
       <x:c r="K117" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8997-1A</x:t>
+          <x:t>DCZONE-9002-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L117" s="1" t="inlineStr">
@@ -14037,29 +14035,29 @@
       </x:c>
       <x:c r="P117" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q117" s="2" t="n">
-        <x:v>46009.4703703704</x:v>
+        <x:v>46009.500150463</x:v>
       </x:c>
       <x:c r="R117" s="2" t="n">
-        <x:v>46009.5198726852</x:v>
+        <x:v>46009.5253472222</x:v>
       </x:c>
       <x:c r="S117" s="2" t="n">
-        <x:v>46009.5733796296</x:v>
+        <x:v>46009.5553935185</x:v>
       </x:c>
       <x:c r="T117" s="3">
         <x:v/>
       </x:c>
       <x:c r="U117" s="3" t="inlineStr">
         <x:is>
-          <x:t>71</x:t>
+          <x:t>36</x:t>
         </x:is>
       </x:c>
       <x:c r="V117" s="3" t="inlineStr">
         <x:is>
-          <x:t>77</x:t>
+          <x:t>43</x:t>
         </x:is>
       </x:c>
       <x:c r="W117" s="1">
@@ -14076,8 +14074,10 @@
       <x:c r="Z117" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA117" s="1">
-        <x:v/>
+      <x:c r="AA117" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001407915  64</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -15497,7 +15497,7 @@
       </x:c>
       <x:c r="C130" s="4" t="inlineStr">
         <x:is>
-          <x:t>1706808</x:t>
+          <x:t>1700365</x:t>
         </x:is>
       </x:c>
       <x:c r="D130" s="4">
@@ -15505,7 +15505,7 @@
       </x:c>
       <x:c r="E130" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679440</x:t>
+          <x:t>4002675811</x:t>
         </x:is>
       </x:c>
       <x:c r="F130" s="1" t="inlineStr">
@@ -15525,17 +15525,17 @@
       </x:c>
       <x:c r="I130" s="1" t="inlineStr">
         <x:is>
-          <x:t>8994</x:t>
+          <x:t>9000</x:t>
         </x:is>
       </x:c>
       <x:c r="J130" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zakroczym</x:t>
+          <x:t>Zwaagdijk</x:t>
         </x:is>
       </x:c>
       <x:c r="K130" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8994-1A</x:t>
+          <x:t>DCZONE-9000-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L130" s="1" t="inlineStr">
@@ -15556,21 +15556,21 @@
       </x:c>
       <x:c r="P130" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Late</x:t>
         </x:is>
       </x:c>
       <x:c r="Q130" s="2" t="n">
-        <x:v>46010.2585300926</x:v>
+        <x:v>46010.2732986111</x:v>
       </x:c>
       <x:c r="R130" s="2" t="n">
-        <x:v>46010.2587152778</x:v>
+        <x:v>46010.2734143519</x:v>
       </x:c>
       <x:c r="S130" s="2" t="n">
-        <x:v>46010.2779976852</x:v>
+        <x:v>46010.2913425926</x:v>
       </x:c>
       <x:c r="T130" s="3" t="inlineStr">
         <x:is>
-          <x:t>12</x:t>
+          <x:t>33</x:t>
         </x:is>
       </x:c>
       <x:c r="U130" s="3" t="inlineStr">
@@ -15580,7 +15580,7 @@
       </x:c>
       <x:c r="V130" s="3" t="inlineStr">
         <x:is>
-          <x:t>28</x:t>
+          <x:t>26</x:t>
         </x:is>
       </x:c>
       <x:c r="W130" s="1">
@@ -15597,10 +15597,8 @@
       <x:c r="Z130" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA130" s="1" t="inlineStr">
-        <x:is>
-          <x:t>508162640</x:t>
-        </x:is>
+      <x:c r="AA130" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -15616,7 +15614,7 @@
       </x:c>
       <x:c r="C131" s="4" t="inlineStr">
         <x:is>
-          <x:t>1706792</x:t>
+          <x:t>1706808</x:t>
         </x:is>
       </x:c>
       <x:c r="D131" s="4">
@@ -15624,7 +15622,7 @@
       </x:c>
       <x:c r="E131" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679349</x:t>
+          <x:t>4002679440</x:t>
         </x:is>
       </x:c>
       <x:c r="F131" s="1" t="inlineStr">
@@ -15644,17 +15642,17 @@
       </x:c>
       <x:c r="I131" s="1" t="inlineStr">
         <x:is>
-          <x:t>9007</x:t>
+          <x:t>8994</x:t>
         </x:is>
       </x:c>
       <x:c r="J131" s="1" t="inlineStr">
         <x:is>
-          <x:t>Peine</x:t>
+          <x:t>Zakroczym</x:t>
         </x:is>
       </x:c>
       <x:c r="K131" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9007-1A</x:t>
+          <x:t>DCZONE-8994-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L131" s="1" t="inlineStr">
@@ -15679,25 +15677,27 @@
         </x:is>
       </x:c>
       <x:c r="Q131" s="2" t="n">
-        <x:v>46010.2481828704</x:v>
+        <x:v>46010.2585300926</x:v>
       </x:c>
       <x:c r="R131" s="2" t="n">
-        <x:v>46010.2489467593</x:v>
+        <x:v>46010.2587152778</x:v>
       </x:c>
       <x:c r="S131" s="2" t="n">
-        <x:v>46010.2654166667</x:v>
-      </x:c>
-      <x:c r="T131" s="3">
-        <x:v/>
+        <x:v>46010.2779976852</x:v>
+      </x:c>
+      <x:c r="T131" s="3" t="inlineStr">
+        <x:is>
+          <x:t>12</x:t>
+        </x:is>
       </x:c>
       <x:c r="U131" s="3" t="inlineStr">
         <x:is>
-          <x:t>1</x:t>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="V131" s="3" t="inlineStr">
         <x:is>
-          <x:t>24</x:t>
+          <x:t>28</x:t>
         </x:is>
       </x:c>
       <x:c r="W131" s="1">
@@ -15714,8 +15714,10 @@
       <x:c r="Z131" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA131" s="1">
-        <x:v/>
+      <x:c r="AA131" s="1" t="inlineStr">
+        <x:is>
+          <x:t>508162640</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -15731,7 +15733,7 @@
       </x:c>
       <x:c r="C132" s="4" t="inlineStr">
         <x:is>
-          <x:t>1700365</x:t>
+          <x:t>1706792</x:t>
         </x:is>
       </x:c>
       <x:c r="D132" s="4">
@@ -15739,7 +15741,7 @@
       </x:c>
       <x:c r="E132" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002675811</x:t>
+          <x:t>4002679349</x:t>
         </x:is>
       </x:c>
       <x:c r="F132" s="1" t="inlineStr">
@@ -15759,17 +15761,17 @@
       </x:c>
       <x:c r="I132" s="1" t="inlineStr">
         <x:is>
-          <x:t>9000</x:t>
+          <x:t>9007</x:t>
         </x:is>
       </x:c>
       <x:c r="J132" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zwaagdijk</x:t>
+          <x:t>Peine</x:t>
         </x:is>
       </x:c>
       <x:c r="K132" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9000-1A</x:t>
+          <x:t>DCZONE-9007-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L132" s="1" t="inlineStr">
@@ -15790,31 +15792,29 @@
       </x:c>
       <x:c r="P132" s="1" t="inlineStr">
         <x:is>
-          <x:t>Late</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q132" s="2" t="n">
-        <x:v>46010.2732986111</x:v>
+        <x:v>46010.2481828704</x:v>
       </x:c>
       <x:c r="R132" s="2" t="n">
-        <x:v>46010.2734143519</x:v>
+        <x:v>46010.2489467593</x:v>
       </x:c>
       <x:c r="S132" s="2" t="n">
-        <x:v>46010.2913425926</x:v>
-      </x:c>
-      <x:c r="T132" s="3" t="inlineStr">
-        <x:is>
-          <x:t>33</x:t>
-        </x:is>
+        <x:v>46010.2654166667</x:v>
+      </x:c>
+      <x:c r="T132" s="3">
+        <x:v/>
       </x:c>
       <x:c r="U132" s="3" t="inlineStr">
         <x:is>
-          <x:t>0</x:t>
+          <x:t>1</x:t>
         </x:is>
       </x:c>
       <x:c r="V132" s="3" t="inlineStr">
         <x:is>
-          <x:t>26</x:t>
+          <x:t>24</x:t>
         </x:is>
       </x:c>
       <x:c r="W132" s="1">
@@ -16197,7 +16197,7 @@
       </x:c>
       <x:c r="C136" s="4" t="inlineStr">
         <x:is>
-          <x:t>1705700</x:t>
+          <x:t>1705827</x:t>
         </x:is>
       </x:c>
       <x:c r="D136" s="4">
@@ -16205,7 +16205,7 @@
       </x:c>
       <x:c r="E136" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679401</x:t>
+          <x:t>4002679436</x:t>
         </x:is>
       </x:c>
       <x:c r="F136" s="1" t="inlineStr">
@@ -16225,17 +16225,17 @@
       </x:c>
       <x:c r="I136" s="1" t="inlineStr">
         <x:is>
-          <x:t>9002</x:t>
+          <x:t>8996</x:t>
         </x:is>
       </x:c>
       <x:c r="J136" s="1" t="inlineStr">
         <x:is>
-          <x:t>Echt</x:t>
+          <x:t>Bierun</x:t>
         </x:is>
       </x:c>
       <x:c r="K136" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9002-1A</x:t>
+          <x:t>DCZONE-8996-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L136" s="1" t="inlineStr">
@@ -16256,31 +16256,29 @@
       </x:c>
       <x:c r="P136" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q136" s="2" t="n">
-        <x:v>46010.2927314815</x:v>
+        <x:v>46010.2668055556</x:v>
       </x:c>
       <x:c r="R136" s="2" t="n">
-        <x:v>46010.293275463</x:v>
+        <x:v>46010.2673611111</x:v>
       </x:c>
       <x:c r="S136" s="2" t="n">
-        <x:v>46010.3132638889</x:v>
-      </x:c>
-      <x:c r="T136" s="3" t="inlineStr">
+        <x:v>46010.3013773148</x:v>
+      </x:c>
+      <x:c r="T136" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U136" s="3" t="inlineStr">
         <x:is>
           <x:t>1</x:t>
         </x:is>
       </x:c>
-      <x:c r="U136" s="3" t="inlineStr">
-        <x:is>
-          <x:t>1</x:t>
-        </x:is>
-      </x:c>
       <x:c r="V136" s="3" t="inlineStr">
         <x:is>
-          <x:t>29</x:t>
+          <x:t>48</x:t>
         </x:is>
       </x:c>
       <x:c r="W136" s="1">
@@ -16288,7 +16286,7 @@
       </x:c>
       <x:c r="X136" s="1" t="inlineStr">
         <x:is>
-          <x:t>Logistic quality: badly foiled</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="Y136" s="1">
@@ -16299,7 +16297,7 @@
       </x:c>
       <x:c r="AA136" s="1" t="inlineStr">
         <x:is>
-          <x:t>5001409471  64 / Chauffeur gaat zelf sealen</x:t>
+          <x:t>570081051</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -16316,7 +16314,7 @@
       </x:c>
       <x:c r="C137" s="4" t="inlineStr">
         <x:is>
-          <x:t>1705827</x:t>
+          <x:t>1705700</x:t>
         </x:is>
       </x:c>
       <x:c r="D137" s="4">
@@ -16324,7 +16322,7 @@
       </x:c>
       <x:c r="E137" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679436</x:t>
+          <x:t>4002679401</x:t>
         </x:is>
       </x:c>
       <x:c r="F137" s="1" t="inlineStr">
@@ -16344,17 +16342,17 @@
       </x:c>
       <x:c r="I137" s="1" t="inlineStr">
         <x:is>
-          <x:t>8996</x:t>
+          <x:t>9002</x:t>
         </x:is>
       </x:c>
       <x:c r="J137" s="1" t="inlineStr">
         <x:is>
-          <x:t>Bierun</x:t>
+          <x:t>Echt</x:t>
         </x:is>
       </x:c>
       <x:c r="K137" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8996-1A</x:t>
+          <x:t>DCZONE-9002-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L137" s="1" t="inlineStr">
@@ -16375,20 +16373,22 @@
       </x:c>
       <x:c r="P137" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q137" s="2" t="n">
-        <x:v>46010.2668055556</x:v>
+        <x:v>46010.2927314815</x:v>
       </x:c>
       <x:c r="R137" s="2" t="n">
-        <x:v>46010.2673611111</x:v>
+        <x:v>46010.293275463</x:v>
       </x:c>
       <x:c r="S137" s="2" t="n">
-        <x:v>46010.3013773148</x:v>
-      </x:c>
-      <x:c r="T137" s="3">
-        <x:v/>
+        <x:v>46010.3132638889</x:v>
+      </x:c>
+      <x:c r="T137" s="3" t="inlineStr">
+        <x:is>
+          <x:t>1</x:t>
+        </x:is>
       </x:c>
       <x:c r="U137" s="3" t="inlineStr">
         <x:is>
@@ -16397,7 +16397,7 @@
       </x:c>
       <x:c r="V137" s="3" t="inlineStr">
         <x:is>
-          <x:t>48</x:t>
+          <x:t>29</x:t>
         </x:is>
       </x:c>
       <x:c r="W137" s="1">
@@ -16405,7 +16405,7 @@
       </x:c>
       <x:c r="X137" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>Logistic quality: badly foiled</x:t>
         </x:is>
       </x:c>
       <x:c r="Y137" s="1">
@@ -16416,7 +16416,7 @@
       </x:c>
       <x:c r="AA137" s="1" t="inlineStr">
         <x:is>
-          <x:t>570081051</x:t>
+          <x:t>5001409471  64 / Chauffeur gaat zelf sealen</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -19689,7 +19689,7 @@
       </x:c>
       <x:c r="C166" s="4" t="inlineStr">
         <x:is>
-          <x:t>1744570</x:t>
+          <x:t>1744552</x:t>
         </x:is>
       </x:c>
       <x:c r="D166" s="4">
@@ -19697,7 +19697,7 @@
       </x:c>
       <x:c r="E166" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002728644</x:t>
+          <x:t>4002728642</x:t>
         </x:is>
       </x:c>
       <x:c r="F166" s="1" t="inlineStr">
@@ -19712,35 +19712,35 @@
       </x:c>
       <x:c r="H166" s="1" t="inlineStr">
         <x:is>
-          <x:t>Removed</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I166" s="1" t="inlineStr">
         <x:is>
-          <x:t>9000</x:t>
+          <x:t>9003</x:t>
         </x:is>
       </x:c>
       <x:c r="J166" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zwaagdijk</x:t>
+          <x:t>Moissy</x:t>
         </x:is>
       </x:c>
       <x:c r="K166" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9000-2A</x:t>
+          <x:t>DCZONE-9003-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L166" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zone 2 Truck</x:t>
+          <x:t>Zone 1 Truck</x:t>
         </x:is>
       </x:c>
       <x:c r="M166" s="3" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N166" s="1" t="inlineStr">
         <x:is>
-          <x:t>No</x:t>
+          <x:t>Yes</x:t>
         </x:is>
       </x:c>
       <x:c r="O166" s="2" t="n">
@@ -19748,29 +19748,29 @@
       </x:c>
       <x:c r="P166" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q166" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R166" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S166" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q166" s="2" t="n">
+        <x:v>46014.348125</x:v>
+      </x:c>
+      <x:c r="R166" s="2" t="n">
+        <x:v>46014.4496759259</x:v>
+      </x:c>
+      <x:c r="S166" s="2" t="n">
+        <x:v>46014.5156481481</x:v>
       </x:c>
       <x:c r="T166" s="3">
         <x:v/>
       </x:c>
       <x:c r="U166" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>146</x:t>
         </x:is>
       </x:c>
       <x:c r="V166" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>95</x:t>
         </x:is>
       </x:c>
       <x:c r="W166" s="1">
@@ -19781,13 +19781,11 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y166" s="1" t="inlineStr">
-        <x:is>
-          <x:t>Good(s)Factory</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Z166" s="2" t="n">
-        <x:v>46003.4545486111</x:v>
+      <x:c r="Y166" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z166" s="2">
+        <x:v/>
       </x:c>
       <x:c r="AA166" s="1">
         <x:v/>
@@ -19806,7 +19804,7 @@
       </x:c>
       <x:c r="C167" s="4" t="inlineStr">
         <x:is>
-          <x:t>1744552</x:t>
+          <x:t>1744570</x:t>
         </x:is>
       </x:c>
       <x:c r="D167" s="4">
@@ -19814,7 +19812,7 @@
       </x:c>
       <x:c r="E167" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002728642</x:t>
+          <x:t>4002728644</x:t>
         </x:is>
       </x:c>
       <x:c r="F167" s="1" t="inlineStr">
@@ -19829,35 +19827,35 @@
       </x:c>
       <x:c r="H167" s="1" t="inlineStr">
         <x:is>
-          <x:t>Finished</x:t>
+          <x:t>Removed</x:t>
         </x:is>
       </x:c>
       <x:c r="I167" s="1" t="inlineStr">
         <x:is>
-          <x:t>9003</x:t>
+          <x:t>9000</x:t>
         </x:is>
       </x:c>
       <x:c r="J167" s="1" t="inlineStr">
         <x:is>
-          <x:t>Moissy</x:t>
+          <x:t>Zwaagdijk</x:t>
         </x:is>
       </x:c>
       <x:c r="K167" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9003-1A</x:t>
+          <x:t>DCZONE-9000-2A</x:t>
         </x:is>
       </x:c>
       <x:c r="L167" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zone 1 Truck</x:t>
+          <x:t>Zone 2 Truck</x:t>
         </x:is>
       </x:c>
       <x:c r="M167" s="3" t="n">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N167" s="1" t="inlineStr">
         <x:is>
-          <x:t>Yes</x:t>
+          <x:t>No</x:t>
         </x:is>
       </x:c>
       <x:c r="O167" s="2" t="n">
@@ -19865,29 +19863,29 @@
       </x:c>
       <x:c r="P167" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q167" s="2" t="n">
-        <x:v>46014.348125</x:v>
-      </x:c>
-      <x:c r="R167" s="2" t="n">
-        <x:v>46014.4496759259</x:v>
-      </x:c>
-      <x:c r="S167" s="2" t="n">
-        <x:v>46014.5156481481</x:v>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q167" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R167" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S167" s="2">
+        <x:v/>
       </x:c>
       <x:c r="T167" s="3">
         <x:v/>
       </x:c>
       <x:c r="U167" s="3" t="inlineStr">
         <x:is>
-          <x:t>146</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="V167" s="3" t="inlineStr">
         <x:is>
-          <x:t>95</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="W167" s="1">
@@ -19898,11 +19896,13 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y167" s="1">
-        <x:v/>
-      </x:c>
-      <x:c r="Z167" s="2">
-        <x:v/>
+      <x:c r="Y167" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z167" s="2" t="n">
+        <x:v>46003.4545486111</x:v>
       </x:c>
       <x:c r="AA167" s="1">
         <x:v/>
@@ -20268,7 +20268,7 @@
       </x:c>
       <x:c r="C171" s="4" t="inlineStr">
         <x:is>
-          <x:t>1744871</x:t>
+          <x:t>1744819</x:t>
         </x:is>
       </x:c>
       <x:c r="D171" s="4">
@@ -20276,7 +20276,7 @@
       </x:c>
       <x:c r="E171" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002728646</x:t>
+          <x:t>4002728651</x:t>
         </x:is>
       </x:c>
       <x:c r="F171" s="1" t="inlineStr">
@@ -20291,22 +20291,22 @@
       </x:c>
       <x:c r="H171" s="1" t="inlineStr">
         <x:is>
-          <x:t>Finished</x:t>
+          <x:t>Removed</x:t>
         </x:is>
       </x:c>
       <x:c r="I171" s="1" t="inlineStr">
         <x:is>
-          <x:t>9000</x:t>
+          <x:t>9002</x:t>
         </x:is>
       </x:c>
       <x:c r="J171" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zwaagdijk</x:t>
+          <x:t>Echt</x:t>
         </x:is>
       </x:c>
       <x:c r="K171" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9000-1A</x:t>
+          <x:t>DCZONE-9002-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L171" s="1" t="inlineStr">
@@ -20315,11 +20315,11 @@
         </x:is>
       </x:c>
       <x:c r="M171" s="3" t="n">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N171" s="1" t="inlineStr">
         <x:is>
-          <x:t>Yes</x:t>
+          <x:t>No</x:t>
         </x:is>
       </x:c>
       <x:c r="O171" s="2" t="n">
@@ -20327,29 +20327,29 @@
       </x:c>
       <x:c r="P171" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q171" s="2" t="n">
-        <x:v>46014.4124305556</x:v>
-      </x:c>
-      <x:c r="R171" s="2" t="n">
-        <x:v>46014.4129861111</x:v>
-      </x:c>
-      <x:c r="S171" s="2" t="n">
-        <x:v>46014.4373726852</x:v>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q171" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R171" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S171" s="2">
+        <x:v/>
       </x:c>
       <x:c r="T171" s="3">
         <x:v/>
       </x:c>
       <x:c r="U171" s="3" t="inlineStr">
         <x:is>
-          <x:t>1</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="V171" s="3" t="inlineStr">
         <x:is>
-          <x:t>35</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="W171" s="1">
@@ -20360,16 +20360,16 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y171" s="1">
-        <x:v/>
-      </x:c>
-      <x:c r="Z171" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="AA171" s="1" t="inlineStr">
-        <x:is>
-          <x:t>DC1</x:t>
-        </x:is>
+      <x:c r="Y171" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z171" s="2" t="n">
+        <x:v>46003.433587963</x:v>
+      </x:c>
+      <x:c r="AA171" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -20385,7 +20385,7 @@
       </x:c>
       <x:c r="C172" s="4" t="inlineStr">
         <x:is>
-          <x:t>1745855</x:t>
+          <x:t>1744871</x:t>
         </x:is>
       </x:c>
       <x:c r="D172" s="4">
@@ -20393,7 +20393,7 @@
       </x:c>
       <x:c r="E172" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002728651</x:t>
+          <x:t>4002728646</x:t>
         </x:is>
       </x:c>
       <x:c r="F172" s="1" t="inlineStr">
@@ -20413,17 +20413,17 @@
       </x:c>
       <x:c r="I172" s="1" t="inlineStr">
         <x:is>
-          <x:t>9002</x:t>
+          <x:t>9000</x:t>
         </x:is>
       </x:c>
       <x:c r="J172" s="1" t="inlineStr">
         <x:is>
-          <x:t>Echt</x:t>
+          <x:t>Zwaagdijk</x:t>
         </x:is>
       </x:c>
       <x:c r="K172" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9002-1A</x:t>
+          <x:t>DCZONE-9000-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L172" s="1" t="inlineStr">
@@ -20432,7 +20432,7 @@
         </x:is>
       </x:c>
       <x:c r="M172" s="3" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="N172" s="1" t="inlineStr">
         <x:is>
@@ -20444,29 +20444,29 @@
       </x:c>
       <x:c r="P172" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q172" s="2" t="n">
-        <x:v>46014.4405671296</x:v>
+        <x:v>46014.4124305556</x:v>
       </x:c>
       <x:c r="R172" s="2" t="n">
-        <x:v>46014.4606481481</x:v>
+        <x:v>46014.4129861111</x:v>
       </x:c>
       <x:c r="S172" s="2" t="n">
-        <x:v>46014.4952314815</x:v>
+        <x:v>46014.4373726852</x:v>
       </x:c>
       <x:c r="T172" s="3">
         <x:v/>
       </x:c>
       <x:c r="U172" s="3" t="inlineStr">
         <x:is>
-          <x:t>29</x:t>
+          <x:t>1</x:t>
         </x:is>
       </x:c>
       <x:c r="V172" s="3" t="inlineStr">
         <x:is>
-          <x:t>50</x:t>
+          <x:t>35</x:t>
         </x:is>
       </x:c>
       <x:c r="W172" s="1">
@@ -20485,7 +20485,7 @@
       </x:c>
       <x:c r="AA172" s="1" t="inlineStr">
         <x:is>
-          <x:t>5001412549  64</x:t>
+          <x:t>DC1</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -20502,7 +20502,7 @@
       </x:c>
       <x:c r="C173" s="4" t="inlineStr">
         <x:is>
-          <x:t>1744819</x:t>
+          <x:t>1745855</x:t>
         </x:is>
       </x:c>
       <x:c r="D173" s="4">
@@ -20525,7 +20525,7 @@
       </x:c>
       <x:c r="H173" s="1" t="inlineStr">
         <x:is>
-          <x:t>Removed</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I173" s="1" t="inlineStr">
@@ -20549,11 +20549,11 @@
         </x:is>
       </x:c>
       <x:c r="M173" s="3" t="n">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="N173" s="1" t="inlineStr">
         <x:is>
-          <x:t>No</x:t>
+          <x:t>Yes</x:t>
         </x:is>
       </x:c>
       <x:c r="O173" s="2" t="n">
@@ -20561,29 +20561,29 @@
       </x:c>
       <x:c r="P173" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q173" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R173" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S173" s="2">
-        <x:v/>
+          <x:t>On time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q173" s="2" t="n">
+        <x:v>46014.4405671296</x:v>
+      </x:c>
+      <x:c r="R173" s="2" t="n">
+        <x:v>46014.4606481481</x:v>
+      </x:c>
+      <x:c r="S173" s="2" t="n">
+        <x:v>46014.4952314815</x:v>
       </x:c>
       <x:c r="T173" s="3">
         <x:v/>
       </x:c>
       <x:c r="U173" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>29</x:t>
         </x:is>
       </x:c>
       <x:c r="V173" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>50</x:t>
         </x:is>
       </x:c>
       <x:c r="W173" s="1">
@@ -20594,16 +20594,16 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y173" s="1" t="inlineStr">
-        <x:is>
-          <x:t>Good(s)Factory</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Z173" s="2" t="n">
-        <x:v>46003.433587963</x:v>
-      </x:c>
-      <x:c r="AA173" s="1">
-        <x:v/>
+      <x:c r="Y173" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z173" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA173" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001412549  64</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -22943,7 +22943,7 @@
       </x:c>
       <x:c r="C194" s="4" t="inlineStr">
         <x:is>
-          <x:t>1752649</x:t>
+          <x:t>1755781</x:t>
         </x:is>
       </x:c>
       <x:c r="D194" s="4">
@@ -22951,7 +22951,7 @@
       </x:c>
       <x:c r="E194" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002681427</x:t>
+          <x:t>4002699451</x:t>
         </x:is>
       </x:c>
       <x:c r="F194" s="1" t="inlineStr">
@@ -22961,7 +22961,7 @@
       </x:c>
       <x:c r="G194" s="1" t="inlineStr">
         <x:is>
-          <x:t>-</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H194" s="1" t="inlineStr">
@@ -22971,17 +22971,17 @@
       </x:c>
       <x:c r="I194" s="1" t="inlineStr">
         <x:is>
-          <x:t>9003</x:t>
+          <x:t>9005</x:t>
         </x:is>
       </x:c>
       <x:c r="J194" s="1" t="inlineStr">
         <x:is>
-          <x:t>Moissy</x:t>
+          <x:t>Labastide</x:t>
         </x:is>
       </x:c>
       <x:c r="K194" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9003-1A</x:t>
+          <x:t>DCZONE-9005-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L194" s="1" t="inlineStr">
@@ -23002,31 +23002,29 @@
       </x:c>
       <x:c r="P194" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q194" s="2" t="n">
-        <x:v>46021.6287615741</x:v>
+        <x:v>46020.5547106481</x:v>
       </x:c>
       <x:c r="R194" s="2" t="n">
-        <x:v>46021.6305902778</x:v>
+        <x:v>46020.554837963</x:v>
       </x:c>
       <x:c r="S194" s="2" t="n">
-        <x:v>46021.6492708333</x:v>
-      </x:c>
-      <x:c r="T194" s="3" t="inlineStr">
-        <x:is>
-          <x:t>5</x:t>
-        </x:is>
+        <x:v>46020.6032523148</x:v>
+      </x:c>
+      <x:c r="T194" s="3">
+        <x:v/>
       </x:c>
       <x:c r="U194" s="3" t="inlineStr">
         <x:is>
-          <x:t>3</x:t>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="V194" s="3" t="inlineStr">
         <x:is>
-          <x:t>26</x:t>
+          <x:t>70</x:t>
         </x:is>
       </x:c>
       <x:c r="W194" s="1">
@@ -23060,7 +23058,7 @@
       </x:c>
       <x:c r="C195" s="4" t="inlineStr">
         <x:is>
-          <x:t>1755781</x:t>
+          <x:t>1752649</x:t>
         </x:is>
       </x:c>
       <x:c r="D195" s="4">
@@ -23068,7 +23066,7 @@
       </x:c>
       <x:c r="E195" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002699451</x:t>
+          <x:t>4002681427</x:t>
         </x:is>
       </x:c>
       <x:c r="F195" s="1" t="inlineStr">
@@ -23078,7 +23076,7 @@
       </x:c>
       <x:c r="G195" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>-</x:t>
         </x:is>
       </x:c>
       <x:c r="H195" s="1" t="inlineStr">
@@ -23088,17 +23086,17 @@
       </x:c>
       <x:c r="I195" s="1" t="inlineStr">
         <x:is>
-          <x:t>9005</x:t>
+          <x:t>9003</x:t>
         </x:is>
       </x:c>
       <x:c r="J195" s="1" t="inlineStr">
         <x:is>
-          <x:t>Labastide</x:t>
+          <x:t>Moissy</x:t>
         </x:is>
       </x:c>
       <x:c r="K195" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9005-1A</x:t>
+          <x:t>DCZONE-9003-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L195" s="1" t="inlineStr">
@@ -23119,29 +23117,31 @@
       </x:c>
       <x:c r="P195" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q195" s="2" t="n">
-        <x:v>46020.5547106481</x:v>
+        <x:v>46021.6287615741</x:v>
       </x:c>
       <x:c r="R195" s="2" t="n">
-        <x:v>46020.554837963</x:v>
+        <x:v>46021.6305902778</x:v>
       </x:c>
       <x:c r="S195" s="2" t="n">
-        <x:v>46020.6032523148</x:v>
-      </x:c>
-      <x:c r="T195" s="3">
-        <x:v/>
+        <x:v>46021.6492708333</x:v>
+      </x:c>
+      <x:c r="T195" s="3" t="inlineStr">
+        <x:is>
+          <x:t>5</x:t>
+        </x:is>
       </x:c>
       <x:c r="U195" s="3" t="inlineStr">
         <x:is>
-          <x:t>0</x:t>
+          <x:t>3</x:t>
         </x:is>
       </x:c>
       <x:c r="V195" s="3" t="inlineStr">
         <x:is>
-          <x:t>70</x:t>
+          <x:t>26</x:t>
         </x:is>
       </x:c>
       <x:c r="W195" s="1">
@@ -26433,27 +26433,25 @@
     <x:row r="224">
       <x:c r="A224" s="1" t="inlineStr">
         <x:is>
-          <x:t>50135</x:t>
+          <x:t>1001634</x:t>
         </x:is>
       </x:c>
       <x:c r="B224" s="1" t="inlineStr">
         <x:is>
-          <x:t>DSV Road sp. z o.o.</x:t>
+          <x:t>Good(s)Factory</x:t>
         </x:is>
       </x:c>
       <x:c r="C224" s="4" t="inlineStr">
         <x:is>
-          <x:t>1770572</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D224" s="4" t="inlineStr">
-        <x:is>
-          <x:t>000002838841</x:t>
-        </x:is>
+          <x:t>1768060</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D224" s="4">
+        <x:v/>
       </x:c>
       <x:c r="E224" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002747727</x:t>
+          <x:t>4002754682</x:t>
         </x:is>
       </x:c>
       <x:c r="F224" s="1" t="inlineStr">
@@ -26463,27 +26461,27 @@
       </x:c>
       <x:c r="G224" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>-</x:t>
         </x:is>
       </x:c>
       <x:c r="H224" s="1" t="inlineStr">
         <x:is>
-          <x:t>Removed</x:t>
+          <x:t>NoShow</x:t>
         </x:is>
       </x:c>
       <x:c r="I224" s="1" t="inlineStr">
         <x:is>
-          <x:t>8994</x:t>
+          <x:t>9002</x:t>
         </x:is>
       </x:c>
       <x:c r="J224" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zakroczym</x:t>
+          <x:t>Echt</x:t>
         </x:is>
       </x:c>
       <x:c r="K224" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8994-1A</x:t>
+          <x:t>DCZONE-9002-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L224" s="1" t="inlineStr">
@@ -26492,7 +26490,7 @@
         </x:is>
       </x:c>
       <x:c r="M224" s="3" t="n">
-        <x:v>24</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="N224" s="1" t="inlineStr">
         <x:is>
@@ -26539,38 +26537,42 @@
       </x:c>
       <x:c r="Y224" s="1" t="inlineStr">
         <x:is>
-          <x:t>DSV Road sp. z o.o.</x:t>
+          <x:t>Echt</x:t>
         </x:is>
       </x:c>
       <x:c r="Z224" s="2" t="n">
-        <x:v>46031.4469328704</x:v>
-      </x:c>
-      <x:c r="AA224" s="1">
-        <x:v/>
+        <x:v>46034.4704398148</x:v>
+      </x:c>
+      <x:c r="AA224" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001424635 -63</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="1" t="inlineStr">
         <x:is>
-          <x:t>1001634</x:t>
+          <x:t>50135</x:t>
         </x:is>
       </x:c>
       <x:c r="B225" s="1" t="inlineStr">
         <x:is>
-          <x:t>Good(s)Factory</x:t>
+          <x:t>DSV Road sp. z o.o.</x:t>
         </x:is>
       </x:c>
       <x:c r="C225" s="4" t="inlineStr">
         <x:is>
-          <x:t>1768060</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D225" s="4">
-        <x:v/>
+          <x:t>1770572</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D225" s="4" t="inlineStr">
+        <x:is>
+          <x:t>000002838841</x:t>
+        </x:is>
       </x:c>
       <x:c r="E225" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002754682</x:t>
+          <x:t>4002747727</x:t>
         </x:is>
       </x:c>
       <x:c r="F225" s="1" t="inlineStr">
@@ -26580,27 +26582,27 @@
       </x:c>
       <x:c r="G225" s="1" t="inlineStr">
         <x:is>
-          <x:t>-</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H225" s="1" t="inlineStr">
         <x:is>
-          <x:t>NoShow</x:t>
+          <x:t>Removed</x:t>
         </x:is>
       </x:c>
       <x:c r="I225" s="1" t="inlineStr">
         <x:is>
-          <x:t>9002</x:t>
+          <x:t>8994</x:t>
         </x:is>
       </x:c>
       <x:c r="J225" s="1" t="inlineStr">
         <x:is>
-          <x:t>Echt</x:t>
+          <x:t>Zakroczym</x:t>
         </x:is>
       </x:c>
       <x:c r="K225" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9002-1A</x:t>
+          <x:t>DCZONE-8994-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L225" s="1" t="inlineStr">
@@ -26609,7 +26611,7 @@
         </x:is>
       </x:c>
       <x:c r="M225" s="3" t="n">
-        <x:v>33</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="N225" s="1" t="inlineStr">
         <x:is>
@@ -26656,16 +26658,14 @@
       </x:c>
       <x:c r="Y225" s="1" t="inlineStr">
         <x:is>
-          <x:t>Echt</x:t>
+          <x:t>DSV Road sp. z o.o.</x:t>
         </x:is>
       </x:c>
       <x:c r="Z225" s="2" t="n">
-        <x:v>46034.4704398148</x:v>
-      </x:c>
-      <x:c r="AA225" s="1" t="inlineStr">
-        <x:is>
-          <x:t>5001424635 -63</x:t>
-        </x:is>
+        <x:v>46031.4469328704</x:v>
+      </x:c>
+      <x:c r="AA225" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="226">
@@ -32168,7 +32168,7 @@
       </x:c>
       <x:c r="C273" s="4" t="inlineStr">
         <x:is>
-          <x:t>1767104</x:t>
+          <x:t>1770353</x:t>
         </x:is>
       </x:c>
       <x:c r="D273" s="4">
@@ -32176,7 +32176,7 @@
       </x:c>
       <x:c r="E273" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002752986</x:t>
+          <x:t>4002679356</x:t>
         </x:is>
       </x:c>
       <x:c r="F273" s="1" t="inlineStr">
@@ -32186,7 +32186,7 @@
       </x:c>
       <x:c r="G273" s="1" t="inlineStr">
         <x:is>
-          <x:t>Gold Allocation</x:t>
+          <x:t>-</x:t>
         </x:is>
       </x:c>
       <x:c r="H273" s="1" t="inlineStr">
@@ -32196,17 +32196,17 @@
       </x:c>
       <x:c r="I273" s="1" t="inlineStr">
         <x:is>
-          <x:t>9002</x:t>
+          <x:t>9003</x:t>
         </x:is>
       </x:c>
       <x:c r="J273" s="1" t="inlineStr">
         <x:is>
-          <x:t>Echt</x:t>
+          <x:t>Moissy</x:t>
         </x:is>
       </x:c>
       <x:c r="K273" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9002-1A</x:t>
+          <x:t>DCZONE-9003-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L273" s="1" t="inlineStr">
@@ -32231,25 +32231,25 @@
         </x:is>
       </x:c>
       <x:c r="Q273" s="2" t="n">
-        <x:v>46037.3873842593</x:v>
+        <x:v>46037.3645833333</x:v>
       </x:c>
       <x:c r="R273" s="2" t="n">
-        <x:v>46037.4323958333</x:v>
+        <x:v>46037.4112152778</x:v>
       </x:c>
       <x:c r="S273" s="2" t="n">
-        <x:v>46037.4506712963</x:v>
+        <x:v>46037.4644212963</x:v>
       </x:c>
       <x:c r="T273" s="3">
         <x:v/>
       </x:c>
       <x:c r="U273" s="3" t="inlineStr">
         <x:is>
-          <x:t>65</x:t>
+          <x:t>67</x:t>
         </x:is>
       </x:c>
       <x:c r="V273" s="3" t="inlineStr">
         <x:is>
-          <x:t>26</x:t>
+          <x:t>76</x:t>
         </x:is>
       </x:c>
       <x:c r="W273" s="1">
@@ -32266,10 +32266,8 @@
       <x:c r="Z273" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA273" s="1" t="inlineStr">
-        <x:is>
-          <x:t>5001428869 -63</x:t>
-        </x:is>
+      <x:c r="AA273" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="274">
@@ -32285,7 +32283,7 @@
       </x:c>
       <x:c r="C274" s="4" t="inlineStr">
         <x:is>
-          <x:t>1770353</x:t>
+          <x:t>1767104</x:t>
         </x:is>
       </x:c>
       <x:c r="D274" s="4">
@@ -32293,7 +32291,7 @@
       </x:c>
       <x:c r="E274" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679356</x:t>
+          <x:t>4002752986</x:t>
         </x:is>
       </x:c>
       <x:c r="F274" s="1" t="inlineStr">
@@ -32303,7 +32301,7 @@
       </x:c>
       <x:c r="G274" s="1" t="inlineStr">
         <x:is>
-          <x:t>-</x:t>
+          <x:t>Gold Allocation</x:t>
         </x:is>
       </x:c>
       <x:c r="H274" s="1" t="inlineStr">
@@ -32313,17 +32311,17 @@
       </x:c>
       <x:c r="I274" s="1" t="inlineStr">
         <x:is>
-          <x:t>9003</x:t>
+          <x:t>9002</x:t>
         </x:is>
       </x:c>
       <x:c r="J274" s="1" t="inlineStr">
         <x:is>
-          <x:t>Moissy</x:t>
+          <x:t>Echt</x:t>
         </x:is>
       </x:c>
       <x:c r="K274" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9003-1A</x:t>
+          <x:t>DCZONE-9002-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L274" s="1" t="inlineStr">
@@ -32348,25 +32346,25 @@
         </x:is>
       </x:c>
       <x:c r="Q274" s="2" t="n">
-        <x:v>46037.3645833333</x:v>
+        <x:v>46037.3873842593</x:v>
       </x:c>
       <x:c r="R274" s="2" t="n">
-        <x:v>46037.4112152778</x:v>
+        <x:v>46037.4323958333</x:v>
       </x:c>
       <x:c r="S274" s="2" t="n">
-        <x:v>46037.4644212963</x:v>
+        <x:v>46037.4506712963</x:v>
       </x:c>
       <x:c r="T274" s="3">
         <x:v/>
       </x:c>
       <x:c r="U274" s="3" t="inlineStr">
         <x:is>
-          <x:t>67</x:t>
+          <x:t>65</x:t>
         </x:is>
       </x:c>
       <x:c r="V274" s="3" t="inlineStr">
         <x:is>
-          <x:t>76</x:t>
+          <x:t>26</x:t>
         </x:is>
       </x:c>
       <x:c r="W274" s="1">
@@ -32383,8 +32381,10 @@
       <x:c r="Z274" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA274" s="1">
-        <x:v/>
+      <x:c r="AA274" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001428869 -63</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="275">
@@ -32519,7 +32519,7 @@
       </x:c>
       <x:c r="C276" s="4" t="inlineStr">
         <x:is>
-          <x:t>1767127</x:t>
+          <x:t>1773140</x:t>
         </x:is>
       </x:c>
       <x:c r="D276" s="4">
@@ -32527,7 +32527,7 @@
       </x:c>
       <x:c r="E276" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002752996</x:t>
+          <x:t>4002679354</x:t>
         </x:is>
       </x:c>
       <x:c r="F276" s="1" t="inlineStr">
@@ -32537,27 +32537,27 @@
       </x:c>
       <x:c r="G276" s="1" t="inlineStr">
         <x:is>
-          <x:t>Gold Allocation</x:t>
+          <x:t>-</x:t>
         </x:is>
       </x:c>
       <x:c r="H276" s="1" t="inlineStr">
         <x:is>
-          <x:t>Removed</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I276" s="1" t="inlineStr">
         <x:is>
-          <x:t>8998</x:t>
+          <x:t>9003</x:t>
         </x:is>
       </x:c>
       <x:c r="J276" s="1" t="inlineStr">
         <x:is>
-          <x:t>Bratislava</x:t>
+          <x:t>Moissy</x:t>
         </x:is>
       </x:c>
       <x:c r="K276" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8998-1A</x:t>
+          <x:t>DCZONE-9003-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L276" s="1" t="inlineStr">
@@ -32570,7 +32570,7 @@
       </x:c>
       <x:c r="N276" s="1" t="inlineStr">
         <x:is>
-          <x:t>No</x:t>
+          <x:t>Yes</x:t>
         </x:is>
       </x:c>
       <x:c r="O276" s="2" t="n">
@@ -32578,29 +32578,29 @@
       </x:c>
       <x:c r="P276" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q276" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R276" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S276" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q276" s="2" t="n">
+        <x:v>46037.3668287037</x:v>
+      </x:c>
+      <x:c r="R276" s="2" t="n">
+        <x:v>46037.47625</x:v>
+      </x:c>
+      <x:c r="S276" s="2" t="n">
+        <x:v>46037.5132060185</x:v>
       </x:c>
       <x:c r="T276" s="3">
         <x:v/>
       </x:c>
       <x:c r="U276" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>157</x:t>
         </x:is>
       </x:c>
       <x:c r="V276" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>54</x:t>
         </x:is>
       </x:c>
       <x:c r="W276" s="1">
@@ -32611,13 +32611,11 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y276" s="1" t="inlineStr">
-        <x:is>
-          <x:t>Good(s)Factory</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Z276" s="2" t="n">
-        <x:v>46035.729375</x:v>
+      <x:c r="Y276" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z276" s="2">
+        <x:v/>
       </x:c>
       <x:c r="AA276" s="1">
         <x:v/>
@@ -32636,7 +32634,7 @@
       </x:c>
       <x:c r="C277" s="4" t="inlineStr">
         <x:is>
-          <x:t>1773140</x:t>
+          <x:t>1767127</x:t>
         </x:is>
       </x:c>
       <x:c r="D277" s="4">
@@ -32644,7 +32642,7 @@
       </x:c>
       <x:c r="E277" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002679354</x:t>
+          <x:t>4002752996</x:t>
         </x:is>
       </x:c>
       <x:c r="F277" s="1" t="inlineStr">
@@ -32654,27 +32652,27 @@
       </x:c>
       <x:c r="G277" s="1" t="inlineStr">
         <x:is>
-          <x:t>-</x:t>
+          <x:t>Gold Allocation</x:t>
         </x:is>
       </x:c>
       <x:c r="H277" s="1" t="inlineStr">
         <x:is>
-          <x:t>Finished</x:t>
+          <x:t>Removed</x:t>
         </x:is>
       </x:c>
       <x:c r="I277" s="1" t="inlineStr">
         <x:is>
-          <x:t>9003</x:t>
+          <x:t>8998</x:t>
         </x:is>
       </x:c>
       <x:c r="J277" s="1" t="inlineStr">
         <x:is>
-          <x:t>Moissy</x:t>
+          <x:t>Bratislava</x:t>
         </x:is>
       </x:c>
       <x:c r="K277" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9003-1A</x:t>
+          <x:t>DCZONE-8998-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L277" s="1" t="inlineStr">
@@ -32687,7 +32685,7 @@
       </x:c>
       <x:c r="N277" s="1" t="inlineStr">
         <x:is>
-          <x:t>Yes</x:t>
+          <x:t>No</x:t>
         </x:is>
       </x:c>
       <x:c r="O277" s="2" t="n">
@@ -32695,29 +32693,29 @@
       </x:c>
       <x:c r="P277" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q277" s="2" t="n">
-        <x:v>46037.3668287037</x:v>
-      </x:c>
-      <x:c r="R277" s="2" t="n">
-        <x:v>46037.47625</x:v>
-      </x:c>
-      <x:c r="S277" s="2" t="n">
-        <x:v>46037.5132060185</x:v>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q277" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R277" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S277" s="2">
+        <x:v/>
       </x:c>
       <x:c r="T277" s="3">
         <x:v/>
       </x:c>
       <x:c r="U277" s="3" t="inlineStr">
         <x:is>
-          <x:t>157</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="V277" s="3" t="inlineStr">
         <x:is>
-          <x:t>54</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="W277" s="1">
@@ -32728,11 +32726,13 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y277" s="1">
-        <x:v/>
-      </x:c>
-      <x:c r="Z277" s="2">
-        <x:v/>
+      <x:c r="Y277" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z277" s="2" t="n">
+        <x:v>46035.729375</x:v>
       </x:c>
       <x:c r="AA277" s="1">
         <x:v/>
@@ -41714,7 +41714,7 @@
       </x:c>
       <x:c r="C355" s="4" t="inlineStr">
         <x:is>
-          <x:t>1782168</x:t>
+          <x:t>1781915</x:t>
         </x:is>
       </x:c>
       <x:c r="D355" s="4">
@@ -41722,7 +41722,7 @@
       </x:c>
       <x:c r="E355" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002769961</x:t>
+          <x:t>4002769969</x:t>
         </x:is>
       </x:c>
       <x:c r="F355" s="1" t="inlineStr">
@@ -41742,17 +41742,17 @@
       </x:c>
       <x:c r="I355" s="1" t="inlineStr">
         <x:is>
-          <x:t>9006</x:t>
+          <x:t>8994</x:t>
         </x:is>
       </x:c>
       <x:c r="J355" s="1" t="inlineStr">
         <x:is>
-          <x:t>Belleville</x:t>
+          <x:t>Zakroczym</x:t>
         </x:is>
       </x:c>
       <x:c r="K355" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9006-1A</x:t>
+          <x:t>DCZONE-8994-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L355" s="1" t="inlineStr">
@@ -41773,29 +41773,31 @@
       </x:c>
       <x:c r="P355" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Late</x:t>
         </x:is>
       </x:c>
       <x:c r="Q355" s="2" t="n">
-        <x:v>46051.2825</x:v>
+        <x:v>46051.5412384259</x:v>
       </x:c>
       <x:c r="R355" s="2" t="n">
-        <x:v>46051.303287037</x:v>
+        <x:v>46051.6163888889</x:v>
       </x:c>
       <x:c r="S355" s="2" t="n">
-        <x:v>46051.3335532407</x:v>
-      </x:c>
-      <x:c r="T355" s="3">
-        <x:v/>
+        <x:v>46051.6258449074</x:v>
+      </x:c>
+      <x:c r="T355" s="3" t="inlineStr">
+        <x:is>
+          <x:t>359</x:t>
+        </x:is>
       </x:c>
       <x:c r="U355" s="3" t="inlineStr">
         <x:is>
-          <x:t>30</x:t>
+          <x:t>108</x:t>
         </x:is>
       </x:c>
       <x:c r="V355" s="3" t="inlineStr">
         <x:is>
-          <x:t>44</x:t>
+          <x:t>14</x:t>
         </x:is>
       </x:c>
       <x:c r="W355" s="1">
@@ -41812,8 +41814,10 @@
       <x:c r="Z355" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA355" s="1">
-        <x:v/>
+      <x:c r="AA355" s="1" t="inlineStr">
+        <x:is>
+          <x:t>666048051</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="356">
@@ -41829,7 +41833,7 @@
       </x:c>
       <x:c r="C356" s="4" t="inlineStr">
         <x:is>
-          <x:t>1781915</x:t>
+          <x:t>1782180</x:t>
         </x:is>
       </x:c>
       <x:c r="D356" s="4">
@@ -41837,7 +41841,7 @@
       </x:c>
       <x:c r="E356" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002769969</x:t>
+          <x:t>4002769963</x:t>
         </x:is>
       </x:c>
       <x:c r="F356" s="1" t="inlineStr">
@@ -41852,22 +41856,22 @@
       </x:c>
       <x:c r="H356" s="1" t="inlineStr">
         <x:is>
-          <x:t>Finished</x:t>
+          <x:t>NoShow</x:t>
         </x:is>
       </x:c>
       <x:c r="I356" s="1" t="inlineStr">
         <x:is>
-          <x:t>8994</x:t>
+          <x:t>9007</x:t>
         </x:is>
       </x:c>
       <x:c r="J356" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zakroczym</x:t>
+          <x:t>Peine</x:t>
         </x:is>
       </x:c>
       <x:c r="K356" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8994-1A</x:t>
+          <x:t>DCZONE-9007-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L356" s="1" t="inlineStr">
@@ -41880,7 +41884,7 @@
       </x:c>
       <x:c r="N356" s="1" t="inlineStr">
         <x:is>
-          <x:t>Yes</x:t>
+          <x:t>No</x:t>
         </x:is>
       </x:c>
       <x:c r="O356" s="2" t="n">
@@ -41888,31 +41892,29 @@
       </x:c>
       <x:c r="P356" s="1" t="inlineStr">
         <x:is>
-          <x:t>Late</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q356" s="2" t="n">
-        <x:v>46051.5412384259</x:v>
-      </x:c>
-      <x:c r="R356" s="2" t="n">
-        <x:v>46051.6163888889</x:v>
-      </x:c>
-      <x:c r="S356" s="2" t="n">
-        <x:v>46051.6258449074</x:v>
-      </x:c>
-      <x:c r="T356" s="3" t="inlineStr">
-        <x:is>
-          <x:t>359</x:t>
-        </x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q356" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R356" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S356" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T356" s="3">
+        <x:v/>
       </x:c>
       <x:c r="U356" s="3" t="inlineStr">
         <x:is>
-          <x:t>108</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="V356" s="3" t="inlineStr">
         <x:is>
-          <x:t>14</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="W356" s="1">
@@ -41923,16 +41925,16 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y356" s="1">
-        <x:v/>
-      </x:c>
-      <x:c r="Z356" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="AA356" s="1" t="inlineStr">
-        <x:is>
-          <x:t>666048051</x:t>
-        </x:is>
+      <x:c r="Y356" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z356" s="2" t="n">
+        <x:v>46051.497337963</x:v>
+      </x:c>
+      <x:c r="AA356" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="357">
@@ -41948,7 +41950,7 @@
       </x:c>
       <x:c r="C357" s="4" t="inlineStr">
         <x:is>
-          <x:t>1782180</x:t>
+          <x:t>1781886</x:t>
         </x:is>
       </x:c>
       <x:c r="D357" s="4">
@@ -41956,7 +41958,7 @@
       </x:c>
       <x:c r="E357" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002769963</x:t>
+          <x:t>4002769973</x:t>
         </x:is>
       </x:c>
       <x:c r="F357" s="1" t="inlineStr">
@@ -41971,22 +41973,22 @@
       </x:c>
       <x:c r="H357" s="1" t="inlineStr">
         <x:is>
-          <x:t>NoShow</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I357" s="1" t="inlineStr">
         <x:is>
-          <x:t>9007</x:t>
+          <x:t>8991</x:t>
         </x:is>
       </x:c>
       <x:c r="J357" s="1" t="inlineStr">
         <x:is>
-          <x:t>Peine</x:t>
+          <x:t>Altedo</x:t>
         </x:is>
       </x:c>
       <x:c r="K357" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9007-1A</x:t>
+          <x:t>DCZONE-8991-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L357" s="1" t="inlineStr">
@@ -41999,7 +42001,7 @@
       </x:c>
       <x:c r="N357" s="1" t="inlineStr">
         <x:is>
-          <x:t>No</x:t>
+          <x:t>Yes</x:t>
         </x:is>
       </x:c>
       <x:c r="O357" s="2" t="n">
@@ -42007,29 +42009,29 @@
       </x:c>
       <x:c r="P357" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q357" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R357" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S357" s="2">
-        <x:v/>
+          <x:t>On time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q357" s="2" t="n">
+        <x:v>46051.2874421296</x:v>
+      </x:c>
+      <x:c r="R357" s="2" t="n">
+        <x:v>46051.2879398148</x:v>
+      </x:c>
+      <x:c r="S357" s="2" t="n">
+        <x:v>46051.3311574074</x:v>
       </x:c>
       <x:c r="T357" s="3">
         <x:v/>
       </x:c>
       <x:c r="U357" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>1</x:t>
         </x:is>
       </x:c>
       <x:c r="V357" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>62</x:t>
         </x:is>
       </x:c>
       <x:c r="W357" s="1">
@@ -42040,13 +42042,11 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y357" s="1" t="inlineStr">
-        <x:is>
-          <x:t>Good(s)Factory</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Z357" s="2" t="n">
-        <x:v>46051.497337963</x:v>
+      <x:c r="Y357" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z357" s="2">
+        <x:v/>
       </x:c>
       <x:c r="AA357" s="1">
         <x:v/>
@@ -42065,7 +42065,7 @@
       </x:c>
       <x:c r="C358" s="4" t="inlineStr">
         <x:is>
-          <x:t>1781886</x:t>
+          <x:t>1782168</x:t>
         </x:is>
       </x:c>
       <x:c r="D358" s="4">
@@ -42073,7 +42073,7 @@
       </x:c>
       <x:c r="E358" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002769973</x:t>
+          <x:t>4002769961</x:t>
         </x:is>
       </x:c>
       <x:c r="F358" s="1" t="inlineStr">
@@ -42093,17 +42093,17 @@
       </x:c>
       <x:c r="I358" s="1" t="inlineStr">
         <x:is>
-          <x:t>8991</x:t>
+          <x:t>9006</x:t>
         </x:is>
       </x:c>
       <x:c r="J358" s="1" t="inlineStr">
         <x:is>
-          <x:t>Altedo</x:t>
+          <x:t>Belleville</x:t>
         </x:is>
       </x:c>
       <x:c r="K358" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8991-1A</x:t>
+          <x:t>DCZONE-9006-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L358" s="1" t="inlineStr">
@@ -42128,25 +42128,25 @@
         </x:is>
       </x:c>
       <x:c r="Q358" s="2" t="n">
-        <x:v>46051.2874421296</x:v>
+        <x:v>46051.2825</x:v>
       </x:c>
       <x:c r="R358" s="2" t="n">
-        <x:v>46051.2879398148</x:v>
+        <x:v>46051.303287037</x:v>
       </x:c>
       <x:c r="S358" s="2" t="n">
-        <x:v>46051.3311574074</x:v>
+        <x:v>46051.3335532407</x:v>
       </x:c>
       <x:c r="T358" s="3">
         <x:v/>
       </x:c>
       <x:c r="U358" s="3" t="inlineStr">
         <x:is>
-          <x:t>1</x:t>
+          <x:t>30</x:t>
         </x:is>
       </x:c>
       <x:c r="V358" s="3" t="inlineStr">
         <x:is>
-          <x:t>62</x:t>
+          <x:t>44</x:t>
         </x:is>
       </x:c>
       <x:c r="W358" s="1">
@@ -42642,7 +42642,7 @@
       </x:c>
       <x:c r="C363" s="4" t="inlineStr">
         <x:is>
-          <x:t>1786477</x:t>
+          <x:t>1782163</x:t>
         </x:is>
       </x:c>
       <x:c r="D363" s="4">
@@ -42650,7 +42650,7 @@
       </x:c>
       <x:c r="E363" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002774912</x:t>
+          <x:t>4002769956</x:t>
         </x:is>
       </x:c>
       <x:c r="F363" s="1" t="inlineStr">
@@ -42660,7 +42660,7 @@
       </x:c>
       <x:c r="G363" s="1" t="inlineStr">
         <x:is>
-          <x:t>Gold Allocation</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H363" s="1" t="inlineStr">
@@ -42670,17 +42670,17 @@
       </x:c>
       <x:c r="I363" s="1" t="inlineStr">
         <x:is>
-          <x:t>9002</x:t>
+          <x:t>9003</x:t>
         </x:is>
       </x:c>
       <x:c r="J363" s="1" t="inlineStr">
         <x:is>
-          <x:t>Echt</x:t>
+          <x:t>Moissy</x:t>
         </x:is>
       </x:c>
       <x:c r="K363" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9002-1A</x:t>
+          <x:t>DCZONE-9003-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L363" s="1" t="inlineStr">
@@ -42705,33 +42705,33 @@
         </x:is>
       </x:c>
       <x:c r="Q363" s="2" t="n">
-        <x:v>46051.3790393519</x:v>
+        <x:v>46051.3745949074</x:v>
       </x:c>
       <x:c r="R363" s="2" t="n">
-        <x:v>46051.3791203704</x:v>
+        <x:v>46051.4626157407</x:v>
       </x:c>
       <x:c r="S363" s="2" t="n">
-        <x:v>46051.4180787037</x:v>
+        <x:v>46051.4629050926</x:v>
       </x:c>
       <x:c r="T363" s="3">
         <x:v/>
       </x:c>
       <x:c r="U363" s="3" t="inlineStr">
         <x:is>
+          <x:t>127</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="V363" s="3" t="inlineStr">
+        <x:is>
           <x:t>0</x:t>
         </x:is>
       </x:c>
-      <x:c r="V363" s="3" t="inlineStr">
-        <x:is>
-          <x:t>57</x:t>
-        </x:is>
-      </x:c>
       <x:c r="W363" s="1">
         <x:v/>
       </x:c>
       <x:c r="X363" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>Logistic quality: pallets are too high</x:t>
         </x:is>
       </x:c>
       <x:c r="Y363" s="1">
@@ -42740,10 +42740,8 @@
       <x:c r="Z363" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA363" s="1" t="inlineStr">
-        <x:is>
-          <x:t>5001442489 -63</x:t>
-        </x:is>
+      <x:c r="AA363" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="364">
@@ -42759,7 +42757,7 @@
       </x:c>
       <x:c r="C364" s="4" t="inlineStr">
         <x:is>
-          <x:t>1782163</x:t>
+          <x:t>1786477</x:t>
         </x:is>
       </x:c>
       <x:c r="D364" s="4">
@@ -42767,7 +42765,7 @@
       </x:c>
       <x:c r="E364" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002769956</x:t>
+          <x:t>4002774912</x:t>
         </x:is>
       </x:c>
       <x:c r="F364" s="1" t="inlineStr">
@@ -42777,7 +42775,7 @@
       </x:c>
       <x:c r="G364" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>Gold Allocation</x:t>
         </x:is>
       </x:c>
       <x:c r="H364" s="1" t="inlineStr">
@@ -42787,17 +42785,17 @@
       </x:c>
       <x:c r="I364" s="1" t="inlineStr">
         <x:is>
-          <x:t>9003</x:t>
+          <x:t>9002</x:t>
         </x:is>
       </x:c>
       <x:c r="J364" s="1" t="inlineStr">
         <x:is>
-          <x:t>Moissy</x:t>
+          <x:t>Echt</x:t>
         </x:is>
       </x:c>
       <x:c r="K364" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9003-1A</x:t>
+          <x:t>DCZONE-9002-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L364" s="1" t="inlineStr">
@@ -42822,25 +42820,25 @@
         </x:is>
       </x:c>
       <x:c r="Q364" s="2" t="n">
-        <x:v>46051.3745949074</x:v>
+        <x:v>46051.3790393519</x:v>
       </x:c>
       <x:c r="R364" s="2" t="n">
-        <x:v>46051.4626157407</x:v>
+        <x:v>46051.3791203704</x:v>
       </x:c>
       <x:c r="S364" s="2" t="n">
-        <x:v>46051.4629050926</x:v>
+        <x:v>46051.4180787037</x:v>
       </x:c>
       <x:c r="T364" s="3">
         <x:v/>
       </x:c>
       <x:c r="U364" s="3" t="inlineStr">
         <x:is>
-          <x:t>127</x:t>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="V364" s="3" t="inlineStr">
         <x:is>
-          <x:t>0</x:t>
+          <x:t>57</x:t>
         </x:is>
       </x:c>
       <x:c r="W364" s="1">
@@ -42848,7 +42846,7 @@
       </x:c>
       <x:c r="X364" s="1" t="inlineStr">
         <x:is>
-          <x:t>Logistic quality: pallets are too high</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="Y364" s="1">
@@ -42857,8 +42855,10 @@
       <x:c r="Z364" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA364" s="1">
-        <x:v/>
+      <x:c r="AA364" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001442489 -63</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="365">
@@ -49953,7 +49953,7 @@
       </x:c>
       <x:c r="C426" s="4" t="inlineStr">
         <x:is>
-          <x:t>1800500</x:t>
+          <x:t>1801291</x:t>
         </x:is>
       </x:c>
       <x:c r="D426" s="4">
@@ -49961,7 +49961,7 @@
       </x:c>
       <x:c r="E426" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002786680</x:t>
+          <x:t>4002786690</x:t>
         </x:is>
       </x:c>
       <x:c r="F426" s="1" t="inlineStr">
@@ -49981,17 +49981,17 @@
       </x:c>
       <x:c r="I426" s="1" t="inlineStr">
         <x:is>
-          <x:t>8993</x:t>
+          <x:t>9007</x:t>
         </x:is>
       </x:c>
       <x:c r="J426" s="1" t="inlineStr">
         <x:is>
-          <x:t>Novara</x:t>
+          <x:t>Peine</x:t>
         </x:is>
       </x:c>
       <x:c r="K426" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8993-1A</x:t>
+          <x:t>DCZONE-9007-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L426" s="1" t="inlineStr">
@@ -50012,29 +50012,31 @@
       </x:c>
       <x:c r="P426" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>Late</x:t>
         </x:is>
       </x:c>
       <x:c r="Q426" s="2" t="n">
-        <x:v>46062.3054050926</x:v>
+        <x:v>46063.2839467593</x:v>
       </x:c>
       <x:c r="R426" s="2" t="n">
-        <x:v>46062.4982523148</x:v>
+        <x:v>46063.2849421296</x:v>
       </x:c>
       <x:c r="S426" s="2" t="n">
-        <x:v>46062.5144791667</x:v>
-      </x:c>
-      <x:c r="T426" s="3">
-        <x:v/>
+        <x:v>46063.3022685185</x:v>
+      </x:c>
+      <x:c r="T426" s="3" t="inlineStr">
+        <x:is>
+          <x:t>48</x:t>
+        </x:is>
       </x:c>
       <x:c r="U426" s="3" t="inlineStr">
         <x:is>
-          <x:t>278</x:t>
+          <x:t>2</x:t>
         </x:is>
       </x:c>
       <x:c r="V426" s="3" t="inlineStr">
         <x:is>
-          <x:t>23</x:t>
+          <x:t>25</x:t>
         </x:is>
       </x:c>
       <x:c r="W426" s="1">
@@ -50051,8 +50053,10 @@
       <x:c r="Z426" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA426" s="1">
-        <x:v/>
+      <x:c r="AA426" s="1" t="inlineStr">
+        <x:is>
+          <x:t>von 17 auf 16 bitte</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="427">
@@ -50068,7 +50072,7 @@
       </x:c>
       <x:c r="C427" s="4" t="inlineStr">
         <x:is>
-          <x:t>1801291</x:t>
+          <x:t>1800500</x:t>
         </x:is>
       </x:c>
       <x:c r="D427" s="4">
@@ -50076,7 +50080,7 @@
       </x:c>
       <x:c r="E427" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002786690</x:t>
+          <x:t>4002786680</x:t>
         </x:is>
       </x:c>
       <x:c r="F427" s="1" t="inlineStr">
@@ -50096,17 +50100,17 @@
       </x:c>
       <x:c r="I427" s="1" t="inlineStr">
         <x:is>
-          <x:t>9007</x:t>
+          <x:t>8993</x:t>
         </x:is>
       </x:c>
       <x:c r="J427" s="1" t="inlineStr">
         <x:is>
-          <x:t>Peine</x:t>
+          <x:t>Novara</x:t>
         </x:is>
       </x:c>
       <x:c r="K427" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9007-1A</x:t>
+          <x:t>DCZONE-8993-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L427" s="1" t="inlineStr">
@@ -50127,31 +50131,29 @@
       </x:c>
       <x:c r="P427" s="1" t="inlineStr">
         <x:is>
-          <x:t>Late</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q427" s="2" t="n">
-        <x:v>46063.2839467593</x:v>
+        <x:v>46062.3054050926</x:v>
       </x:c>
       <x:c r="R427" s="2" t="n">
-        <x:v>46063.2849421296</x:v>
+        <x:v>46062.4982523148</x:v>
       </x:c>
       <x:c r="S427" s="2" t="n">
-        <x:v>46063.3022685185</x:v>
-      </x:c>
-      <x:c r="T427" s="3" t="inlineStr">
-        <x:is>
-          <x:t>48</x:t>
-        </x:is>
+        <x:v>46062.5144791667</x:v>
+      </x:c>
+      <x:c r="T427" s="3">
+        <x:v/>
       </x:c>
       <x:c r="U427" s="3" t="inlineStr">
         <x:is>
-          <x:t>2</x:t>
+          <x:t>278</x:t>
         </x:is>
       </x:c>
       <x:c r="V427" s="3" t="inlineStr">
         <x:is>
-          <x:t>25</x:t>
+          <x:t>23</x:t>
         </x:is>
       </x:c>
       <x:c r="W427" s="1">
@@ -50168,10 +50170,8 @@
       <x:c r="Z427" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA427" s="1" t="inlineStr">
-        <x:is>
-          <x:t>von 17 auf 16 bitte</x:t>
-        </x:is>
+      <x:c r="AA427" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="428">
@@ -52160,25 +52160,27 @@
     <x:row r="445">
       <x:c r="A445" s="1" t="inlineStr">
         <x:is>
-          <x:t>1001634</x:t>
+          <x:t>50135</x:t>
         </x:is>
       </x:c>
       <x:c r="B445" s="1" t="inlineStr">
         <x:is>
-          <x:t>Good(s)Factory</x:t>
+          <x:t>DSV Road sp. z o.o.</x:t>
         </x:is>
       </x:c>
       <x:c r="C445" s="4" t="inlineStr">
         <x:is>
-          <x:t>1801301</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D445" s="4">
-        <x:v/>
+          <x:t>1806306</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D445" s="4" t="inlineStr">
+        <x:is>
+          <x:t>000002858764</x:t>
+        </x:is>
       </x:c>
       <x:c r="E445" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002786687</x:t>
+          <x:t>4002783199, 4002784832</x:t>
         </x:is>
       </x:c>
       <x:c r="F445" s="1" t="inlineStr">
@@ -52198,17 +52200,17 @@
       </x:c>
       <x:c r="I445" s="1" t="inlineStr">
         <x:is>
-          <x:t>9004</x:t>
+          <x:t>8996</x:t>
         </x:is>
       </x:c>
       <x:c r="J445" s="1" t="inlineStr">
         <x:is>
-          <x:t>Biblis</x:t>
+          <x:t>Bierun</x:t>
         </x:is>
       </x:c>
       <x:c r="K445" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9004-1A</x:t>
+          <x:t>DCZONE-8996-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L445" s="1" t="inlineStr">
@@ -52217,7 +52219,7 @@
         </x:is>
       </x:c>
       <x:c r="M445" s="3" t="n">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N445" s="1" t="inlineStr">
         <x:is>
@@ -52229,29 +52231,29 @@
       </x:c>
       <x:c r="P445" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q445" s="2" t="n">
-        <x:v>46064.3556481482</x:v>
+        <x:v>46064.3255671296</x:v>
       </x:c>
       <x:c r="R445" s="2" t="n">
-        <x:v>46064.3696412037</x:v>
+        <x:v>46064.4187731482</x:v>
       </x:c>
       <x:c r="S445" s="2" t="n">
-        <x:v>46064.4355787037</x:v>
+        <x:v>46064.4423148148</x:v>
       </x:c>
       <x:c r="T445" s="3">
         <x:v/>
       </x:c>
       <x:c r="U445" s="3" t="inlineStr">
         <x:is>
-          <x:t>20</x:t>
+          <x:t>135</x:t>
         </x:is>
       </x:c>
       <x:c r="V445" s="3" t="inlineStr">
         <x:is>
-          <x:t>95</x:t>
+          <x:t>33</x:t>
         </x:is>
       </x:c>
       <x:c r="W445" s="1">
@@ -52268,34 +52270,34 @@
       <x:c r="Z445" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA445" s="1">
-        <x:v/>
+      <x:c r="AA445" s="1" t="inlineStr">
+        <x:is>
+          <x:t>783479987</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="446">
       <x:c r="A446" s="1" t="inlineStr">
         <x:is>
-          <x:t>50135</x:t>
+          <x:t>1001634</x:t>
         </x:is>
       </x:c>
       <x:c r="B446" s="1" t="inlineStr">
         <x:is>
-          <x:t>DSV Road sp. z o.o.</x:t>
+          <x:t>Good(s)Factory</x:t>
         </x:is>
       </x:c>
       <x:c r="C446" s="4" t="inlineStr">
         <x:is>
-          <x:t>1806306</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D446" s="4" t="inlineStr">
-        <x:is>
-          <x:t>000002858764</x:t>
-        </x:is>
+          <x:t>1801301</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D446" s="4">
+        <x:v/>
       </x:c>
       <x:c r="E446" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002783199, 4002784832</x:t>
+          <x:t>4002786687</x:t>
         </x:is>
       </x:c>
       <x:c r="F446" s="1" t="inlineStr">
@@ -52315,17 +52317,17 @@
       </x:c>
       <x:c r="I446" s="1" t="inlineStr">
         <x:is>
-          <x:t>8996</x:t>
+          <x:t>9004</x:t>
         </x:is>
       </x:c>
       <x:c r="J446" s="1" t="inlineStr">
         <x:is>
-          <x:t>Bierun</x:t>
+          <x:t>Biblis</x:t>
         </x:is>
       </x:c>
       <x:c r="K446" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8996-1A</x:t>
+          <x:t>DCZONE-9004-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L446" s="1" t="inlineStr">
@@ -52334,7 +52336,7 @@
         </x:is>
       </x:c>
       <x:c r="M446" s="3" t="n">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="N446" s="1" t="inlineStr">
         <x:is>
@@ -52346,29 +52348,29 @@
       </x:c>
       <x:c r="P446" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q446" s="2" t="n">
-        <x:v>46064.3255671296</x:v>
+        <x:v>46064.3556481482</x:v>
       </x:c>
       <x:c r="R446" s="2" t="n">
-        <x:v>46064.4187731482</x:v>
+        <x:v>46064.3696412037</x:v>
       </x:c>
       <x:c r="S446" s="2" t="n">
-        <x:v>46064.4423148148</x:v>
+        <x:v>46064.4355787037</x:v>
       </x:c>
       <x:c r="T446" s="3">
         <x:v/>
       </x:c>
       <x:c r="U446" s="3" t="inlineStr">
         <x:is>
-          <x:t>135</x:t>
+          <x:t>20</x:t>
         </x:is>
       </x:c>
       <x:c r="V446" s="3" t="inlineStr">
         <x:is>
-          <x:t>33</x:t>
+          <x:t>95</x:t>
         </x:is>
       </x:c>
       <x:c r="W446" s="1">
@@ -52385,10 +52387,8 @@
       <x:c r="Z446" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA446" s="1" t="inlineStr">
-        <x:is>
-          <x:t>783479987</x:t>
-        </x:is>
+      <x:c r="AA446" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="447">
@@ -53681,7 +53681,7 @@
       </x:c>
       <x:c r="C458" s="4" t="inlineStr">
         <x:is>
-          <x:t>1803863</x:t>
+          <x:t>1801511</x:t>
         </x:is>
       </x:c>
       <x:c r="D458" s="4">
@@ -53689,7 +53689,7 @@
       </x:c>
       <x:c r="E458" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002791657</x:t>
+          <x:t>4002786694</x:t>
         </x:is>
       </x:c>
       <x:c r="F458" s="1" t="inlineStr">
@@ -53704,22 +53704,22 @@
       </x:c>
       <x:c r="H458" s="1" t="inlineStr">
         <x:is>
-          <x:t>Refused</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I458" s="1" t="inlineStr">
         <x:is>
-          <x:t>9003</x:t>
+          <x:t>8996</x:t>
         </x:is>
       </x:c>
       <x:c r="J458" s="1" t="inlineStr">
         <x:is>
-          <x:t>Moissy</x:t>
+          <x:t>Bierun</x:t>
         </x:is>
       </x:c>
       <x:c r="K458" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9003-1A</x:t>
+          <x:t>DCZONE-8996-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L458" s="1" t="inlineStr">
@@ -53732,7 +53732,7 @@
       </x:c>
       <x:c r="N458" s="1" t="inlineStr">
         <x:is>
-          <x:t>No</x:t>
+          <x:t>Yes</x:t>
         </x:is>
       </x:c>
       <x:c r="O458" s="2" t="n">
@@ -53740,37 +53740,33 @@
       </x:c>
       <x:c r="P458" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q458" s="2" t="n">
-        <x:v>46065.4250578704</x:v>
-      </x:c>
-      <x:c r="R458" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S458" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="T458" s="3" t="inlineStr">
-        <x:is>
-          <x:t>12</x:t>
-        </x:is>
+        <x:v>46065.3652777778</x:v>
+      </x:c>
+      <x:c r="R458" s="2" t="n">
+        <x:v>46065.3766550926</x:v>
+      </x:c>
+      <x:c r="S458" s="2" t="n">
+        <x:v>46065.4531828704</x:v>
+      </x:c>
+      <x:c r="T458" s="3">
+        <x:v/>
       </x:c>
       <x:c r="U458" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>16</x:t>
         </x:is>
       </x:c>
       <x:c r="V458" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="W458" s="1" t="inlineStr">
-        <x:is>
-          <x:t>No inbound capacity</x:t>
-        </x:is>
+          <x:t>110</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W458" s="1">
+        <x:v/>
       </x:c>
       <x:c r="X458" s="1" t="inlineStr">
         <x:is>
@@ -53785,7 +53781,7 @@
       </x:c>
       <x:c r="AA458" s="1" t="inlineStr">
         <x:is>
-          <x:t>UEP sees with its boss</x:t>
+          <x:t>+3725012961</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -53802,7 +53798,7 @@
       </x:c>
       <x:c r="C459" s="4" t="inlineStr">
         <x:is>
-          <x:t>1801511</x:t>
+          <x:t>1803863</x:t>
         </x:is>
       </x:c>
       <x:c r="D459" s="4">
@@ -53810,7 +53806,7 @@
       </x:c>
       <x:c r="E459" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002786694</x:t>
+          <x:t>4002791657</x:t>
         </x:is>
       </x:c>
       <x:c r="F459" s="1" t="inlineStr">
@@ -53825,22 +53821,22 @@
       </x:c>
       <x:c r="H459" s="1" t="inlineStr">
         <x:is>
-          <x:t>Finished</x:t>
+          <x:t>Refused</x:t>
         </x:is>
       </x:c>
       <x:c r="I459" s="1" t="inlineStr">
         <x:is>
-          <x:t>8996</x:t>
+          <x:t>9003</x:t>
         </x:is>
       </x:c>
       <x:c r="J459" s="1" t="inlineStr">
         <x:is>
-          <x:t>Bierun</x:t>
+          <x:t>Moissy</x:t>
         </x:is>
       </x:c>
       <x:c r="K459" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8996-1A</x:t>
+          <x:t>DCZONE-9003-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L459" s="1" t="inlineStr">
@@ -53853,7 +53849,7 @@
       </x:c>
       <x:c r="N459" s="1" t="inlineStr">
         <x:is>
-          <x:t>Yes</x:t>
+          <x:t>No</x:t>
         </x:is>
       </x:c>
       <x:c r="O459" s="2" t="n">
@@ -53861,33 +53857,37 @@
       </x:c>
       <x:c r="P459" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q459" s="2" t="n">
-        <x:v>46065.3652777778</x:v>
-      </x:c>
-      <x:c r="R459" s="2" t="n">
-        <x:v>46065.3766550926</x:v>
-      </x:c>
-      <x:c r="S459" s="2" t="n">
-        <x:v>46065.4531828704</x:v>
-      </x:c>
-      <x:c r="T459" s="3">
-        <x:v/>
+        <x:v>46065.4250578704</x:v>
+      </x:c>
+      <x:c r="R459" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S459" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T459" s="3" t="inlineStr">
+        <x:is>
+          <x:t>12</x:t>
+        </x:is>
       </x:c>
       <x:c r="U459" s="3" t="inlineStr">
         <x:is>
-          <x:t>16</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="V459" s="3" t="inlineStr">
         <x:is>
-          <x:t>110</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="W459" s="1">
-        <x:v/>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W459" s="1" t="inlineStr">
+        <x:is>
+          <x:t>No inbound capacity</x:t>
+        </x:is>
       </x:c>
       <x:c r="X459" s="1" t="inlineStr">
         <x:is>
@@ -53902,7 +53902,7 @@
       </x:c>
       <x:c r="AA459" s="1" t="inlineStr">
         <x:is>
-          <x:t>+3725012961</x:t>
+          <x:t>UEP sees with its boss</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -60574,7 +60574,7 @@
       </x:c>
       <x:c r="C517" s="4" t="inlineStr">
         <x:is>
-          <x:t>1811831</x:t>
+          <x:t>1812322</x:t>
         </x:is>
       </x:c>
       <x:c r="D517" s="4">
@@ -60582,7 +60582,7 @@
       </x:c>
       <x:c r="E517" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002799468</x:t>
+          <x:t>4002799515</x:t>
         </x:is>
       </x:c>
       <x:c r="F517" s="1" t="inlineStr">
@@ -60602,17 +60602,17 @@
       </x:c>
       <x:c r="I517" s="1" t="inlineStr">
         <x:is>
-          <x:t>8991</x:t>
+          <x:t>8995</x:t>
         </x:is>
       </x:c>
       <x:c r="J517" s="1" t="inlineStr">
         <x:is>
-          <x:t>Altedo</x:t>
+          <x:t>Ensues</x:t>
         </x:is>
       </x:c>
       <x:c r="K517" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8991-1A</x:t>
+          <x:t>DCZONE-8995-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L517" s="1" t="inlineStr">
@@ -60637,25 +60637,25 @@
         </x:is>
       </x:c>
       <x:c r="Q517" s="2" t="n">
-        <x:v>46076.4445023148</x:v>
+        <x:v>46076.4148842593</x:v>
       </x:c>
       <x:c r="R517" s="2" t="n">
-        <x:v>46076.4452083333</x:v>
+        <x:v>46076.460462963</x:v>
       </x:c>
       <x:c r="S517" s="2" t="n">
-        <x:v>46076.5086342593</x:v>
+        <x:v>46076.4788310185</x:v>
       </x:c>
       <x:c r="T517" s="3">
         <x:v/>
       </x:c>
       <x:c r="U517" s="3" t="inlineStr">
         <x:is>
-          <x:t>1</x:t>
+          <x:t>66</x:t>
         </x:is>
       </x:c>
       <x:c r="V517" s="3" t="inlineStr">
         <x:is>
-          <x:t>91</x:t>
+          <x:t>26</x:t>
         </x:is>
       </x:c>
       <x:c r="W517" s="1">
@@ -60689,7 +60689,7 @@
       </x:c>
       <x:c r="C518" s="4" t="inlineStr">
         <x:is>
-          <x:t>1812322</x:t>
+          <x:t>1811831</x:t>
         </x:is>
       </x:c>
       <x:c r="D518" s="4">
@@ -60697,7 +60697,7 @@
       </x:c>
       <x:c r="E518" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002799515</x:t>
+          <x:t>4002799468</x:t>
         </x:is>
       </x:c>
       <x:c r="F518" s="1" t="inlineStr">
@@ -60717,17 +60717,17 @@
       </x:c>
       <x:c r="I518" s="1" t="inlineStr">
         <x:is>
-          <x:t>8995</x:t>
+          <x:t>8991</x:t>
         </x:is>
       </x:c>
       <x:c r="J518" s="1" t="inlineStr">
         <x:is>
-          <x:t>Ensues</x:t>
+          <x:t>Altedo</x:t>
         </x:is>
       </x:c>
       <x:c r="K518" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8995-1A</x:t>
+          <x:t>DCZONE-8991-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L518" s="1" t="inlineStr">
@@ -60752,25 +60752,25 @@
         </x:is>
       </x:c>
       <x:c r="Q518" s="2" t="n">
-        <x:v>46076.4148842593</x:v>
+        <x:v>46076.4445023148</x:v>
       </x:c>
       <x:c r="R518" s="2" t="n">
-        <x:v>46076.460462963</x:v>
+        <x:v>46076.4452083333</x:v>
       </x:c>
       <x:c r="S518" s="2" t="n">
-        <x:v>46076.4788310185</x:v>
+        <x:v>46076.5086342593</x:v>
       </x:c>
       <x:c r="T518" s="3">
         <x:v/>
       </x:c>
       <x:c r="U518" s="3" t="inlineStr">
         <x:is>
-          <x:t>66</x:t>
+          <x:t>1</x:t>
         </x:is>
       </x:c>
       <x:c r="V518" s="3" t="inlineStr">
         <x:is>
-          <x:t>26</x:t>
+          <x:t>91</x:t>
         </x:is>
       </x:c>
       <x:c r="W518" s="1">
@@ -63245,7 +63245,7 @@
       </x:c>
       <x:c r="C540" s="4" t="inlineStr">
         <x:is>
-          <x:t>1811870</x:t>
+          <x:t>1811982</x:t>
         </x:is>
       </x:c>
       <x:c r="D540" s="4">
@@ -63253,7 +63253,7 @@
       </x:c>
       <x:c r="E540" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002799469</x:t>
+          <x:t>4002799524</x:t>
         </x:is>
       </x:c>
       <x:c r="F540" s="1" t="inlineStr">
@@ -63273,17 +63273,17 @@
       </x:c>
       <x:c r="I540" s="1" t="inlineStr">
         <x:is>
-          <x:t>8991</x:t>
+          <x:t>9006</x:t>
         </x:is>
       </x:c>
       <x:c r="J540" s="1" t="inlineStr">
         <x:is>
-          <x:t>Altedo</x:t>
+          <x:t>Belleville</x:t>
         </x:is>
       </x:c>
       <x:c r="K540" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8991-1A</x:t>
+          <x:t>DCZONE-9006-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L540" s="1" t="inlineStr">
@@ -63308,25 +63308,25 @@
         </x:is>
       </x:c>
       <x:c r="Q540" s="2" t="n">
-        <x:v>46077.3762615741</x:v>
+        <x:v>46077.3883449074</x:v>
       </x:c>
       <x:c r="R540" s="2" t="n">
-        <x:v>46077.3771064815</x:v>
+        <x:v>46077.5160532407</x:v>
       </x:c>
       <x:c r="S540" s="2" t="n">
-        <x:v>46077.4287268519</x:v>
+        <x:v>46077.6093171296</x:v>
       </x:c>
       <x:c r="T540" s="3">
         <x:v/>
       </x:c>
       <x:c r="U540" s="3" t="inlineStr">
         <x:is>
-          <x:t>2</x:t>
+          <x:t>184</x:t>
         </x:is>
       </x:c>
       <x:c r="V540" s="3" t="inlineStr">
         <x:is>
-          <x:t>74</x:t>
+          <x:t>134</x:t>
         </x:is>
       </x:c>
       <x:c r="W540" s="1">
@@ -63334,7 +63334,7 @@
       </x:c>
       <x:c r="X540" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>Logistic quality: unstable pallets or incorrectly loaded</x:t>
         </x:is>
       </x:c>
       <x:c r="Y540" s="1">
@@ -63360,7 +63360,7 @@
       </x:c>
       <x:c r="C541" s="4" t="inlineStr">
         <x:is>
-          <x:t>1811982</x:t>
+          <x:t>1811870</x:t>
         </x:is>
       </x:c>
       <x:c r="D541" s="4">
@@ -63368,7 +63368,7 @@
       </x:c>
       <x:c r="E541" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002799524</x:t>
+          <x:t>4002799469</x:t>
         </x:is>
       </x:c>
       <x:c r="F541" s="1" t="inlineStr">
@@ -63388,17 +63388,17 @@
       </x:c>
       <x:c r="I541" s="1" t="inlineStr">
         <x:is>
-          <x:t>9006</x:t>
+          <x:t>8991</x:t>
         </x:is>
       </x:c>
       <x:c r="J541" s="1" t="inlineStr">
         <x:is>
-          <x:t>Belleville</x:t>
+          <x:t>Altedo</x:t>
         </x:is>
       </x:c>
       <x:c r="K541" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9006-1A</x:t>
+          <x:t>DCZONE-8991-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L541" s="1" t="inlineStr">
@@ -63423,25 +63423,25 @@
         </x:is>
       </x:c>
       <x:c r="Q541" s="2" t="n">
-        <x:v>46077.3883449074</x:v>
+        <x:v>46077.3762615741</x:v>
       </x:c>
       <x:c r="R541" s="2" t="n">
-        <x:v>46077.5160532407</x:v>
+        <x:v>46077.3771064815</x:v>
       </x:c>
       <x:c r="S541" s="2" t="n">
-        <x:v>46077.6093171296</x:v>
+        <x:v>46077.4287268519</x:v>
       </x:c>
       <x:c r="T541" s="3">
         <x:v/>
       </x:c>
       <x:c r="U541" s="3" t="inlineStr">
         <x:is>
-          <x:t>184</x:t>
+          <x:t>2</x:t>
         </x:is>
       </x:c>
       <x:c r="V541" s="3" t="inlineStr">
         <x:is>
-          <x:t>134</x:t>
+          <x:t>74</x:t>
         </x:is>
       </x:c>
       <x:c r="W541" s="1">
@@ -63449,7 +63449,7 @@
       </x:c>
       <x:c r="X541" s="1" t="inlineStr">
         <x:is>
-          <x:t>Logistic quality: unstable pallets or incorrectly loaded</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="Y541" s="1">
@@ -63826,7 +63826,7 @@
       </x:c>
       <x:c r="C545" s="4" t="inlineStr">
         <x:is>
-          <x:t>1811861</x:t>
+          <x:t>1812470</x:t>
         </x:is>
       </x:c>
       <x:c r="D545" s="4">
@@ -63834,7 +63834,7 @@
       </x:c>
       <x:c r="E545" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002799470</x:t>
+          <x:t>4002799689</x:t>
         </x:is>
       </x:c>
       <x:c r="F545" s="1" t="inlineStr">
@@ -63854,22 +63854,22 @@
       </x:c>
       <x:c r="I545" s="1" t="inlineStr">
         <x:is>
-          <x:t>8991</x:t>
+          <x:t>9003</x:t>
         </x:is>
       </x:c>
       <x:c r="J545" s="1" t="inlineStr">
         <x:is>
-          <x:t>Altedo</x:t>
+          <x:t>Moissy</x:t>
         </x:is>
       </x:c>
       <x:c r="K545" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8991-1A</x:t>
+          <x:t>DCZONE-9003-1C</x:t>
         </x:is>
       </x:c>
       <x:c r="L545" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zone 1 Truck</x:t>
+          <x:t>Zone 1 Handling</x:t>
         </x:is>
       </x:c>
       <x:c r="M545" s="3" t="n">
@@ -63889,27 +63889,25 @@
         </x:is>
       </x:c>
       <x:c r="Q545" s="2" t="n">
-        <x:v>46078.2554976852</x:v>
+        <x:v>46078.2476851852</x:v>
       </x:c>
       <x:c r="R545" s="2" t="n">
-        <x:v>46078.2560416667</x:v>
+        <x:v>46078.2836805556</x:v>
       </x:c>
       <x:c r="S545" s="2" t="n">
-        <x:v>46078.2942592593</x:v>
-      </x:c>
-      <x:c r="T545" s="3" t="inlineStr">
-        <x:is>
-          <x:t>7</x:t>
-        </x:is>
+        <x:v>46078.3247337963</x:v>
+      </x:c>
+      <x:c r="T545" s="3">
+        <x:v/>
       </x:c>
       <x:c r="U545" s="3" t="inlineStr">
         <x:is>
-          <x:t>1</x:t>
+          <x:t>52</x:t>
         </x:is>
       </x:c>
       <x:c r="V545" s="3" t="inlineStr">
         <x:is>
-          <x:t>55</x:t>
+          <x:t>59</x:t>
         </x:is>
       </x:c>
       <x:c r="W545" s="1">
@@ -63917,7 +63915,7 @@
       </x:c>
       <x:c r="X545" s="1" t="inlineStr">
         <x:is>
-          <x:t>Logistic quality: badly foiled, Logistic quality: unstable pallets or incorrectly loaded</x:t>
+          <x:t>Logistic quality: loaded in width, Logistic quality: pallets are too high</x:t>
         </x:is>
       </x:c>
       <x:c r="Y545" s="1">
@@ -63943,7 +63941,7 @@
       </x:c>
       <x:c r="C546" s="4" t="inlineStr">
         <x:is>
-          <x:t>1812470</x:t>
+          <x:t>1811861</x:t>
         </x:is>
       </x:c>
       <x:c r="D546" s="4">
@@ -63951,7 +63949,7 @@
       </x:c>
       <x:c r="E546" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002799689</x:t>
+          <x:t>4002799470</x:t>
         </x:is>
       </x:c>
       <x:c r="F546" s="1" t="inlineStr">
@@ -63971,22 +63969,22 @@
       </x:c>
       <x:c r="I546" s="1" t="inlineStr">
         <x:is>
-          <x:t>9003</x:t>
+          <x:t>8991</x:t>
         </x:is>
       </x:c>
       <x:c r="J546" s="1" t="inlineStr">
         <x:is>
-          <x:t>Moissy</x:t>
+          <x:t>Altedo</x:t>
         </x:is>
       </x:c>
       <x:c r="K546" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9003-1C</x:t>
+          <x:t>DCZONE-8991-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L546" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zone 1 Handling</x:t>
+          <x:t>Zone 1 Truck</x:t>
         </x:is>
       </x:c>
       <x:c r="M546" s="3" t="n">
@@ -64006,25 +64004,27 @@
         </x:is>
       </x:c>
       <x:c r="Q546" s="2" t="n">
-        <x:v>46078.2476851852</x:v>
+        <x:v>46078.2554976852</x:v>
       </x:c>
       <x:c r="R546" s="2" t="n">
-        <x:v>46078.2836805556</x:v>
+        <x:v>46078.2560416667</x:v>
       </x:c>
       <x:c r="S546" s="2" t="n">
-        <x:v>46078.3247337963</x:v>
-      </x:c>
-      <x:c r="T546" s="3">
-        <x:v/>
+        <x:v>46078.2942592593</x:v>
+      </x:c>
+      <x:c r="T546" s="3" t="inlineStr">
+        <x:is>
+          <x:t>7</x:t>
+        </x:is>
       </x:c>
       <x:c r="U546" s="3" t="inlineStr">
         <x:is>
-          <x:t>52</x:t>
+          <x:t>1</x:t>
         </x:is>
       </x:c>
       <x:c r="V546" s="3" t="inlineStr">
         <x:is>
-          <x:t>59</x:t>
+          <x:t>55</x:t>
         </x:is>
       </x:c>
       <x:c r="W546" s="1">
@@ -64032,7 +64032,7 @@
       </x:c>
       <x:c r="X546" s="1" t="inlineStr">
         <x:is>
-          <x:t>Logistic quality: loaded in width, Logistic quality: pallets are too high</x:t>
+          <x:t>Logistic quality: badly foiled, Logistic quality: unstable pallets or incorrectly loaded</x:t>
         </x:is>
       </x:c>
       <x:c r="Y546" s="1">
@@ -75117,7 +75117,7 @@
       </x:c>
       <x:c r="C642" s="4" t="inlineStr">
         <x:is>
-          <x:t>1827477</x:t>
+          <x:t>1827455</x:t>
         </x:is>
       </x:c>
       <x:c r="D642" s="4">
@@ -75125,7 +75125,7 @@
       </x:c>
       <x:c r="E642" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002821260</x:t>
+          <x:t>4002821189</x:t>
         </x:is>
       </x:c>
       <x:c r="F642" s="1" t="inlineStr">
@@ -75145,17 +75145,17 @@
       </x:c>
       <x:c r="I642" s="1" t="inlineStr">
         <x:is>
-          <x:t>9000</x:t>
+          <x:t>9005</x:t>
         </x:is>
       </x:c>
       <x:c r="J642" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zwaagdijk</x:t>
+          <x:t>Labastide</x:t>
         </x:is>
       </x:c>
       <x:c r="K642" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9000-1A</x:t>
+          <x:t>DCZONE-9005-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L642" s="1" t="inlineStr">
@@ -75180,25 +75180,25 @@
         </x:is>
       </x:c>
       <x:c r="Q642" s="2" t="n">
-        <x:v>46091.3442708333</x:v>
+        <x:v>46091.3462962963</x:v>
       </x:c>
       <x:c r="R642" s="2" t="n">
-        <x:v>46091.3446643519</x:v>
+        <x:v>46091.4064467593</x:v>
       </x:c>
       <x:c r="S642" s="2" t="n">
-        <x:v>46091.3738310185</x:v>
+        <x:v>46091.5000231481</x:v>
       </x:c>
       <x:c r="T642" s="3">
         <x:v/>
       </x:c>
       <x:c r="U642" s="3" t="inlineStr">
         <x:is>
-          <x:t>1</x:t>
+          <x:t>87</x:t>
         </x:is>
       </x:c>
       <x:c r="V642" s="3" t="inlineStr">
         <x:is>
-          <x:t>42</x:t>
+          <x:t>135</x:t>
         </x:is>
       </x:c>
       <x:c r="W642" s="1">
@@ -75232,7 +75232,7 @@
       </x:c>
       <x:c r="C643" s="4" t="inlineStr">
         <x:is>
-          <x:t>1827455</x:t>
+          <x:t>1827477</x:t>
         </x:is>
       </x:c>
       <x:c r="D643" s="4">
@@ -75240,7 +75240,7 @@
       </x:c>
       <x:c r="E643" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002821189</x:t>
+          <x:t>4002821260</x:t>
         </x:is>
       </x:c>
       <x:c r="F643" s="1" t="inlineStr">
@@ -75260,17 +75260,17 @@
       </x:c>
       <x:c r="I643" s="1" t="inlineStr">
         <x:is>
-          <x:t>9005</x:t>
+          <x:t>9000</x:t>
         </x:is>
       </x:c>
       <x:c r="J643" s="1" t="inlineStr">
         <x:is>
-          <x:t>Labastide</x:t>
+          <x:t>Zwaagdijk</x:t>
         </x:is>
       </x:c>
       <x:c r="K643" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9005-1A</x:t>
+          <x:t>DCZONE-9000-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L643" s="1" t="inlineStr">
@@ -75295,25 +75295,25 @@
         </x:is>
       </x:c>
       <x:c r="Q643" s="2" t="n">
-        <x:v>46091.3462962963</x:v>
+        <x:v>46091.3442708333</x:v>
       </x:c>
       <x:c r="R643" s="2" t="n">
-        <x:v>46091.4064467593</x:v>
+        <x:v>46091.3446643519</x:v>
       </x:c>
       <x:c r="S643" s="2" t="n">
-        <x:v>46091.5000231481</x:v>
+        <x:v>46091.3738310185</x:v>
       </x:c>
       <x:c r="T643" s="3">
         <x:v/>
       </x:c>
       <x:c r="U643" s="3" t="inlineStr">
         <x:is>
-          <x:t>87</x:t>
+          <x:t>1</x:t>
         </x:is>
       </x:c>
       <x:c r="V643" s="3" t="inlineStr">
         <x:is>
-          <x:t>135</x:t>
+          <x:t>42</x:t>
         </x:is>
       </x:c>
       <x:c r="W643" s="1">
@@ -76392,25 +76392,27 @@
     <x:row r="653">
       <x:c r="A653" s="1" t="inlineStr">
         <x:is>
-          <x:t>1001634</x:t>
+          <x:t>50135</x:t>
         </x:is>
       </x:c>
       <x:c r="B653" s="1" t="inlineStr">
         <x:is>
-          <x:t>Good(s)Factory</x:t>
+          <x:t>DSV Road sp. z o.o.</x:t>
         </x:is>
       </x:c>
       <x:c r="C653" s="4" t="inlineStr">
         <x:is>
-          <x:t>1827478</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D653" s="4">
-        <x:v/>
+          <x:t>1832049</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D653" s="4" t="inlineStr">
+        <x:is>
+          <x:t>2876259</x:t>
+        </x:is>
       </x:c>
       <x:c r="E653" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002821262</x:t>
+          <x:t>4002817860, 4002818125, 4002819374, 4002821880, 4002827316</x:t>
         </x:is>
       </x:c>
       <x:c r="F653" s="1" t="inlineStr">
@@ -76430,17 +76432,17 @@
       </x:c>
       <x:c r="I653" s="1" t="inlineStr">
         <x:is>
-          <x:t>9004</x:t>
+          <x:t>8989</x:t>
         </x:is>
       </x:c>
       <x:c r="J653" s="1" t="inlineStr">
         <x:is>
-          <x:t>Biblis</x:t>
+          <x:t>Dunikowo</x:t>
         </x:is>
       </x:c>
       <x:c r="K653" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9004-1A</x:t>
+          <x:t>DCZONE-8989-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L653" s="1" t="inlineStr">
@@ -76449,7 +76451,7 @@
         </x:is>
       </x:c>
       <x:c r="M653" s="3" t="n">
-        <x:v>33</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="N653" s="1" t="inlineStr">
         <x:is>
@@ -76461,29 +76463,31 @@
       </x:c>
       <x:c r="P653" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q653" s="2" t="n">
-        <x:v>46092.3441087963</x:v>
+        <x:v>46092.3953472222</x:v>
       </x:c>
       <x:c r="R653" s="2" t="n">
-        <x:v>46092.3722685185</x:v>
+        <x:v>46092.3954050926</x:v>
       </x:c>
       <x:c r="S653" s="2" t="n">
-        <x:v>46092.4435185185</x:v>
-      </x:c>
-      <x:c r="T653" s="3">
-        <x:v/>
+        <x:v>46092.4230092593</x:v>
+      </x:c>
+      <x:c r="T653" s="3" t="inlineStr">
+        <x:is>
+          <x:t>29</x:t>
+        </x:is>
       </x:c>
       <x:c r="U653" s="3" t="inlineStr">
         <x:is>
-          <x:t>41</x:t>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="V653" s="3" t="inlineStr">
         <x:is>
-          <x:t>102</x:t>
+          <x:t>40</x:t>
         </x:is>
       </x:c>
       <x:c r="W653" s="1">
@@ -76500,36 +76504,32 @@
       <x:c r="Z653" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA653" s="1" t="inlineStr">
-        <x:is>
-          <x:t>Zweite an 38</x:t>
-        </x:is>
+      <x:c r="AA653" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="654">
       <x:c r="A654" s="1" t="inlineStr">
         <x:is>
-          <x:t>50135</x:t>
+          <x:t>1001634</x:t>
         </x:is>
       </x:c>
       <x:c r="B654" s="1" t="inlineStr">
         <x:is>
-          <x:t>DSV Road sp. z o.o.</x:t>
+          <x:t>Good(s)Factory</x:t>
         </x:is>
       </x:c>
       <x:c r="C654" s="4" t="inlineStr">
         <x:is>
-          <x:t>1832049</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D654" s="4" t="inlineStr">
-        <x:is>
-          <x:t>2876259</x:t>
-        </x:is>
+          <x:t>1827478</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D654" s="4">
+        <x:v/>
       </x:c>
       <x:c r="E654" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002817860, 4002818125, 4002819374, 4002821880, 4002827316</x:t>
+          <x:t>4002821262</x:t>
         </x:is>
       </x:c>
       <x:c r="F654" s="1" t="inlineStr">
@@ -76549,17 +76549,17 @@
       </x:c>
       <x:c r="I654" s="1" t="inlineStr">
         <x:is>
-          <x:t>8989</x:t>
+          <x:t>9004</x:t>
         </x:is>
       </x:c>
       <x:c r="J654" s="1" t="inlineStr">
         <x:is>
-          <x:t>Dunikowo</x:t>
+          <x:t>Biblis</x:t>
         </x:is>
       </x:c>
       <x:c r="K654" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8989-1A</x:t>
+          <x:t>DCZONE-9004-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L654" s="1" t="inlineStr">
@@ -76568,7 +76568,7 @@
         </x:is>
       </x:c>
       <x:c r="M654" s="3" t="n">
-        <x:v>21</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="N654" s="1" t="inlineStr">
         <x:is>
@@ -76580,31 +76580,29 @@
       </x:c>
       <x:c r="P654" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q654" s="2" t="n">
-        <x:v>46092.3953472222</x:v>
+        <x:v>46092.3441087963</x:v>
       </x:c>
       <x:c r="R654" s="2" t="n">
-        <x:v>46092.3954050926</x:v>
+        <x:v>46092.3722685185</x:v>
       </x:c>
       <x:c r="S654" s="2" t="n">
-        <x:v>46092.4230092593</x:v>
-      </x:c>
-      <x:c r="T654" s="3" t="inlineStr">
-        <x:is>
-          <x:t>29</x:t>
-        </x:is>
+        <x:v>46092.4435185185</x:v>
+      </x:c>
+      <x:c r="T654" s="3">
+        <x:v/>
       </x:c>
       <x:c r="U654" s="3" t="inlineStr">
         <x:is>
-          <x:t>0</x:t>
+          <x:t>41</x:t>
         </x:is>
       </x:c>
       <x:c r="V654" s="3" t="inlineStr">
         <x:is>
-          <x:t>40</x:t>
+          <x:t>102</x:t>
         </x:is>
       </x:c>
       <x:c r="W654" s="1">
@@ -76621,8 +76619,10 @@
       <x:c r="Z654" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA654" s="1">
-        <x:v/>
+      <x:c r="AA654" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zweite an 38</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="655">
@@ -76876,7 +76876,7 @@
       </x:c>
       <x:c r="C657" s="4" t="inlineStr">
         <x:is>
-          <x:t>1827479</x:t>
+          <x:t>1831612</x:t>
         </x:is>
       </x:c>
       <x:c r="D657" s="4">
@@ -76884,7 +76884,7 @@
       </x:c>
       <x:c r="E657" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002821250</x:t>
+          <x:t>4002826003</x:t>
         </x:is>
       </x:c>
       <x:c r="F657" s="1" t="inlineStr">
@@ -76894,7 +76894,7 @@
       </x:c>
       <x:c r="G657" s="1" t="inlineStr">
         <x:is>
-          <x:t>Gold Allocation</x:t>
+          <x:t>GOLD Regular</x:t>
         </x:is>
       </x:c>
       <x:c r="H657" s="1" t="inlineStr">
@@ -76904,17 +76904,17 @@
       </x:c>
       <x:c r="I657" s="1" t="inlineStr">
         <x:is>
-          <x:t>8994</x:t>
+          <x:t>8997</x:t>
         </x:is>
       </x:c>
       <x:c r="J657" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zakroczym</x:t>
+          <x:t>Verrières</x:t>
         </x:is>
       </x:c>
       <x:c r="K657" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8994-1A</x:t>
+          <x:t>DCZONE-8997-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L657" s="1" t="inlineStr">
@@ -76935,31 +76935,29 @@
       </x:c>
       <x:c r="P657" s="1" t="inlineStr">
         <x:is>
-          <x:t>On time</x:t>
+          <x:t>Early</x:t>
         </x:is>
       </x:c>
       <x:c r="Q657" s="2" t="n">
-        <x:v>46092.4284953704</x:v>
+        <x:v>46092.3725115741</x:v>
       </x:c>
       <x:c r="R657" s="2" t="n">
-        <x:v>46092.4308564815</x:v>
+        <x:v>46092.3963425926</x:v>
       </x:c>
       <x:c r="S657" s="2" t="n">
-        <x:v>46092.4575462963</x:v>
-      </x:c>
-      <x:c r="T657" s="3" t="inlineStr">
-        <x:is>
-          <x:t>17</x:t>
-        </x:is>
+        <x:v>46092.4725925926</x:v>
+      </x:c>
+      <x:c r="T657" s="3">
+        <x:v/>
       </x:c>
       <x:c r="U657" s="3" t="inlineStr">
         <x:is>
-          <x:t>3</x:t>
+          <x:t>34</x:t>
         </x:is>
       </x:c>
       <x:c r="V657" s="3" t="inlineStr">
         <x:is>
-          <x:t>38</x:t>
+          <x:t>110</x:t>
         </x:is>
       </x:c>
       <x:c r="W657" s="1">
@@ -76976,10 +76974,8 @@
       <x:c r="Z657" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA657" s="1" t="inlineStr">
-        <x:is>
-          <x:t>609050184</x:t>
-        </x:is>
+      <x:c r="AA657" s="1">
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="658">
@@ -76995,7 +76991,7 @@
       </x:c>
       <x:c r="C658" s="4" t="inlineStr">
         <x:is>
-          <x:t>1831612</x:t>
+          <x:t>1827479</x:t>
         </x:is>
       </x:c>
       <x:c r="D658" s="4">
@@ -77003,7 +76999,7 @@
       </x:c>
       <x:c r="E658" s="1" t="inlineStr">
         <x:is>
-          <x:t>4002826003</x:t>
+          <x:t>4002821250</x:t>
         </x:is>
       </x:c>
       <x:c r="F658" s="1" t="inlineStr">
@@ -77013,7 +77009,7 @@
       </x:c>
       <x:c r="G658" s="1" t="inlineStr">
         <x:is>
-          <x:t>GOLD Regular</x:t>
+          <x:t>Gold Allocation</x:t>
         </x:is>
       </x:c>
       <x:c r="H658" s="1" t="inlineStr">
@@ -77023,17 +77019,17 @@
       </x:c>
       <x:c r="I658" s="1" t="inlineStr">
         <x:is>
-          <x:t>8997</x:t>
+          <x:t>8994</x:t>
         </x:is>
       </x:c>
       <x:c r="J658" s="1" t="inlineStr">
         <x:is>
-          <x:t>Verrières</x:t>
+          <x:t>Zakroczym</x:t>
         </x:is>
       </x:c>
       <x:c r="K658" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-8997-1A</x:t>
+          <x:t>DCZONE-8994-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L658" s="1" t="inlineStr">
@@ -77054,29 +77050,31 @@
       </x:c>
       <x:c r="P658" s="1" t="inlineStr">
         <x:is>
-          <x:t>Early</x:t>
+          <x:t>On time</x:t>
         </x:is>
       </x:c>
       <x:c r="Q658" s="2" t="n">
-        <x:v>46092.3725115741</x:v>
+        <x:v>46092.4284953704</x:v>
       </x:c>
       <x:c r="R658" s="2" t="n">
-        <x:v>46092.3963425926</x:v>
+        <x:v>46092.4308564815</x:v>
       </x:c>
       <x:c r="S658" s="2" t="n">
-        <x:v>46092.4725925926</x:v>
-      </x:c>
-      <x:c r="T658" s="3">
-        <x:v/>
+        <x:v>46092.4575462963</x:v>
+      </x:c>
+      <x:c r="T658" s="3" t="inlineStr">
+        <x:is>
+          <x:t>17</x:t>
+        </x:is>
       </x:c>
       <x:c r="U658" s="3" t="inlineStr">
         <x:is>
-          <x:t>34</x:t>
+          <x:t>3</x:t>
         </x:is>
       </x:c>
       <x:c r="V658" s="3" t="inlineStr">
         <x:is>
-          <x:t>110</x:t>
+          <x:t>38</x:t>
         </x:is>
       </x:c>
       <x:c r="W658" s="1">
@@ -77093,8 +77091,10 @@
       <x:c r="Z658" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA658" s="1">
-        <x:v/>
+      <x:c r="AA658" s="1" t="inlineStr">
+        <x:is>
+          <x:t>609050184</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="659">
@@ -77833,7 +77833,7 @@
       </x:c>
       <x:c r="H665" s="1" t="inlineStr">
         <x:is>
-          <x:t>Unloading</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I665" s="1" t="inlineStr">
@@ -77878,8 +77878,8 @@
       <x:c r="R665" s="2" t="n">
         <x:v>46093.2776157407</x:v>
       </x:c>
-      <x:c r="S665" s="2">
-        <x:v/>
+      <x:c r="S665" s="2" t="n">
+        <x:v>46093.4620023148</x:v>
       </x:c>
       <x:c r="T665" s="3">
         <x:v/>
@@ -77891,7 +77891,7 @@
       </x:c>
       <x:c r="V665" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>266</x:t>
         </x:is>
       </x:c>
       <x:c r="W665" s="1">
@@ -78180,7 +78180,7 @@
       </x:c>
       <x:c r="H668" s="1" t="inlineStr">
         <x:is>
-          <x:t>Arrived</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I668" s="1" t="inlineStr">
@@ -78222,23 +78222,23 @@
       <x:c r="Q668" s="2" t="n">
         <x:v>46093.3267708333</x:v>
       </x:c>
-      <x:c r="R668" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S668" s="2">
-        <x:v/>
+      <x:c r="R668" s="2" t="n">
+        <x:v>46093.362662037</x:v>
+      </x:c>
+      <x:c r="S668" s="2" t="n">
+        <x:v>46093.3836342593</x:v>
       </x:c>
       <x:c r="T668" s="3">
         <x:v/>
       </x:c>
       <x:c r="U668" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>52</x:t>
         </x:is>
       </x:c>
       <x:c r="V668" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>30</x:t>
         </x:is>
       </x:c>
       <x:c r="W668" s="1">
@@ -78295,7 +78295,7 @@
       </x:c>
       <x:c r="H669" s="1" t="inlineStr">
         <x:is>
-          <x:t>Arrived</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I669" s="1" t="inlineStr">
@@ -78337,23 +78337,23 @@
       <x:c r="Q669" s="2" t="n">
         <x:v>46093.340775463</x:v>
       </x:c>
-      <x:c r="R669" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S669" s="2">
-        <x:v/>
+      <x:c r="R669" s="2" t="n">
+        <x:v>46093.3699421296</x:v>
+      </x:c>
+      <x:c r="S669" s="2" t="n">
+        <x:v>46093.4077777778</x:v>
       </x:c>
       <x:c r="T669" s="3">
         <x:v/>
       </x:c>
       <x:c r="U669" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>42</x:t>
         </x:is>
       </x:c>
       <x:c r="V669" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>55</x:t>
         </x:is>
       </x:c>
       <x:c r="W669" s="1">
@@ -78644,7 +78644,7 @@
       </x:c>
       <x:c r="H672" s="1" t="inlineStr">
         <x:is>
-          <x:t>Arrived</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I672" s="1" t="inlineStr">
@@ -78686,23 +78686,23 @@
       <x:c r="Q672" s="2" t="n">
         <x:v>46093.2863773148</x:v>
       </x:c>
-      <x:c r="R672" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S672" s="2">
-        <x:v/>
+      <x:c r="R672" s="2" t="n">
+        <x:v>46093.3953587963</x:v>
+      </x:c>
+      <x:c r="S672" s="2" t="n">
+        <x:v>46093.4789236111</x:v>
       </x:c>
       <x:c r="T672" s="3">
         <x:v/>
       </x:c>
       <x:c r="U672" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>157</x:t>
         </x:is>
       </x:c>
       <x:c r="V672" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>120</x:t>
         </x:is>
       </x:c>
       <x:c r="W672" s="1">
@@ -78761,7 +78761,7 @@
       </x:c>
       <x:c r="H673" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I673" s="1" t="inlineStr">
@@ -78797,29 +78797,29 @@
       </x:c>
       <x:c r="P673" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q673" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R673" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S673" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q673" s="2" t="n">
+        <x:v>46093.3677083333</x:v>
+      </x:c>
+      <x:c r="R673" s="2" t="n">
+        <x:v>46093.4786921296</x:v>
+      </x:c>
+      <x:c r="S673" s="2" t="n">
+        <x:v>46093.5299652778</x:v>
       </x:c>
       <x:c r="T673" s="3">
         <x:v/>
       </x:c>
       <x:c r="U673" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>160</x:t>
         </x:is>
       </x:c>
       <x:c r="V673" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>74</x:t>
         </x:is>
       </x:c>
       <x:c r="W673" s="1">
@@ -78876,7 +78876,7 @@
       </x:c>
       <x:c r="H674" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>NoShow</x:t>
         </x:is>
       </x:c>
       <x:c r="I674" s="1" t="inlineStr">
@@ -78904,7 +78904,7 @@
       </x:c>
       <x:c r="N674" s="1" t="inlineStr">
         <x:is>
-          <x:t>Yes</x:t>
+          <x:t>No</x:t>
         </x:is>
       </x:c>
       <x:c r="O674" s="2" t="n">
@@ -78945,11 +78945,13 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y674" s="1">
-        <x:v/>
-      </x:c>
-      <x:c r="Z674" s="2">
-        <x:v/>
+      <x:c r="Y674" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z674" s="2" t="n">
+        <x:v>46093.411724537</x:v>
       </x:c>
       <x:c r="AA674" s="1">
         <x:v/>
@@ -79108,7 +79110,7 @@
       </x:c>
       <x:c r="H676" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I676" s="1" t="inlineStr">
@@ -79144,29 +79146,29 @@
       </x:c>
       <x:c r="P676" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q676" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R676" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S676" s="2">
-        <x:v/>
+          <x:t>On time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q676" s="2" t="n">
+        <x:v>46093.3959606482</x:v>
+      </x:c>
+      <x:c r="R676" s="2" t="n">
+        <x:v>46093.4323842593</x:v>
+      </x:c>
+      <x:c r="S676" s="2" t="n">
+        <x:v>46093.4447106481</x:v>
       </x:c>
       <x:c r="T676" s="3">
         <x:v/>
       </x:c>
       <x:c r="U676" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>52</x:t>
         </x:is>
       </x:c>
       <x:c r="V676" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>18</x:t>
         </x:is>
       </x:c>
       <x:c r="W676" s="1">
@@ -79225,7 +79227,7 @@
       </x:c>
       <x:c r="H677" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I677" s="1" t="inlineStr">
@@ -79261,29 +79263,29 @@
       </x:c>
       <x:c r="P677" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q677" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R677" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S677" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q677" s="2" t="n">
+        <x:v>46093.3664467593</x:v>
+      </x:c>
+      <x:c r="R677" s="2" t="n">
+        <x:v>46093.3665393519</x:v>
+      </x:c>
+      <x:c r="S677" s="2" t="n">
+        <x:v>46093.388125</x:v>
       </x:c>
       <x:c r="T677" s="3">
         <x:v/>
       </x:c>
       <x:c r="U677" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="V677" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>31</x:t>
         </x:is>
       </x:c>
       <x:c r="W677" s="1">
@@ -79342,7 +79344,7 @@
       </x:c>
       <x:c r="H678" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I678" s="1" t="inlineStr">
@@ -79378,29 +79380,29 @@
       </x:c>
       <x:c r="P678" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q678" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R678" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S678" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q678" s="2" t="n">
+        <x:v>46093.431412037</x:v>
+      </x:c>
+      <x:c r="R678" s="2" t="n">
+        <x:v>46093.4314930556</x:v>
+      </x:c>
+      <x:c r="S678" s="2" t="n">
+        <x:v>46093.432650463</x:v>
       </x:c>
       <x:c r="T678" s="3">
         <x:v/>
       </x:c>
       <x:c r="U678" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="V678" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>2</x:t>
         </x:is>
       </x:c>
       <x:c r="W678" s="1">
@@ -79457,7 +79459,7 @@
       </x:c>
       <x:c r="H679" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I679" s="1" t="inlineStr">
@@ -79493,29 +79495,29 @@
       </x:c>
       <x:c r="P679" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q679" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R679" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S679" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q679" s="2" t="n">
+        <x:v>46093.4123842593</x:v>
+      </x:c>
+      <x:c r="R679" s="2" t="n">
+        <x:v>46093.4784722222</x:v>
+      </x:c>
+      <x:c r="S679" s="2" t="n">
+        <x:v>46093.5154050926</x:v>
       </x:c>
       <x:c r="T679" s="3">
         <x:v/>
       </x:c>
       <x:c r="U679" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>96</x:t>
         </x:is>
       </x:c>
       <x:c r="V679" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>53</x:t>
         </x:is>
       </x:c>
       <x:c r="W679" s="1">
@@ -79572,7 +79574,7 @@
       </x:c>
       <x:c r="H680" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I680" s="1" t="inlineStr">
@@ -79608,29 +79610,29 @@
       </x:c>
       <x:c r="P680" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q680" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R680" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S680" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q680" s="2" t="n">
+        <x:v>46093.4700347222</x:v>
+      </x:c>
+      <x:c r="R680" s="2" t="n">
+        <x:v>46093.5103587963</x:v>
+      </x:c>
+      <x:c r="S680" s="2" t="n">
+        <x:v>46093.5847453704</x:v>
       </x:c>
       <x:c r="T680" s="3">
         <x:v/>
       </x:c>
       <x:c r="U680" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>58</x:t>
         </x:is>
       </x:c>
       <x:c r="V680" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>108</x:t>
         </x:is>
       </x:c>
       <x:c r="W680" s="1">
@@ -79687,7 +79689,7 @@
       </x:c>
       <x:c r="H681" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I681" s="1" t="inlineStr">
@@ -79723,29 +79725,31 @@
       </x:c>
       <x:c r="P681" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q681" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R681" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S681" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="T681" s="3">
-        <x:v/>
+          <x:t>Late - Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q681" s="2" t="n">
+        <x:v>46093.5540162037</x:v>
+      </x:c>
+      <x:c r="R681" s="2" t="n">
+        <x:v>46093.6043287037</x:v>
+      </x:c>
+      <x:c r="S681" s="2" t="n">
+        <x:v>46093.6344907407</x:v>
+      </x:c>
+      <x:c r="T681" s="3" t="inlineStr">
+        <x:is>
+          <x:t>77</x:t>
+        </x:is>
       </x:c>
       <x:c r="U681" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>73</x:t>
         </x:is>
       </x:c>
       <x:c r="V681" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>43</x:t>
         </x:is>
       </x:c>
       <x:c r="W681" s="1">
@@ -79762,8 +79766,10 @@
       <x:c r="Z681" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA681" s="1">
-        <x:v/>
+      <x:c r="AA681" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001479700 opt. dock 15</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="682">
@@ -79802,7 +79808,7 @@
       </x:c>
       <x:c r="H682" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I682" s="1" t="inlineStr">
@@ -79838,29 +79844,29 @@
       </x:c>
       <x:c r="P682" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q682" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R682" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S682" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q682" s="2" t="n">
+        <x:v>46093.4615393519</x:v>
+      </x:c>
+      <x:c r="R682" s="2" t="n">
+        <x:v>46093.5202893519</x:v>
+      </x:c>
+      <x:c r="S682" s="2" t="n">
+        <x:v>46093.5536574074</x:v>
       </x:c>
       <x:c r="T682" s="3">
         <x:v/>
       </x:c>
       <x:c r="U682" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>85</x:t>
         </x:is>
       </x:c>
       <x:c r="V682" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>48</x:t>
         </x:is>
       </x:c>
       <x:c r="W682" s="1">
@@ -79919,7 +79925,7 @@
       </x:c>
       <x:c r="H683" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I683" s="1" t="inlineStr">
@@ -79955,29 +79961,29 @@
       </x:c>
       <x:c r="P683" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q683" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R683" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S683" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q683" s="2" t="n">
+        <x:v>46093.4871527778</x:v>
+      </x:c>
+      <x:c r="R683" s="2" t="n">
+        <x:v>46093.5415625</x:v>
+      </x:c>
+      <x:c r="S683" s="2" t="n">
+        <x:v>46093.5416087963</x:v>
       </x:c>
       <x:c r="T683" s="3">
         <x:v/>
       </x:c>
       <x:c r="U683" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>78</x:t>
         </x:is>
       </x:c>
       <x:c r="V683" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="W683" s="1">
@@ -80034,7 +80040,7 @@
       </x:c>
       <x:c r="H684" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I684" s="1" t="inlineStr">
@@ -80070,29 +80076,31 @@
       </x:c>
       <x:c r="P684" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q684" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R684" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S684" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="T684" s="3">
-        <x:v/>
+          <x:t>On time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q684" s="2" t="n">
+        <x:v>46093.5522337963</x:v>
+      </x:c>
+      <x:c r="R684" s="2" t="n">
+        <x:v>46093.5623263889</x:v>
+      </x:c>
+      <x:c r="S684" s="2" t="n">
+        <x:v>46093.5846064815</x:v>
+      </x:c>
+      <x:c r="T684" s="3" t="inlineStr">
+        <x:is>
+          <x:t>15</x:t>
+        </x:is>
       </x:c>
       <x:c r="U684" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>14</x:t>
         </x:is>
       </x:c>
       <x:c r="V684" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>32</x:t>
         </x:is>
       </x:c>
       <x:c r="W684" s="1">
@@ -80151,7 +80159,7 @@
       </x:c>
       <x:c r="H685" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I685" s="1" t="inlineStr">
@@ -80187,29 +80195,29 @@
       </x:c>
       <x:c r="P685" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q685" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R685" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S685" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q685" s="2" t="n">
+        <x:v>46093.4787962963</x:v>
+      </x:c>
+      <x:c r="R685" s="2" t="n">
+        <x:v>46093.5550578704</x:v>
+      </x:c>
+      <x:c r="S685" s="2" t="n">
+        <x:v>46093.576099537</x:v>
       </x:c>
       <x:c r="T685" s="3">
         <x:v/>
       </x:c>
       <x:c r="U685" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>110</x:t>
         </x:is>
       </x:c>
       <x:c r="V685" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>30</x:t>
         </x:is>
       </x:c>
       <x:c r="W685" s="1">
@@ -80266,7 +80274,7 @@
       </x:c>
       <x:c r="H686" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I686" s="1" t="inlineStr">
@@ -80302,29 +80310,29 @@
       </x:c>
       <x:c r="P686" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q686" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R686" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S686" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q686" s="2" t="n">
+        <x:v>46093.6458912037</x:v>
+      </x:c>
+      <x:c r="R686" s="2" t="n">
+        <x:v>46093.720150463</x:v>
+      </x:c>
+      <x:c r="S686" s="2" t="n">
+        <x:v>46093.7547569444</x:v>
       </x:c>
       <x:c r="T686" s="3">
         <x:v/>
       </x:c>
       <x:c r="U686" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>107</x:t>
         </x:is>
       </x:c>
       <x:c r="V686" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>49</x:t>
         </x:is>
       </x:c>
       <x:c r="W686" s="1">
@@ -80345,82 +80353,1585 @@
         <x:v/>
       </x:c>
     </x:row>
-    <x:row r="687" spans="1:27" x14ac:dyDescent="0.25">
-      <x:c r="A687" s="1" t="s">
+    <x:row r="687">
+      <x:c r="A687" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B687" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C687" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1827486</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D687" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E687" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002821258</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F687" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G687" s="1" t="inlineStr">
+        <x:is>
+          <x:t>GOLD Regular</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H687" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I687" s="1" t="inlineStr">
+        <x:is>
+          <x:t>8987</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J687" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Ferentino</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K687" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-8987-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L687" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M687" s="3" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N687" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O687" s="2" t="n">
+        <x:v>46094.2916666667</x:v>
+      </x:c>
+      <x:c r="P687" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q687" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R687" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S687" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T687" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U687" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V687" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W687" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X687" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y687" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z687" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA687" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="688">
+      <x:c r="A688" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B688" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C688" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1833802</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D688" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E688" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002826185</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F688" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G688" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Gold Allocation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H688" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I688" s="1" t="inlineStr">
+        <x:is>
+          <x:t>9002</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J688" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Echt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K688" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-9002-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L688" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M688" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N688" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O688" s="2" t="n">
+        <x:v>46094.2916666667</x:v>
+      </x:c>
+      <x:c r="P688" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q688" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R688" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S688" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T688" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U688" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V688" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W688" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X688" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y688" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z688" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA688" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001481662 -63</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="689">
+      <x:c r="A689" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B689" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C689" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1827422</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D689" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E689" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002821200</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F689" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G689" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Gold Allocation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H689" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Cancelled</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I689" s="1" t="inlineStr">
+        <x:is>
+          <x:t>8997</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J689" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Verrières</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K689" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-8997-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L689" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M689" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N689" s="1" t="inlineStr">
+        <x:is>
+          <x:t>No</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O689" s="2" t="n">
+        <x:v>46094.2916666667</x:v>
+      </x:c>
+      <x:c r="P689" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q689" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R689" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S689" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T689" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U689" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V689" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W689" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X689" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y689" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z689" s="2" t="n">
+        <x:v>46093.6734837963</x:v>
+      </x:c>
+      <x:c r="AA689" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="690">
+      <x:c r="A690" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B690" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C690" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1832764</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D690" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E690" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002826158</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F690" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G690" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Gold Allocation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H690" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I690" s="1" t="inlineStr">
+        <x:is>
+          <x:t>9000</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J690" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zwaagdijk</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K690" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-9000-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L690" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M690" s="3" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N690" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O690" s="2" t="n">
+        <x:v>46094.375</x:v>
+      </x:c>
+      <x:c r="P690" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q690" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R690" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S690" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T690" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U690" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V690" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W690" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X690" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y690" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z690" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA690" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="691">
+      <x:c r="A691" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B691" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C691" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1827461</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D691" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E691" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002821203</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F691" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G691" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Gold Allocation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H691" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I691" s="1" t="inlineStr">
+        <x:is>
+          <x:t>8996</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J691" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Bierun</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K691" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-8996-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L691" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M691" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N691" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O691" s="2" t="n">
+        <x:v>46094.375</x:v>
+      </x:c>
+      <x:c r="P691" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q691" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R691" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S691" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T691" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U691" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V691" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W691" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X691" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y691" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z691" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA691" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="692">
+      <x:c r="A692" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B692" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C692" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1832771</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D692" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E692" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002825835</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F692" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G692" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Gold Allocation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H692" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I692" s="1" t="inlineStr">
+        <x:is>
+          <x:t>9000</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J692" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zwaagdijk</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K692" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-9000-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L692" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M692" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N692" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O692" s="2" t="n">
+        <x:v>46094.4166666667</x:v>
+      </x:c>
+      <x:c r="P692" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q692" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R692" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S692" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T692" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U692" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V692" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W692" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X692" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y692" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z692" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA692" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="693">
+      <x:c r="A693" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B693" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C693" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1827425</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D693" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E693" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002821188</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F693" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G693" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Gold Allocation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H693" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I693" s="1" t="inlineStr">
+        <x:is>
+          <x:t>9005</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J693" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Labastide</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K693" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-9005-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L693" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M693" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N693" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O693" s="2" t="n">
+        <x:v>46094.4166666667</x:v>
+      </x:c>
+      <x:c r="P693" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q693" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R693" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S693" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T693" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U693" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V693" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W693" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X693" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y693" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z693" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA693" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="694">
+      <x:c r="A694" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B694" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C694" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1831529</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D694" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E694" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002826004</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F694" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G694" s="1" t="inlineStr">
+        <x:is>
+          <x:t>GOLD Regular</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H694" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I694" s="1" t="inlineStr">
+        <x:is>
+          <x:t>8987</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J694" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Ferentino</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K694" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-8987-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L694" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M694" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N694" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O694" s="2" t="n">
+        <x:v>46094.4375</x:v>
+      </x:c>
+      <x:c r="P694" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q694" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R694" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S694" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T694" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U694" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V694" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W694" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X694" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y694" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z694" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA694" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="695">
+      <x:c r="A695" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B695" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C695" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1827482</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D695" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E695" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002821253</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F695" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G695" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Gold Allocation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H695" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I695" s="1" t="inlineStr">
+        <x:is>
+          <x:t>8992</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J695" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Illescas</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K695" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-8992-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L695" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M695" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N695" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O695" s="2" t="n">
+        <x:v>46094.4583333333</x:v>
+      </x:c>
+      <x:c r="P695" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q695" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R695" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S695" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T695" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U695" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V695" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W695" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X695" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y695" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z695" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA695" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="696">
+      <x:c r="A696" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B696" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C696" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1827800</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D696" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E696" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002821199</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F696" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G696" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Gold Allocation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H696" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I696" s="1" t="inlineStr">
+        <x:is>
+          <x:t>8998</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J696" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Bratislava</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K696" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-8998-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L696" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M696" s="3" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N696" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O696" s="2" t="n">
+        <x:v>46094.5416666667</x:v>
+      </x:c>
+      <x:c r="P696" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q696" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R696" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S696" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T696" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U696" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V696" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W696" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X696" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y696" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z696" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA696" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="697">
+      <x:c r="A697" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B697" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C697" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1827483</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D697" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E697" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002821252</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F697" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G697" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Gold Allocation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H697" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I697" s="1" t="inlineStr">
+        <x:is>
+          <x:t>8993</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J697" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Novara</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K697" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-8993-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L697" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M697" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N697" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O697" s="2" t="n">
+        <x:v>46094.5833333333</x:v>
+      </x:c>
+      <x:c r="P697" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q697" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R697" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S697" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T697" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U697" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V697" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W697" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X697" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y697" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z697" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA697" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="698">
+      <x:c r="A698" s="1" t="inlineStr">
+        <x:is>
+          <x:t>1001634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B698" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Good(s)Factory</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C698" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1836025</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D698" s="4">
+        <x:v/>
+      </x:c>
+      <x:c r="E698" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002830171</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F698" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G698" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Gold Allocation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H698" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I698" s="1" t="inlineStr">
+        <x:is>
+          <x:t>9000</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J698" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zwaagdijk</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K698" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-9000-2A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L698" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 2 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M698" s="3" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N698" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O698" s="2" t="n">
+        <x:v>46094.6041666667</x:v>
+      </x:c>
+      <x:c r="P698" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q698" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R698" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S698" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T698" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U698" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V698" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W698" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X698" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y698" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z698" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA698" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DC1 10-kant</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="699">
+      <x:c r="A699" s="1" t="inlineStr">
+        <x:is>
+          <x:t>50135</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B699" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DSV Road sp. z o.o.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C699" s="4" t="inlineStr">
+        <x:is>
+          <x:t>1838129</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D699" s="4" t="inlineStr">
+        <x:is>
+          <x:t>ACDE30-0424</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E699" s="1" t="inlineStr">
+        <x:is>
+          <x:t>4002817861, 4002819375, 4002819598, 4002822740</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F699" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Regular order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G699" s="1" t="inlineStr">
+        <x:is>
+          <x:t>GOLD Regular</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H699" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Expected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I699" s="1" t="inlineStr">
+        <x:is>
+          <x:t>8990</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J699" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Wallersdorf</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K699" s="1" t="inlineStr">
+        <x:is>
+          <x:t>DCZONE-8990-1A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L699" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Zone 1 Truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M699" s="3" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="N699" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O699" s="2" t="n">
+        <x:v>46094.625</x:v>
+      </x:c>
+      <x:c r="P699" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Q699" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="R699" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="S699" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="T699" s="3">
+        <x:v/>
+      </x:c>
+      <x:c r="U699" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="V699" s="3" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="W699" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="X699" s="1" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="Y699" s="1">
+        <x:v/>
+      </x:c>
+      <x:c r="Z699" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="AA699" s="1">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="700" spans="1:27" x14ac:dyDescent="0.25">
+      <x:c r="A700" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B687" s="1" t="s">
+      <x:c r="B700" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C687" s="4" t="s">
+      <x:c r="C700" s="4" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D687" s="4" t="s">
+      <x:c r="D700" s="4" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="E687" s="1" t="s">
+      <x:c r="E700" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F687" s="1"/>
-      <x:c r="G687" s="1"/>
-      <x:c r="H687" s="1" t="s">
+      <x:c r="F700" s="1"/>
+      <x:c r="G700" s="1"/>
+      <x:c r="H700" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I687" s="1" t="s">
+      <x:c r="I700" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="J687" s="1" t="s">
+      <x:c r="J700" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K687" s="1" t="s">
+      <x:c r="K700" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="L687" s="1" t="s">
+      <x:c r="L700" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="M687" s="3" t="s">
+      <x:c r="M700" s="3" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="N687" s="1" t="s">
+      <x:c r="N700" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="O687" s="2" t="s">
+      <x:c r="O700" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="P687" s="1" t="s">
+      <x:c r="P700" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="Q687" s="2" t="s">
+      <x:c r="Q700" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="R687" s="2" t="s">
+      <x:c r="R700" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="S687" s="2" t="s">
+      <x:c r="S700" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="T687" s="3" t="s">
+      <x:c r="T700" s="3" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="U687" s="3" t="s">
+      <x:c r="U700" s="3" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="V687" s="3" t="s">
+      <x:c r="V700" s="3" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="W687" s="1" t="s">
+      <x:c r="W700" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="X687" s="1" t="s">
+      <x:c r="X700" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="Y687" s="1" t="s">
+      <x:c r="Y700" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="Z687" s="2" t="s">
+      <x:c r="Z700" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="AA687" s="1"/>
+      <x:c r="AA700" s="1"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/AppointmentReport_latest.xlsx
+++ b/data/AppointmentReport_latest.xlsx
@@ -80389,7 +80389,7 @@
       </x:c>
       <x:c r="H687" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I687" s="1" t="inlineStr">
@@ -80425,29 +80425,31 @@
       </x:c>
       <x:c r="P687" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q687" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R687" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S687" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="T687" s="3">
-        <x:v/>
+          <x:t>On time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q687" s="2" t="n">
+        <x:v>46094.3121064815</x:v>
+      </x:c>
+      <x:c r="R687" s="2" t="n">
+        <x:v>46094.3136921296</x:v>
+      </x:c>
+      <x:c r="S687" s="2" t="n">
+        <x:v>46094.3853240741</x:v>
+      </x:c>
+      <x:c r="T687" s="3" t="inlineStr">
+        <x:is>
+          <x:t>29</x:t>
+        </x:is>
       </x:c>
       <x:c r="U687" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>2</x:t>
         </x:is>
       </x:c>
       <x:c r="V687" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>103</x:t>
         </x:is>
       </x:c>
       <x:c r="W687" s="1">
@@ -80504,7 +80506,7 @@
       </x:c>
       <x:c r="H688" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I688" s="1" t="inlineStr">
@@ -80540,29 +80542,31 @@
       </x:c>
       <x:c r="P688" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q688" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R688" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S688" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="T688" s="3">
-        <x:v/>
+          <x:t>Late - Reported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q688" s="2" t="n">
+        <x:v>46094.5219675926</x:v>
+      </x:c>
+      <x:c r="R688" s="2" t="n">
+        <x:v>46094.5220717593</x:v>
+      </x:c>
+      <x:c r="S688" s="2" t="n">
+        <x:v>46094.551724537</x:v>
+      </x:c>
+      <x:c r="T688" s="3" t="inlineStr">
+        <x:is>
+          <x:t>331</x:t>
+        </x:is>
       </x:c>
       <x:c r="U688" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="V688" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>43</x:t>
         </x:is>
       </x:c>
       <x:c r="W688" s="1">
@@ -80581,7 +80585,7 @@
       </x:c>
       <x:c r="AA688" s="1" t="inlineStr">
         <x:is>
-          <x:t>5001481662 -63</x:t>
+          <x:t>eta 13:15   5001481662 -63</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -80738,7 +80742,7 @@
       </x:c>
       <x:c r="H690" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I690" s="1" t="inlineStr">
@@ -80774,29 +80778,29 @@
       </x:c>
       <x:c r="P690" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q690" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R690" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S690" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q690" s="2" t="n">
+        <x:v>46094.3519675926</x:v>
+      </x:c>
+      <x:c r="R690" s="2" t="n">
+        <x:v>46094.3523263889</x:v>
+      </x:c>
+      <x:c r="S690" s="2" t="n">
+        <x:v>46094.3764814815</x:v>
       </x:c>
       <x:c r="T690" s="3">
         <x:v/>
       </x:c>
       <x:c r="U690" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>1</x:t>
         </x:is>
       </x:c>
       <x:c r="V690" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>35</x:t>
         </x:is>
       </x:c>
       <x:c r="W690" s="1">
@@ -80853,7 +80857,7 @@
       </x:c>
       <x:c r="H691" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I691" s="1" t="inlineStr">
@@ -80889,29 +80893,29 @@
       </x:c>
       <x:c r="P691" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q691" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R691" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S691" s="2">
-        <x:v/>
+          <x:t>On time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q691" s="2" t="n">
+        <x:v>46094.3592708333</x:v>
+      </x:c>
+      <x:c r="R691" s="2" t="n">
+        <x:v>46094.3600347222</x:v>
+      </x:c>
+      <x:c r="S691" s="2" t="n">
+        <x:v>46094.4292013889</x:v>
       </x:c>
       <x:c r="T691" s="3">
         <x:v/>
       </x:c>
       <x:c r="U691" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>1</x:t>
         </x:is>
       </x:c>
       <x:c r="V691" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>100</x:t>
         </x:is>
       </x:c>
       <x:c r="W691" s="1">
@@ -80928,8 +80932,10 @@
       <x:c r="Z691" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA691" s="1">
-        <x:v/>
+      <x:c r="AA691" s="1" t="inlineStr">
+        <x:is>
+          <x:t>784574677</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="692">
@@ -80968,7 +80974,7 @@
       </x:c>
       <x:c r="H692" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I692" s="1" t="inlineStr">
@@ -81004,29 +81010,29 @@
       </x:c>
       <x:c r="P692" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q692" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R692" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S692" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q692" s="2" t="n">
+        <x:v>46094.3737615741</x:v>
+      </x:c>
+      <x:c r="R692" s="2" t="n">
+        <x:v>46094.3741435185</x:v>
+      </x:c>
+      <x:c r="S692" s="2" t="n">
+        <x:v>46094.4076157407</x:v>
       </x:c>
       <x:c r="T692" s="3">
         <x:v/>
       </x:c>
       <x:c r="U692" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>0</x:t>
         </x:is>
       </x:c>
       <x:c r="V692" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>48</x:t>
         </x:is>
       </x:c>
       <x:c r="W692" s="1">
@@ -81083,7 +81089,7 @@
       </x:c>
       <x:c r="H693" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I693" s="1" t="inlineStr">
@@ -81119,29 +81125,29 @@
       </x:c>
       <x:c r="P693" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q693" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R693" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S693" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q693" s="2" t="n">
+        <x:v>46094.3564236111</x:v>
+      </x:c>
+      <x:c r="R693" s="2" t="n">
+        <x:v>46094.4051967593</x:v>
+      </x:c>
+      <x:c r="S693" s="2" t="n">
+        <x:v>46094.5466898148</x:v>
       </x:c>
       <x:c r="T693" s="3">
         <x:v/>
       </x:c>
       <x:c r="U693" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>70</x:t>
         </x:is>
       </x:c>
       <x:c r="V693" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>204</x:t>
         </x:is>
       </x:c>
       <x:c r="W693" s="1">
@@ -81198,7 +81204,7 @@
       </x:c>
       <x:c r="H694" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I694" s="1" t="inlineStr">
@@ -81234,29 +81240,29 @@
       </x:c>
       <x:c r="P694" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q694" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R694" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S694" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q694" s="2" t="n">
+        <x:v>46094.3190856481</x:v>
+      </x:c>
+      <x:c r="R694" s="2" t="n">
+        <x:v>46094.4255555556</x:v>
+      </x:c>
+      <x:c r="S694" s="2" t="n">
+        <x:v>46094.4623611111</x:v>
       </x:c>
       <x:c r="T694" s="3">
         <x:v/>
       </x:c>
       <x:c r="U694" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>153</x:t>
         </x:is>
       </x:c>
       <x:c r="V694" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>53</x:t>
         </x:is>
       </x:c>
       <x:c r="W694" s="1">
@@ -81264,7 +81270,7 @@
       </x:c>
       <x:c r="X694" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>Logistic quality: loaded in width</x:t>
         </x:is>
       </x:c>
       <x:c r="Y694" s="1">
@@ -81313,7 +81319,7 @@
       </x:c>
       <x:c r="H695" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I695" s="1" t="inlineStr">
@@ -81349,29 +81355,29 @@
       </x:c>
       <x:c r="P695" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q695" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R695" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S695" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q695" s="2" t="n">
+        <x:v>46094.3320833333</x:v>
+      </x:c>
+      <x:c r="R695" s="2" t="n">
+        <x:v>46094.5022337963</x:v>
+      </x:c>
+      <x:c r="S695" s="2" t="n">
+        <x:v>46094.5410069444</x:v>
       </x:c>
       <x:c r="T695" s="3">
         <x:v/>
       </x:c>
       <x:c r="U695" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>245</x:t>
         </x:is>
       </x:c>
       <x:c r="V695" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>56</x:t>
         </x:is>
       </x:c>
       <x:c r="W695" s="1">
@@ -81388,8 +81394,10 @@
       <x:c r="Z695" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA695" s="1">
-        <x:v/>
+      <x:c r="AA695" s="1" t="inlineStr">
+        <x:is>
+          <x:t>5001480849</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="696">
@@ -81428,7 +81436,7 @@
       </x:c>
       <x:c r="H696" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>NoShow</x:t>
         </x:is>
       </x:c>
       <x:c r="I696" s="1" t="inlineStr">
@@ -81456,7 +81464,7 @@
       </x:c>
       <x:c r="N696" s="1" t="inlineStr">
         <x:is>
-          <x:t>Yes</x:t>
+          <x:t>No</x:t>
         </x:is>
       </x:c>
       <x:c r="O696" s="2" t="n">
@@ -81497,11 +81505,13 @@
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="Y696" s="1">
-        <x:v/>
-      </x:c>
-      <x:c r="Z696" s="2">
-        <x:v/>
+      <x:c r="Y696" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Bratislava</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z696" s="2" t="n">
+        <x:v>46094.5585532407</x:v>
       </x:c>
       <x:c r="AA696" s="1">
         <x:v/>
@@ -81543,7 +81553,7 @@
       </x:c>
       <x:c r="H697" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I697" s="1" t="inlineStr">
@@ -81579,29 +81589,29 @@
       </x:c>
       <x:c r="P697" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q697" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R697" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S697" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q697" s="2" t="n">
+        <x:v>46094.5140162037</x:v>
+      </x:c>
+      <x:c r="R697" s="2" t="n">
+        <x:v>46094.5984953704</x:v>
+      </x:c>
+      <x:c r="S697" s="2" t="n">
+        <x:v>46094.6331944444</x:v>
       </x:c>
       <x:c r="T697" s="3">
         <x:v/>
       </x:c>
       <x:c r="U697" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>121</x:t>
         </x:is>
       </x:c>
       <x:c r="V697" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>50</x:t>
         </x:is>
       </x:c>
       <x:c r="W697" s="1">
@@ -81658,7 +81668,7 @@
       </x:c>
       <x:c r="H698" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I698" s="1" t="inlineStr">
@@ -81673,12 +81683,12 @@
       </x:c>
       <x:c r="K698" s="1" t="inlineStr">
         <x:is>
-          <x:t>DCZONE-9000-2A</x:t>
+          <x:t>DCZONE-9000-1A</x:t>
         </x:is>
       </x:c>
       <x:c r="L698" s="1" t="inlineStr">
         <x:is>
-          <x:t>Zone 2 Truck</x:t>
+          <x:t>Zone 1 Truck</x:t>
         </x:is>
       </x:c>
       <x:c r="M698" s="3" t="n">
@@ -81694,29 +81704,29 @@
       </x:c>
       <x:c r="P698" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q698" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R698" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S698" s="2">
-        <x:v/>
+          <x:t>On time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q698" s="2" t="n">
+        <x:v>46094.6011226852</x:v>
+      </x:c>
+      <x:c r="R698" s="2" t="n">
+        <x:v>46094.601712963</x:v>
+      </x:c>
+      <x:c r="S698" s="2" t="n">
+        <x:v>46094.6207060185</x:v>
       </x:c>
       <x:c r="T698" s="3">
         <x:v/>
       </x:c>
       <x:c r="U698" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>1</x:t>
         </x:is>
       </x:c>
       <x:c r="V698" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>27</x:t>
         </x:is>
       </x:c>
       <x:c r="W698" s="1">
@@ -81777,7 +81787,7 @@
       </x:c>
       <x:c r="H699" s="1" t="inlineStr">
         <x:is>
-          <x:t>Expected</x:t>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c r="I699" s="1" t="inlineStr">
@@ -81813,29 +81823,29 @@
       </x:c>
       <x:c r="P699" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="Q699" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="R699" s="2">
-        <x:v/>
-      </x:c>
-      <x:c r="S699" s="2">
-        <x:v/>
+          <x:t>Early</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q699" s="2" t="n">
+        <x:v>46094.3283912037</x:v>
+      </x:c>
+      <x:c r="R699" s="2" t="n">
+        <x:v>46094.3305555556</x:v>
+      </x:c>
+      <x:c r="S699" s="2" t="n">
+        <x:v>46094.3515046296</x:v>
       </x:c>
       <x:c r="T699" s="3">
         <x:v/>
       </x:c>
       <x:c r="U699" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>4</x:t>
         </x:is>
       </x:c>
       <x:c r="V699" s="3" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>30</x:t>
         </x:is>
       </x:c>
       <x:c r="W699" s="1">
@@ -81843,7 +81853,7 @@
       </x:c>
       <x:c r="X699" s="1" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>Logistic quality: pallets are too high</x:t>
         </x:is>
       </x:c>
       <x:c r="Y699" s="1">
@@ -81852,8 +81862,10 @@
       <x:c r="Z699" s="2">
         <x:v/>
       </x:c>
-      <x:c r="AA699" s="1">
-        <x:v/>
+      <x:c r="AA699" s="1" t="inlineStr">
+        <x:is>
+          <x:t>HG TU 5001481027 normale TU 5001481028 opt. dock 15</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="700" spans="1:27" x14ac:dyDescent="0.25">
